--- a/data/raw/returns/WhiteMulberry.xlsx
+++ b/data/raw/returns/WhiteMulberry.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L137"/>
+  <dimension ref="A1:L139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,32 +493,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24T08:29:31+00:00</t>
+          <t>2026-06-28T19:38:03+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>402-0120877-0312362</t>
+          <t>402-4296829-1337133</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -526,7 +526,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -536,12 +536,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>LPNSPUN59333</t>
+          <t>LPNCCX1B2440445</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -549,12 +549,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24T06:17:22+00:00</t>
+          <t>2026-06-28T08:39:43+00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>403-8864299-1768360</t>
+          <t>402-6090489-2032337</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -587,17 +587,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7854241</t>
+          <t>LPNBLR7Y7855923</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -605,32 +605,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23T15:36:47+00:00</t>
+          <t>2026-06-27T11:00:01+00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>402-8717460-5700310</t>
+          <t>408-3896665-0021948</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -638,22 +638,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LPNHDX8A005873</t>
+          <t>LPNBLR7Y7855626</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -661,32 +661,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23T11:54:27+00:00</t>
+          <t>2026-06-27T10:32:22+00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>403-7688253-5273167</t>
+          <t>407-5462207-4616334</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -694,22 +694,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LPNBOM5F5694482</t>
+          <t>LPNSBOB1388621</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -717,32 +717,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23T09:27:19+00:00</t>
+          <t>2026-06-26T18:08:18+00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>408-9857262-4357961</t>
+          <t>171-5586406-9945900</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -750,22 +750,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7853975</t>
+          <t>LPNSBOB1388302</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -773,32 +773,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-23T08:32:44+00:00</t>
+          <t>2026-06-26T06:57:42+00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>404-2029470-0977929</t>
+          <t>405-2746376-7486724</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3925027</t>
+          <t>LPNBLX1C140655</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -829,32 +829,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-23T06:25:18+00:00</t>
+          <t>2026-06-26T05:19:18+00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>408-7120729-6837923</t>
+          <t>406-4442109-5330751</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -862,7 +862,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>LPNSBOB1385946</t>
+          <t>LPNDEL4AA3990308</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -885,12 +885,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-23T05:29:18+00:00</t>
+          <t>2026-06-25T18:24:43+00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>403-5101653-2865108</t>
+          <t>405-2433007-9289947</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>LPNHDX8005941</t>
+          <t>LPNSBOB1387687</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -941,32 +941,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-22T15:00:37+00:00</t>
+          <t>2026-06-25T10:05:58+00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>408-2886313-6344340</t>
+          <t>407-3034951-4675566</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -974,22 +974,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>LPNSBOB1385291</t>
+          <t>LPNMAA4Z2273850</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -997,32 +997,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-22T15:00:11+00:00</t>
+          <t>2026-06-24T08:29:31+00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>403-4065197-2565940</t>
+          <t>402-0120877-0312362</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>LPNSBOB1385290</t>
+          <t>LPNSPUN59333</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1053,32 +1053,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-22T13:49:32+00:00</t>
+          <t>2026-06-24T06:17:22+00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>171-3328269-2691534</t>
+          <t>403-8864299-1768360</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1086,22 +1086,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>LPNBLX1C049419</t>
+          <t>LPNBLR7Y7854241</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1109,32 +1109,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-22T13:44:52+00:00</t>
+          <t>2026-06-23T15:36:47+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>407-2806960-6949923</t>
+          <t>402-8717460-5700310</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>LPNBLX1C049418</t>
+          <t>LPNHDX8A005873</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1165,12 +1165,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-22T12:43:38+00:00</t>
+          <t>2026-06-23T11:54:27+00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>402-2531413-4073130</t>
+          <t>403-7688253-5273167</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>LPNHYD8EF41160</t>
+          <t>LPNBOM5F5694482</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1221,12 +1221,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-22T09:02:33+00:00</t>
+          <t>2026-06-23T09:27:19+00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>404-4254275-9061104</t>
+          <t>408-9857262-4357961</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1264,12 +1264,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>LPNHYD8ED01352</t>
+          <t>LPNBLR7Y7853975</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1277,12 +1277,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-22T06:27:11+00:00</t>
+          <t>2026-06-23T08:32:44+00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>407-5289320-1468336</t>
+          <t>404-2029470-0977929</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7287766</t>
+          <t>LPNDEL4AA3925027</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1333,32 +1333,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-21T15:48:42+00:00</t>
+          <t>2026-06-23T06:25:18+00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>408-1433377-1765942</t>
+          <t>408-7120729-6837923</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1371,17 +1371,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>LPNSBOB1385218</t>
+          <t>LPNSBOB1385946</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1389,32 +1389,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-21T09:50:13+00:00</t>
+          <t>2026-06-23T05:29:18+00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>405-1204534-8479517</t>
+          <t>403-5101653-2865108</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>LPNDEL4AA4027730</t>
+          <t>LPNHDX8005941</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1445,32 +1445,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-21T08:35:03+00:00</t>
+          <t>2026-06-22T15:00:37+00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>171-0025867-6612374</t>
+          <t>408-2886313-6344340</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7853300</t>
+          <t>LPNSBOB1385291</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1501,32 +1501,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-20T13:05:37+00:00</t>
+          <t>2026-06-22T15:00:11+00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>402-8590404-8535510</t>
+          <t>403-4065197-2565940</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1534,22 +1534,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>LPNMAA4G898204</t>
+          <t>LPNSBOB1385290</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1557,32 +1557,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-19T14:24:04+00:00</t>
+          <t>2026-06-22T13:49:32+00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>403-3269966-6849104</t>
+          <t>171-3328269-2691534</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>LPNHDX8A004693</t>
+          <t>LPNBLX1C049419</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1613,32 +1613,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-18T09:53:43+00:00</t>
+          <t>2026-06-22T13:44:52+00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>408-1513827-8090763</t>
+          <t>407-2806960-6949923</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2273003</t>
+          <t>LPNBLX1C049418</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1669,32 +1669,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-18T09:01:23+00:00</t>
+          <t>2026-06-22T12:43:38+00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>402-6972876-7770702</t>
+          <t>402-2531413-4073130</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FBA76765</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B0BMQQQ7YD</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>X001O7YYCV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>White Mulberry Motorized Height Adjustable Sit-Stand Desk | Electronic Height Adjustable | Motor &amp; Memory Preset Controller | Office, Workstation or Home | Carbon Fibre | 120 * 60*H(75-118) cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>LPNSPUN58279</t>
+          <t>LPNHYD8EF41160</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1725,32 +1725,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-18T06:34:47+00:00</t>
+          <t>2026-06-22T09:02:33+00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>171-5595331-6677926</t>
+          <t>404-4254275-9061104</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1758,22 +1758,22 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>LPNSPUN58332</t>
+          <t>LPNHYD8ED01352</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1781,32 +1781,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-18T06:13:54+00:00</t>
+          <t>2026-06-22T06:27:11+00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>405-9716650-4190754</t>
+          <t>407-5289320-1468336</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>LPNSPUN58348</t>
+          <t>LPNBLR7Y7287766</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1837,32 +1837,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-18T05:06:11+00:00</t>
+          <t>2026-06-21T15:48:42+00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>405-0242402-8315559</t>
+          <t>408-1433377-1765942</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1870,22 +1870,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>LPNHYD8DY89222</t>
+          <t>LPNSBOB1385218</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1893,12 +1893,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-18T03:18:32+00:00</t>
+          <t>2026-06-21T09:50:13+00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>403-8790017-7829152</t>
+          <t>405-1204534-8479517</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>LPNHYD8DY89148</t>
+          <t>LPNDEL4AA4027730</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1949,12 +1949,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-17T17:18:11+00:00</t>
+          <t>2026-06-21T08:35:03+00:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>408-3294486-3424329</t>
+          <t>171-0025867-6612374</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1982,12 +1982,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>LPNCCX1B4206954</t>
+          <t>LPNBLR7Y7853300</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -2005,32 +2005,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-17T11:01:26+00:00</t>
+          <t>2026-06-20T13:05:37+00:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>171-3399563-8885966</t>
+          <t>402-8590404-8535510</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2038,22 +2038,22 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>LPNLMAA0019039</t>
+          <t>LPNMAA4G898204</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2061,32 +2061,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-15T09:24:30+00:00</t>
+          <t>2026-06-19T14:24:04+00:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>171-3194001-5187538</t>
+          <t>403-3269966-6849104</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>LPNHYD8DY92591</t>
+          <t>LPNHDX8A004693</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2117,32 +2117,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-15T08:53:22+00:00</t>
+          <t>2026-06-18T09:53:43+00:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>406-3765893-9779536</t>
+          <t>408-1513827-8090763</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>LPNHDX8A0002233</t>
+          <t>LPNMAA4Z2273003</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2173,32 +2173,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-14T11:15:53+00:00</t>
+          <t>2026-06-18T09:01:23+00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>171-1282309-9677932</t>
+          <t>402-6972876-7770702</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76765</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BMQQQ7YD</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001O7YYCV</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Motorized Height Adjustable Sit-Stand Desk | Electronic Height Adjustable | Motor &amp; Memory Preset Controller | Office, Workstation or Home | Carbon Fibre | 120 * 60*H(75-118) cm</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2206,22 +2206,22 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2198432</t>
+          <t>LPNSPUN58279</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2229,32 +2229,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-14T06:26:57+00:00</t>
+          <t>2026-06-18T06:34:47+00:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>407-1845667-2313146</t>
+          <t>171-5595331-6677926</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3677498</t>
+          <t>LPNSPUN58332</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2285,32 +2285,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-13T12:21:24+00:00</t>
+          <t>2026-06-18T06:13:54+00:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>405-5466299-6857906</t>
+          <t>405-9716650-4190754</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>LPNSBOB1375958</t>
+          <t>LPNSPUN58348</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2341,32 +2341,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-13T12:20:57+00:00</t>
+          <t>2026-06-18T05:06:11+00:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>404-9976514-7382743</t>
+          <t>405-0242402-8315559</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>LPNSBOB1375957</t>
+          <t>LPNHYD8DY89222</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2397,32 +2397,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-12T11:47:28+00:00</t>
+          <t>2026-06-18T03:18:32+00:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>407-2845785-4936332</t>
+          <t>403-8790017-7829152</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2430,22 +2430,22 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>LPNSHTI00009280</t>
+          <t>LPNHYD8DY89148</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2453,32 +2453,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-11T12:39:34+00:00</t>
+          <t>2026-06-17T17:18:11+00:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>405-0836953-9114742</t>
+          <t>408-3294486-3424329</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>DAMAGED</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>LPNHDX8A001607</t>
+          <t>LPNCCX1B4206954</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2509,32 +2509,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-11T10:43:03+00:00</t>
+          <t>2026-06-17T11:01:26+00:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>407-7053626-1929962</t>
+          <t>171-3399563-8885966</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FBA79667</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>B0DQPK7MFH</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>X0027512Z1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk with Shelf|DIY Assembly| Monitor Raising Shelf |Engineered Wood &amp; Sturdy Steel Leg|Perfect for Computer Table Office Home Gaming Study Desk|L(130+130)*45*77cm|White</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SCUY</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>LPNSCUY00017897</t>
+          <t>LPNLMAA0019039</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -2565,12 +2565,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-10T22:26:08+00:00</t>
+          <t>2026-06-15T09:24:30+00:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>404-0639682-6860336</t>
+          <t>171-3194001-5187538</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2598,22 +2598,22 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>LPNCX1B4784440</t>
+          <t>LPNHYD8DY92591</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -2621,32 +2621,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-10T12:14:02+00:00</t>
+          <t>2026-06-15T08:53:22+00:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>171-1027170-0049924</t>
+          <t>406-3765893-9779536</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2654,22 +2654,22 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2407733</t>
+          <t>LPNHDX8A0002233</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2677,32 +2677,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-10T08:20:03+00:00</t>
+          <t>2026-06-14T11:15:53+00:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>406-6295410-5869130</t>
+          <t>171-1282309-9677932</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2710,22 +2710,22 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>LPNBLX1C159057</t>
+          <t>LPNMAA4Z2198432</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -2733,12 +2733,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-10T05:42:02+00:00</t>
+          <t>2026-06-14T06:26:57+00:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>405-8329990-8940345</t>
+          <t>407-1845667-2313146</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4745942</t>
+          <t>LPNDEL4AA3677498</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -2789,32 +2789,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-10T04:51:41+00:00</t>
+          <t>2026-06-13T12:21:24+00:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>405-7954322-6131539</t>
+          <t>405-5466299-6857906</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>LPNBOM5F5675078</t>
+          <t>LPNSBOB1375958</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2845,32 +2845,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-10T03:51:05+00:00</t>
+          <t>2026-06-13T12:20:57+00:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>407-5527946-4998741</t>
+          <t>404-9976514-7382743</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2878,22 +2878,22 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7287766</t>
+          <t>LPNSBOB1375957</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -2901,32 +2901,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-08T09:59:30+00:00</t>
+          <t>2026-06-12T11:47:28+00:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>404-4052225-7064331</t>
+          <t>407-2845785-4936332</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3631375</t>
+          <t>LPNSHTI00009280</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -2957,32 +2957,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-08T08:59:50+00:00</t>
+          <t>2026-06-11T12:39:34+00:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>404-3123106-0929939</t>
+          <t>405-0836953-9114742</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FBK76387</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>B0BF4S7V8C</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>X00242V9DH</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | White</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2990,22 +2990,22 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>LPNSPUN56234</t>
+          <t>LPNHDX8A001607</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3013,32 +3013,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-08T08:59:02+00:00</t>
+          <t>2026-06-11T10:43:03+00:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>408-8800113-8391502</t>
+          <t>407-7053626-1929962</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79667</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0DQPK7MFH</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X0027512Z1</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry L-Shape Corner Desk with Shelf|DIY Assembly| Monitor Raising Shelf |Engineered Wood &amp; Sturdy Steel Leg|Perfect for Computer Table Office Home Gaming Study Desk|L(130+130)*45*77cm|White</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>SCUY</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>LPNSPUN56235</t>
+          <t>LPNSCUY00017897</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3069,12 +3069,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-08T08:43:30+00:00</t>
+          <t>2026-06-10T22:26:08+00:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>407-4254200-0562712</t>
+          <t>404-0639682-6860336</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3102,12 +3102,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3631346</t>
+          <t>LPNCX1B4784440</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -3125,12 +3125,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-07T16:09:41+00:00</t>
+          <t>2026-06-10T12:14:02+00:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>405-9852474-3831538</t>
+          <t>171-1027170-0049924</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3158,22 +3158,22 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>LPNCCX1B4179343</t>
+          <t>LPNMAA4Z2407733</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -3181,32 +3181,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-07T11:20:49+00:00</t>
+          <t>2026-06-10T08:20:03+00:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>406-9783608-9093148</t>
+          <t>406-6295410-5869130</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3214,22 +3214,22 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>LPNLMAA0016237</t>
+          <t>LPNBLX1C159057</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3237,32 +3237,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-07T10:24:17+00:00</t>
+          <t>2026-06-10T05:42:02+00:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>406-6392223-8173930</t>
+          <t>405-8329990-8940345</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -3270,22 +3270,22 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>LPNBLX1C047099</t>
+          <t>LPNBLR7Y4745942</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3293,12 +3293,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-06T10:45:59+00:00</t>
+          <t>2026-06-10T04:51:41+00:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>406-9111649-3125130</t>
+          <t>405-7954322-6131539</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>LPNBOM5F5579985</t>
+          <t>LPNBOM5F5675078</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -3349,12 +3349,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-05T09:54:50+00:00</t>
+          <t>2026-06-10T03:51:05+00:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>405-7328472-7893901</t>
+          <t>407-5527946-4998741</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679697</t>
+          <t>LPNBLR7Y7287766</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -3405,32 +3405,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-05T08:35:28+00:00</t>
+          <t>2026-06-08T09:59:30+00:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>404-9218549-9930734</t>
+          <t>404-4052225-7064331</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FBA79659</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>X0026ZDA2F</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, Black, 3 Year Warranty</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>LPNSDEGF082043</t>
+          <t>LPNDEL4AA3631375</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -3461,32 +3461,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-05T08:17:03+00:00</t>
+          <t>2026-06-08T08:59:50+00:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>171-6540897-0152357</t>
+          <t>404-3123106-0929939</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBK76387</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BF4S7V8C</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00242V9DH</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | White</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3494,22 +3494,22 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679650</t>
+          <t>LPNSPUN56234</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -3517,32 +3517,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-05T04:33:06+00:00</t>
+          <t>2026-06-08T08:59:02+00:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>171-6354444-3723505</t>
+          <t>408-8800113-8391502</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3550,22 +3550,22 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>LPNBOM5F5574228</t>
+          <t>LPNSPUN56235</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -3573,12 +3573,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-05T04:28:18+00:00</t>
+          <t>2026-06-08T08:43:30+00:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>406-6103690-9310748</t>
+          <t>407-4254200-0562712</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679535</t>
+          <t>LPNDEL4AA3631346</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3629,12 +3629,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-04T03:47:36+00:00</t>
+          <t>2026-06-07T16:09:41+00:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>406-2278126-7841949</t>
+          <t>405-9852474-3831538</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679185</t>
+          <t>LPNCCX1B4179343</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -3685,32 +3685,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-06-01T09:32:55+00:00</t>
+          <t>2026-06-07T11:20:49+00:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>402-3794541-2581168</t>
+          <t>406-9783608-9093148</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -3718,22 +3718,22 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4743333</t>
+          <t>LPNLMAA0016237</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -3741,32 +3741,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-06-01T04:42:36+00:00</t>
+          <t>2026-06-07T10:24:17+00:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>408-0143238-4374708</t>
+          <t>406-6392223-8173930</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3774,22 +3774,22 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>LPNBOM5F5524445</t>
+          <t>LPNBLX1C047099</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -3797,12 +3797,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-06-01T03:58:27+00:00</t>
+          <t>2026-06-06T10:45:59+00:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>406-4355667-6072332</t>
+          <t>406-9111649-3125130</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4743158</t>
+          <t>LPNBOM5F5579985</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -3853,12 +3853,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-31T09:10:34+00:00</t>
+          <t>2026-06-05T09:54:50+00:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>404-2518539-4406712</t>
+          <t>405-7328472-7893901</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3891,17 +3891,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3976607</t>
+          <t>LPNDEL4AA3679697</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -3909,32 +3909,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-30T22:18:28+00:00</t>
+          <t>2026-06-05T08:35:28+00:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>407-1474707-0478726</t>
+          <t>404-9218549-9930734</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79659</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZDA2F</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, Black, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>LPNCCX1B4554643</t>
+          <t>LPNSDEGF082043</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -3965,12 +3965,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-30T04:13:42+00:00</t>
+          <t>2026-06-05T08:17:03+00:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>406-7941139-9225906</t>
+          <t>171-6540897-0152357</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3998,22 +3998,22 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>LPNBOM5F5507643</t>
+          <t>LPNDEL4AA3679650</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4021,12 +4021,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-29T23:01:15+00:00</t>
+          <t>2026-06-05T04:33:06+00:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>405-0096078-8521126</t>
+          <t>171-6354444-3723505</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4054,22 +4054,22 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>LPNCCX1B2941120</t>
+          <t>LPNBOM5F5574228</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -4077,12 +4077,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-29T15:27:20+00:00</t>
+          <t>2026-06-05T04:28:18+00:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>404-8418070-5981124</t>
+          <t>406-6103690-9310748</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>LPNCCX1B4508596</t>
+          <t>LPNDEL4AA3679535</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -4133,12 +4133,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-29T05:18:33+00:00</t>
+          <t>2026-06-04T03:47:36+00:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>171-0407209-4266756</t>
+          <t>406-2278126-7841949</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4171,17 +4171,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937926</t>
+          <t>LPNDEL4AA3679185</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -4189,12 +4189,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-28T11:56:49+00:00</t>
+          <t>2026-06-01T09:32:55+00:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>407-4902279-0189155</t>
+          <t>402-3794541-2581168</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7363000</t>
+          <t>LPNBLR7Y4743333</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -4245,12 +4245,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-28T08:40:02+00:00</t>
+          <t>2026-06-01T04:42:36+00:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>408-1128142-0248321</t>
+          <t>408-0143238-4374708</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>DAMAGED_BY_FC</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937756</t>
+          <t>LPNBOM5F5524445</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -4301,12 +4301,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-28T06:36:17+00:00</t>
+          <t>2026-06-01T03:58:27+00:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>402-4776409-4471512</t>
+          <t>406-4355667-6072332</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7286354</t>
+          <t>LPNBLR7Y4743158</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -4357,12 +4357,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-27T12:42:16+00:00</t>
+          <t>2026-05-31T09:10:34+00:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>404-6762038-7137955</t>
+          <t>404-2518539-4406712</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4395,17 +4395,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937575</t>
+          <t>LPNDEL4AA3976607</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -4413,12 +4413,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-27T09:44:17+00:00</t>
+          <t>2026-05-30T22:18:28+00:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>403-3444915-0085109</t>
+          <t>407-1474707-0478726</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7362686</t>
+          <t>LPNCCX1B4554643</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -4469,32 +4469,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-27T09:25:47+00:00</t>
+          <t>2026-05-30T04:13:42+00:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>405-8410325-7933918</t>
+          <t>406-7941139-9225906</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>LPNSPUN53913</t>
+          <t>LPNBOM5F5507643</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -4525,12 +4525,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-26T23:02:43+00:00</t>
+          <t>2026-05-29T23:01:15+00:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>407-0645348-4574732</t>
+          <t>405-0096078-8521126</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4563,17 +4563,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>LPNCCX1B5292913</t>
+          <t>LPNCCX1B2941120</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -4581,12 +4581,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-26T11:06:29+00:00</t>
+          <t>2026-05-29T15:27:20+00:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>402-2949127-9513917</t>
+          <t>404-8418070-5981124</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937227</t>
+          <t>LPNCCX1B4508596</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -4637,12 +4637,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-26T08:48:10+00:00</t>
+          <t>2026-05-29T05:18:33+00:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>403-5510263-6469912</t>
+          <t>171-0407209-4266756</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4670,22 +4670,22 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273675</t>
+          <t>LPNDEL4AA3937926</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -4693,12 +4693,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-25T15:22:25+00:00</t>
+          <t>2026-05-28T11:56:49+00:00</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>402-5203149-1906724</t>
+          <t>407-4902279-0189155</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4736,12 +4736,12 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>LPNCCX1B5331017</t>
+          <t>LPNBLR7Y7363000</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -4749,12 +4749,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-24T09:24:39+00:00</t>
+          <t>2026-05-28T08:40:02+00:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>171-7709339-0701117</t>
+          <t>408-1128142-0248321</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>DAMAGED_BY_FC</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273169</t>
+          <t>LPNDEL4AA3937756</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -4805,12 +4805,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-24T08:29:52+00:00</t>
+          <t>2026-05-28T06:36:17+00:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>406-7042486-7436314</t>
+          <t>402-4776409-4471512</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273150</t>
+          <t>LPNBLR7Y7286354</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -4861,32 +4861,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-23T23:07:27+00:00</t>
+          <t>2026-05-27T12:42:16+00:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>406-2954542-5857925</t>
+          <t>404-6762038-7137955</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -4894,22 +4894,22 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>LPNSBOB1370158</t>
+          <t>LPNDEL4AA3937575</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -4917,12 +4917,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-23T10:58:04+00:00</t>
+          <t>2026-05-27T09:44:17+00:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>406-4758725-2077907</t>
+          <t>403-3444915-0085109</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4960,12 +4960,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7272896</t>
+          <t>LPNBLR7Y7362686</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -4973,12 +4973,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-22T09:58:26+00:00</t>
+          <t>2026-05-27T09:25:47+00:00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>403-7800011-6937966</t>
+          <t>405-8410325-7933918</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5006,22 +5006,22 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>LPNSDEGF010003</t>
+          <t>LPNSPUN53913</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -5029,32 +5029,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-21T04:38:32+00:00</t>
+          <t>2026-05-26T23:02:43+00:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>403-2400247-1930753</t>
+          <t>407-0645348-4574732</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -5062,22 +5062,22 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>LPNSDEGF099136</t>
+          <t>LPNCCX1B5292913</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -5085,12 +5085,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-20T11:30:45+00:00</t>
+          <t>2026-05-26T11:06:29+00:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>406-2648444-6601917</t>
+          <t>402-2949127-9513917</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5128,12 +5128,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2147464</t>
+          <t>LPNDEL4AA3937227</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -5141,32 +5141,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-19T08:03:32+00:00</t>
+          <t>2026-05-26T08:48:10+00:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>405-4744559-6958733</t>
+          <t>403-5510263-6469912</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>LPNSDEGF097985</t>
+          <t>LPNBLR7Y7273675</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -5197,32 +5197,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-18T11:36:05+00:00</t>
+          <t>2026-05-25T15:22:25+00:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>171-1585723-0908356</t>
+          <t>402-5203149-1906724</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -5230,22 +5230,22 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>LPNBLX1C155145</t>
+          <t>LPNCCX1B5331017</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -5253,32 +5253,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-15T08:29:30+00:00</t>
+          <t>2026-05-24T09:24:39+00:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>402-4856546-1261939</t>
+          <t>171-7709339-0701117</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>LPNSDEGF074601</t>
+          <t>LPNBLR7Y7273169</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -5309,32 +5309,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-13T13:50:43+00:00</t>
+          <t>2026-05-24T08:29:52+00:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>403-7495250-9937954</t>
+          <t>406-7042486-7436314</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>LPNBLX1C154096</t>
+          <t>LPNBLR7Y7273150</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -5365,32 +5365,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-12T07:19:54+00:00</t>
+          <t>2026-05-23T23:07:27+00:00</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>408-0473775-6641108</t>
+          <t>406-2954542-5857925</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>LPNSBOB1362246</t>
+          <t>LPNSBOB1370158</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -5421,32 +5421,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-11T10:31:39+00:00</t>
+          <t>2026-05-23T10:58:04+00:00</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>404-1750959-8518722</t>
+          <t>406-4758725-2077907</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -5454,22 +5454,22 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>LPNSHTI00006165</t>
+          <t>LPNBLR7Y7272896</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -5477,32 +5477,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-10T09:15:43+00:00</t>
+          <t>2026-05-22T09:58:26+00:00</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>402-1548587-3227555</t>
+          <t>403-7800011-6937966</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -5510,22 +5510,22 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>LPNBOM5F5057136</t>
+          <t>LPNSDEGF010003</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -5533,12 +5533,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-08T15:43:17+00:00</t>
+          <t>2026-05-21T04:38:32+00:00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>402-8374307-7441113</t>
+          <t>403-2400247-1930753</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>LPNSDEGF064205</t>
+          <t>LPNSDEGF099136</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -5589,32 +5589,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-08T13:25:23+00:00</t>
+          <t>2026-05-20T11:30:45+00:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>171-7381542-8368365</t>
+          <t>406-2648444-6601917</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -5622,22 +5622,22 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>LPNBLX1C042486</t>
+          <t>LPNDEL4AA2147464</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -5645,32 +5645,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-08T07:49:38+00:00</t>
+          <t>2026-05-19T08:03:32+00:00</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>403-3056736-6311553</t>
+          <t>405-4744559-6958733</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5321963</t>
+          <t>LPNSDEGF097985</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -5701,32 +5701,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-06T06:52:28+00:00</t>
+          <t>2026-05-18T11:36:05+00:00</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>403-2654029-0716338</t>
+          <t>171-1585723-0908356</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -5734,12 +5734,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>LPNSHTI00005958</t>
+          <t>LPNBLX1C155145</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -5757,32 +5757,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-06T05:51:00+00:00</t>
+          <t>2026-05-15T08:29:30+00:00</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>404-9426288-6037168</t>
+          <t>402-4856546-1261939</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -5790,22 +5790,22 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>LPNBOM5F5236158</t>
+          <t>LPNSDEGF074601</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -5813,12 +5813,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-02T04:54:42+00:00</t>
+          <t>2026-05-13T13:50:43+00:00</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>407-6201969-2856316</t>
+          <t>403-7495250-9937954</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>LPNLMAA0004457</t>
+          <t>LPNBLX1C154096</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -5869,32 +5869,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-04-28T08:52:43+00:00</t>
+          <t>2026-05-12T07:19:54+00:00</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>171-6713241-8377149</t>
+          <t>408-0473775-6641108</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -5902,22 +5902,22 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>LPNLMAA0003844</t>
+          <t>LPNSBOB1362246</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -5925,12 +5925,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-04-27T06:04:11+00:00</t>
+          <t>2026-05-11T10:31:39+00:00</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>403-6021111-3520325</t>
+          <t>404-1750959-8518722</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>LPNLMAA0003335</t>
+          <t>LPNSHTI00006165</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -5981,12 +5981,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-04-26T08:09:27+00:00</t>
+          <t>2026-05-10T09:15:43+00:00</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>402-4881396-1030704</t>
+          <t>402-1548587-3227555</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6014,22 +6014,22 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2253845</t>
+          <t>LPNBOM5F5057136</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -6037,32 +6037,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-04-26T04:14:08+00:00</t>
+          <t>2026-05-08T15:43:17+00:00</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>408-1134010-7973925</t>
+          <t>402-8374307-7441113</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5321963</t>
+          <t>LPNSDEGF064205</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -6093,32 +6093,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-04-26T03:22:50+00:00</t>
+          <t>2026-05-08T13:25:23+00:00</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>406-9614580-4613163</t>
+          <t>171-7381542-8368365</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -6126,22 +6126,22 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>LPNSPUN46511</t>
+          <t>LPNBLX1C042486</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -6149,32 +6149,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-04-25T05:33:44+00:00</t>
+          <t>2026-05-08T07:49:38+00:00</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>171-3077342-1790757</t>
+          <t>403-3056736-6311553</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>LPNLMAA0002840</t>
+          <t>LPNBLR7Y5321963</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -6205,32 +6205,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-04-25T03:48:59+00:00</t>
+          <t>2026-05-06T06:52:28+00:00</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>404-4908572-3783532</t>
+          <t>403-2654029-0716338</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>X002FOAUSJ</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>LPNBLR7Y6090385</t>
+          <t>LPNSHTI00005958</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -6261,32 +6261,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-04-22T10:55:13+00:00</t>
+          <t>2026-05-06T05:51:00+00:00</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>407-4868470-8499505</t>
+          <t>404-9426288-6037168</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -6294,22 +6294,22 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>LPNLMAA0001354</t>
+          <t>LPNBOM5F5236158</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -6317,32 +6317,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-04-22T04:17:57+00:00</t>
+          <t>2026-05-02T04:54:42+00:00</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>406-5030280-5555520</t>
+          <t>407-6201969-2856316</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -6350,22 +6350,22 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>LPNSDEGF117193</t>
+          <t>LPNLMAA0004457</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -6373,32 +6373,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-04-21T20:42:51+00:00</t>
+          <t>2026-04-28T08:52:43+00:00</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>403-7744956-9735520</t>
+          <t>171-6713241-8377149</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>LPNCCX1B1519621</t>
+          <t>LPNLMAA0003844</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -6429,32 +6429,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-04-20T05:04:40+00:00</t>
+          <t>2026-04-27T06:04:11+00:00</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>171-5598784-9947515</t>
+          <t>403-6021111-3520325</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>X002FOAUSJ</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -6462,22 +6462,22 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5552415</t>
+          <t>LPNLMAA0003335</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -6485,12 +6485,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-18T05:41:14+00:00</t>
+          <t>2026-04-26T08:09:27+00:00</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>404-0309463-1310709</t>
+          <t>402-4881396-1030704</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>LPNDEL4AA0788989</t>
+          <t>LPNDEL4AA2253845</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -6541,32 +6541,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-15T13:55:57+00:00</t>
+          <t>2026-04-26T04:14:08+00:00</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>407-7885481-2445152</t>
+          <t>408-1134010-7973925</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -6574,22 +6574,22 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>SMAB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>LPNSMAB1153810</t>
+          <t>LPNBLR7Y5321963</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -6597,12 +6597,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-15T08:47:44+00:00</t>
+          <t>2026-04-26T03:22:50+00:00</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>407-3585151-4323522</t>
+          <t>406-9614580-4613163</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6630,22 +6630,22 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>LPNSDEGF027993</t>
+          <t>LPNSPUN46511</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -6653,32 +6653,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-12T10:47:54+00:00</t>
+          <t>2026-04-25T05:33:44+00:00</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>407-0802588-3857957</t>
+          <t>171-3077342-1790757</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -6686,22 +6686,22 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>LPNSDEGF026167</t>
+          <t>LPNLMAA0002840</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -6709,32 +6709,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-11T06:17:07+00:00</t>
+          <t>2026-04-25T03:48:59+00:00</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>408-2417441-1123516</t>
+          <t>404-4908572-3783532</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FBK76764</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>B0BMV1WPHL</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>X00242TZTH</t>
+          <t>X002FOAUSJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>White Mulberry Ergonomic Sit Stand Desk | Standing Desk for Office, Home &amp; Study | Everyday Ergonomic Desk | 1200mm x 600mm | Carbon Fibre</t>
+          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>LPNSHTI00004704</t>
+          <t>LPNBLR7Y6090385</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
@@ -6765,32 +6765,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-09T03:38:39+00:00</t>
+          <t>2026-04-22T10:55:13+00:00</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>406-0798045-4525148</t>
+          <t>407-4868470-8499505</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -6798,22 +6798,22 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>LPNSDEGF168570</t>
+          <t>LPNLMAA0001354</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -6821,32 +6821,32 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-08T10:17:09+00:00</t>
+          <t>2026-04-22T04:17:57+00:00</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>406-3115014-9939528</t>
+          <t>406-5030280-5555520</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -6854,22 +6854,22 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2155169</t>
+          <t>LPNSDEGF117193</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
@@ -6877,12 +6877,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-08T09:53:57+00:00</t>
+          <t>2026-04-21T20:42:51+00:00</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>403-7697438-5361950</t>
+          <t>403-7744956-9735520</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>LPNMAA4Z0044638</t>
+          <t>LPNCCX1B1519621</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -6933,32 +6933,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-07T23:27:35+00:00</t>
+          <t>2026-04-20T05:04:40+00:00</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>402-3182844-0423531</t>
+          <t>171-5598784-9947515</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X002FOAUSJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -6966,22 +6966,22 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>NO_REASON_GIVEN</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>LPNCCX1B1676425</t>
+          <t>LPNBLR7Y5552415</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -6989,32 +6989,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-07T08:05:07+00:00</t>
+          <t>2026-04-18T05:41:14+00:00</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>404-2599173-5513112</t>
+          <t>404-0309463-1310709</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -7022,22 +7022,22 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>LPNBLX1C066978</t>
+          <t>LPNDEL4AA0788989</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -7045,32 +7045,32 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-06T21:28:06+00:00</t>
+          <t>2026-04-15T13:55:57+00:00</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>408-0894434-7394724</t>
+          <t>407-7885481-2445152</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -7078,22 +7078,22 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SMAB</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>LPNCCX1B1676919</t>
+          <t>LPNSMAB1153810</t>
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
@@ -7101,32 +7101,32 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-06T19:49:19+00:00</t>
+          <t>2026-04-15T08:47:44+00:00</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>402-0299451-2765120</t>
+          <t>407-3585151-4323522</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -7134,22 +7134,22 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>LPNCCX1B2787065</t>
+          <t>LPNSDEGF027993</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -7157,32 +7157,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-06T09:26:15+00:00</t>
+          <t>2026-04-12T10:47:54+00:00</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>402-1769603-3523555</t>
+          <t>407-0802588-3857957</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7200,12 +7200,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>LPNMAA4Z0044156</t>
+          <t>LPNSDEGF026167</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -7213,32 +7213,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-06T08:31:32+00:00</t>
+          <t>2026-04-11T06:17:07+00:00</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>408-6381953-4631553</t>
+          <t>408-2417441-1123516</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBK76764</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BMV1WPHL</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X00242TZTH</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Ergonomic Sit Stand Desk | Standing Desk for Office, Home &amp; Study | Everyday Ergonomic Desk | 1200mm x 600mm | Carbon Fibre</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -7246,22 +7246,22 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>LPNSPUN45721</t>
+          <t>LPNSHTI00004704</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -7269,32 +7269,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-05T06:19:10+00:00</t>
+          <t>2026-04-09T03:38:39+00:00</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>408-5061007-8220304</t>
+          <t>406-0798045-4525148</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -7302,22 +7302,22 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>LPNBLR7Y6062118</t>
+          <t>LPNSDEGF168570</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
@@ -7325,12 +7325,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-04T08:29:33+00:00</t>
+          <t>2026-04-08T10:17:09+00:00</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>404-3586878-1942709</t>
+          <t>406-3115014-9939528</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2909513</t>
+          <t>LPNDEL4AA2155169</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -7381,12 +7381,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-04T05:05:55+00:00</t>
+          <t>2026-04-08T09:53:57+00:00</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>406-7410699-4348354</t>
+          <t>403-7697438-5361950</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7414,22 +7414,22 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>LPNBOM5F4750684</t>
+          <t>LPNMAA4Z0044638</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -7437,12 +7437,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-03T06:19:12+00:00</t>
+          <t>2026-04-07T23:27:35+00:00</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>402-5121290-6150762</t>
+          <t>402-3182844-0423531</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NO_REASON_GIVEN</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>LPNBLR7Y6061498</t>
+          <t>LPNCCX1B1676425</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -7493,32 +7493,32 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-02T22:22:31+00:00</t>
+          <t>2026-04-07T08:05:07+00:00</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>408-3588035-4966746</t>
+          <t>404-2599173-5513112</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>LPNCCX1B1791593</t>
+          <t>LPNBLX1C066978</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -7549,32 +7549,32 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-02T09:06:26+00:00</t>
+          <t>2026-04-06T21:28:06+00:00</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>407-9710322-7452309</t>
+          <t>408-0894434-7394724</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>SMAB</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>LPNSMAB1152091</t>
+          <t>LPNCCX1B1676919</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -7605,12 +7605,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-01T07:39:28+00:00</t>
+          <t>2026-04-06T19:49:19+00:00</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>406-6943963-1269164</t>
+          <t>402-0299451-2765120</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7638,22 +7638,22 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>LPNMAA4Z0042841</t>
+          <t>LPNCCX1B2787065</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -7661,12 +7661,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-01T04:41:19+00:00</t>
+          <t>2026-04-06T09:26:15+00:00</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>407-5389538-7877131</t>
+          <t>402-1769603-3523555</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>LPNBLR7Y6066340</t>
+          <t>LPNMAA4Z0044156</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -7717,32 +7717,32 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-03-30T05:18:49+00:00</t>
+          <t>2026-04-06T08:31:32+00:00</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>404-1982461-8334714</t>
+          <t>408-6381953-4631553</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -7750,22 +7750,22 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>LPNSBOB1349280</t>
+          <t>LPNSPUN45721</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -7773,12 +7773,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-03-29T10:53:53+00:00</t>
+          <t>2026-04-05T06:19:10+00:00</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>405-8091328-8864306</t>
+          <t>408-5061007-8220304</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7811,17 +7811,17 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5210343</t>
+          <t>LPNBLR7Y6062118</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -7829,12 +7829,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-03-29T08:39:47+00:00</t>
+          <t>2026-04-04T08:29:33+00:00</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>404-0275397-5471541</t>
+          <t>404-3586878-1942709</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>LPNMAA4Z0042171</t>
+          <t>LPNDEL4AA2909513</t>
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
@@ -7885,32 +7885,32 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-03-29T04:27:01+00:00</t>
+          <t>2026-04-04T05:05:55+00:00</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>408-2590879-7685922</t>
+          <t>406-7410699-4348354</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -7918,22 +7918,22 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>SCCE</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>LPNSCCE00184933</t>
+          <t>LPNBOM5F4750684</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
@@ -7941,12 +7941,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-03-28T09:39:21+00:00</t>
+          <t>2026-04-03T06:19:12+00:00</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>404-8968142-0792368</t>
+          <t>402-5121290-6150762</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7974,22 +7974,22 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2286093</t>
+          <t>LPNBLR7Y6061498</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -7997,32 +7997,32 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-03-27T07:20:53+00:00</t>
+          <t>2026-04-02T22:22:31+00:00</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>171-0125093-8349152</t>
+          <t>408-3588035-4966746</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>LPNSDEGF065164</t>
+          <t>LPNCCX1B1791593</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -8053,58 +8053,170 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-03-27T06:20:12+00:00</t>
+          <t>2026-04-02T09:06:26+00:00</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>404-1687880-6063541</t>
+          <t>407-9710322-7452309</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
+          <t>FBA76415</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>X001MZYX7L</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>SMAB</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>CUSTOMER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>DEFECTIVE</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>LPNSMAB1152091</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-04-01T07:39:28+00:00</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>406-6943963-1269164</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
           <t>FBA79167</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>B0CPFS24ML</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="E138" t="inlineStr">
         <is>
           <t>X001Y5UYX1</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
-      <c r="G137" t="n">
-        <v>1</v>
-      </c>
-      <c r="H137" t="inlineStr">
+      <c r="G138" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" t="inlineStr">
         <is>
           <t>MAA4</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>SELLABLE</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>LPNMAA4Z0059504</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>CUSTOMER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>QUALITY_UNACCEPTABLE</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>LPNMAA4Z0042841</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-04-01T04:41:19+00:00</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>407-5389538-7877131</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>FBA79167</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>X001Y5UYX1</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>BLR7</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>CARRIER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>UNDELIVERABLE_REFUSED</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>LPNBLR7Y6066340</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/raw/returns/WhiteMulberry.xlsx
+++ b/data/raw/returns/WhiteMulberry.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,66 +413,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L139"/>
+  <dimension ref="A1:L140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>return-date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>order-id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>fnsku</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>product-name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>fulfillment-center-id</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>detailed-disposition</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>license-plate-number</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>customer-comments</t>
         </is>
@@ -493,12 +481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-28T19:38:03+00:00</t>
+          <t>2026-06-29T12:22:41+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>402-4296829-1337133</t>
+          <t>405-6904525-0069903</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -526,22 +514,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>LPNCCX1B2440445</t>
+          <t>LPNHYD8EF20503</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -549,12 +537,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-28T08:39:43+00:00</t>
+          <t>2026-06-28T19:38:03+00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>402-6090489-2032337</t>
+          <t>402-4296829-1337133</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -582,7 +570,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -597,7 +585,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7855923</t>
+          <t>LPNCCX1B2440445</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -605,12 +593,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-27T11:00:01+00:00</t>
+          <t>2026-06-28T08:39:43+00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>408-3896665-0021948</t>
+          <t>402-6090489-2032337</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -643,17 +631,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7855626</t>
+          <t>LPNBLR7Y7855923</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -661,32 +649,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-27T10:32:22+00:00</t>
+          <t>2026-06-27T11:00:01+00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>407-5462207-4616334</t>
+          <t>408-3896665-0021948</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -694,12 +682,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -709,7 +697,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LPNSBOB1388621</t>
+          <t>LPNBLR7Y7855626</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -717,32 +705,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26T18:08:18+00:00</t>
+          <t>2026-06-27T10:32:22+00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>171-5586406-9945900</t>
+          <t>407-5462207-4616334</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -760,12 +748,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LPNSBOB1388302</t>
+          <t>LPNSBOB1388621</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -773,12 +761,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26T06:57:42+00:00</t>
+          <t>2026-06-26T18:08:18+00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>405-2746376-7486724</t>
+          <t>171-5586406-9945900</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -806,22 +794,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LPNBLX1C140655</t>
+          <t>LPNSBOB1388302</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -829,32 +817,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26T05:19:18+00:00</t>
+          <t>2026-06-26T06:57:42+00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>406-4442109-5330751</t>
+          <t>405-2746376-7486724</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -862,7 +850,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -877,7 +865,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3990308</t>
+          <t>LPNBLX1C140655</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -885,32 +873,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-25T18:24:43+00:00</t>
+          <t>2026-06-26T05:19:18+00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>405-2433007-9289947</t>
+          <t>406-4442109-5330751</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -918,22 +906,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>LPNSBOB1387687</t>
+          <t>LPNDEL4AA3990308</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -941,32 +929,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-25T10:05:58+00:00</t>
+          <t>2026-06-25T18:24:43+00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>407-3034951-4675566</t>
+          <t>405-2433007-9289947</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -974,22 +962,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2273850</t>
+          <t>LPNSBOB1387687</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -997,32 +985,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-24T08:29:31+00:00</t>
+          <t>2026-06-25T10:05:58+00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>402-0120877-0312362</t>
+          <t>407-3034951-4675566</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1030,22 +1018,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>LPNSPUN59333</t>
+          <t>LPNMAA4Z2273850</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1053,32 +1041,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-24T06:17:22+00:00</t>
+          <t>2026-06-24T08:29:31+00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>403-8864299-1768360</t>
+          <t>402-0120877-0312362</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1086,22 +1074,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7854241</t>
+          <t>LPNSPUN59333</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1109,32 +1097,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-23T15:36:47+00:00</t>
+          <t>2026-06-24T06:17:22+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>402-8717460-5700310</t>
+          <t>403-8864299-1768360</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1142,7 +1130,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1152,12 +1140,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>LPNHDX8A005873</t>
+          <t>LPNBLR7Y7854241</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1165,32 +1153,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-23T11:54:27+00:00</t>
+          <t>2026-06-23T15:36:47+00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>403-7688253-5273167</t>
+          <t>402-8717460-5700310</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1198,22 +1186,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>LPNBOM5F5694482</t>
+          <t>LPNHDX8A005873</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1221,12 +1209,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-23T09:27:19+00:00</t>
+          <t>2026-06-23T11:54:27+00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>408-9857262-4357961</t>
+          <t>403-7688253-5273167</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1254,7 +1242,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1269,7 +1257,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7853975</t>
+          <t>LPNBOM5F5694482</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1277,12 +1265,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-23T08:32:44+00:00</t>
+          <t>2026-06-23T09:27:19+00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>404-2029470-0977929</t>
+          <t>408-9857262-4357961</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1310,7 +1298,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1320,12 +1308,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3925027</t>
+          <t>LPNBLR7Y7853975</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1333,32 +1321,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-23T06:25:18+00:00</t>
+          <t>2026-06-23T08:32:44+00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>408-7120729-6837923</t>
+          <t>404-2029470-0977929</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1366,7 +1354,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1376,12 +1364,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>LPNSBOB1385946</t>
+          <t>LPNDEL4AA3925027</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1389,12 +1377,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-23T05:29:18+00:00</t>
+          <t>2026-06-23T06:25:18+00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>403-5101653-2865108</t>
+          <t>408-7120729-6837923</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1422,22 +1410,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>LPNHDX8005941</t>
+          <t>LPNSBOB1385946</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1445,32 +1433,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-22T15:00:37+00:00</t>
+          <t>2026-06-23T05:29:18+00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>408-2886313-6344340</t>
+          <t>403-5101653-2865108</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1478,7 +1466,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1488,12 +1476,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>LPNSBOB1385291</t>
+          <t>LPNHDX8005941</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1501,32 +1489,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-22T15:00:11+00:00</t>
+          <t>2026-06-22T15:00:37+00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>403-4065197-2565940</t>
+          <t>408-2886313-6344340</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1549,7 +1537,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>LPNSBOB1385290</t>
+          <t>LPNSBOB1385291</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1557,32 +1545,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-22T13:49:32+00:00</t>
+          <t>2026-06-22T15:00:11+00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>171-3328269-2691534</t>
+          <t>403-4065197-2565940</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1590,22 +1578,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>LPNBLX1C049419</t>
+          <t>LPNSBOB1385290</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1613,32 +1601,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-22T13:44:52+00:00</t>
+          <t>2026-06-22T13:49:32+00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>407-2806960-6949923</t>
+          <t>171-3328269-2691534</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1651,17 +1639,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>LPNBLX1C049418</t>
+          <t>LPNBLX1C049419</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1669,32 +1657,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-22T12:43:38+00:00</t>
+          <t>2026-06-22T13:44:52+00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>402-2531413-4073130</t>
+          <t>407-2806960-6949923</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1702,22 +1690,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>LPNHYD8EF41160</t>
+          <t>LPNBLX1C049418</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1725,12 +1713,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-22T09:02:33+00:00</t>
+          <t>2026-06-22T12:43:38+00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>404-4254275-9061104</t>
+          <t>402-2531413-4073130</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1763,17 +1751,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>LPNHYD8ED01352</t>
+          <t>LPNHYD8EF41160</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1781,12 +1769,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-22T06:27:11+00:00</t>
+          <t>2026-06-22T09:02:33+00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>407-5289320-1468336</t>
+          <t>404-4254275-9061104</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1814,22 +1802,22 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7287766</t>
+          <t>LPNHYD8ED01352</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1837,32 +1825,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-21T15:48:42+00:00</t>
+          <t>2026-06-22T06:27:11+00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>408-1433377-1765942</t>
+          <t>407-5289320-1468336</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1870,22 +1858,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>LPNSBOB1385218</t>
+          <t>LPNBLR7Y7287766</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1893,32 +1881,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-21T09:50:13+00:00</t>
+          <t>2026-06-21T15:48:42+00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>405-1204534-8479517</t>
+          <t>408-1433377-1765942</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1926,22 +1914,22 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>LPNDEL4AA4027730</t>
+          <t>LPNSBOB1385218</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1949,12 +1937,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-21T08:35:03+00:00</t>
+          <t>2026-06-21T09:50:13+00:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>171-0025867-6612374</t>
+          <t>405-1204534-8479517</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1982,7 +1970,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1997,7 +1985,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7853300</t>
+          <t>LPNDEL4AA4027730</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -2005,12 +1993,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-20T13:05:37+00:00</t>
+          <t>2026-06-21T08:35:03+00:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>402-8590404-8535510</t>
+          <t>171-0025867-6612374</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2038,7 +2026,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2053,7 +2041,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>LPNMAA4G898204</t>
+          <t>LPNBLR7Y7853300</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2061,32 +2049,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-19T14:24:04+00:00</t>
+          <t>2026-06-20T13:05:37+00:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>403-3269966-6849104</t>
+          <t>402-8590404-8535510</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2094,7 +2082,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2109,7 +2097,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>LPNHDX8A004693</t>
+          <t>LPNMAA4G898204</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2117,32 +2105,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-18T09:53:43+00:00</t>
+          <t>2026-06-19T14:24:04+00:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>408-1513827-8090763</t>
+          <t>403-3269966-6849104</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2150,22 +2138,22 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2273003</t>
+          <t>LPNHDX8A004693</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2173,32 +2161,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-18T09:01:23+00:00</t>
+          <t>2026-06-18T09:53:43+00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>402-6972876-7770702</t>
+          <t>408-1513827-8090763</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FBA76765</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B0BMQQQ7YD</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>X001O7YYCV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>White Mulberry Motorized Height Adjustable Sit-Stand Desk | Electronic Height Adjustable | Motor &amp; Memory Preset Controller | Office, Workstation or Home | Carbon Fibre | 120 * 60*H(75-118) cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2206,22 +2194,22 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>LPNSPUN58279</t>
+          <t>LPNMAA4Z2273003</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2229,32 +2217,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-18T06:34:47+00:00</t>
+          <t>2026-06-18T09:01:23+00:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>171-5595331-6677926</t>
+          <t>402-6972876-7770702</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA76765</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BMQQQ7YD</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001O7YYCV</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Motorized Height Adjustable Sit-Stand Desk | Electronic Height Adjustable | Motor &amp; Memory Preset Controller | Office, Workstation or Home | Carbon Fibre | 120 * 60*H(75-118) cm</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2272,12 +2260,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>LPNSPUN58332</t>
+          <t>LPNSPUN58279</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2285,32 +2273,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-18T06:13:54+00:00</t>
+          <t>2026-06-18T06:34:47+00:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>405-9716650-4190754</t>
+          <t>171-5595331-6677926</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2328,12 +2316,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>LPNSPUN58348</t>
+          <t>LPNSPUN58332</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2341,32 +2329,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-18T05:06:11+00:00</t>
+          <t>2026-06-18T06:13:54+00:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>405-0242402-8315559</t>
+          <t>405-9716650-4190754</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2374,7 +2362,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2384,12 +2372,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>LPNHYD8DY89222</t>
+          <t>LPNSPUN58348</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2397,12 +2385,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-18T03:18:32+00:00</t>
+          <t>2026-06-18T05:06:11+00:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>403-8790017-7829152</t>
+          <t>405-0242402-8315559</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2445,7 +2433,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>LPNHYD8DY89148</t>
+          <t>LPNHYD8DY89222</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2453,12 +2441,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-17T17:18:11+00:00</t>
+          <t>2026-06-18T03:18:32+00:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>408-3294486-3424329</t>
+          <t>403-8790017-7829152</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2486,12 +2474,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2501,7 +2489,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>LPNCCX1B4206954</t>
+          <t>LPNHYD8DY89148</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2509,32 +2497,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-17T11:01:26+00:00</t>
+          <t>2026-06-17T17:18:11+00:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>171-3399563-8885966</t>
+          <t>408-3294486-3424329</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2542,22 +2530,22 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>DAMAGED</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>LPNLMAA0019039</t>
+          <t>LPNCCX1B4206954</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -2565,32 +2553,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-15T09:24:30+00:00</t>
+          <t>2026-06-17T11:01:26+00:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>171-3194001-5187538</t>
+          <t>171-3399563-8885966</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2598,22 +2586,22 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>LPNHYD8DY92591</t>
+          <t>LPNLMAA0019039</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -2621,32 +2609,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15T08:53:22+00:00</t>
+          <t>2026-06-15T09:24:30+00:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>406-3765893-9779536</t>
+          <t>171-3194001-5187538</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2654,22 +2642,22 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>LPNHDX8A0002233</t>
+          <t>LPNHYD8DY92591</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2677,32 +2665,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-14T11:15:53+00:00</t>
+          <t>2026-06-15T08:53:22+00:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>171-1282309-9677932</t>
+          <t>406-3765893-9779536</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2710,22 +2698,22 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2198432</t>
+          <t>LPNHDX8A0002233</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -2733,12 +2721,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-14T06:26:57+00:00</t>
+          <t>2026-06-14T11:15:53+00:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>407-1845667-2313146</t>
+          <t>171-1282309-9677932</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2766,7 +2754,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2781,7 +2769,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3677498</t>
+          <t>LPNMAA4Z2198432</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -2789,32 +2777,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-13T12:21:24+00:00</t>
+          <t>2026-06-14T06:26:57+00:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>405-5466299-6857906</t>
+          <t>407-1845667-2313146</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2822,12 +2810,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2837,7 +2825,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>LPNSBOB1375958</t>
+          <t>LPNDEL4AA3677498</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2845,32 +2833,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-13T12:20:57+00:00</t>
+          <t>2026-06-13T12:21:24+00:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>404-9976514-7382743</t>
+          <t>405-5466299-6857906</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2883,17 +2871,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>LPNSBOB1375957</t>
+          <t>LPNSBOB1375958</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -2901,32 +2889,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-12T11:47:28+00:00</t>
+          <t>2026-06-13T12:20:57+00:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>407-2845785-4936332</t>
+          <t>404-9976514-7382743</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2934,22 +2922,22 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>LPNSHTI00009280</t>
+          <t>LPNSBOB1375957</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -2957,32 +2945,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-11T12:39:34+00:00</t>
+          <t>2026-06-12T11:47:28+00:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>405-0836953-9114742</t>
+          <t>407-2845785-4936332</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2990,7 +2978,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3000,12 +2988,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>LPNHDX8A001607</t>
+          <t>LPNSHTI00009280</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3013,32 +3001,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-11T10:43:03+00:00</t>
+          <t>2026-06-11T12:39:34+00:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>407-7053626-1929962</t>
+          <t>405-0836953-9114742</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FBA79667</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>B0DQPK7MFH</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>X0027512Z1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk with Shelf|DIY Assembly| Monitor Raising Shelf |Engineered Wood &amp; Sturdy Steel Leg|Perfect for Computer Table Office Home Gaming Study Desk|L(130+130)*45*77cm|White</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3046,22 +3034,22 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SCUY</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>LPNSCUY00017897</t>
+          <t>LPNHDX8A001607</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3069,32 +3057,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-10T22:26:08+00:00</t>
+          <t>2026-06-11T10:43:03+00:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>404-0639682-6860336</t>
+          <t>407-7053626-1929962</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79667</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQPK7MFH</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0027512Z1</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk with Shelf|DIY Assembly| Monitor Raising Shelf |Engineered Wood &amp; Sturdy Steel Leg|Perfect for Computer Table Office Home Gaming Study Desk|L(130+130)*45*77cm|White</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3102,7 +3090,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SCUY</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3112,12 +3100,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>LPNCX1B4784440</t>
+          <t>LPNSCUY00017897</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -3125,12 +3113,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-10T12:14:02+00:00</t>
+          <t>2026-06-10T22:26:08+00:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>171-1027170-0049924</t>
+          <t>404-0639682-6860336</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3158,12 +3146,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3173,7 +3161,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2407733</t>
+          <t>LPNCX1B4784440</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -3181,32 +3169,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-10T08:20:03+00:00</t>
+          <t>2026-06-10T12:14:02+00:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>406-6295410-5869130</t>
+          <t>171-1027170-0049924</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3214,22 +3202,22 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>LPNBLX1C159057</t>
+          <t>LPNMAA4Z2407733</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3237,32 +3225,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-10T05:42:02+00:00</t>
+          <t>2026-06-10T08:20:03+00:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>405-8329990-8940345</t>
+          <t>406-6295410-5869130</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -3270,22 +3258,22 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4745942</t>
+          <t>LPNBLX1C159057</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3293,12 +3281,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-10T04:51:41+00:00</t>
+          <t>2026-06-10T05:42:02+00:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>405-7954322-6131539</t>
+          <t>405-8329990-8940345</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3326,12 +3314,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3341,7 +3329,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>LPNBOM5F5675078</t>
+          <t>LPNBLR7Y4745942</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -3349,12 +3337,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-10T03:51:05+00:00</t>
+          <t>2026-06-10T04:51:41+00:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>407-5527946-4998741</t>
+          <t>405-7954322-6131539</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3382,12 +3370,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3397,7 +3385,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7287766</t>
+          <t>LPNBOM5F5675078</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -3405,12 +3393,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-08T09:59:30+00:00</t>
+          <t>2026-06-10T03:51:05+00:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>404-4052225-7064331</t>
+          <t>407-5527946-4998741</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3438,7 +3426,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3448,12 +3436,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3631375</t>
+          <t>LPNBLR7Y7287766</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -3461,32 +3449,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-08T08:59:50+00:00</t>
+          <t>2026-06-08T09:59:30+00:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>404-3123106-0929939</t>
+          <t>404-4052225-7064331</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FBK76387</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>B0BF4S7V8C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>X00242V9DH</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3494,22 +3482,22 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>LPNSPUN56234</t>
+          <t>LPNDEL4AA3631375</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -3517,32 +3505,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-08T08:59:02+00:00</t>
+          <t>2026-06-08T08:59:50+00:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>408-8800113-8391502</t>
+          <t>404-3123106-0929939</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBK76387</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0BF4S7V8C</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X00242V9DH</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | White</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3560,12 +3548,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>LPNSPUN56235</t>
+          <t>LPNSPUN56234</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -3573,32 +3561,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-08T08:43:30+00:00</t>
+          <t>2026-06-08T08:59:02+00:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>407-4254200-0562712</t>
+          <t>408-8800113-8391502</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3606,22 +3594,22 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3631346</t>
+          <t>LPNSPUN56235</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3629,12 +3617,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-07T16:09:41+00:00</t>
+          <t>2026-06-08T08:43:30+00:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>405-9852474-3831538</t>
+          <t>407-4254200-0562712</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3662,22 +3650,22 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>LPNCCX1B4179343</t>
+          <t>LPNDEL4AA3631346</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -3685,32 +3673,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-06-07T11:20:49+00:00</t>
+          <t>2026-06-07T16:09:41+00:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>406-9783608-9093148</t>
+          <t>405-9852474-3831538</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -3718,7 +3706,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3728,12 +3716,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>LPNLMAA0016237</t>
+          <t>LPNCCX1B4179343</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -3741,32 +3729,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-06-07T10:24:17+00:00</t>
+          <t>2026-06-07T11:20:49+00:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>406-6392223-8173930</t>
+          <t>406-9783608-9093148</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3774,12 +3762,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3789,7 +3777,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>LPNBLX1C047099</t>
+          <t>LPNLMAA0016237</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -3797,32 +3785,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-06-06T10:45:59+00:00</t>
+          <t>2026-06-07T10:24:17+00:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>406-9111649-3125130</t>
+          <t>406-6392223-8173930</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -3830,22 +3818,22 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>LPNBOM5F5579985</t>
+          <t>LPNBLX1C047099</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -3853,12 +3841,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-06-05T09:54:50+00:00</t>
+          <t>2026-06-06T10:45:59+00:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>405-7328472-7893901</t>
+          <t>406-9111649-3125130</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3886,7 +3874,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3896,12 +3884,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679697</t>
+          <t>LPNBOM5F5579985</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -3909,32 +3897,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-06-05T08:35:28+00:00</t>
+          <t>2026-06-05T09:54:50+00:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>404-9218549-9930734</t>
+          <t>405-7328472-7893901</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FBA79659</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>X0026ZDA2F</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, Black, 3 Year Warranty</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -3942,7 +3930,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3952,12 +3940,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>LPNSDEGF082043</t>
+          <t>LPNDEL4AA3679697</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -3965,32 +3953,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-06-05T08:17:03+00:00</t>
+          <t>2026-06-05T08:35:28+00:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>171-6540897-0152357</t>
+          <t>404-9218549-9930734</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79659</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZDA2F</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, Black, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -3998,7 +3986,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4008,12 +3996,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679650</t>
+          <t>LPNSDEGF082043</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4021,12 +4009,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-06-05T04:33:06+00:00</t>
+          <t>2026-06-05T08:17:03+00:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>171-6354444-3723505</t>
+          <t>171-6540897-0152357</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4054,22 +4042,22 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>LPNBOM5F5574228</t>
+          <t>LPNDEL4AA3679650</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -4077,12 +4065,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-06-05T04:28:18+00:00</t>
+          <t>2026-06-05T04:33:06+00:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>406-6103690-9310748</t>
+          <t>171-6354444-3723505</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4110,22 +4098,22 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679535</t>
+          <t>LPNBOM5F5574228</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -4133,12 +4121,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-06-04T03:47:36+00:00</t>
+          <t>2026-06-05T04:28:18+00:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>406-2278126-7841949</t>
+          <t>406-6103690-9310748</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4181,7 +4169,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679185</t>
+          <t>LPNDEL4AA3679535</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -4189,12 +4177,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-06-01T09:32:55+00:00</t>
+          <t>2026-06-04T03:47:36+00:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>402-3794541-2581168</t>
+          <t>406-2278126-7841949</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4222,7 +4210,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4232,12 +4220,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4743333</t>
+          <t>LPNDEL4AA3679185</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -4245,12 +4233,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-06-01T04:42:36+00:00</t>
+          <t>2026-06-01T09:32:55+00:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>408-0143238-4374708</t>
+          <t>402-3794541-2581168</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4278,7 +4266,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4293,7 +4281,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>LPNBOM5F5524445</t>
+          <t>LPNBLR7Y4743333</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -4301,12 +4289,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-06-01T03:58:27+00:00</t>
+          <t>2026-06-01T04:42:36+00:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>406-4355667-6072332</t>
+          <t>408-0143238-4374708</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4334,7 +4322,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4344,12 +4332,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4743158</t>
+          <t>LPNBOM5F5524445</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -4357,12 +4345,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-31T09:10:34+00:00</t>
+          <t>2026-06-01T03:58:27+00:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>404-2518539-4406712</t>
+          <t>406-4355667-6072332</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4390,22 +4378,22 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3976607</t>
+          <t>LPNBLR7Y4743158</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -4413,12 +4401,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-30T22:18:28+00:00</t>
+          <t>2026-05-31T09:10:34+00:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>407-1474707-0478726</t>
+          <t>404-2518539-4406712</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4446,22 +4434,22 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>LPNCCX1B4554643</t>
+          <t>LPNDEL4AA3976607</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -4469,12 +4457,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-30T04:13:42+00:00</t>
+          <t>2026-05-30T22:18:28+00:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>406-7941139-9225906</t>
+          <t>407-1474707-0478726</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4502,12 +4490,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4517,7 +4505,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>LPNBOM5F5507643</t>
+          <t>LPNCCX1B4554643</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -4525,12 +4513,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-29T23:01:15+00:00</t>
+          <t>2026-05-30T04:13:42+00:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>405-0096078-8521126</t>
+          <t>406-7941139-9225906</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4558,12 +4546,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4573,7 +4561,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>LPNCCX1B2941120</t>
+          <t>LPNBOM5F5507643</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -4581,12 +4569,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-29T15:27:20+00:00</t>
+          <t>2026-05-29T23:01:15+00:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>404-8418070-5981124</t>
+          <t>405-0096078-8521126</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4629,7 +4617,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>LPNCCX1B4508596</t>
+          <t>LPNCCX1B2941120</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -4637,12 +4625,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-29T05:18:33+00:00</t>
+          <t>2026-05-29T15:27:20+00:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>171-0407209-4266756</t>
+          <t>404-8418070-5981124</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4670,22 +4658,22 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937926</t>
+          <t>LPNCCX1B4508596</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -4693,12 +4681,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-28T11:56:49+00:00</t>
+          <t>2026-05-29T05:18:33+00:00</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>407-4902279-0189155</t>
+          <t>171-0407209-4266756</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4726,22 +4714,22 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7363000</t>
+          <t>LPNDEL4AA3937926</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -4749,12 +4737,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-28T08:40:02+00:00</t>
+          <t>2026-05-28T11:56:49+00:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>408-1128142-0248321</t>
+          <t>407-4902279-0189155</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4782,7 +4770,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4792,12 +4780,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>DAMAGED_BY_FC</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937756</t>
+          <t>LPNBLR7Y7363000</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -4805,12 +4793,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-28T06:36:17+00:00</t>
+          <t>2026-05-28T08:40:02+00:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>402-4776409-4471512</t>
+          <t>408-1128142-0248321</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4838,7 +4826,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4848,12 +4836,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>DAMAGED_BY_FC</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7286354</t>
+          <t>LPNDEL4AA3937756</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -4861,12 +4849,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-27T12:42:16+00:00</t>
+          <t>2026-05-28T06:36:17+00:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>404-6762038-7137955</t>
+          <t>402-4776409-4471512</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4894,7 +4882,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4904,12 +4892,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937575</t>
+          <t>LPNBLR7Y7286354</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -4917,12 +4905,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-27T09:44:17+00:00</t>
+          <t>2026-05-27T12:42:16+00:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>403-3444915-0085109</t>
+          <t>404-6762038-7137955</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4950,7 +4938,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4965,7 +4953,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7362686</t>
+          <t>LPNDEL4AA3937575</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -4973,32 +4961,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-27T09:25:47+00:00</t>
+          <t>2026-05-27T09:44:17+00:00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>405-8410325-7933918</t>
+          <t>403-3444915-0085109</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -5006,22 +4994,22 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>LPNSPUN53913</t>
+          <t>LPNBLR7Y7362686</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -5029,32 +5017,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-26T23:02:43+00:00</t>
+          <t>2026-05-27T09:25:47+00:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>407-0645348-4574732</t>
+          <t>405-8410325-7933918</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -5062,22 +5050,22 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>LPNCCX1B5292913</t>
+          <t>LPNSPUN53913</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -5085,12 +5073,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-26T11:06:29+00:00</t>
+          <t>2026-05-26T23:02:43+00:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>402-2949127-9513917</t>
+          <t>407-0645348-4574732</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5118,22 +5106,22 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937227</t>
+          <t>LPNCCX1B5292913</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -5141,12 +5129,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-26T08:48:10+00:00</t>
+          <t>2026-05-26T11:06:29+00:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>403-5510263-6469912</t>
+          <t>402-2949127-9513917</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5174,7 +5162,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5189,7 +5177,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273675</t>
+          <t>LPNDEL4AA3937227</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -5197,12 +5185,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-25T15:22:25+00:00</t>
+          <t>2026-05-26T08:48:10+00:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>402-5203149-1906724</t>
+          <t>403-5510263-6469912</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5230,7 +5218,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5240,12 +5228,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>LPNCCX1B5331017</t>
+          <t>LPNBLR7Y7273675</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -5253,12 +5241,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-24T09:24:39+00:00</t>
+          <t>2026-05-25T15:22:25+00:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>171-7709339-0701117</t>
+          <t>402-5203149-1906724</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5286,7 +5274,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5296,12 +5284,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273169</t>
+          <t>LPNCCX1B5331017</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -5309,12 +5297,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-24T08:29:52+00:00</t>
+          <t>2026-05-24T09:24:39+00:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>406-7042486-7436314</t>
+          <t>171-7709339-0701117</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5357,7 +5345,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273150</t>
+          <t>LPNBLR7Y7273169</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -5365,32 +5353,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-23T23:07:27+00:00</t>
+          <t>2026-05-24T08:29:52+00:00</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>406-2954542-5857925</t>
+          <t>406-7042486-7436314</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -5398,22 +5386,22 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>LPNSBOB1370158</t>
+          <t>LPNBLR7Y7273150</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -5421,32 +5409,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-23T10:58:04+00:00</t>
+          <t>2026-05-23T23:07:27+00:00</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>406-4758725-2077907</t>
+          <t>406-2954542-5857925</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -5454,22 +5442,22 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7272896</t>
+          <t>LPNSBOB1370158</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -5477,32 +5465,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-22T09:58:26+00:00</t>
+          <t>2026-05-23T10:58:04+00:00</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>403-7800011-6937966</t>
+          <t>406-4758725-2077907</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -5510,7 +5498,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5525,7 +5513,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>LPNSDEGF010003</t>
+          <t>LPNBLR7Y7272896</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -5533,32 +5521,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-21T04:38:32+00:00</t>
+          <t>2026-05-22T09:58:26+00:00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>403-2400247-1930753</t>
+          <t>403-7800011-6937966</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -5581,7 +5569,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>LPNSDEGF099136</t>
+          <t>LPNSDEGF010003</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -5589,32 +5577,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-20T11:30:45+00:00</t>
+          <t>2026-05-21T04:38:32+00:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>406-2648444-6601917</t>
+          <t>403-2400247-1930753</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -5622,7 +5610,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5632,12 +5620,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2147464</t>
+          <t>LPNSDEGF099136</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -5645,32 +5633,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-19T08:03:32+00:00</t>
+          <t>2026-05-20T11:30:45+00:00</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>405-4744559-6958733</t>
+          <t>406-2648444-6601917</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -5678,7 +5666,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5688,12 +5676,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>LPNSDEGF097985</t>
+          <t>LPNDEL4AA2147464</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -5701,32 +5689,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-18T11:36:05+00:00</t>
+          <t>2026-05-19T08:03:32+00:00</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>171-1585723-0908356</t>
+          <t>405-4744559-6958733</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -5734,12 +5722,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5749,7 +5737,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>LPNBLX1C155145</t>
+          <t>LPNSDEGF097985</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -5757,32 +5745,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-15T08:29:30+00:00</t>
+          <t>2026-05-18T11:36:05+00:00</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>402-4856546-1261939</t>
+          <t>171-1585723-0908356</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -5790,12 +5778,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5805,7 +5793,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>LPNSDEGF074601</t>
+          <t>LPNBLX1C155145</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -5813,12 +5801,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-13T13:50:43+00:00</t>
+          <t>2026-05-15T08:29:30+00:00</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>403-7495250-9937954</t>
+          <t>402-4856546-1261939</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5846,22 +5834,22 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>LPNBLX1C154096</t>
+          <t>LPNSDEGF074601</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -5869,32 +5857,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-12T07:19:54+00:00</t>
+          <t>2026-05-13T13:50:43+00:00</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>408-0473775-6641108</t>
+          <t>403-7495250-9937954</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -5902,22 +5890,22 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>LPNSBOB1362246</t>
+          <t>LPNBLX1C154096</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -5925,12 +5913,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-11T10:31:39+00:00</t>
+          <t>2026-05-12T07:19:54+00:00</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>404-1750959-8518722</t>
+          <t>408-0473775-6641108</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5958,22 +5946,22 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>LPNSHTI00006165</t>
+          <t>LPNSBOB1362246</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -5981,32 +5969,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-10T09:15:43+00:00</t>
+          <t>2026-05-11T10:31:39+00:00</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>402-1548587-3227555</t>
+          <t>404-1750959-8518722</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -6014,22 +6002,22 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>LPNBOM5F5057136</t>
+          <t>LPNSHTI00006165</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -6037,32 +6025,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-08T15:43:17+00:00</t>
+          <t>2026-05-10T09:15:43+00:00</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>402-8374307-7441113</t>
+          <t>402-1548587-3227555</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -6070,7 +6058,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6085,7 +6073,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>LPNSDEGF064205</t>
+          <t>LPNBOM5F5057136</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -6093,32 +6081,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-08T13:25:23+00:00</t>
+          <t>2026-05-08T15:43:17+00:00</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>171-7381542-8368365</t>
+          <t>402-8374307-7441113</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -6126,7 +6114,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6136,12 +6124,12 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>LPNBLX1C042486</t>
+          <t>LPNSDEGF064205</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -6149,32 +6137,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-08T07:49:38+00:00</t>
+          <t>2026-05-08T13:25:23+00:00</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>403-3056736-6311553</t>
+          <t>171-7381542-8368365</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -6182,22 +6170,22 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5321963</t>
+          <t>LPNBLX1C042486</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -6205,32 +6193,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-06T06:52:28+00:00</t>
+          <t>2026-05-08T07:49:38+00:00</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>403-2654029-0716338</t>
+          <t>403-3056736-6311553</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -6238,12 +6226,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6253,7 +6241,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>LPNSHTI00005958</t>
+          <t>LPNBLR7Y5321963</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -6261,32 +6249,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-06T05:51:00+00:00</t>
+          <t>2026-05-06T06:52:28+00:00</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>404-9426288-6037168</t>
+          <t>403-2654029-0716338</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -6294,22 +6282,22 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>LPNBOM5F5236158</t>
+          <t>LPNSHTI00005958</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -6317,32 +6305,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-02T04:54:42+00:00</t>
+          <t>2026-05-06T05:51:00+00:00</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>407-6201969-2856316</t>
+          <t>404-9426288-6037168</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -6350,22 +6338,22 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>LPNLMAA0004457</t>
+          <t>LPNBOM5F5236158</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -6373,12 +6361,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-04-28T08:52:43+00:00</t>
+          <t>2026-05-02T04:54:42+00:00</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>171-6713241-8377149</t>
+          <t>407-6201969-2856316</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6421,7 +6409,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>LPNLMAA0003844</t>
+          <t>LPNLMAA0004457</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -6429,32 +6417,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-04-27T06:04:11+00:00</t>
+          <t>2026-04-28T08:52:43+00:00</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>403-6021111-3520325</t>
+          <t>171-6713241-8377149</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -6467,17 +6455,17 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>LPNLMAA0003335</t>
+          <t>LPNLMAA0003844</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -6485,32 +6473,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-26T08:09:27+00:00</t>
+          <t>2026-04-27T06:04:11+00:00</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>402-4881396-1030704</t>
+          <t>403-6021111-3520325</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -6518,7 +6506,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6528,12 +6516,12 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2253845</t>
+          <t>LPNLMAA0003335</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -6541,12 +6529,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-26T04:14:08+00:00</t>
+          <t>2026-04-26T08:09:27+00:00</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>408-1134010-7973925</t>
+          <t>402-4881396-1030704</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6574,7 +6562,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6584,12 +6572,12 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5321963</t>
+          <t>LPNDEL4AA2253845</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -6597,32 +6585,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-26T03:22:50+00:00</t>
+          <t>2026-04-26T04:14:08+00:00</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>406-9614580-4613163</t>
+          <t>408-1134010-7973925</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -6630,12 +6618,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6645,7 +6633,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>LPNSPUN46511</t>
+          <t>LPNBLR7Y5321963</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -6653,32 +6641,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-25T05:33:44+00:00</t>
+          <t>2026-04-26T03:22:50+00:00</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>171-3077342-1790757</t>
+          <t>406-9614580-4613163</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -6686,7 +6674,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6701,7 +6689,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>LPNLMAA0002840</t>
+          <t>LPNSPUN46511</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -6709,32 +6697,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-25T03:48:59+00:00</t>
+          <t>2026-04-25T05:33:44+00:00</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>404-4908572-3783532</t>
+          <t>171-3077342-1790757</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>X002FOAUSJ</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -6742,7 +6730,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -6752,12 +6740,12 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>LPNBLR7Y6090385</t>
+          <t>LPNLMAA0002840</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
@@ -6765,32 +6753,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-22T10:55:13+00:00</t>
+          <t>2026-04-25T03:48:59+00:00</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>407-4868470-8499505</t>
+          <t>404-4908572-3783532</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X002FOAUSJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -6798,22 +6786,22 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>LPNLMAA0001354</t>
+          <t>LPNBLR7Y6090385</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -6821,32 +6809,32 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-22T04:17:57+00:00</t>
+          <t>2026-04-22T10:55:13+00:00</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>406-5030280-5555520</t>
+          <t>407-4868470-8499505</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -6854,22 +6842,22 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>LPNSDEGF117193</t>
+          <t>LPNLMAA0001354</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
@@ -6877,32 +6865,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-21T20:42:51+00:00</t>
+          <t>2026-04-22T04:17:57+00:00</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>403-7744956-9735520</t>
+          <t>406-5030280-5555520</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -6910,22 +6898,22 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>LPNCCX1B1519621</t>
+          <t>LPNSDEGF117193</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -6933,32 +6921,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-20T05:04:40+00:00</t>
+          <t>2026-04-21T20:42:51+00:00</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>171-5598784-9947515</t>
+          <t>403-7744956-9735520</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>X002FOAUSJ</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -6966,22 +6954,22 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5552415</t>
+          <t>LPNCCX1B1519621</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -6989,32 +6977,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-18T05:41:14+00:00</t>
+          <t>2026-04-20T05:04:40+00:00</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>404-0309463-1310709</t>
+          <t>171-5598784-9947515</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X002FOAUSJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -7022,22 +7010,22 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>LPNDEL4AA0788989</t>
+          <t>LPNBLR7Y5552415</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -7045,32 +7033,32 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-15T13:55:57+00:00</t>
+          <t>2026-04-18T05:41:14+00:00</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>407-7885481-2445152</t>
+          <t>404-0309463-1310709</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -7078,12 +7066,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>SMAB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7093,7 +7081,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>LPNSMAB1153810</t>
+          <t>LPNDEL4AA0788989</t>
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
@@ -7101,12 +7089,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-15T08:47:44+00:00</t>
+          <t>2026-04-15T13:55:57+00:00</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>407-3585151-4323522</t>
+          <t>407-7885481-2445152</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7134,22 +7122,22 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>SMAB</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>LPNSDEGF027993</t>
+          <t>LPNSMAB1153810</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -7157,32 +7145,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-12T10:47:54+00:00</t>
+          <t>2026-04-15T08:47:44+00:00</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>407-0802588-3857957</t>
+          <t>407-3585151-4323522</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -7195,17 +7183,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>LPNSDEGF026167</t>
+          <t>LPNSDEGF027993</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -7213,32 +7201,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-11T06:17:07+00:00</t>
+          <t>2026-04-12T10:47:54+00:00</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>408-2417441-1123516</t>
+          <t>407-0802588-3857957</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FBK76764</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>B0BMV1WPHL</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>X00242TZTH</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>White Mulberry Ergonomic Sit Stand Desk | Standing Desk for Office, Home &amp; Study | Everyday Ergonomic Desk | 1200mm x 600mm | Carbon Fibre</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -7246,22 +7234,22 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>LPNSHTI00004704</t>
+          <t>LPNSDEGF026167</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -7269,32 +7257,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-09T03:38:39+00:00</t>
+          <t>2026-04-11T06:17:07+00:00</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>406-0798045-4525148</t>
+          <t>408-2417441-1123516</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBK76764</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BMV1WPHL</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X00242TZTH</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Ergonomic Sit Stand Desk | Standing Desk for Office, Home &amp; Study | Everyday Ergonomic Desk | 1200mm x 600mm | Carbon Fibre</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -7302,7 +7290,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7312,12 +7300,12 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>LPNSDEGF168570</t>
+          <t>LPNSHTI00004704</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
@@ -7325,32 +7313,32 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-08T10:17:09+00:00</t>
+          <t>2026-04-09T03:38:39+00:00</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>406-3115014-9939528</t>
+          <t>406-0798045-4525148</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -7358,22 +7346,22 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2155169</t>
+          <t>LPNSDEGF168570</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -7381,12 +7369,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-08T09:53:57+00:00</t>
+          <t>2026-04-08T10:17:09+00:00</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>403-7697438-5361950</t>
+          <t>406-3115014-9939528</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7414,22 +7402,22 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>LPNMAA4Z0044638</t>
+          <t>LPNDEL4AA2155169</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -7437,12 +7425,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-07T23:27:35+00:00</t>
+          <t>2026-04-08T09:53:57+00:00</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>402-3182844-0423531</t>
+          <t>403-7697438-5361950</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7470,22 +7458,22 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>NO_REASON_GIVEN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>LPNCCX1B1676425</t>
+          <t>LPNMAA4Z0044638</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -7493,32 +7481,32 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-07T08:05:07+00:00</t>
+          <t>2026-04-07T23:27:35+00:00</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>404-2599173-5513112</t>
+          <t>402-3182844-0423531</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -7526,22 +7514,22 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>NO_REASON_GIVEN</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>LPNBLX1C066978</t>
+          <t>LPNCCX1B1676425</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -7549,32 +7537,32 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-06T21:28:06+00:00</t>
+          <t>2026-04-07T08:05:07+00:00</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>408-0894434-7394724</t>
+          <t>404-2599173-5513112</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -7582,7 +7570,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7592,12 +7580,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>LPNCCX1B1676919</t>
+          <t>LPNBLX1C066978</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -7605,12 +7593,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-06T19:49:19+00:00</t>
+          <t>2026-04-06T21:28:06+00:00</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>402-0299451-2765120</t>
+          <t>408-0894434-7394724</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7643,17 +7631,17 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>LPNCCX1B2787065</t>
+          <t>LPNCCX1B1676919</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -7661,12 +7649,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-06T09:26:15+00:00</t>
+          <t>2026-04-06T19:49:19+00:00</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>402-1769603-3523555</t>
+          <t>402-0299451-2765120</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7694,7 +7682,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7709,7 +7697,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>LPNMAA4Z0044156</t>
+          <t>LPNCCX1B2787065</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -7717,32 +7705,32 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-04-06T08:31:32+00:00</t>
+          <t>2026-04-06T09:26:15+00:00</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>408-6381953-4631553</t>
+          <t>402-1769603-3523555</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -7750,22 +7738,22 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>LPNSPUN45721</t>
+          <t>LPNMAA4Z0044156</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -7773,32 +7761,32 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-04-05T06:19:10+00:00</t>
+          <t>2026-04-06T08:31:32+00:00</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>408-5061007-8220304</t>
+          <t>408-6381953-4631553</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -7806,22 +7794,22 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>LPNBLR7Y6062118</t>
+          <t>LPNSPUN45721</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -7829,12 +7817,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-04-04T08:29:33+00:00</t>
+          <t>2026-04-05T06:19:10+00:00</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>404-3586878-1942709</t>
+          <t>408-5061007-8220304</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7862,7 +7850,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -7872,12 +7860,12 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2909513</t>
+          <t>LPNBLR7Y6062118</t>
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
@@ -7885,12 +7873,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-04-04T05:05:55+00:00</t>
+          <t>2026-04-04T08:29:33+00:00</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>406-7410699-4348354</t>
+          <t>404-3586878-1942709</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7918,7 +7906,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7928,12 +7916,12 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>LPNBOM5F4750684</t>
+          <t>LPNDEL4AA2909513</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
@@ -7941,12 +7929,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-04-03T06:19:12+00:00</t>
+          <t>2026-04-04T05:05:55+00:00</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>402-5121290-6150762</t>
+          <t>406-7410699-4348354</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7974,7 +7962,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7984,12 +7972,12 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>LPNBLR7Y6061498</t>
+          <t>LPNBOM5F4750684</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -7997,12 +7985,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-04-02T22:22:31+00:00</t>
+          <t>2026-04-03T06:19:12+00:00</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>408-3588035-4966746</t>
+          <t>402-5121290-6150762</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8030,22 +8018,22 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>LPNCCX1B1791593</t>
+          <t>LPNBLR7Y6061498</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -8053,32 +8041,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-04-02T09:06:26+00:00</t>
+          <t>2026-04-02T22:22:31+00:00</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>407-9710322-7452309</t>
+          <t>408-3588035-4966746</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -8086,7 +8074,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>SMAB</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8096,12 +8084,12 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>LPNSMAB1152091</t>
+          <t>LPNCCX1B1791593</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
@@ -8109,32 +8097,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-04-01T07:39:28+00:00</t>
+          <t>2026-04-02T09:06:26+00:00</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>406-6943963-1269164</t>
+          <t>407-9710322-7452309</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -8142,7 +8130,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>SMAB</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8152,12 +8140,12 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>LPNMAA4Z0042841</t>
+          <t>LPNSMAB1152091</t>
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
@@ -8165,58 +8153,114 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>2026-04-01T07:39:28+00:00</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>406-6943963-1269164</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>FBA79167</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>X001Y5UYX1</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>MAA4</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>CUSTOMER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>QUALITY_UNACCEPTABLE</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>LPNMAA4Z0042841</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
           <t>2026-04-01T04:41:19+00:00</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>407-5389538-7877131</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>FBA79167</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>B0CPFS24ML</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E140" t="inlineStr">
         <is>
           <t>X001Y5UYX1</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
-      <c r="G139" t="n">
-        <v>1</v>
-      </c>
-      <c r="H139" t="inlineStr">
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="inlineStr">
         <is>
           <t>BLR7</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
+      <c r="I140" t="inlineStr">
         <is>
           <t>CARRIER_DAMAGED</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr">
+      <c r="J140" t="inlineStr">
         <is>
           <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
+      <c r="K140" t="inlineStr">
         <is>
           <t>LPNBLR7Y6066340</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/raw/returns/WhiteMulberry.xlsx
+++ b/data/raw/returns/WhiteMulberry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L140"/>
+  <dimension ref="A1:L141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29T12:22:41+00:00</t>
+          <t>2026-07-02T17:30:33+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>405-6904525-0069903</t>
+          <t>402-1004506-0818747</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -514,22 +514,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>LPNHYD8EF20503</t>
+          <t>LPNBLR8Z5514346</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -537,12 +537,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-28T19:38:03+00:00</t>
+          <t>2026-07-02T06:41:10+00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>402-4296829-1337133</t>
+          <t>403-6072724-5581966</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,22 +570,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>LPNCCX1B2440445</t>
+          <t>LPNBLR8Z4303742</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -593,12 +593,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-28T08:39:43+00:00</t>
+          <t>2026-07-01T22:20:26+00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>402-6090489-2032337</t>
+          <t>402-4598141-9561917</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,12 +626,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7855923</t>
+          <t>LPNCCX1B4170658</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -649,32 +649,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-27T11:00:01+00:00</t>
+          <t>2026-07-01T15:09:10+00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>408-3896665-0021948</t>
+          <t>402-3081497-7409144</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -682,12 +682,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7855626</t>
+          <t>LPNBLX1C093497</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -705,32 +705,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-27T10:32:22+00:00</t>
+          <t>2026-07-01T09:24:20+00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>407-5462207-4616334</t>
+          <t>405-3824107-9644368</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -738,22 +738,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LPNSBOB1388621</t>
+          <t>LPNBOM5F5465051</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -761,32 +761,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26T18:08:18+00:00</t>
+          <t>2026-07-01T06:49:32+00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>171-5586406-9945900</t>
+          <t>404-6104605-6788338</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -794,22 +794,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LPNSBOB1388302</t>
+          <t>LPNBOM5F5435891</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -817,32 +817,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26T06:57:42+00:00</t>
+          <t>2026-07-01T05:46:54+00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>405-2746376-7486724</t>
+          <t>407-2497737-1874765</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -850,7 +850,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>LPNBLX1C140655</t>
+          <t>LPNBOM5F5407228</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -873,12 +873,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26T05:19:18+00:00</t>
+          <t>2026-07-01T03:55:07+00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>406-4442109-5330751</t>
+          <t>403-6044286-1801115</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3990308</t>
+          <t>LPNCCX2B2262224</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -929,32 +929,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-25T18:24:43+00:00</t>
+          <t>2026-06-29T12:22:41+00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>405-2433007-9289947</t>
+          <t>405-6904525-0069903</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>LPNSBOB1387687</t>
+          <t>LPNHYD8EF20503</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -985,12 +985,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-25T10:05:58+00:00</t>
+          <t>2026-06-28T19:38:03+00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>407-3034951-4675566</t>
+          <t>402-4296829-1337133</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1018,22 +1018,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2273850</t>
+          <t>LPNCCX1B2440445</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1041,32 +1041,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-24T08:29:31+00:00</t>
+          <t>2026-06-28T08:39:43+00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>402-0120877-0312362</t>
+          <t>402-6090489-2032337</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>LPNSPUN59333</t>
+          <t>LPNBLR7Y7855923</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1097,12 +1097,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-24T06:17:22+00:00</t>
+          <t>2026-06-27T11:00:01+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>403-8864299-1768360</t>
+          <t>408-3896665-0021948</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1135,17 +1135,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7854241</t>
+          <t>LPNBLR7Y7855626</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1153,32 +1153,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-23T15:36:47+00:00</t>
+          <t>2026-06-27T10:32:22+00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>402-8717460-5700310</t>
+          <t>407-5462207-4616334</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1196,12 +1196,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>LPNHDX8A005873</t>
+          <t>LPNSBOB1388621</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1209,32 +1209,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-23T11:54:27+00:00</t>
+          <t>2026-06-26T18:08:18+00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>403-7688253-5273167</t>
+          <t>171-5586406-9945900</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1242,22 +1242,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>LPNBOM5F5694482</t>
+          <t>LPNSBOB1388302</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1265,32 +1265,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-23T09:27:19+00:00</t>
+          <t>2026-06-26T06:57:42+00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>408-9857262-4357961</t>
+          <t>405-2746376-7486724</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7853975</t>
+          <t>LPNBLX1C140655</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1321,12 +1321,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-23T08:32:44+00:00</t>
+          <t>2026-06-26T05:19:18+00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>404-2029470-0977929</t>
+          <t>406-4442109-5330751</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1364,12 +1364,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3925027</t>
+          <t>LPNDEL4AA3990308</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1377,12 +1377,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-23T06:25:18+00:00</t>
+          <t>2026-06-25T18:24:43+00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>408-7120729-6837923</t>
+          <t>405-2433007-9289947</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>LPNSBOB1385946</t>
+          <t>LPNSBOB1387687</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1433,32 +1433,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-23T05:29:18+00:00</t>
+          <t>2026-06-25T10:05:58+00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>403-5101653-2865108</t>
+          <t>407-3034951-4675566</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1466,22 +1466,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>LPNHDX8005941</t>
+          <t>LPNMAA4Z2273850</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1489,32 +1489,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-22T15:00:37+00:00</t>
+          <t>2026-06-24T08:29:31+00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>408-2886313-6344340</t>
+          <t>402-0120877-0312362</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1522,12 +1522,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>LPNSBOB1385291</t>
+          <t>LPNSPUN59333</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1545,32 +1545,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-22T15:00:11+00:00</t>
+          <t>2026-06-24T06:17:22+00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>403-4065197-2565940</t>
+          <t>403-8864299-1768360</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1588,12 +1588,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>LPNSBOB1385290</t>
+          <t>LPNBLR7Y7854241</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1601,12 +1601,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-22T13:49:32+00:00</t>
+          <t>2026-06-23T15:36:47+00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>171-3328269-2691534</t>
+          <t>402-8717460-5700310</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1634,22 +1634,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>LPNBLX1C049419</t>
+          <t>LPNHDX8A005873</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1657,32 +1657,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-22T13:44:52+00:00</t>
+          <t>2026-06-23T11:54:27+00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>407-2806960-6949923</t>
+          <t>403-7688253-5273167</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1690,22 +1690,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>LPNBLX1C049418</t>
+          <t>LPNBOM5F5694482</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1713,12 +1713,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-22T12:43:38+00:00</t>
+          <t>2026-06-23T09:27:19+00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>402-2531413-4073130</t>
+          <t>408-9857262-4357961</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>LPNHYD8EF41160</t>
+          <t>LPNBLR7Y7853975</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1769,12 +1769,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-22T09:02:33+00:00</t>
+          <t>2026-06-23T08:32:44+00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>404-4254275-9061104</t>
+          <t>404-2029470-0977929</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>LPNHYD8ED01352</t>
+          <t>LPNDEL4AA3925027</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1825,32 +1825,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-22T06:27:11+00:00</t>
+          <t>2026-06-23T06:25:18+00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>407-5289320-1468336</t>
+          <t>408-7120729-6837923</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1858,22 +1858,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7287766</t>
+          <t>LPNSBOB1385946</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1881,32 +1881,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-21T15:48:42+00:00</t>
+          <t>2026-06-23T05:29:18+00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>408-1433377-1765942</t>
+          <t>403-5101653-2865108</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>LPNSBOB1385218</t>
+          <t>LPNHDX8005941</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1937,32 +1937,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-21T09:50:13+00:00</t>
+          <t>2026-06-22T15:00:37+00:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>405-1204534-8479517</t>
+          <t>408-2886313-6344340</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1970,22 +1970,22 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>LPNDEL4AA4027730</t>
+          <t>LPNSBOB1385291</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -1993,32 +1993,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-21T08:35:03+00:00</t>
+          <t>2026-06-22T15:00:11+00:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>171-0025867-6612374</t>
+          <t>403-4065197-2565940</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2026,22 +2026,22 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7853300</t>
+          <t>LPNSBOB1385290</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2049,32 +2049,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-20T13:05:37+00:00</t>
+          <t>2026-06-22T13:49:32+00:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>402-8590404-8535510</t>
+          <t>171-3328269-2691534</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>LPNMAA4G898204</t>
+          <t>LPNBLX1C049419</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2105,12 +2105,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-19T14:24:04+00:00</t>
+          <t>2026-06-22T13:44:52+00:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>403-3269966-6849104</t>
+          <t>407-2806960-6949923</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2138,22 +2138,22 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>LPNHDX8A004693</t>
+          <t>LPNBLX1C049418</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2161,12 +2161,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-18T09:53:43+00:00</t>
+          <t>2026-06-22T12:43:38+00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>408-1513827-8090763</t>
+          <t>402-2531413-4073130</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2194,22 +2194,22 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2273003</t>
+          <t>LPNHYD8EF41160</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2217,32 +2217,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-18T09:01:23+00:00</t>
+          <t>2026-06-22T09:02:33+00:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>402-6972876-7770702</t>
+          <t>404-4254275-9061104</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FBA76765</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>B0BMQQQ7YD</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>X001O7YYCV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>White Mulberry Motorized Height Adjustable Sit-Stand Desk | Electronic Height Adjustable | Motor &amp; Memory Preset Controller | Office, Workstation or Home | Carbon Fibre | 120 * 60*H(75-118) cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2250,22 +2250,22 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>LPNSPUN58279</t>
+          <t>LPNHYD8ED01352</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2273,32 +2273,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-18T06:34:47+00:00</t>
+          <t>2026-06-22T06:27:11+00:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>171-5595331-6677926</t>
+          <t>407-5289320-1468336</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>LPNSPUN58332</t>
+          <t>LPNBLR7Y7287766</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2329,12 +2329,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-18T06:13:54+00:00</t>
+          <t>2026-06-21T15:48:42+00:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>405-9716650-4190754</t>
+          <t>408-1433377-1765942</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>LPNSPUN58348</t>
+          <t>LPNSBOB1385218</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2385,12 +2385,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-18T05:06:11+00:00</t>
+          <t>2026-06-21T09:50:13+00:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>405-0242402-8315559</t>
+          <t>405-1204534-8479517</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>LPNHYD8DY89222</t>
+          <t>LPNDEL4AA4027730</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2441,12 +2441,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-18T03:18:32+00:00</t>
+          <t>2026-06-21T08:35:03+00:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>403-8790017-7829152</t>
+          <t>171-0025867-6612374</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>LPNHYD8DY89148</t>
+          <t>LPNBLR7Y7853300</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2497,12 +2497,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-17T17:18:11+00:00</t>
+          <t>2026-06-20T13:05:37+00:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>408-3294486-3424329</t>
+          <t>402-8590404-8535510</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>LPNCCX1B4206954</t>
+          <t>LPNMAA4G898204</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -2553,12 +2553,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-17T11:01:26+00:00</t>
+          <t>2026-06-19T14:24:04+00:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>171-3399563-8885966</t>
+          <t>403-3269966-6849104</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2586,22 +2586,22 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>LPNLMAA0019039</t>
+          <t>LPNHDX8A004693</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -2609,12 +2609,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15T09:24:30+00:00</t>
+          <t>2026-06-18T09:53:43+00:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>171-3194001-5187538</t>
+          <t>408-1513827-8090763</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2642,22 +2642,22 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>LPNHYD8DY92591</t>
+          <t>LPNMAA4Z2273003</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2665,32 +2665,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-15T08:53:22+00:00</t>
+          <t>2026-06-18T09:01:23+00:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>406-3765893-9779536</t>
+          <t>402-6972876-7770702</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA76765</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0BMQQQ7YD</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001O7YYCV</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
+          <t>White Mulberry Motorized Height Adjustable Sit-Stand Desk | Electronic Height Adjustable | Motor &amp; Memory Preset Controller | Office, Workstation or Home | Carbon Fibre | 120 * 60*H(75-118) cm</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>LPNHDX8A0002233</t>
+          <t>LPNSPUN58279</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -2721,32 +2721,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-14T11:15:53+00:00</t>
+          <t>2026-06-18T06:34:47+00:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>171-1282309-9677932</t>
+          <t>171-5595331-6677926</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2754,22 +2754,22 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2198432</t>
+          <t>LPNSPUN58332</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -2777,32 +2777,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-14T06:26:57+00:00</t>
+          <t>2026-06-18T06:13:54+00:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>407-1845667-2313146</t>
+          <t>405-9716650-4190754</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2810,22 +2810,22 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3677498</t>
+          <t>LPNSPUN58348</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2833,32 +2833,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-13T12:21:24+00:00</t>
+          <t>2026-06-18T05:06:11+00:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>405-5466299-6857906</t>
+          <t>405-0242402-8315559</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>LPNSBOB1375958</t>
+          <t>LPNHYD8DY89222</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -2889,32 +2889,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-13T12:20:57+00:00</t>
+          <t>2026-06-18T03:18:32+00:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>404-9976514-7382743</t>
+          <t>403-8790017-7829152</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2922,22 +2922,22 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>LPNSBOB1375957</t>
+          <t>LPNHYD8DY89148</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -2945,32 +2945,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-12T11:47:28+00:00</t>
+          <t>2026-06-17T17:18:11+00:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>407-2845785-4936332</t>
+          <t>408-3294486-3424329</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2978,22 +2978,22 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>DAMAGED</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>LPNSHTI00009280</t>
+          <t>LPNCCX1B4206954</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3001,32 +3001,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-11T12:39:34+00:00</t>
+          <t>2026-06-17T11:01:26+00:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>405-0836953-9114742</t>
+          <t>171-3399563-8885966</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3034,22 +3034,22 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>LPNHDX8A001607</t>
+          <t>LPNLMAA0019039</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3057,32 +3057,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-11T10:43:03+00:00</t>
+          <t>2026-06-15T09:24:30+00:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>407-7053626-1929962</t>
+          <t>171-3194001-5187538</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FBA79667</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>B0DQPK7MFH</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>X0027512Z1</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk with Shelf|DIY Assembly| Monitor Raising Shelf |Engineered Wood &amp; Sturdy Steel Leg|Perfect for Computer Table Office Home Gaming Study Desk|L(130+130)*45*77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3090,22 +3090,22 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SCUY</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>LPNSCUY00017897</t>
+          <t>LPNHYD8DY92591</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -3113,32 +3113,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-10T22:26:08+00:00</t>
+          <t>2026-06-15T08:53:22+00:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>404-0639682-6860336</t>
+          <t>406-3765893-9779536</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3146,22 +3146,22 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>LPNCX1B4784440</t>
+          <t>LPNHDX8A0002233</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -3169,12 +3169,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-10T12:14:02+00:00</t>
+          <t>2026-06-14T11:15:53+00:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>171-1027170-0049924</t>
+          <t>171-1282309-9677932</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2407733</t>
+          <t>LPNMAA4Z2198432</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3225,32 +3225,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-10T08:20:03+00:00</t>
+          <t>2026-06-14T06:26:57+00:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>406-6295410-5869130</t>
+          <t>407-1845667-2313146</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -3258,22 +3258,22 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>LPNBLX1C159057</t>
+          <t>LPNDEL4AA3677498</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3281,32 +3281,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-10T05:42:02+00:00</t>
+          <t>2026-06-13T12:21:24+00:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>405-8329990-8940345</t>
+          <t>405-5466299-6857906</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4745942</t>
+          <t>LPNSBOB1375958</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -3337,32 +3337,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-10T04:51:41+00:00</t>
+          <t>2026-06-13T12:20:57+00:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>405-7954322-6131539</t>
+          <t>404-9976514-7382743</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3370,22 +3370,22 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>LPNBOM5F5675078</t>
+          <t>LPNSBOB1375957</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -3393,32 +3393,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-10T03:51:05+00:00</t>
+          <t>2026-06-12T11:47:28+00:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>407-5527946-4998741</t>
+          <t>407-2845785-4936332</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7287766</t>
+          <t>LPNSHTI00009280</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -3449,32 +3449,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-08T09:59:30+00:00</t>
+          <t>2026-06-11T12:39:34+00:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>404-4052225-7064331</t>
+          <t>405-0836953-9114742</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3631375</t>
+          <t>LPNHDX8A001607</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -3505,32 +3505,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-08T08:59:50+00:00</t>
+          <t>2026-06-11T10:43:03+00:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>404-3123106-0929939</t>
+          <t>407-7053626-1929962</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FBK76387</t>
+          <t>FBA79667</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>B0BF4S7V8C</t>
+          <t>B0DQPK7MFH</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>X00242V9DH</t>
+          <t>X0027512Z1</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | White</t>
+          <t>White Mulberry L-Shape Corner Desk with Shelf|DIY Assembly| Monitor Raising Shelf |Engineered Wood &amp; Sturdy Steel Leg|Perfect for Computer Table Office Home Gaming Study Desk|L(130+130)*45*77cm|White</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>SCUY</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>LPNSPUN56234</t>
+          <t>LPNSCUY00017897</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -3561,32 +3561,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-08T08:59:02+00:00</t>
+          <t>2026-06-10T22:26:08+00:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>408-8800113-8391502</t>
+          <t>404-0639682-6860336</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>LPNSPUN56235</t>
+          <t>LPNCX1B4784440</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3617,12 +3617,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-08T08:43:30+00:00</t>
+          <t>2026-06-10T12:14:02+00:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>407-4254200-0562712</t>
+          <t>171-1027170-0049924</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3631346</t>
+          <t>LPNMAA4Z2407733</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -3673,32 +3673,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-06-07T16:09:41+00:00</t>
+          <t>2026-06-10T08:20:03+00:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>405-9852474-3831538</t>
+          <t>406-6295410-5869130</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -3706,22 +3706,22 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>LPNCCX1B4179343</t>
+          <t>LPNBLX1C159057</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -3729,32 +3729,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-06-07T11:20:49+00:00</t>
+          <t>2026-06-10T05:42:02+00:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>406-9783608-9093148</t>
+          <t>405-8329990-8940345</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3762,22 +3762,22 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>LPNLMAA0016237</t>
+          <t>LPNBLR7Y4745942</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -3785,32 +3785,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-06-07T10:24:17+00:00</t>
+          <t>2026-06-10T04:51:41+00:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>406-6392223-8173930</t>
+          <t>405-7954322-6131539</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -3818,22 +3818,22 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>LPNBLX1C047099</t>
+          <t>LPNBOM5F5675078</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -3841,12 +3841,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-06-06T10:45:59+00:00</t>
+          <t>2026-06-10T03:51:05+00:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>406-9111649-3125130</t>
+          <t>407-5527946-4998741</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>LPNBOM5F5579985</t>
+          <t>LPNBLR7Y7287766</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -3897,12 +3897,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-06-05T09:54:50+00:00</t>
+          <t>2026-06-08T09:59:30+00:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>405-7328472-7893901</t>
+          <t>404-4052225-7064331</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679697</t>
+          <t>LPNDEL4AA3631375</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -3953,32 +3953,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-06-05T08:35:28+00:00</t>
+          <t>2026-06-08T08:59:50+00:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>404-9218549-9930734</t>
+          <t>404-3123106-0929939</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FBA79659</t>
+          <t>FBK76387</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0BF4S7V8C</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>X0026ZDA2F</t>
+          <t>X00242V9DH</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, Black, 3 Year Warranty</t>
+          <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | White</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -3986,22 +3986,22 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>LPNSDEGF082043</t>
+          <t>LPNSPUN56234</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4009,32 +4009,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-06-05T08:17:03+00:00</t>
+          <t>2026-06-08T08:59:02+00:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>171-6540897-0152357</t>
+          <t>408-8800113-8391502</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679650</t>
+          <t>LPNSPUN56235</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -4065,12 +4065,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-06-05T04:33:06+00:00</t>
+          <t>2026-06-08T08:43:30+00:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>171-6354444-3723505</t>
+          <t>407-4254200-0562712</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4098,22 +4098,22 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>LPNBOM5F5574228</t>
+          <t>LPNDEL4AA3631346</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -4121,12 +4121,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-06-05T04:28:18+00:00</t>
+          <t>2026-06-07T16:09:41+00:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>406-6103690-9310748</t>
+          <t>405-9852474-3831538</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4154,12 +4154,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679535</t>
+          <t>LPNCCX1B4179343</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -4177,32 +4177,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-06-04T03:47:36+00:00</t>
+          <t>2026-06-07T11:20:49+00:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>406-2278126-7841949</t>
+          <t>406-9783608-9093148</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -4210,22 +4210,22 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679185</t>
+          <t>LPNLMAA0016237</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -4233,32 +4233,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-06-01T09:32:55+00:00</t>
+          <t>2026-06-07T10:24:17+00:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>402-3794541-2581168</t>
+          <t>406-6392223-8173930</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -4266,22 +4266,22 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4743333</t>
+          <t>LPNBLX1C047099</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -4289,12 +4289,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-06-01T04:42:36+00:00</t>
+          <t>2026-06-06T10:45:59+00:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>408-0143238-4374708</t>
+          <t>406-9111649-3125130</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>LPNBOM5F5524445</t>
+          <t>LPNBOM5F5579985</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -4345,12 +4345,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-06-01T03:58:27+00:00</t>
+          <t>2026-06-05T09:54:50+00:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>406-4355667-6072332</t>
+          <t>405-7328472-7893901</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4743158</t>
+          <t>LPNDEL4AA3679697</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -4401,32 +4401,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-31T09:10:34+00:00</t>
+          <t>2026-06-05T08:35:28+00:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>404-2518539-4406712</t>
+          <t>404-9218549-9930734</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79659</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZDA2F</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, Black, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -4434,22 +4434,22 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3976607</t>
+          <t>LPNSDEGF082043</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -4457,12 +4457,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-30T22:18:28+00:00</t>
+          <t>2026-06-05T08:17:03+00:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>407-1474707-0478726</t>
+          <t>171-6540897-0152357</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>LPNCCX1B4554643</t>
+          <t>LPNDEL4AA3679650</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -4513,12 +4513,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-30T04:13:42+00:00</t>
+          <t>2026-06-05T04:33:06+00:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>406-7941139-9225906</t>
+          <t>171-6354444-3723505</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4551,17 +4551,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>LPNBOM5F5507643</t>
+          <t>LPNBOM5F5574228</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -4569,12 +4569,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-29T23:01:15+00:00</t>
+          <t>2026-06-05T04:28:18+00:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>405-0096078-8521126</t>
+          <t>406-6103690-9310748</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4612,12 +4612,12 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>LPNCCX1B2941120</t>
+          <t>LPNDEL4AA3679535</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -4625,12 +4625,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-29T15:27:20+00:00</t>
+          <t>2026-06-04T03:47:36+00:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>404-8418070-5981124</t>
+          <t>406-2278126-7841949</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>LPNCCX1B4508596</t>
+          <t>LPNDEL4AA3679185</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -4681,12 +4681,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-29T05:18:33+00:00</t>
+          <t>2026-06-01T09:32:55+00:00</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>171-0407209-4266756</t>
+          <t>402-3794541-2581168</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4714,22 +4714,22 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937926</t>
+          <t>LPNBLR7Y4743333</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -4737,12 +4737,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-28T11:56:49+00:00</t>
+          <t>2026-06-01T04:42:36+00:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>407-4902279-0189155</t>
+          <t>408-0143238-4374708</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7363000</t>
+          <t>LPNBOM5F5524445</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -4793,12 +4793,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-28T08:40:02+00:00</t>
+          <t>2026-06-01T03:58:27+00:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>408-1128142-0248321</t>
+          <t>406-4355667-6072332</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4836,12 +4836,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>DAMAGED_BY_FC</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937756</t>
+          <t>LPNBLR7Y4743158</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -4849,12 +4849,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-28T06:36:17+00:00</t>
+          <t>2026-05-31T09:10:34+00:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>402-4776409-4471512</t>
+          <t>404-2518539-4406712</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4882,12 +4882,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7286354</t>
+          <t>LPNDEL4AA3976607</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -4905,12 +4905,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-27T12:42:16+00:00</t>
+          <t>2026-05-30T22:18:28+00:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>404-6762038-7137955</t>
+          <t>407-1474707-0478726</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4948,12 +4948,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937575</t>
+          <t>LPNCCX1B4554643</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -4961,12 +4961,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-27T09:44:17+00:00</t>
+          <t>2026-05-30T04:13:42+00:00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>403-3444915-0085109</t>
+          <t>406-7941139-9225906</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7362686</t>
+          <t>LPNBOM5F5507643</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -5017,32 +5017,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-27T09:25:47+00:00</t>
+          <t>2026-05-29T23:01:15+00:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>405-8410325-7933918</t>
+          <t>405-0096078-8521126</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -5050,22 +5050,22 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>LPNSPUN53913</t>
+          <t>LPNCCX1B2941120</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -5073,12 +5073,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-26T23:02:43+00:00</t>
+          <t>2026-05-29T15:27:20+00:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>407-0645348-4574732</t>
+          <t>404-8418070-5981124</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5111,17 +5111,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>LPNCCX1B5292913</t>
+          <t>LPNCCX1B4508596</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -5129,12 +5129,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-26T11:06:29+00:00</t>
+          <t>2026-05-29T05:18:33+00:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>402-2949127-9513917</t>
+          <t>171-0407209-4266756</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5167,17 +5167,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937227</t>
+          <t>LPNDEL4AA3937926</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -5185,12 +5185,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-26T08:48:10+00:00</t>
+          <t>2026-05-28T11:56:49+00:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>403-5510263-6469912</t>
+          <t>407-4902279-0189155</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5228,12 +5228,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273675</t>
+          <t>LPNBLR7Y7363000</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -5241,12 +5241,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-25T15:22:25+00:00</t>
+          <t>2026-05-28T08:40:02+00:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>402-5203149-1906724</t>
+          <t>408-1128142-0248321</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>DAMAGED_BY_FC</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>LPNCCX1B5331017</t>
+          <t>LPNDEL4AA3937756</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -5297,12 +5297,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-24T09:24:39+00:00</t>
+          <t>2026-05-28T06:36:17+00:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>171-7709339-0701117</t>
+          <t>402-4776409-4471512</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273169</t>
+          <t>LPNBLR7Y7286354</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -5353,12 +5353,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-24T08:29:52+00:00</t>
+          <t>2026-05-27T12:42:16+00:00</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>406-7042486-7436314</t>
+          <t>404-6762038-7137955</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273150</t>
+          <t>LPNDEL4AA3937575</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -5409,32 +5409,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-23T23:07:27+00:00</t>
+          <t>2026-05-27T09:44:17+00:00</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>406-2954542-5857925</t>
+          <t>403-3444915-0085109</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -5442,22 +5442,22 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>LPNSBOB1370158</t>
+          <t>LPNBLR7Y7362686</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -5465,32 +5465,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-23T10:58:04+00:00</t>
+          <t>2026-05-27T09:25:47+00:00</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>406-4758725-2077907</t>
+          <t>405-8410325-7933918</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -5498,22 +5498,22 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7272896</t>
+          <t>LPNSPUN53913</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -5521,32 +5521,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-22T09:58:26+00:00</t>
+          <t>2026-05-26T23:02:43+00:00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>403-7800011-6937966</t>
+          <t>407-0645348-4574732</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -5554,22 +5554,22 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>LPNSDEGF010003</t>
+          <t>LPNCCX1B5292913</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -5577,32 +5577,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-21T04:38:32+00:00</t>
+          <t>2026-05-26T11:06:29+00:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>403-2400247-1930753</t>
+          <t>402-2949127-9513917</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>LPNSDEGF099136</t>
+          <t>LPNDEL4AA3937227</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -5633,12 +5633,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-20T11:30:45+00:00</t>
+          <t>2026-05-26T08:48:10+00:00</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>406-2648444-6601917</t>
+          <t>403-5510263-6469912</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2147464</t>
+          <t>LPNBLR7Y7273675</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -5689,32 +5689,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-19T08:03:32+00:00</t>
+          <t>2026-05-25T15:22:25+00:00</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>405-4744559-6958733</t>
+          <t>402-5203149-1906724</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>LPNSDEGF097985</t>
+          <t>LPNCCX1B5331017</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -5745,32 +5745,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-18T11:36:05+00:00</t>
+          <t>2026-05-24T09:24:39+00:00</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>171-1585723-0908356</t>
+          <t>171-7709339-0701117</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -5778,22 +5778,22 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>LPNBLX1C155145</t>
+          <t>LPNBLR7Y7273169</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -5801,32 +5801,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-15T08:29:30+00:00</t>
+          <t>2026-05-24T08:29:52+00:00</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>402-4856546-1261939</t>
+          <t>406-7042486-7436314</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5844,12 +5844,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>LPNSDEGF074601</t>
+          <t>LPNBLR7Y7273150</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -5857,32 +5857,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-13T13:50:43+00:00</t>
+          <t>2026-05-23T23:07:27+00:00</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>403-7495250-9937954</t>
+          <t>406-2954542-5857925</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -5890,22 +5890,22 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>LPNBLX1C154096</t>
+          <t>LPNSBOB1370158</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -5913,32 +5913,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-12T07:19:54+00:00</t>
+          <t>2026-05-23T10:58:04+00:00</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>408-0473775-6641108</t>
+          <t>406-4758725-2077907</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -5946,22 +5946,22 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>LPNSBOB1362246</t>
+          <t>LPNBLR7Y7272896</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -5969,32 +5969,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-11T10:31:39+00:00</t>
+          <t>2026-05-22T09:58:26+00:00</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>404-1750959-8518722</t>
+          <t>403-7800011-6937966</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -6002,22 +6002,22 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>LPNSHTI00006165</t>
+          <t>LPNSDEGF010003</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -6025,32 +6025,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-10T09:15:43+00:00</t>
+          <t>2026-05-21T04:38:32+00:00</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>402-1548587-3227555</t>
+          <t>403-2400247-1930753</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -6058,22 +6058,22 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>LPNBOM5F5057136</t>
+          <t>LPNSDEGF099136</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -6081,32 +6081,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-08T15:43:17+00:00</t>
+          <t>2026-05-20T11:30:45+00:00</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>402-8374307-7441113</t>
+          <t>406-2648444-6601917</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -6114,22 +6114,22 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>LPNSDEGF064205</t>
+          <t>LPNDEL4AA2147464</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -6137,32 +6137,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-08T13:25:23+00:00</t>
+          <t>2026-05-19T08:03:32+00:00</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>171-7381542-8368365</t>
+          <t>405-4744559-6958733</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -6170,22 +6170,22 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>LPNBLX1C042486</t>
+          <t>LPNSDEGF097985</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -6193,32 +6193,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-08T07:49:38+00:00</t>
+          <t>2026-05-18T11:36:05+00:00</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>403-3056736-6311553</t>
+          <t>171-1585723-0908356</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5321963</t>
+          <t>LPNBLX1C155145</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -6249,32 +6249,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-06T06:52:28+00:00</t>
+          <t>2026-05-15T08:29:30+00:00</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>403-2654029-0716338</t>
+          <t>402-4856546-1261939</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>LPNSHTI00005958</t>
+          <t>LPNSDEGF074601</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -6305,32 +6305,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-06T05:51:00+00:00</t>
+          <t>2026-05-13T13:50:43+00:00</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>404-9426288-6037168</t>
+          <t>403-7495250-9937954</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -6338,22 +6338,22 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>LPNBOM5F5236158</t>
+          <t>LPNBLX1C154096</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -6361,32 +6361,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-02T04:54:42+00:00</t>
+          <t>2026-05-12T07:19:54+00:00</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>407-6201969-2856316</t>
+          <t>408-0473775-6641108</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -6394,22 +6394,22 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>LPNLMAA0004457</t>
+          <t>LPNSBOB1362246</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -6417,32 +6417,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-04-28T08:52:43+00:00</t>
+          <t>2026-05-11T10:31:39+00:00</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>171-6713241-8377149</t>
+          <t>404-1750959-8518722</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>LPNLMAA0003844</t>
+          <t>LPNSHTI00006165</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -6473,32 +6473,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-27T06:04:11+00:00</t>
+          <t>2026-05-10T09:15:43+00:00</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>403-6021111-3520325</t>
+          <t>402-1548587-3227555</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -6506,22 +6506,22 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>LPNLMAA0003335</t>
+          <t>LPNBOM5F5057136</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -6529,32 +6529,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-26T08:09:27+00:00</t>
+          <t>2026-05-08T15:43:17+00:00</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>402-4881396-1030704</t>
+          <t>402-8374307-7441113</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -6562,22 +6562,22 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2253845</t>
+          <t>LPNSDEGF064205</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -6585,32 +6585,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-26T04:14:08+00:00</t>
+          <t>2026-05-08T13:25:23+00:00</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>408-1134010-7973925</t>
+          <t>171-7381542-8368365</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -6618,22 +6618,22 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5321963</t>
+          <t>LPNBLX1C042486</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -6641,32 +6641,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-26T03:22:50+00:00</t>
+          <t>2026-05-08T07:49:38+00:00</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>406-9614580-4613163</t>
+          <t>403-3056736-6311553</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>LPNSPUN46511</t>
+          <t>LPNBLR7Y5321963</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -6697,32 +6697,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-25T05:33:44+00:00</t>
+          <t>2026-05-06T06:52:28+00:00</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>171-3077342-1790757</t>
+          <t>403-2654029-0716338</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -6730,22 +6730,22 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>LPNLMAA0002840</t>
+          <t>LPNSHTI00005958</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
@@ -6753,32 +6753,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-25T03:48:59+00:00</t>
+          <t>2026-05-06T05:51:00+00:00</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>404-4908572-3783532</t>
+          <t>404-9426288-6037168</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>X002FOAUSJ</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -6786,22 +6786,22 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>LPNBLR7Y6090385</t>
+          <t>LPNBOM5F5236158</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -6809,32 +6809,32 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-22T10:55:13+00:00</t>
+          <t>2026-05-02T04:54:42+00:00</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>407-4868470-8499505</t>
+          <t>407-6201969-2856316</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -6847,17 +6847,17 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>LPNLMAA0001354</t>
+          <t>LPNLMAA0004457</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
@@ -6865,32 +6865,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-22T04:17:57+00:00</t>
+          <t>2026-04-28T08:52:43+00:00</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>406-5030280-5555520</t>
+          <t>171-6713241-8377149</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -6898,22 +6898,22 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>LPNSDEGF117193</t>
+          <t>LPNLMAA0003844</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -6921,32 +6921,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-21T20:42:51+00:00</t>
+          <t>2026-04-27T06:04:11+00:00</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>403-7744956-9735520</t>
+          <t>403-6021111-3520325</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>LPNCCX1B1519621</t>
+          <t>LPNLMAA0003335</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -6977,32 +6977,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-20T05:04:40+00:00</t>
+          <t>2026-04-26T08:09:27+00:00</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>171-5598784-9947515</t>
+          <t>402-4881396-1030704</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>X002FOAUSJ</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -7010,22 +7010,22 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5552415</t>
+          <t>LPNDEL4AA2253845</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -7033,12 +7033,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-18T05:41:14+00:00</t>
+          <t>2026-04-26T04:14:08+00:00</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>404-0309463-1310709</t>
+          <t>408-1134010-7973925</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7076,12 +7076,12 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>LPNDEL4AA0788989</t>
+          <t>LPNBLR7Y5321963</t>
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
@@ -7089,12 +7089,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-15T13:55:57+00:00</t>
+          <t>2026-04-26T03:22:50+00:00</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>407-7885481-2445152</t>
+          <t>406-9614580-4613163</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>SMAB</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7132,12 +7132,12 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>LPNSMAB1153810</t>
+          <t>LPNSPUN46511</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -7145,32 +7145,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-15T08:47:44+00:00</t>
+          <t>2026-04-25T05:33:44+00:00</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>407-3585151-4323522</t>
+          <t>171-3077342-1790757</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -7178,22 +7178,22 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>LPNSDEGF027993</t>
+          <t>LPNLMAA0002840</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -7201,32 +7201,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-12T10:47:54+00:00</t>
+          <t>2026-04-25T03:48:59+00:00</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>407-0802588-3857957</t>
+          <t>404-4908572-3783532</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X002FOAUSJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -7234,22 +7234,22 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>LPNSDEGF026167</t>
+          <t>LPNBLR7Y6090385</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -7257,32 +7257,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-11T06:17:07+00:00</t>
+          <t>2026-04-22T10:55:13+00:00</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>408-2417441-1123516</t>
+          <t>407-4868470-8499505</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FBK76764</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>B0BMV1WPHL</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>X00242TZTH</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>White Mulberry Ergonomic Sit Stand Desk | Standing Desk for Office, Home &amp; Study | Everyday Ergonomic Desk | 1200mm x 600mm | Carbon Fibre</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -7290,22 +7290,22 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>LPNSHTI00004704</t>
+          <t>LPNLMAA0001354</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
@@ -7313,32 +7313,32 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-09T03:38:39+00:00</t>
+          <t>2026-04-22T04:17:57+00:00</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>406-0798045-4525148</t>
+          <t>406-5030280-5555520</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -7351,17 +7351,17 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>LPNSDEGF168570</t>
+          <t>LPNSDEGF117193</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -7369,12 +7369,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-08T10:17:09+00:00</t>
+          <t>2026-04-21T20:42:51+00:00</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>406-3115014-9939528</t>
+          <t>403-7744956-9735520</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7402,22 +7402,22 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2155169</t>
+          <t>LPNCCX1B1519621</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -7425,32 +7425,32 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-08T09:53:57+00:00</t>
+          <t>2026-04-20T05:04:40+00:00</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>403-7697438-5361950</t>
+          <t>171-5598784-9947515</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X002FOAUSJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -7458,22 +7458,22 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>LPNMAA4Z0044638</t>
+          <t>LPNBLR7Y5552415</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -7481,12 +7481,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-07T23:27:35+00:00</t>
+          <t>2026-04-18T05:41:14+00:00</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>402-3182844-0423531</t>
+          <t>404-0309463-1310709</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>NO_REASON_GIVEN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>LPNCCX1B1676425</t>
+          <t>LPNDEL4AA0788989</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -7537,32 +7537,32 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-07T08:05:07+00:00</t>
+          <t>2026-04-15T13:55:57+00:00</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>404-2599173-5513112</t>
+          <t>407-7885481-2445152</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -7570,22 +7570,22 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SMAB</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>LPNBLX1C066978</t>
+          <t>LPNSMAB1153810</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -7593,32 +7593,32 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-06T21:28:06+00:00</t>
+          <t>2026-04-15T08:47:44+00:00</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>408-0894434-7394724</t>
+          <t>407-3585151-4323522</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>LPNCCX1B1676919</t>
+          <t>LPNSDEGF027993</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -7649,32 +7649,32 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-06T19:49:19+00:00</t>
+          <t>2026-04-12T10:47:54+00:00</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>402-0299451-2765120</t>
+          <t>407-0802588-3857957</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7692,12 +7692,12 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>LPNCCX1B2787065</t>
+          <t>LPNSDEGF026167</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -7705,32 +7705,32 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-04-06T09:26:15+00:00</t>
+          <t>2026-04-11T06:17:07+00:00</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>402-1769603-3523555</t>
+          <t>408-2417441-1123516</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBK76764</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BMV1WPHL</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00242TZTH</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Ergonomic Sit Stand Desk | Standing Desk for Office, Home &amp; Study | Everyday Ergonomic Desk | 1200mm x 600mm | Carbon Fibre</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -7738,22 +7738,22 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>LPNMAA4Z0044156</t>
+          <t>LPNSHTI00004704</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -7761,12 +7761,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-04-06T08:31:32+00:00</t>
+          <t>2026-04-09T03:38:39+00:00</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>408-6381953-4631553</t>
+          <t>406-0798045-4525148</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7794,22 +7794,22 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>LPNSPUN45721</t>
+          <t>LPNSDEGF168570</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -7817,12 +7817,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-04-05T06:19:10+00:00</t>
+          <t>2026-04-08T10:17:09+00:00</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>408-5061007-8220304</t>
+          <t>406-3115014-9939528</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>LPNBLR7Y6062118</t>
+          <t>LPNDEL4AA2155169</t>
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
@@ -7873,12 +7873,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-04-04T08:29:33+00:00</t>
+          <t>2026-04-08T09:53:57+00:00</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>404-3586878-1942709</t>
+          <t>403-7697438-5361950</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7906,12 +7906,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2909513</t>
+          <t>LPNMAA4Z0044638</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
@@ -7929,12 +7929,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-04-04T05:05:55+00:00</t>
+          <t>2026-04-07T23:27:35+00:00</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>406-7410699-4348354</t>
+          <t>402-3182844-0423531</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>NO_REASON_GIVEN</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>LPNBOM5F4750684</t>
+          <t>LPNCCX1B1676425</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -7985,32 +7985,32 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-04-03T06:19:12+00:00</t>
+          <t>2026-04-07T08:05:07+00:00</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>402-5121290-6150762</t>
+          <t>404-2599173-5513112</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -8018,22 +8018,22 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>LPNBLR7Y6061498</t>
+          <t>LPNBLX1C066978</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -8041,12 +8041,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-04-02T22:22:31+00:00</t>
+          <t>2026-04-06T21:28:06+00:00</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>408-3588035-4966746</t>
+          <t>408-0894434-7394724</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>LPNCCX1B1791593</t>
+          <t>LPNCCX1B1676919</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
@@ -8097,32 +8097,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-04-02T09:06:26+00:00</t>
+          <t>2026-04-06T19:49:19+00:00</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>407-9710322-7452309</t>
+          <t>402-0299451-2765120</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -8130,22 +8130,22 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>SMAB</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>LPNSMAB1152091</t>
+          <t>LPNCCX1B2787065</t>
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
@@ -8153,12 +8153,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-04-01T07:39:28+00:00</t>
+          <t>2026-04-06T09:26:15+00:00</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>406-6943963-1269164</t>
+          <t>402-1769603-3523555</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8191,17 +8191,17 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>LPNMAA4Z0042841</t>
+          <t>LPNMAA4Z0044156</t>
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
@@ -8209,58 +8209,114 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-04-01T04:41:19+00:00</t>
+          <t>2026-04-06T08:31:32+00:00</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>407-5389538-7877131</t>
+          <t>408-6381953-4631553</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
+          <t>FBA79662</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>B0DQ4YWSMC</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>X00270AW07</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>SPUN</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>CUSTOMER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>SWITCHEROO</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>LPNSPUN45721</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-04-05T06:19:10+00:00</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>408-5061007-8220304</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
           <t>FBA79167</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>B0CPFS24ML</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t>X001Y5UYX1</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
-      <c r="G140" t="n">
-        <v>1</v>
-      </c>
-      <c r="H140" t="inlineStr">
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="inlineStr">
         <is>
           <t>BLR7</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>CARRIER_DAMAGED</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>UNDELIVERABLE_REFUSED</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>LPNBLR7Y6066340</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>SELLABLE</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>NOT_COMPATIBLE</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>LPNBLR7Y6062118</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/raw/returns/WhiteMulberry.xlsx
+++ b/data/raw/returns/WhiteMulberry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L141"/>
+  <dimension ref="A1:L142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02T17:30:33+00:00</t>
+          <t>2026-07-03T11:38:57+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>402-1004506-0818747</t>
+          <t>403-6645337-2467540</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -514,12 +514,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>LPNBLR8Z5514346</t>
+          <t>LPNDEL4AA2082724</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -537,12 +537,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02T06:41:10+00:00</t>
+          <t>2026-07-02T17:30:33+00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>403-6072724-5581966</t>
+          <t>402-1004506-0818747</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -580,12 +580,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4303742</t>
+          <t>LPNBLR8Z5514346</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -593,12 +593,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01T22:20:26+00:00</t>
+          <t>2026-07-02T06:41:10+00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>402-4598141-9561917</t>
+          <t>403-6072724-5581966</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LPNCCX1B4170658</t>
+          <t>LPNBLR8Z4303742</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -649,32 +649,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01T15:09:10+00:00</t>
+          <t>2026-07-01T22:20:26+00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>402-3081497-7409144</t>
+          <t>402-4598141-9561917</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -682,22 +682,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LPNBLX1C093497</t>
+          <t>LPNCCX1B4170658</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -705,32 +705,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01T09:24:20+00:00</t>
+          <t>2026-07-01T15:09:10+00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>405-3824107-9644368</t>
+          <t>402-3081497-7409144</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -738,22 +738,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LPNBOM5F5465051</t>
+          <t>LPNBLX1C093497</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -761,12 +761,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01T06:49:32+00:00</t>
+          <t>2026-07-01T09:24:20+00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>404-6104605-6788338</t>
+          <t>405-3824107-9644368</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LPNBOM5F5435891</t>
+          <t>LPNBOM5F5465051</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -817,12 +817,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01T05:46:54+00:00</t>
+          <t>2026-07-01T06:49:32+00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>407-2497737-1874765</t>
+          <t>404-6104605-6788338</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>LPNBOM5F5407228</t>
+          <t>LPNBOM5F5435891</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -873,12 +873,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01T03:55:07+00:00</t>
+          <t>2026-07-01T05:46:54+00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>403-6044286-1801115</t>
+          <t>407-2497737-1874765</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CCX2</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>LPNCCX2B2262224</t>
+          <t>LPNBOM5F5407228</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -929,12 +929,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29T12:22:41+00:00</t>
+          <t>2026-07-01T03:55:07+00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>405-6904525-0069903</t>
+          <t>403-6044286-1801115</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -962,22 +962,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>CCX2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>LPNHYD8EF20503</t>
+          <t>LPNCCX2B2262224</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -985,12 +985,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-28T19:38:03+00:00</t>
+          <t>2026-06-29T12:22:41+00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>402-4296829-1337133</t>
+          <t>405-6904525-0069903</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1018,22 +1018,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>LPNCCX1B2440445</t>
+          <t>LPNHYD8EF20503</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1041,12 +1041,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-28T08:39:43+00:00</t>
+          <t>2026-06-28T19:38:03+00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>402-6090489-2032337</t>
+          <t>402-4296829-1337133</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7855923</t>
+          <t>LPNCCX1B2440445</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1097,12 +1097,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-27T11:00:01+00:00</t>
+          <t>2026-06-28T08:39:43+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>408-3896665-0021948</t>
+          <t>402-6090489-2032337</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1135,17 +1135,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7855626</t>
+          <t>LPNBLR7Y7855923</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1153,32 +1153,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-27T10:32:22+00:00</t>
+          <t>2026-06-27T11:00:01+00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>407-5462207-4616334</t>
+          <t>408-3896665-0021948</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>LPNSBOB1388621</t>
+          <t>LPNBLR7Y7855626</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1209,32 +1209,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-26T18:08:18+00:00</t>
+          <t>2026-06-27T10:32:22+00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>171-5586406-9945900</t>
+          <t>407-5462207-4616334</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>LPNSBOB1388302</t>
+          <t>LPNSBOB1388621</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1265,12 +1265,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-26T06:57:42+00:00</t>
+          <t>2026-06-26T18:08:18+00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>405-2746376-7486724</t>
+          <t>171-5586406-9945900</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LPNBLX1C140655</t>
+          <t>LPNSBOB1388302</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1321,32 +1321,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26T05:19:18+00:00</t>
+          <t>2026-06-26T06:57:42+00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>406-4442109-5330751</t>
+          <t>405-2746376-7486724</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3990308</t>
+          <t>LPNBLX1C140655</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1377,32 +1377,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-25T18:24:43+00:00</t>
+          <t>2026-06-26T05:19:18+00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>405-2433007-9289947</t>
+          <t>406-4442109-5330751</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1410,22 +1410,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>LPNSBOB1387687</t>
+          <t>LPNDEL4AA3990308</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1433,32 +1433,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-25T10:05:58+00:00</t>
+          <t>2026-06-25T18:24:43+00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>407-3034951-4675566</t>
+          <t>405-2433007-9289947</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1466,22 +1466,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2273850</t>
+          <t>LPNSBOB1387687</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1489,32 +1489,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-24T08:29:31+00:00</t>
+          <t>2026-06-25T10:05:58+00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>402-0120877-0312362</t>
+          <t>407-3034951-4675566</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1522,22 +1522,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>LPNSPUN59333</t>
+          <t>LPNMAA4Z2273850</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1545,32 +1545,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-24T06:17:22+00:00</t>
+          <t>2026-06-24T08:29:31+00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>403-8864299-1768360</t>
+          <t>402-0120877-0312362</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1578,22 +1578,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7854241</t>
+          <t>LPNSPUN59333</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1601,32 +1601,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-23T15:36:47+00:00</t>
+          <t>2026-06-24T06:17:22+00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>402-8717460-5700310</t>
+          <t>403-8864299-1768360</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>LPNHDX8A005873</t>
+          <t>LPNBLR7Y7854241</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1657,32 +1657,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-23T11:54:27+00:00</t>
+          <t>2026-06-23T15:36:47+00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>403-7688253-5273167</t>
+          <t>402-8717460-5700310</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1690,22 +1690,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>LPNBOM5F5694482</t>
+          <t>LPNHDX8A005873</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1713,12 +1713,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-23T09:27:19+00:00</t>
+          <t>2026-06-23T11:54:27+00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>408-9857262-4357961</t>
+          <t>403-7688253-5273167</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7853975</t>
+          <t>LPNBOM5F5694482</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1769,12 +1769,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-23T08:32:44+00:00</t>
+          <t>2026-06-23T09:27:19+00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>404-2029470-0977929</t>
+          <t>408-9857262-4357961</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3925027</t>
+          <t>LPNBLR7Y7853975</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1825,32 +1825,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-23T06:25:18+00:00</t>
+          <t>2026-06-23T08:32:44+00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>408-7120729-6837923</t>
+          <t>404-2029470-0977929</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>LPNSBOB1385946</t>
+          <t>LPNDEL4AA3925027</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1881,12 +1881,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-23T05:29:18+00:00</t>
+          <t>2026-06-23T06:25:18+00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>403-5101653-2865108</t>
+          <t>408-7120729-6837923</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1914,22 +1914,22 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>LPNHDX8005941</t>
+          <t>LPNSBOB1385946</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1937,32 +1937,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-22T15:00:37+00:00</t>
+          <t>2026-06-23T05:29:18+00:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>408-2886313-6344340</t>
+          <t>403-5101653-2865108</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>LPNSBOB1385291</t>
+          <t>LPNHDX8005941</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -1993,32 +1993,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-22T15:00:11+00:00</t>
+          <t>2026-06-22T15:00:37+00:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>403-4065197-2565940</t>
+          <t>408-2886313-6344340</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>LPNSBOB1385290</t>
+          <t>LPNSBOB1385291</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2049,32 +2049,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-22T13:49:32+00:00</t>
+          <t>2026-06-22T15:00:11+00:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>171-3328269-2691534</t>
+          <t>403-4065197-2565940</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2082,22 +2082,22 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>LPNBLX1C049419</t>
+          <t>LPNSBOB1385290</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2105,32 +2105,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-22T13:44:52+00:00</t>
+          <t>2026-06-22T13:49:32+00:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>407-2806960-6949923</t>
+          <t>171-3328269-2691534</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2143,17 +2143,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>LPNBLX1C049418</t>
+          <t>LPNBLX1C049419</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2161,32 +2161,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-22T12:43:38+00:00</t>
+          <t>2026-06-22T13:44:52+00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>402-2531413-4073130</t>
+          <t>407-2806960-6949923</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2194,22 +2194,22 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>LPNHYD8EF41160</t>
+          <t>LPNBLX1C049418</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2217,12 +2217,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-22T09:02:33+00:00</t>
+          <t>2026-06-22T12:43:38+00:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>404-4254275-9061104</t>
+          <t>402-2531413-4073130</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>LPNHYD8ED01352</t>
+          <t>LPNHYD8EF41160</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2273,12 +2273,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-22T06:27:11+00:00</t>
+          <t>2026-06-22T09:02:33+00:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>407-5289320-1468336</t>
+          <t>404-4254275-9061104</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2306,22 +2306,22 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7287766</t>
+          <t>LPNHYD8ED01352</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2329,32 +2329,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-21T15:48:42+00:00</t>
+          <t>2026-06-22T06:27:11+00:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>408-1433377-1765942</t>
+          <t>407-5289320-1468336</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>LPNSBOB1385218</t>
+          <t>LPNBLR7Y7287766</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2385,32 +2385,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-21T09:50:13+00:00</t>
+          <t>2026-06-21T15:48:42+00:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>405-1204534-8479517</t>
+          <t>408-1433377-1765942</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2418,22 +2418,22 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>LPNDEL4AA4027730</t>
+          <t>LPNSBOB1385218</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2441,12 +2441,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-21T08:35:03+00:00</t>
+          <t>2026-06-21T09:50:13+00:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>171-0025867-6612374</t>
+          <t>405-1204534-8479517</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7853300</t>
+          <t>LPNDEL4AA4027730</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2497,12 +2497,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-20T13:05:37+00:00</t>
+          <t>2026-06-21T08:35:03+00:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>402-8590404-8535510</t>
+          <t>171-0025867-6612374</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>LPNMAA4G898204</t>
+          <t>LPNBLR7Y7853300</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -2553,32 +2553,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-19T14:24:04+00:00</t>
+          <t>2026-06-20T13:05:37+00:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>403-3269966-6849104</t>
+          <t>402-8590404-8535510</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>LPNHDX8A004693</t>
+          <t>LPNMAA4G898204</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -2609,32 +2609,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-18T09:53:43+00:00</t>
+          <t>2026-06-19T14:24:04+00:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>408-1513827-8090763</t>
+          <t>403-3269966-6849104</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2642,22 +2642,22 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2273003</t>
+          <t>LPNHDX8A004693</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2665,32 +2665,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-18T09:01:23+00:00</t>
+          <t>2026-06-18T09:53:43+00:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>402-6972876-7770702</t>
+          <t>408-1513827-8090763</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FBA76765</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>B0BMQQQ7YD</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>X001O7YYCV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>White Mulberry Motorized Height Adjustable Sit-Stand Desk | Electronic Height Adjustable | Motor &amp; Memory Preset Controller | Office, Workstation or Home | Carbon Fibre | 120 * 60*H(75-118) cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2698,22 +2698,22 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>LPNSPUN58279</t>
+          <t>LPNMAA4Z2273003</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -2721,32 +2721,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-18T06:34:47+00:00</t>
+          <t>2026-06-18T09:01:23+00:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>171-5595331-6677926</t>
+          <t>402-6972876-7770702</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA76765</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BMQQQ7YD</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001O7YYCV</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Motorized Height Adjustable Sit-Stand Desk | Electronic Height Adjustable | Motor &amp; Memory Preset Controller | Office, Workstation or Home | Carbon Fibre | 120 * 60*H(75-118) cm</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>LPNSPUN58332</t>
+          <t>LPNSPUN58279</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -2777,32 +2777,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-18T06:13:54+00:00</t>
+          <t>2026-06-18T06:34:47+00:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>405-9716650-4190754</t>
+          <t>171-5595331-6677926</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>LPNSPUN58348</t>
+          <t>LPNSPUN58332</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2833,32 +2833,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-18T05:06:11+00:00</t>
+          <t>2026-06-18T06:13:54+00:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>405-0242402-8315559</t>
+          <t>405-9716650-4190754</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>LPNHYD8DY89222</t>
+          <t>LPNSPUN58348</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -2889,12 +2889,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-18T03:18:32+00:00</t>
+          <t>2026-06-18T05:06:11+00:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>403-8790017-7829152</t>
+          <t>405-0242402-8315559</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>LPNHYD8DY89148</t>
+          <t>LPNHYD8DY89222</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -2945,12 +2945,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-17T17:18:11+00:00</t>
+          <t>2026-06-18T03:18:32+00:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>408-3294486-3424329</t>
+          <t>403-8790017-7829152</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2978,12 +2978,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>LPNCCX1B4206954</t>
+          <t>LPNHYD8DY89148</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3001,32 +3001,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-17T11:01:26+00:00</t>
+          <t>2026-06-17T17:18:11+00:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>171-3399563-8885966</t>
+          <t>408-3294486-3424329</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3034,22 +3034,22 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>DAMAGED</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>LPNLMAA0019039</t>
+          <t>LPNCCX1B4206954</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3057,32 +3057,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-15T09:24:30+00:00</t>
+          <t>2026-06-17T11:01:26+00:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>171-3194001-5187538</t>
+          <t>171-3399563-8885966</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3090,22 +3090,22 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>LPNHYD8DY92591</t>
+          <t>LPNLMAA0019039</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -3113,32 +3113,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-15T08:53:22+00:00</t>
+          <t>2026-06-15T09:24:30+00:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>406-3765893-9779536</t>
+          <t>171-3194001-5187538</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3146,22 +3146,22 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>LPNHDX8A0002233</t>
+          <t>LPNHYD8DY92591</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -3169,32 +3169,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-14T11:15:53+00:00</t>
+          <t>2026-06-15T08:53:22+00:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>171-1282309-9677932</t>
+          <t>406-3765893-9779536</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3202,22 +3202,22 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2198432</t>
+          <t>LPNHDX8A0002233</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3225,12 +3225,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-14T06:26:57+00:00</t>
+          <t>2026-06-14T11:15:53+00:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>407-1845667-2313146</t>
+          <t>171-1282309-9677932</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3677498</t>
+          <t>LPNMAA4Z2198432</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3281,32 +3281,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-13T12:21:24+00:00</t>
+          <t>2026-06-14T06:26:57+00:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>405-5466299-6857906</t>
+          <t>407-1845667-2313146</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>LPNSBOB1375958</t>
+          <t>LPNDEL4AA3677498</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -3337,32 +3337,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-13T12:20:57+00:00</t>
+          <t>2026-06-13T12:21:24+00:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>404-9976514-7382743</t>
+          <t>405-5466299-6857906</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3375,17 +3375,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>LPNSBOB1375957</t>
+          <t>LPNSBOB1375958</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -3393,32 +3393,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-12T11:47:28+00:00</t>
+          <t>2026-06-13T12:20:57+00:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>407-2845785-4936332</t>
+          <t>404-9976514-7382743</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3426,22 +3426,22 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>LPNSHTI00009280</t>
+          <t>LPNSBOB1375957</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -3449,32 +3449,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-11T12:39:34+00:00</t>
+          <t>2026-06-12T11:47:28+00:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>405-0836953-9114742</t>
+          <t>407-2845785-4936332</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>LPNHDX8A001607</t>
+          <t>LPNSHTI00009280</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -3505,32 +3505,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-11T10:43:03+00:00</t>
+          <t>2026-06-11T12:39:34+00:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>407-7053626-1929962</t>
+          <t>405-0836953-9114742</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FBA79667</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>B0DQPK7MFH</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>X0027512Z1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk with Shelf|DIY Assembly| Monitor Raising Shelf |Engineered Wood &amp; Sturdy Steel Leg|Perfect for Computer Table Office Home Gaming Study Desk|L(130+130)*45*77cm|White</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3538,22 +3538,22 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SCUY</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>LPNSCUY00017897</t>
+          <t>LPNHDX8A001607</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -3561,32 +3561,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-10T22:26:08+00:00</t>
+          <t>2026-06-11T10:43:03+00:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>404-0639682-6860336</t>
+          <t>407-7053626-1929962</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79667</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQPK7MFH</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0027512Z1</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk with Shelf|DIY Assembly| Monitor Raising Shelf |Engineered Wood &amp; Sturdy Steel Leg|Perfect for Computer Table Office Home Gaming Study Desk|L(130+130)*45*77cm|White</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SCUY</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>LPNCX1B4784440</t>
+          <t>LPNSCUY00017897</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3617,12 +3617,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-10T12:14:02+00:00</t>
+          <t>2026-06-10T22:26:08+00:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>171-1027170-0049924</t>
+          <t>404-0639682-6860336</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2407733</t>
+          <t>LPNCX1B4784440</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -3673,32 +3673,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-06-10T08:20:03+00:00</t>
+          <t>2026-06-10T12:14:02+00:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>406-6295410-5869130</t>
+          <t>171-1027170-0049924</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -3706,22 +3706,22 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>LPNBLX1C159057</t>
+          <t>LPNMAA4Z2407733</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -3729,32 +3729,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-06-10T05:42:02+00:00</t>
+          <t>2026-06-10T08:20:03+00:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>405-8329990-8940345</t>
+          <t>406-6295410-5869130</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3762,22 +3762,22 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4745942</t>
+          <t>LPNBLX1C159057</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -3785,12 +3785,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-06-10T04:51:41+00:00</t>
+          <t>2026-06-10T05:42:02+00:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>405-7954322-6131539</t>
+          <t>405-8329990-8940345</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>LPNBOM5F5675078</t>
+          <t>LPNBLR7Y4745942</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -3841,12 +3841,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-06-10T03:51:05+00:00</t>
+          <t>2026-06-10T04:51:41+00:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>407-5527946-4998741</t>
+          <t>405-7954322-6131539</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7287766</t>
+          <t>LPNBOM5F5675078</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -3897,12 +3897,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-06-08T09:59:30+00:00</t>
+          <t>2026-06-10T03:51:05+00:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>404-4052225-7064331</t>
+          <t>407-5527946-4998741</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3631375</t>
+          <t>LPNBLR7Y7287766</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -3953,32 +3953,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-06-08T08:59:50+00:00</t>
+          <t>2026-06-08T09:59:30+00:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>404-3123106-0929939</t>
+          <t>404-4052225-7064331</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FBK76387</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>B0BF4S7V8C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>X00242V9DH</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -3986,22 +3986,22 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>LPNSPUN56234</t>
+          <t>LPNDEL4AA3631375</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4009,32 +4009,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-06-08T08:59:02+00:00</t>
+          <t>2026-06-08T08:59:50+00:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>408-8800113-8391502</t>
+          <t>404-3123106-0929939</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBK76387</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0BF4S7V8C</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X00242V9DH</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | White</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>LPNSPUN56235</t>
+          <t>LPNSPUN56234</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -4065,32 +4065,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-06-08T08:43:30+00:00</t>
+          <t>2026-06-08T08:59:02+00:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>407-4254200-0562712</t>
+          <t>408-8800113-8391502</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -4098,22 +4098,22 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3631346</t>
+          <t>LPNSPUN56235</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -4121,12 +4121,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-06-07T16:09:41+00:00</t>
+          <t>2026-06-08T08:43:30+00:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>405-9852474-3831538</t>
+          <t>407-4254200-0562712</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4154,22 +4154,22 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>LPNCCX1B4179343</t>
+          <t>LPNDEL4AA3631346</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -4177,32 +4177,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-06-07T11:20:49+00:00</t>
+          <t>2026-06-07T16:09:41+00:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>406-9783608-9093148</t>
+          <t>405-9852474-3831538</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>LPNLMAA0016237</t>
+          <t>LPNCCX1B4179343</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -4233,32 +4233,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-06-07T10:24:17+00:00</t>
+          <t>2026-06-07T11:20:49+00:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>406-6392223-8173930</t>
+          <t>406-9783608-9093148</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -4266,12 +4266,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>LPNBLX1C047099</t>
+          <t>LPNLMAA0016237</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -4289,32 +4289,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-06-06T10:45:59+00:00</t>
+          <t>2026-06-07T10:24:17+00:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>406-9111649-3125130</t>
+          <t>406-6392223-8173930</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -4322,22 +4322,22 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>LPNBOM5F5579985</t>
+          <t>LPNBLX1C047099</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -4345,12 +4345,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-06-05T09:54:50+00:00</t>
+          <t>2026-06-06T10:45:59+00:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>405-7328472-7893901</t>
+          <t>406-9111649-3125130</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679697</t>
+          <t>LPNBOM5F5579985</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -4401,32 +4401,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-06-05T08:35:28+00:00</t>
+          <t>2026-06-05T09:54:50+00:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>404-9218549-9930734</t>
+          <t>405-7328472-7893901</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FBA79659</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>X0026ZDA2F</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, Black, 3 Year Warranty</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>LPNSDEGF082043</t>
+          <t>LPNDEL4AA3679697</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -4457,32 +4457,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-06-05T08:17:03+00:00</t>
+          <t>2026-06-05T08:35:28+00:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>171-6540897-0152357</t>
+          <t>404-9218549-9930734</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79659</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZDA2F</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, Black, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679650</t>
+          <t>LPNSDEGF082043</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -4513,12 +4513,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-06-05T04:33:06+00:00</t>
+          <t>2026-06-05T08:17:03+00:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>171-6354444-3723505</t>
+          <t>171-6540897-0152357</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4546,22 +4546,22 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>LPNBOM5F5574228</t>
+          <t>LPNDEL4AA3679650</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -4569,12 +4569,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-06-05T04:28:18+00:00</t>
+          <t>2026-06-05T04:33:06+00:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>406-6103690-9310748</t>
+          <t>171-6354444-3723505</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4602,22 +4602,22 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679535</t>
+          <t>LPNBOM5F5574228</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -4625,12 +4625,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-06-04T03:47:36+00:00</t>
+          <t>2026-06-05T04:28:18+00:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>406-2278126-7841949</t>
+          <t>406-6103690-9310748</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679185</t>
+          <t>LPNDEL4AA3679535</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -4681,12 +4681,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-06-01T09:32:55+00:00</t>
+          <t>2026-06-04T03:47:36+00:00</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>402-3794541-2581168</t>
+          <t>406-2278126-7841949</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4743333</t>
+          <t>LPNDEL4AA3679185</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -4737,12 +4737,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-06-01T04:42:36+00:00</t>
+          <t>2026-06-01T09:32:55+00:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>408-0143238-4374708</t>
+          <t>402-3794541-2581168</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>LPNBOM5F5524445</t>
+          <t>LPNBLR7Y4743333</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -4793,12 +4793,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-06-01T03:58:27+00:00</t>
+          <t>2026-06-01T04:42:36+00:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>406-4355667-6072332</t>
+          <t>408-0143238-4374708</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4836,12 +4836,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4743158</t>
+          <t>LPNBOM5F5524445</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -4849,12 +4849,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-31T09:10:34+00:00</t>
+          <t>2026-06-01T03:58:27+00:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>404-2518539-4406712</t>
+          <t>406-4355667-6072332</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4882,22 +4882,22 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3976607</t>
+          <t>LPNBLR7Y4743158</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -4905,12 +4905,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-30T22:18:28+00:00</t>
+          <t>2026-05-31T09:10:34+00:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>407-1474707-0478726</t>
+          <t>404-2518539-4406712</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4938,22 +4938,22 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>LPNCCX1B4554643</t>
+          <t>LPNDEL4AA3976607</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -4961,12 +4961,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-30T04:13:42+00:00</t>
+          <t>2026-05-30T22:18:28+00:00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>406-7941139-9225906</t>
+          <t>407-1474707-0478726</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4994,12 +4994,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>LPNBOM5F5507643</t>
+          <t>LPNCCX1B4554643</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -5017,12 +5017,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-29T23:01:15+00:00</t>
+          <t>2026-05-30T04:13:42+00:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>405-0096078-8521126</t>
+          <t>406-7941139-9225906</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5050,12 +5050,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>LPNCCX1B2941120</t>
+          <t>LPNBOM5F5507643</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -5073,12 +5073,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-29T15:27:20+00:00</t>
+          <t>2026-05-29T23:01:15+00:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>404-8418070-5981124</t>
+          <t>405-0096078-8521126</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>LPNCCX1B4508596</t>
+          <t>LPNCCX1B2941120</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -5129,12 +5129,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-29T05:18:33+00:00</t>
+          <t>2026-05-29T15:27:20+00:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>171-0407209-4266756</t>
+          <t>404-8418070-5981124</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5162,22 +5162,22 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937926</t>
+          <t>LPNCCX1B4508596</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -5185,12 +5185,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-28T11:56:49+00:00</t>
+          <t>2026-05-29T05:18:33+00:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>407-4902279-0189155</t>
+          <t>171-0407209-4266756</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5218,22 +5218,22 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7363000</t>
+          <t>LPNDEL4AA3937926</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -5241,12 +5241,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-28T08:40:02+00:00</t>
+          <t>2026-05-28T11:56:49+00:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>408-1128142-0248321</t>
+          <t>407-4902279-0189155</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>DAMAGED_BY_FC</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937756</t>
+          <t>LPNBLR7Y7363000</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -5297,12 +5297,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-28T06:36:17+00:00</t>
+          <t>2026-05-28T08:40:02+00:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>402-4776409-4471512</t>
+          <t>408-1128142-0248321</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>DAMAGED_BY_FC</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7286354</t>
+          <t>LPNDEL4AA3937756</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -5353,12 +5353,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-27T12:42:16+00:00</t>
+          <t>2026-05-28T06:36:17+00:00</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>404-6762038-7137955</t>
+          <t>402-4776409-4471512</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5396,12 +5396,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937575</t>
+          <t>LPNBLR7Y7286354</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -5409,12 +5409,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-27T09:44:17+00:00</t>
+          <t>2026-05-27T12:42:16+00:00</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>403-3444915-0085109</t>
+          <t>404-6762038-7137955</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7362686</t>
+          <t>LPNDEL4AA3937575</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -5465,32 +5465,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-27T09:25:47+00:00</t>
+          <t>2026-05-27T09:44:17+00:00</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>405-8410325-7933918</t>
+          <t>403-3444915-0085109</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -5498,22 +5498,22 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>LPNSPUN53913</t>
+          <t>LPNBLR7Y7362686</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -5521,32 +5521,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-26T23:02:43+00:00</t>
+          <t>2026-05-27T09:25:47+00:00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>407-0645348-4574732</t>
+          <t>405-8410325-7933918</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -5554,22 +5554,22 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>LPNCCX1B5292913</t>
+          <t>LPNSPUN53913</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -5577,12 +5577,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-26T11:06:29+00:00</t>
+          <t>2026-05-26T23:02:43+00:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>402-2949127-9513917</t>
+          <t>407-0645348-4574732</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5610,22 +5610,22 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937227</t>
+          <t>LPNCCX1B5292913</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -5633,12 +5633,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-26T08:48:10+00:00</t>
+          <t>2026-05-26T11:06:29+00:00</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>403-5510263-6469912</t>
+          <t>402-2949127-9513917</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273675</t>
+          <t>LPNDEL4AA3937227</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -5689,12 +5689,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-25T15:22:25+00:00</t>
+          <t>2026-05-26T08:48:10+00:00</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>402-5203149-1906724</t>
+          <t>403-5510263-6469912</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>LPNCCX1B5331017</t>
+          <t>LPNBLR7Y7273675</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -5745,12 +5745,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-24T09:24:39+00:00</t>
+          <t>2026-05-25T15:22:25+00:00</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>171-7709339-0701117</t>
+          <t>402-5203149-1906724</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273169</t>
+          <t>LPNCCX1B5331017</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -5801,12 +5801,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-24T08:29:52+00:00</t>
+          <t>2026-05-24T09:24:39+00:00</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>406-7042486-7436314</t>
+          <t>171-7709339-0701117</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273150</t>
+          <t>LPNBLR7Y7273169</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -5857,32 +5857,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-23T23:07:27+00:00</t>
+          <t>2026-05-24T08:29:52+00:00</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>406-2954542-5857925</t>
+          <t>406-7042486-7436314</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -5890,22 +5890,22 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>LPNSBOB1370158</t>
+          <t>LPNBLR7Y7273150</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -5913,32 +5913,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-23T10:58:04+00:00</t>
+          <t>2026-05-23T23:07:27+00:00</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>406-4758725-2077907</t>
+          <t>406-2954542-5857925</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -5946,22 +5946,22 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7272896</t>
+          <t>LPNSBOB1370158</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -5969,32 +5969,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-22T09:58:26+00:00</t>
+          <t>2026-05-23T10:58:04+00:00</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>403-7800011-6937966</t>
+          <t>406-4758725-2077907</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>LPNSDEGF010003</t>
+          <t>LPNBLR7Y7272896</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -6025,32 +6025,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-21T04:38:32+00:00</t>
+          <t>2026-05-22T09:58:26+00:00</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>403-2400247-1930753</t>
+          <t>403-7800011-6937966</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>LPNSDEGF099136</t>
+          <t>LPNSDEGF010003</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -6081,32 +6081,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-20T11:30:45+00:00</t>
+          <t>2026-05-21T04:38:32+00:00</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>406-2648444-6601917</t>
+          <t>403-2400247-1930753</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2147464</t>
+          <t>LPNSDEGF099136</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -6137,32 +6137,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-19T08:03:32+00:00</t>
+          <t>2026-05-20T11:30:45+00:00</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>405-4744559-6958733</t>
+          <t>406-2648444-6601917</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>LPNSDEGF097985</t>
+          <t>LPNDEL4AA2147464</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -6193,32 +6193,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-18T11:36:05+00:00</t>
+          <t>2026-05-19T08:03:32+00:00</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>171-1585723-0908356</t>
+          <t>405-4744559-6958733</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>LPNBLX1C155145</t>
+          <t>LPNSDEGF097985</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -6249,32 +6249,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-15T08:29:30+00:00</t>
+          <t>2026-05-18T11:36:05+00:00</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>402-4856546-1261939</t>
+          <t>171-1585723-0908356</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>LPNSDEGF074601</t>
+          <t>LPNBLX1C155145</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -6305,12 +6305,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-13T13:50:43+00:00</t>
+          <t>2026-05-15T08:29:30+00:00</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>403-7495250-9937954</t>
+          <t>402-4856546-1261939</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6338,22 +6338,22 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>LPNBLX1C154096</t>
+          <t>LPNSDEGF074601</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -6361,32 +6361,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-12T07:19:54+00:00</t>
+          <t>2026-05-13T13:50:43+00:00</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>408-0473775-6641108</t>
+          <t>403-7495250-9937954</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -6394,22 +6394,22 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>LPNSBOB1362246</t>
+          <t>LPNBLX1C154096</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -6417,12 +6417,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-11T10:31:39+00:00</t>
+          <t>2026-05-12T07:19:54+00:00</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>404-1750959-8518722</t>
+          <t>408-0473775-6641108</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6450,22 +6450,22 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>LPNSHTI00006165</t>
+          <t>LPNSBOB1362246</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -6473,32 +6473,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-10T09:15:43+00:00</t>
+          <t>2026-05-11T10:31:39+00:00</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>402-1548587-3227555</t>
+          <t>404-1750959-8518722</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -6506,22 +6506,22 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>LPNBOM5F5057136</t>
+          <t>LPNSHTI00006165</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -6529,32 +6529,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-08T15:43:17+00:00</t>
+          <t>2026-05-10T09:15:43+00:00</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>402-8374307-7441113</t>
+          <t>402-1548587-3227555</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>LPNSDEGF064205</t>
+          <t>LPNBOM5F5057136</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -6585,32 +6585,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-08T13:25:23+00:00</t>
+          <t>2026-05-08T15:43:17+00:00</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>171-7381542-8368365</t>
+          <t>402-8374307-7441113</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>LPNBLX1C042486</t>
+          <t>LPNSDEGF064205</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -6641,32 +6641,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-08T07:49:38+00:00</t>
+          <t>2026-05-08T13:25:23+00:00</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>403-3056736-6311553</t>
+          <t>171-7381542-8368365</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -6674,22 +6674,22 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5321963</t>
+          <t>LPNBLX1C042486</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -6697,32 +6697,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-06T06:52:28+00:00</t>
+          <t>2026-05-08T07:49:38+00:00</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>403-2654029-0716338</t>
+          <t>403-3056736-6311553</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>LPNSHTI00005958</t>
+          <t>LPNBLR7Y5321963</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
@@ -6753,32 +6753,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-06T05:51:00+00:00</t>
+          <t>2026-05-06T06:52:28+00:00</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>404-9426288-6037168</t>
+          <t>403-2654029-0716338</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -6786,22 +6786,22 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>LPNBOM5F5236158</t>
+          <t>LPNSHTI00005958</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -6809,32 +6809,32 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-02T04:54:42+00:00</t>
+          <t>2026-05-06T05:51:00+00:00</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>407-6201969-2856316</t>
+          <t>404-9426288-6037168</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -6842,22 +6842,22 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>LPNLMAA0004457</t>
+          <t>LPNBOM5F5236158</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
@@ -6865,12 +6865,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-28T08:52:43+00:00</t>
+          <t>2026-05-02T04:54:42+00:00</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>171-6713241-8377149</t>
+          <t>407-6201969-2856316</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>LPNLMAA0003844</t>
+          <t>LPNLMAA0004457</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -6921,32 +6921,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-27T06:04:11+00:00</t>
+          <t>2026-04-28T08:52:43+00:00</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>403-6021111-3520325</t>
+          <t>171-6713241-8377149</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -6959,17 +6959,17 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>LPNLMAA0003335</t>
+          <t>LPNLMAA0003844</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -6977,32 +6977,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-26T08:09:27+00:00</t>
+          <t>2026-04-27T06:04:11+00:00</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>402-4881396-1030704</t>
+          <t>403-6021111-3520325</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2253845</t>
+          <t>LPNLMAA0003335</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -7033,12 +7033,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-26T04:14:08+00:00</t>
+          <t>2026-04-26T08:09:27+00:00</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>408-1134010-7973925</t>
+          <t>402-4881396-1030704</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7076,12 +7076,12 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5321963</t>
+          <t>LPNDEL4AA2253845</t>
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
@@ -7089,32 +7089,32 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-26T03:22:50+00:00</t>
+          <t>2026-04-26T04:14:08+00:00</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>406-9614580-4613163</t>
+          <t>408-1134010-7973925</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -7122,12 +7122,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>LPNSPUN46511</t>
+          <t>LPNBLR7Y5321963</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -7145,32 +7145,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-25T05:33:44+00:00</t>
+          <t>2026-04-26T03:22:50+00:00</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>171-3077342-1790757</t>
+          <t>406-9614580-4613163</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>LPNLMAA0002840</t>
+          <t>LPNSPUN46511</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -7201,32 +7201,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-25T03:48:59+00:00</t>
+          <t>2026-04-25T05:33:44+00:00</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>404-4908572-3783532</t>
+          <t>171-3077342-1790757</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>X002FOAUSJ</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7244,12 +7244,12 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>LPNBLR7Y6090385</t>
+          <t>LPNLMAA0002840</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -7257,32 +7257,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-22T10:55:13+00:00</t>
+          <t>2026-04-25T03:48:59+00:00</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>407-4868470-8499505</t>
+          <t>404-4908572-3783532</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X002FOAUSJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -7290,22 +7290,22 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>LPNLMAA0001354</t>
+          <t>LPNBLR7Y6090385</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
@@ -7313,32 +7313,32 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-22T04:17:57+00:00</t>
+          <t>2026-04-22T10:55:13+00:00</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>406-5030280-5555520</t>
+          <t>407-4868470-8499505</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -7346,22 +7346,22 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>LPNSDEGF117193</t>
+          <t>LPNLMAA0001354</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -7369,32 +7369,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-21T20:42:51+00:00</t>
+          <t>2026-04-22T04:17:57+00:00</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>403-7744956-9735520</t>
+          <t>406-5030280-5555520</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -7402,22 +7402,22 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>LPNCCX1B1519621</t>
+          <t>LPNSDEGF117193</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -7425,32 +7425,32 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-20T05:04:40+00:00</t>
+          <t>2026-04-21T20:42:51+00:00</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>171-5598784-9947515</t>
+          <t>403-7744956-9735520</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>X002FOAUSJ</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -7458,22 +7458,22 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5552415</t>
+          <t>LPNCCX1B1519621</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -7481,32 +7481,32 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-18T05:41:14+00:00</t>
+          <t>2026-04-20T05:04:40+00:00</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>404-0309463-1310709</t>
+          <t>171-5598784-9947515</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X002FOAUSJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -7514,22 +7514,22 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>LPNDEL4AA0788989</t>
+          <t>LPNBLR7Y5552415</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -7537,32 +7537,32 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-15T13:55:57+00:00</t>
+          <t>2026-04-18T05:41:14+00:00</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>407-7885481-2445152</t>
+          <t>404-0309463-1310709</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>SMAB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>LPNSMAB1153810</t>
+          <t>LPNDEL4AA0788989</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -7593,12 +7593,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-15T08:47:44+00:00</t>
+          <t>2026-04-15T13:55:57+00:00</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>407-3585151-4323522</t>
+          <t>407-7885481-2445152</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7626,22 +7626,22 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>SMAB</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>LPNSDEGF027993</t>
+          <t>LPNSMAB1153810</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -7649,32 +7649,32 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-12T10:47:54+00:00</t>
+          <t>2026-04-15T08:47:44+00:00</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>407-0802588-3857957</t>
+          <t>407-3585151-4323522</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -7687,17 +7687,17 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>LPNSDEGF026167</t>
+          <t>LPNSDEGF027993</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -7705,32 +7705,32 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-04-11T06:17:07+00:00</t>
+          <t>2026-04-12T10:47:54+00:00</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>408-2417441-1123516</t>
+          <t>407-0802588-3857957</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FBK76764</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>B0BMV1WPHL</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>X00242TZTH</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>White Mulberry Ergonomic Sit Stand Desk | Standing Desk for Office, Home &amp; Study | Everyday Ergonomic Desk | 1200mm x 600mm | Carbon Fibre</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -7738,22 +7738,22 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>LPNSHTI00004704</t>
+          <t>LPNSDEGF026167</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -7761,32 +7761,32 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-04-09T03:38:39+00:00</t>
+          <t>2026-04-11T06:17:07+00:00</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>406-0798045-4525148</t>
+          <t>408-2417441-1123516</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBK76764</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BMV1WPHL</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X00242TZTH</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Ergonomic Sit Stand Desk | Standing Desk for Office, Home &amp; Study | Everyday Ergonomic Desk | 1200mm x 600mm | Carbon Fibre</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>LPNSDEGF168570</t>
+          <t>LPNSHTI00004704</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -7817,32 +7817,32 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-04-08T10:17:09+00:00</t>
+          <t>2026-04-09T03:38:39+00:00</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>406-3115014-9939528</t>
+          <t>406-0798045-4525148</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -7850,22 +7850,22 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2155169</t>
+          <t>LPNSDEGF168570</t>
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
@@ -7873,12 +7873,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-04-08T09:53:57+00:00</t>
+          <t>2026-04-08T10:17:09+00:00</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>403-7697438-5361950</t>
+          <t>406-3115014-9939528</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7906,22 +7906,22 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>LPNMAA4Z0044638</t>
+          <t>LPNDEL4AA2155169</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
@@ -7929,12 +7929,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-04-07T23:27:35+00:00</t>
+          <t>2026-04-08T09:53:57+00:00</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>402-3182844-0423531</t>
+          <t>403-7697438-5361950</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7962,22 +7962,22 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>NO_REASON_GIVEN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>LPNCCX1B1676425</t>
+          <t>LPNMAA4Z0044638</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -7985,32 +7985,32 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-04-07T08:05:07+00:00</t>
+          <t>2026-04-07T23:27:35+00:00</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>404-2599173-5513112</t>
+          <t>402-3182844-0423531</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -8018,22 +8018,22 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>NO_REASON_GIVEN</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>LPNBLX1C066978</t>
+          <t>LPNCCX1B1676425</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -8041,32 +8041,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-04-06T21:28:06+00:00</t>
+          <t>2026-04-07T08:05:07+00:00</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>408-0894434-7394724</t>
+          <t>404-2599173-5513112</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>LPNCCX1B1676919</t>
+          <t>LPNBLX1C066978</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
@@ -8097,12 +8097,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-04-06T19:49:19+00:00</t>
+          <t>2026-04-06T21:28:06+00:00</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>402-0299451-2765120</t>
+          <t>408-0894434-7394724</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8135,17 +8135,17 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>LPNCCX1B2787065</t>
+          <t>LPNCCX1B1676919</t>
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
@@ -8153,12 +8153,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-04-06T09:26:15+00:00</t>
+          <t>2026-04-06T19:49:19+00:00</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>402-1769603-3523555</t>
+          <t>402-0299451-2765120</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>LPNMAA4Z0044156</t>
+          <t>LPNCCX1B2787065</t>
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
@@ -8209,32 +8209,32 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-04-06T08:31:32+00:00</t>
+          <t>2026-04-06T09:26:15+00:00</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>408-6381953-4631553</t>
+          <t>402-1769603-3523555</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -8242,22 +8242,22 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>LPNSPUN45721</t>
+          <t>LPNMAA4Z0044156</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
@@ -8265,58 +8265,114 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>2026-04-06T08:31:32+00:00</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>408-6381953-4631553</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>FBA79662</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>B0DQ4YWSMC</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>X00270AW07</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>SPUN</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>CUSTOMER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>SWITCHEROO</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>LPNSPUN45721</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
           <t>2026-04-05T06:19:10+00:00</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>408-5061007-8220304</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>FBA79167</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>B0CPFS24ML</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E142" t="inlineStr">
         <is>
           <t>X001Y5UYX1</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
-      <c r="G141" t="n">
-        <v>1</v>
-      </c>
-      <c r="H141" t="inlineStr">
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" t="inlineStr">
         <is>
           <t>BLR7</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
+      <c r="I142" t="inlineStr">
         <is>
           <t>SELLABLE</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
+      <c r="J142" t="inlineStr">
         <is>
           <t>NOT_COMPATIBLE</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
+      <c r="K142" t="inlineStr">
         <is>
           <t>LPNBLR7Y6062118</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/raw/returns/WhiteMulberry.xlsx
+++ b/data/raw/returns/WhiteMulberry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L142"/>
+  <dimension ref="A1:L148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-03T11:38:57+00:00</t>
+          <t>2026-07-06T12:33:49+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>403-6645337-2467540</t>
+          <t>404-5401376-5513111</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -514,22 +514,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2082724</t>
+          <t>LPNHYD8EJ59560</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -537,12 +537,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02T17:30:33+00:00</t>
+          <t>2026-07-05T20:21:02+00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>402-1004506-0818747</t>
+          <t>408-9802796-1211539</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>LPNBLR8Z5514346</t>
+          <t>LPNCCX1A8722775</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -593,12 +593,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02T06:41:10+00:00</t>
+          <t>2026-07-05T07:23:15+00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>403-6072724-5581966</t>
+          <t>407-2308442-1499512</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4303742</t>
+          <t>LPNBLR8Z4813630</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -649,12 +649,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01T22:20:26+00:00</t>
+          <t>2026-07-05T06:48:36+00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>402-4598141-9561917</t>
+          <t>407-8970250-4543519</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LPNCCX1B4170658</t>
+          <t>LPNBLR8Z4814250</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -705,32 +705,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01T15:09:10+00:00</t>
+          <t>2026-07-05T04:41:04+00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>402-3081497-7409144</t>
+          <t>405-1245096-1377920</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -738,22 +738,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LPNBLX1C093497</t>
+          <t>LPNBOM5F5826513</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -761,12 +761,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01T09:24:20+00:00</t>
+          <t>2026-07-04T12:12:23+00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>405-3824107-9644368</t>
+          <t>404-7913029-6157962</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LPNBOM5F5465051</t>
+          <t>LPNHYD8EJ58729</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -817,12 +817,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01T06:49:32+00:00</t>
+          <t>2026-07-04T08:48:05+00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>404-6104605-6788338</t>
+          <t>405-3423037-8257160</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -850,22 +850,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DAMAGED_BY_FC</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>LPNBOM5F5435891</t>
+          <t>LPNDEL4AA3108992</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -873,12 +873,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01T05:46:54+00:00</t>
+          <t>2026-07-04T04:21:28+00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>407-2497737-1874765</t>
+          <t>405-3646440-7662737</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>LPNBOM5F5407228</t>
+          <t>LPNBOM5F5455146</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -929,12 +929,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01T03:55:07+00:00</t>
+          <t>2026-07-03T19:29:57+00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>403-6044286-1801115</t>
+          <t>403-0547582-3197132</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CCX2</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>LPNCCX2B2262224</t>
+          <t>LPNCCX1B4102605</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -985,32 +985,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-29T12:22:41+00:00</t>
+          <t>2026-07-03T14:02:46+00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>405-6904525-0069903</t>
+          <t>171-7464293-7220360</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>NO_REASON_GIVEN</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>LPNHYD8EF20503</t>
+          <t>LPNSBOB1392052</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1041,12 +1041,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-28T19:38:03+00:00</t>
+          <t>2026-07-03T11:38:57+00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>402-4296829-1337133</t>
+          <t>403-6645337-2467540</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>LPNCCX1B2440445</t>
+          <t>LPNDEL4AA2082724</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1097,12 +1097,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-28T08:39:43+00:00</t>
+          <t>2026-07-02T17:30:33+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>402-6090489-2032337</t>
+          <t>402-1004506-0818747</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7855923</t>
+          <t>LPNBLR8Z5514346</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1153,12 +1153,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-27T11:00:01+00:00</t>
+          <t>2026-07-02T14:56:15+00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>408-3896665-0021948</t>
+          <t>407-7003476-1816350</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1196,12 +1196,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>NO_REASON_GIVEN</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7855626</t>
+          <t>LPNDEL4AA3108265</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1209,32 +1209,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-27T10:32:22+00:00</t>
+          <t>2026-07-02T11:24:54+00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>407-5462207-4616334</t>
+          <t>408-9621782-0261114</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1242,22 +1242,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>LPNSBOB1388621</t>
+          <t>LPNDEL4AA3950616</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1265,32 +1265,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-26T18:08:18+00:00</t>
+          <t>2026-07-02T06:41:10+00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>171-5586406-9945900</t>
+          <t>403-6072724-5581966</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LPNSBOB1388302</t>
+          <t>LPNBLR8Z4303742</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1321,32 +1321,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26T06:57:42+00:00</t>
+          <t>2026-07-01T22:20:26+00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>405-2746376-7486724</t>
+          <t>402-4598141-9561917</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>LPNBLX1C140655</t>
+          <t>LPNCCX1B4170658</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1377,32 +1377,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-26T05:19:18+00:00</t>
+          <t>2026-07-01T15:09:10+00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>406-4442109-5330751</t>
+          <t>402-3081497-7409144</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1410,22 +1410,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3990308</t>
+          <t>LPNBLX1C093497</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1433,32 +1433,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-25T18:24:43+00:00</t>
+          <t>2026-07-01T09:24:20+00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>405-2433007-9289947</t>
+          <t>405-3824107-9644368</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1466,22 +1466,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>LPNSBOB1387687</t>
+          <t>LPNBOM5F5465051</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1489,12 +1489,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-25T10:05:58+00:00</t>
+          <t>2026-07-01T06:49:32+00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>407-3034951-4675566</t>
+          <t>404-6104605-6788338</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2273850</t>
+          <t>LPNBOM5F5435891</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1545,32 +1545,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-24T08:29:31+00:00</t>
+          <t>2026-07-01T05:46:54+00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>402-0120877-0312362</t>
+          <t>407-2497737-1874765</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1578,22 +1578,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>LPNSPUN59333</t>
+          <t>LPNBOM5F5407228</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1601,12 +1601,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-24T06:17:22+00:00</t>
+          <t>2026-07-01T03:55:07+00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>403-8864299-1768360</t>
+          <t>403-6044286-1801115</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1634,22 +1634,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7854241</t>
+          <t>LPNCCX2B2262224</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1657,32 +1657,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-23T15:36:47+00:00</t>
+          <t>2026-06-29T12:22:41+00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>402-8717460-5700310</t>
+          <t>405-6904525-0069903</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>LPNHDX8A005873</t>
+          <t>LPNHYD8EF20503</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1713,12 +1713,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-23T11:54:27+00:00</t>
+          <t>2026-06-28T19:38:03+00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>403-7688253-5273167</t>
+          <t>402-4296829-1337133</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>LPNBOM5F5694482</t>
+          <t>LPNCCX1B2440445</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1769,12 +1769,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-23T09:27:19+00:00</t>
+          <t>2026-06-28T08:39:43+00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>408-9857262-4357961</t>
+          <t>402-6090489-2032337</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7853975</t>
+          <t>LPNBLR7Y7855923</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1825,12 +1825,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-23T08:32:44+00:00</t>
+          <t>2026-06-27T11:00:01+00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>404-2029470-0977929</t>
+          <t>408-3896665-0021948</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3925027</t>
+          <t>LPNBLR7Y7855626</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1881,32 +1881,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-23T06:25:18+00:00</t>
+          <t>2026-06-27T10:32:22+00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>408-7120729-6837923</t>
+          <t>407-5462207-4616334</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1919,17 +1919,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>LPNSBOB1385946</t>
+          <t>LPNSBOB1388621</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1937,12 +1937,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-23T05:29:18+00:00</t>
+          <t>2026-06-26T18:08:18+00:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>403-5101653-2865108</t>
+          <t>171-5586406-9945900</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>LPNHDX8005941</t>
+          <t>LPNSBOB1388302</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -1993,32 +1993,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-22T15:00:37+00:00</t>
+          <t>2026-06-26T06:57:42+00:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>408-2886313-6344340</t>
+          <t>405-2746376-7486724</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2026,22 +2026,22 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>LPNSBOB1385291</t>
+          <t>LPNBLX1C140655</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2049,32 +2049,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-22T15:00:11+00:00</t>
+          <t>2026-06-26T05:19:18+00:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>403-4065197-2565940</t>
+          <t>406-4442109-5330751</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2082,22 +2082,22 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>LPNSBOB1385290</t>
+          <t>LPNDEL4AA3990308</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2105,32 +2105,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-22T13:49:32+00:00</t>
+          <t>2026-06-25T18:24:43+00:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>171-3328269-2691534</t>
+          <t>405-2433007-9289947</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2138,22 +2138,22 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>LPNBLX1C049419</t>
+          <t>LPNSBOB1387687</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2161,32 +2161,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-22T13:44:52+00:00</t>
+          <t>2026-06-25T10:05:58+00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>407-2806960-6949923</t>
+          <t>407-3034951-4675566</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2194,22 +2194,22 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>LPNBLX1C049418</t>
+          <t>LPNMAA4Z2273850</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2217,32 +2217,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-22T12:43:38+00:00</t>
+          <t>2026-06-24T08:29:31+00:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>402-2531413-4073130</t>
+          <t>402-0120877-0312362</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>LPNHYD8EF41160</t>
+          <t>LPNSPUN59333</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2273,12 +2273,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-22T09:02:33+00:00</t>
+          <t>2026-06-24T06:17:22+00:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>404-4254275-9061104</t>
+          <t>403-8864299-1768360</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>LPNHYD8ED01352</t>
+          <t>LPNBLR7Y7854241</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2329,32 +2329,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-22T06:27:11+00:00</t>
+          <t>2026-06-23T15:36:47+00:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>407-5289320-1468336</t>
+          <t>402-8717460-5700310</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7287766</t>
+          <t>LPNHDX8A005873</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2385,32 +2385,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-21T15:48:42+00:00</t>
+          <t>2026-06-23T11:54:27+00:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>408-1433377-1765942</t>
+          <t>403-7688253-5273167</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2418,22 +2418,22 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>LPNSBOB1385218</t>
+          <t>LPNBOM5F5694482</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2441,12 +2441,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-21T09:50:13+00:00</t>
+          <t>2026-06-23T09:27:19+00:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>405-1204534-8479517</t>
+          <t>408-9857262-4357961</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>LPNDEL4AA4027730</t>
+          <t>LPNBLR7Y7853975</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2497,12 +2497,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-21T08:35:03+00:00</t>
+          <t>2026-06-23T08:32:44+00:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>171-0025867-6612374</t>
+          <t>404-2029470-0977929</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2540,12 +2540,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7853300</t>
+          <t>LPNDEL4AA3925027</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -2553,32 +2553,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-20T13:05:37+00:00</t>
+          <t>2026-06-23T06:25:18+00:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>402-8590404-8535510</t>
+          <t>408-7120729-6837923</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>LPNMAA4G898204</t>
+          <t>LPNSBOB1385946</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -2609,32 +2609,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-19T14:24:04+00:00</t>
+          <t>2026-06-23T05:29:18+00:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>403-3269966-6849104</t>
+          <t>403-5101653-2865108</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2647,17 +2647,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>LPNHDX8A004693</t>
+          <t>LPNHDX8005941</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2665,32 +2665,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-18T09:53:43+00:00</t>
+          <t>2026-06-22T15:00:37+00:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>408-1513827-8090763</t>
+          <t>408-2886313-6344340</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2708,12 +2708,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2273003</t>
+          <t>LPNSBOB1385291</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -2721,32 +2721,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-18T09:01:23+00:00</t>
+          <t>2026-06-22T15:00:11+00:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>402-6972876-7770702</t>
+          <t>403-4065197-2565940</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FBA76765</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>B0BMQQQ7YD</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>X001O7YYCV</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>White Mulberry Motorized Height Adjustable Sit-Stand Desk | Electronic Height Adjustable | Motor &amp; Memory Preset Controller | Office, Workstation or Home | Carbon Fibre | 120 * 60*H(75-118) cm</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>LPNSPUN58279</t>
+          <t>LPNSBOB1385290</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -2777,32 +2777,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-18T06:34:47+00:00</t>
+          <t>2026-06-22T13:49:32+00:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>171-5595331-6677926</t>
+          <t>171-3328269-2691534</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2810,22 +2810,22 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>LPNSPUN58332</t>
+          <t>LPNBLX1C049419</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2833,12 +2833,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-18T06:13:54+00:00</t>
+          <t>2026-06-22T13:44:52+00:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>405-9716650-4190754</t>
+          <t>407-2806960-6949923</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2866,22 +2866,22 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>LPNSPUN58348</t>
+          <t>LPNBLX1C049418</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -2889,12 +2889,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-18T05:06:11+00:00</t>
+          <t>2026-06-22T12:43:38+00:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>405-0242402-8315559</t>
+          <t>402-2531413-4073130</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>LPNHYD8DY89222</t>
+          <t>LPNHYD8EF41160</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -2945,12 +2945,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-18T03:18:32+00:00</t>
+          <t>2026-06-22T09:02:33+00:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>403-8790017-7829152</t>
+          <t>404-4254275-9061104</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2983,17 +2983,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>LPNHYD8DY89148</t>
+          <t>LPNHYD8ED01352</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3001,12 +3001,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-17T17:18:11+00:00</t>
+          <t>2026-06-22T06:27:11+00:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>408-3294486-3424329</t>
+          <t>407-5289320-1468336</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3034,22 +3034,22 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>LPNCCX1B4206954</t>
+          <t>LPNBLR7Y7287766</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3057,12 +3057,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-17T11:01:26+00:00</t>
+          <t>2026-06-21T15:48:42+00:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>171-3399563-8885966</t>
+          <t>408-1433377-1765942</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3090,22 +3090,22 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>LPNLMAA0019039</t>
+          <t>LPNSBOB1385218</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -3113,12 +3113,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-15T09:24:30+00:00</t>
+          <t>2026-06-21T09:50:13+00:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>171-3194001-5187538</t>
+          <t>405-1204534-8479517</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>LPNHYD8DY92591</t>
+          <t>LPNDEL4AA4027730</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -3169,32 +3169,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-15T08:53:22+00:00</t>
+          <t>2026-06-21T08:35:03+00:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>406-3765893-9779536</t>
+          <t>171-0025867-6612374</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3202,22 +3202,22 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>LPNHDX8A0002233</t>
+          <t>LPNBLR7Y7853300</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3225,12 +3225,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-14T11:15:53+00:00</t>
+          <t>2026-06-20T13:05:37+00:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>171-1282309-9677932</t>
+          <t>402-8590404-8535510</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2198432</t>
+          <t>LPNMAA4G898204</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3281,32 +3281,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-14T06:26:57+00:00</t>
+          <t>2026-06-19T14:24:04+00:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>407-1845667-2313146</t>
+          <t>403-3269966-6849104</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3677498</t>
+          <t>LPNHDX8A004693</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -3337,32 +3337,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-13T12:21:24+00:00</t>
+          <t>2026-06-18T09:53:43+00:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>405-5466299-6857906</t>
+          <t>408-1513827-8090763</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3370,22 +3370,22 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>LPNSBOB1375958</t>
+          <t>LPNMAA4Z2273003</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -3393,32 +3393,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-13T12:20:57+00:00</t>
+          <t>2026-06-18T09:01:23+00:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>404-9976514-7382743</t>
+          <t>402-6972876-7770702</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76765</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BMQQQ7YD</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001O7YYCV</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Motorized Height Adjustable Sit-Stand Desk | Electronic Height Adjustable | Motor &amp; Memory Preset Controller | Office, Workstation or Home | Carbon Fibre | 120 * 60*H(75-118) cm</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3426,22 +3426,22 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>LPNSBOB1375957</t>
+          <t>LPNSPUN58279</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -3449,12 +3449,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-12T11:47:28+00:00</t>
+          <t>2026-06-18T06:34:47+00:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>407-2845785-4936332</t>
+          <t>171-5595331-6677926</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>LPNSHTI00009280</t>
+          <t>LPNSPUN58332</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -3505,32 +3505,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-11T12:39:34+00:00</t>
+          <t>2026-06-18T06:13:54+00:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>405-0836953-9114742</t>
+          <t>405-9716650-4190754</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3538,22 +3538,22 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>LPNHDX8A001607</t>
+          <t>LPNSPUN58348</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -3561,32 +3561,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-11T10:43:03+00:00</t>
+          <t>2026-06-18T05:06:11+00:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>407-7053626-1929962</t>
+          <t>405-0242402-8315559</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FBA79667</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>B0DQPK7MFH</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>X0027512Z1</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk with Shelf|DIY Assembly| Monitor Raising Shelf |Engineered Wood &amp; Sturdy Steel Leg|Perfect for Computer Table Office Home Gaming Study Desk|L(130+130)*45*77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>SCUY</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>LPNSCUY00017897</t>
+          <t>LPNHYD8DY89222</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3617,12 +3617,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-10T22:26:08+00:00</t>
+          <t>2026-06-18T03:18:32+00:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>404-0639682-6860336</t>
+          <t>403-8790017-7829152</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>LPNCX1B4784440</t>
+          <t>LPNHYD8DY89148</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -3673,12 +3673,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-06-10T12:14:02+00:00</t>
+          <t>2026-06-17T17:18:11+00:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>171-1027170-0049924</t>
+          <t>408-3294486-3424329</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>DAMAGED</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2407733</t>
+          <t>LPNCCX1B4206954</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -3729,32 +3729,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-06-10T08:20:03+00:00</t>
+          <t>2026-06-17T11:01:26+00:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>406-6295410-5869130</t>
+          <t>171-3399563-8885966</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3762,22 +3762,22 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>LPNBLX1C159057</t>
+          <t>LPNLMAA0019039</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -3785,12 +3785,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-06-10T05:42:02+00:00</t>
+          <t>2026-06-15T09:24:30+00:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>405-8329990-8940345</t>
+          <t>171-3194001-5187538</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4745942</t>
+          <t>LPNHYD8DY92591</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -3841,32 +3841,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-06-10T04:51:41+00:00</t>
+          <t>2026-06-15T08:53:22+00:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>405-7954322-6131539</t>
+          <t>406-3765893-9779536</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -3874,22 +3874,22 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>LPNBOM5F5675078</t>
+          <t>LPNHDX8A0002233</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -3897,12 +3897,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-06-10T03:51:05+00:00</t>
+          <t>2026-06-14T11:15:53+00:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>407-5527946-4998741</t>
+          <t>171-1282309-9677932</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7287766</t>
+          <t>LPNMAA4Z2198432</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -3953,12 +3953,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-06-08T09:59:30+00:00</t>
+          <t>2026-06-14T06:26:57+00:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>404-4052225-7064331</t>
+          <t>407-1845667-2313146</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3631375</t>
+          <t>LPNDEL4AA3677498</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4009,32 +4009,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-06-08T08:59:50+00:00</t>
+          <t>2026-06-13T12:21:24+00:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>404-3123106-0929939</t>
+          <t>405-5466299-6857906</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FBK76387</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>B0BF4S7V8C</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>X00242V9DH</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | White</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>LPNSPUN56234</t>
+          <t>LPNSBOB1375958</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -4065,32 +4065,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-06-08T08:59:02+00:00</t>
+          <t>2026-06-13T12:20:57+00:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>408-8800113-8391502</t>
+          <t>404-9976514-7382743</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -4098,22 +4098,22 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>LPNSPUN56235</t>
+          <t>LPNSBOB1375957</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -4121,32 +4121,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-06-08T08:43:30+00:00</t>
+          <t>2026-06-12T11:47:28+00:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>407-4254200-0562712</t>
+          <t>407-2845785-4936332</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3631346</t>
+          <t>LPNSHTI00009280</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -4177,32 +4177,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-06-07T16:09:41+00:00</t>
+          <t>2026-06-11T12:39:34+00:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>405-9852474-3831538</t>
+          <t>405-0836953-9114742</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -4210,22 +4210,22 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>LPNCCX1B4179343</t>
+          <t>LPNHDX8A001607</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -4233,32 +4233,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-06-07T11:20:49+00:00</t>
+          <t>2026-06-11T10:43:03+00:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>406-9783608-9093148</t>
+          <t>407-7053626-1929962</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79667</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0DQPK7MFH</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X0027512Z1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
+          <t>White Mulberry L-Shape Corner Desk with Shelf|DIY Assembly| Monitor Raising Shelf |Engineered Wood &amp; Sturdy Steel Leg|Perfect for Computer Table Office Home Gaming Study Desk|L(130+130)*45*77cm|White</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>SCUY</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>LPNLMAA0016237</t>
+          <t>LPNSCUY00017897</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -4289,32 +4289,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-06-07T10:24:17+00:00</t>
+          <t>2026-06-10T22:26:08+00:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>406-6392223-8173930</t>
+          <t>404-0639682-6860336</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -4322,22 +4322,22 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>LPNBLX1C047099</t>
+          <t>LPNCX1B4784440</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -4345,12 +4345,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-06-06T10:45:59+00:00</t>
+          <t>2026-06-10T12:14:02+00:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>406-9111649-3125130</t>
+          <t>171-1027170-0049924</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>LPNBOM5F5579985</t>
+          <t>LPNMAA4Z2407733</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -4401,32 +4401,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-06-05T09:54:50+00:00</t>
+          <t>2026-06-10T08:20:03+00:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>405-7328472-7893901</t>
+          <t>406-6295410-5869130</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -4434,22 +4434,22 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679697</t>
+          <t>LPNBLX1C159057</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -4457,32 +4457,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-06-05T08:35:28+00:00</t>
+          <t>2026-06-10T05:42:02+00:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>404-9218549-9930734</t>
+          <t>405-8329990-8940345</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FBA79659</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>X0026ZDA2F</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, Black, 3 Year Warranty</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>LPNSDEGF082043</t>
+          <t>LPNBLR7Y4745942</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -4513,12 +4513,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-06-05T08:17:03+00:00</t>
+          <t>2026-06-10T04:51:41+00:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>171-6540897-0152357</t>
+          <t>405-7954322-6131539</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4546,22 +4546,22 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679650</t>
+          <t>LPNBOM5F5675078</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -4569,12 +4569,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-06-05T04:33:06+00:00</t>
+          <t>2026-06-10T03:51:05+00:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>171-6354444-3723505</t>
+          <t>407-5527946-4998741</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4602,22 +4602,22 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>LPNBOM5F5574228</t>
+          <t>LPNBLR7Y7287766</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -4625,12 +4625,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-06-05T04:28:18+00:00</t>
+          <t>2026-06-08T09:59:30+00:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>406-6103690-9310748</t>
+          <t>404-4052225-7064331</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679535</t>
+          <t>LPNDEL4AA3631375</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -4681,32 +4681,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-06-04T03:47:36+00:00</t>
+          <t>2026-06-08T08:59:50+00:00</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>406-2278126-7841949</t>
+          <t>404-3123106-0929939</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBK76387</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BF4S7V8C</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00242V9DH</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | White</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -4714,22 +4714,22 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679185</t>
+          <t>LPNSPUN56234</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -4737,32 +4737,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-06-01T09:32:55+00:00</t>
+          <t>2026-06-08T08:59:02+00:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>402-3794541-2581168</t>
+          <t>408-8800113-8391502</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -4770,22 +4770,22 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4743333</t>
+          <t>LPNSPUN56235</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -4793,12 +4793,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-06-01T04:42:36+00:00</t>
+          <t>2026-06-08T08:43:30+00:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>408-0143238-4374708</t>
+          <t>407-4254200-0562712</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>LPNBOM5F5524445</t>
+          <t>LPNDEL4AA3631346</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -4849,12 +4849,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-06-01T03:58:27+00:00</t>
+          <t>2026-06-07T16:09:41+00:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>406-4355667-6072332</t>
+          <t>405-9852474-3831538</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4882,22 +4882,22 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4743158</t>
+          <t>LPNCCX1B4179343</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -4905,32 +4905,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-31T09:10:34+00:00</t>
+          <t>2026-06-07T11:20:49+00:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>404-2518539-4406712</t>
+          <t>406-9783608-9093148</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -4938,22 +4938,22 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3976607</t>
+          <t>LPNLMAA0016237</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -4961,32 +4961,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-30T22:18:28+00:00</t>
+          <t>2026-06-07T10:24:17+00:00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>407-1474707-0478726</t>
+          <t>406-6392223-8173930</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>LPNCCX1B4554643</t>
+          <t>LPNBLX1C047099</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -5017,12 +5017,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-30T04:13:42+00:00</t>
+          <t>2026-06-06T10:45:59+00:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>406-7941139-9225906</t>
+          <t>406-9111649-3125130</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5055,17 +5055,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>LPNBOM5F5507643</t>
+          <t>LPNBOM5F5579985</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -5073,12 +5073,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-29T23:01:15+00:00</t>
+          <t>2026-06-05T09:54:50+00:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>405-0096078-8521126</t>
+          <t>405-7328472-7893901</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>LPNCCX1B2941120</t>
+          <t>LPNDEL4AA3679697</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -5129,32 +5129,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-29T15:27:20+00:00</t>
+          <t>2026-06-05T08:35:28+00:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>404-8418070-5981124</t>
+          <t>404-9218549-9930734</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79659</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZDA2F</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, Black, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>LPNCCX1B4508596</t>
+          <t>LPNSDEGF082043</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -5185,12 +5185,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-29T05:18:33+00:00</t>
+          <t>2026-06-05T08:17:03+00:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>171-0407209-4266756</t>
+          <t>171-6540897-0152357</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937926</t>
+          <t>LPNDEL4AA3679650</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -5241,12 +5241,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-28T11:56:49+00:00</t>
+          <t>2026-06-05T04:33:06+00:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>407-4902279-0189155</t>
+          <t>171-6354444-3723505</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5274,22 +5274,22 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7363000</t>
+          <t>LPNBOM5F5574228</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -5297,12 +5297,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-28T08:40:02+00:00</t>
+          <t>2026-06-05T04:28:18+00:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>408-1128142-0248321</t>
+          <t>406-6103690-9310748</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>DAMAGED_BY_FC</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937756</t>
+          <t>LPNDEL4AA3679535</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -5353,12 +5353,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-28T06:36:17+00:00</t>
+          <t>2026-06-04T03:47:36+00:00</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>402-4776409-4471512</t>
+          <t>406-2278126-7841949</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5396,12 +5396,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7286354</t>
+          <t>LPNDEL4AA3679185</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -5409,12 +5409,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-27T12:42:16+00:00</t>
+          <t>2026-06-01T09:32:55+00:00</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>404-6762038-7137955</t>
+          <t>402-3794541-2581168</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937575</t>
+          <t>LPNBLR7Y4743333</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -5465,12 +5465,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-27T09:44:17+00:00</t>
+          <t>2026-06-01T04:42:36+00:00</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>403-3444915-0085109</t>
+          <t>408-0143238-4374708</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7362686</t>
+          <t>LPNBOM5F5524445</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -5521,32 +5521,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-27T09:25:47+00:00</t>
+          <t>2026-06-01T03:58:27+00:00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>405-8410325-7933918</t>
+          <t>406-4355667-6072332</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -5554,22 +5554,22 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>LPNSPUN53913</t>
+          <t>LPNBLR7Y4743158</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -5577,12 +5577,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-26T23:02:43+00:00</t>
+          <t>2026-05-31T09:10:34+00:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>407-0645348-4574732</t>
+          <t>404-2518539-4406712</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5620,12 +5620,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>LPNCCX1B5292913</t>
+          <t>LPNDEL4AA3976607</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -5633,12 +5633,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-26T11:06:29+00:00</t>
+          <t>2026-05-30T22:18:28+00:00</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>402-2949127-9513917</t>
+          <t>407-1474707-0478726</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937227</t>
+          <t>LPNCCX1B4554643</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -5689,12 +5689,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-26T08:48:10+00:00</t>
+          <t>2026-05-30T04:13:42+00:00</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>403-5510263-6469912</t>
+          <t>406-7941139-9225906</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273675</t>
+          <t>LPNBOM5F5507643</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -5745,12 +5745,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-25T15:22:25+00:00</t>
+          <t>2026-05-29T23:01:15+00:00</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>402-5203149-1906724</t>
+          <t>405-0096078-8521126</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>LPNCCX1B5331017</t>
+          <t>LPNCCX1B2941120</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -5801,12 +5801,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-24T09:24:39+00:00</t>
+          <t>2026-05-29T15:27:20+00:00</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>171-7709339-0701117</t>
+          <t>404-8418070-5981124</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5844,12 +5844,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273169</t>
+          <t>LPNCCX1B4508596</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -5857,12 +5857,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-24T08:29:52+00:00</t>
+          <t>2026-05-29T05:18:33+00:00</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>406-7042486-7436314</t>
+          <t>171-0407209-4266756</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5890,22 +5890,22 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273150</t>
+          <t>LPNDEL4AA3937926</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -5913,32 +5913,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-23T23:07:27+00:00</t>
+          <t>2026-05-28T11:56:49+00:00</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>406-2954542-5857925</t>
+          <t>407-4902279-0189155</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>LPNSBOB1370158</t>
+          <t>LPNBLR7Y7363000</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -5969,12 +5969,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-23T10:58:04+00:00</t>
+          <t>2026-05-28T08:40:02+00:00</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>406-4758725-2077907</t>
+          <t>408-1128142-0248321</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DAMAGED_BY_FC</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7272896</t>
+          <t>LPNDEL4AA3937756</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -6025,32 +6025,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-22T09:58:26+00:00</t>
+          <t>2026-05-28T06:36:17+00:00</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>403-7800011-6937966</t>
+          <t>402-4776409-4471512</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>LPNSDEGF010003</t>
+          <t>LPNBLR7Y7286354</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -6081,32 +6081,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-21T04:38:32+00:00</t>
+          <t>2026-05-27T12:42:16+00:00</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>403-2400247-1930753</t>
+          <t>404-6762038-7137955</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>LPNSDEGF099136</t>
+          <t>LPNDEL4AA3937575</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -6137,12 +6137,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-20T11:30:45+00:00</t>
+          <t>2026-05-27T09:44:17+00:00</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>406-2648444-6601917</t>
+          <t>403-3444915-0085109</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2147464</t>
+          <t>LPNBLR7Y7362686</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -6193,32 +6193,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-19T08:03:32+00:00</t>
+          <t>2026-05-27T09:25:47+00:00</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>405-4744559-6958733</t>
+          <t>405-8410325-7933918</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -6226,22 +6226,22 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>LPNSDEGF097985</t>
+          <t>LPNSPUN53913</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -6249,32 +6249,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-18T11:36:05+00:00</t>
+          <t>2026-05-26T23:02:43+00:00</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>171-1585723-0908356</t>
+          <t>407-0645348-4574732</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -6282,22 +6282,22 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>LPNBLX1C155145</t>
+          <t>LPNCCX1B5292913</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -6305,32 +6305,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-15T08:29:30+00:00</t>
+          <t>2026-05-26T11:06:29+00:00</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>402-4856546-1261939</t>
+          <t>402-2949127-9513917</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>LPNSDEGF074601</t>
+          <t>LPNDEL4AA3937227</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -6361,32 +6361,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-13T13:50:43+00:00</t>
+          <t>2026-05-26T08:48:10+00:00</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>403-7495250-9937954</t>
+          <t>403-5510263-6469912</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -6394,22 +6394,22 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>LPNBLX1C154096</t>
+          <t>LPNBLR7Y7273675</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -6417,32 +6417,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-12T07:19:54+00:00</t>
+          <t>2026-05-25T15:22:25+00:00</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>408-0473775-6641108</t>
+          <t>402-5203149-1906724</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -6450,22 +6450,22 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>LPNSBOB1362246</t>
+          <t>LPNCCX1B5331017</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -6473,32 +6473,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-11T10:31:39+00:00</t>
+          <t>2026-05-24T09:24:39+00:00</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>404-1750959-8518722</t>
+          <t>171-7709339-0701117</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>LPNSHTI00006165</t>
+          <t>LPNBLR7Y7273169</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -6529,12 +6529,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-10T09:15:43+00:00</t>
+          <t>2026-05-24T08:29:52+00:00</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>402-1548587-3227555</t>
+          <t>406-7042486-7436314</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6562,22 +6562,22 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>LPNBOM5F5057136</t>
+          <t>LPNBLR7Y7273150</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -6585,32 +6585,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-08T15:43:17+00:00</t>
+          <t>2026-05-23T23:07:27+00:00</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>402-8374307-7441113</t>
+          <t>406-2954542-5857925</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>LPNSDEGF064205</t>
+          <t>LPNSBOB1370158</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -6641,32 +6641,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-08T13:25:23+00:00</t>
+          <t>2026-05-23T10:58:04+00:00</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>171-7381542-8368365</t>
+          <t>406-4758725-2077907</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -6674,22 +6674,22 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>LPNBLX1C042486</t>
+          <t>LPNBLR7Y7272896</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -6697,32 +6697,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-08T07:49:38+00:00</t>
+          <t>2026-05-22T09:58:26+00:00</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>403-3056736-6311553</t>
+          <t>403-7800011-6937966</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5321963</t>
+          <t>LPNSDEGF010003</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
@@ -6753,12 +6753,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-06T06:52:28+00:00</t>
+          <t>2026-05-21T04:38:32+00:00</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>403-2654029-0716338</t>
+          <t>403-2400247-1930753</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>LPNSHTI00005958</t>
+          <t>LPNSDEGF099136</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -6809,12 +6809,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-06T05:51:00+00:00</t>
+          <t>2026-05-20T11:30:45+00:00</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>404-9426288-6037168</t>
+          <t>406-2648444-6601917</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6842,22 +6842,22 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>LPNBOM5F5236158</t>
+          <t>LPNDEL4AA2147464</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
@@ -6865,32 +6865,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-02T04:54:42+00:00</t>
+          <t>2026-05-19T08:03:32+00:00</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>407-6201969-2856316</t>
+          <t>405-4744559-6958733</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -6898,22 +6898,22 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>LPNLMAA0004457</t>
+          <t>LPNSDEGF097985</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -6921,32 +6921,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-28T08:52:43+00:00</t>
+          <t>2026-05-18T11:36:05+00:00</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>171-6713241-8377149</t>
+          <t>171-1585723-0908356</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>LPNLMAA0003844</t>
+          <t>LPNBLX1C155145</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -6977,32 +6977,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-27T06:04:11+00:00</t>
+          <t>2026-05-15T08:29:30+00:00</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>403-6021111-3520325</t>
+          <t>402-4856546-1261939</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>LPNLMAA0003335</t>
+          <t>LPNSDEGF074601</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -7033,32 +7033,32 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-26T08:09:27+00:00</t>
+          <t>2026-05-13T13:50:43+00:00</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>402-4881396-1030704</t>
+          <t>403-7495250-9937954</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2253845</t>
+          <t>LPNBLX1C154096</t>
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
@@ -7089,32 +7089,32 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-26T04:14:08+00:00</t>
+          <t>2026-05-12T07:19:54+00:00</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>408-1134010-7973925</t>
+          <t>408-0473775-6641108</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -7122,12 +7122,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5321963</t>
+          <t>LPNSBOB1362246</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -7145,12 +7145,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-26T03:22:50+00:00</t>
+          <t>2026-05-11T10:31:39+00:00</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>406-9614580-4613163</t>
+          <t>404-1750959-8518722</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>LPNSPUN46511</t>
+          <t>LPNSHTI00006165</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -7201,32 +7201,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-25T05:33:44+00:00</t>
+          <t>2026-05-10T09:15:43+00:00</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>171-3077342-1790757</t>
+          <t>402-1548587-3227555</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>LPNLMAA0002840</t>
+          <t>LPNBOM5F5057136</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -7257,32 +7257,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-25T03:48:59+00:00</t>
+          <t>2026-05-08T15:43:17+00:00</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>404-4908572-3783532</t>
+          <t>402-8374307-7441113</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>X002FOAUSJ</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -7290,22 +7290,22 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>LPNBLR7Y6090385</t>
+          <t>LPNSDEGF064205</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
@@ -7313,32 +7313,32 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-22T10:55:13+00:00</t>
+          <t>2026-05-08T13:25:23+00:00</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>407-4868470-8499505</t>
+          <t>171-7381542-8368365</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -7346,22 +7346,22 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>LPNLMAA0001354</t>
+          <t>LPNBLX1C042486</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -7369,32 +7369,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-22T04:17:57+00:00</t>
+          <t>2026-05-08T07:49:38+00:00</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>406-5030280-5555520</t>
+          <t>403-3056736-6311553</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -7402,22 +7402,22 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>LPNSDEGF117193</t>
+          <t>LPNBLR7Y5321963</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -7425,32 +7425,32 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-21T20:42:51+00:00</t>
+          <t>2026-05-06T06:52:28+00:00</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>403-7744956-9735520</t>
+          <t>403-2654029-0716338</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>LPNCCX1B1519621</t>
+          <t>LPNSHTI00005958</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -7481,32 +7481,32 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-20T05:04:40+00:00</t>
+          <t>2026-05-06T05:51:00+00:00</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>171-5598784-9947515</t>
+          <t>404-9426288-6037168</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>X002FOAUSJ</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5552415</t>
+          <t>LPNBOM5F5236158</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -7537,32 +7537,32 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-18T05:41:14+00:00</t>
+          <t>2026-05-02T04:54:42+00:00</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>404-0309463-1310709</t>
+          <t>407-6201969-2856316</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -7570,22 +7570,22 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>LPNDEL4AA0788989</t>
+          <t>LPNLMAA0004457</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -7593,32 +7593,32 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-15T13:55:57+00:00</t>
+          <t>2026-04-28T08:52:43+00:00</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>407-7885481-2445152</t>
+          <t>171-6713241-8377149</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>SMAB</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>LPNSMAB1153810</t>
+          <t>LPNLMAA0003844</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -7649,12 +7649,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-15T08:47:44+00:00</t>
+          <t>2026-04-27T06:04:11+00:00</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>407-3585151-4323522</t>
+          <t>403-6021111-3520325</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7682,22 +7682,22 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>LPNSDEGF027993</t>
+          <t>LPNLMAA0003335</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -7705,32 +7705,32 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-04-12T10:47:54+00:00</t>
+          <t>2026-04-26T08:09:27+00:00</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>407-0802588-3857957</t>
+          <t>402-4881396-1030704</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>LPNSDEGF026167</t>
+          <t>LPNDEL4AA2253845</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -7761,32 +7761,32 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-04-11T06:17:07+00:00</t>
+          <t>2026-04-26T04:14:08+00:00</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>408-2417441-1123516</t>
+          <t>408-1134010-7973925</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>FBK76764</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>B0BMV1WPHL</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>X00242TZTH</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>White Mulberry Ergonomic Sit Stand Desk | Standing Desk for Office, Home &amp; Study | Everyday Ergonomic Desk | 1200mm x 600mm | Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -7794,12 +7794,12 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>LPNSHTI00004704</t>
+          <t>LPNBLR7Y5321963</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -7817,32 +7817,32 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-04-09T03:38:39+00:00</t>
+          <t>2026-04-26T03:22:50+00:00</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>406-0798045-4525148</t>
+          <t>406-9614580-4613163</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>LPNSDEGF168570</t>
+          <t>LPNSPUN46511</t>
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
@@ -7873,32 +7873,32 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-04-08T10:17:09+00:00</t>
+          <t>2026-04-25T05:33:44+00:00</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>406-3115014-9939528</t>
+          <t>171-3077342-1790757</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -7906,22 +7906,22 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2155169</t>
+          <t>LPNLMAA0002840</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
@@ -7929,32 +7929,32 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-04-08T09:53:57+00:00</t>
+          <t>2026-04-25T03:48:59+00:00</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>403-7697438-5361950</t>
+          <t>404-4908572-3783532</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X002FOAUSJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>LPNMAA4Z0044638</t>
+          <t>LPNBLR7Y6090385</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -7985,32 +7985,32 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-04-07T23:27:35+00:00</t>
+          <t>2026-04-22T10:55:13+00:00</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>402-3182844-0423531</t>
+          <t>407-4868470-8499505</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>NO_REASON_GIVEN</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>LPNCCX1B1676425</t>
+          <t>LPNLMAA0001354</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -8041,32 +8041,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-04-07T08:05:07+00:00</t>
+          <t>2026-04-22T04:17:57+00:00</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>404-2599173-5513112</t>
+          <t>406-5030280-5555520</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>LPNBLX1C066978</t>
+          <t>LPNSDEGF117193</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
@@ -8097,12 +8097,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-04-06T21:28:06+00:00</t>
+          <t>2026-04-21T20:42:51+00:00</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>408-0894434-7394724</t>
+          <t>403-7744956-9735520</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8135,17 +8135,17 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>LPNCCX1B1676919</t>
+          <t>LPNCCX1B1519621</t>
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
@@ -8153,32 +8153,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-04-06T19:49:19+00:00</t>
+          <t>2026-04-20T05:04:40+00:00</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>402-0299451-2765120</t>
+          <t>171-5598784-9947515</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X002FOAUSJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -8186,22 +8186,22 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>LPNCCX1B2787065</t>
+          <t>LPNBLR7Y5552415</t>
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
@@ -8209,12 +8209,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-04-06T09:26:15+00:00</t>
+          <t>2026-04-18T05:41:14+00:00</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>402-1769603-3523555</t>
+          <t>404-0309463-1310709</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>LPNMAA4Z0044156</t>
+          <t>LPNDEL4AA0788989</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
@@ -8265,32 +8265,32 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-04-06T08:31:32+00:00</t>
+          <t>2026-04-15T13:55:57+00:00</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>408-6381953-4631553</t>
+          <t>407-7885481-2445152</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -8298,22 +8298,22 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>SMAB</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>LPNSPUN45721</t>
+          <t>LPNSMAB1153810</t>
         </is>
       </c>
       <c r="L141" t="inlineStr"/>
@@ -8321,58 +8321,394 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-04-05T06:19:10+00:00</t>
+          <t>2026-04-15T08:47:44+00:00</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>408-5061007-8220304</t>
+          <t>407-3585151-4323522</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
+          <t>FBA76417</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>X001MZZQ8V</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>SDEG</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>CUSTOMER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>DEFECTIVE</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>LPNSDEGF027993</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-04-12T10:47:54+00:00</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>407-0802588-3857957</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>FBA76415</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>X001MZYX7L</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>SDEG</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>SELLABLE</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>UNDELIVERABLE_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>LPNSDEGF026167</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-04-11T06:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>408-2417441-1123516</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>FBK76764</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>B0BMV1WPHL</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>X00242TZTH</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>White Mulberry Ergonomic Sit Stand Desk | Standing Desk for Office, Home &amp; Study | Everyday Ergonomic Desk | 1200mm x 600mm | Carbon Fibre</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>SHTI</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>CARRIER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>QUALITY_UNACCEPTABLE</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>LPNSHTI00004704</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-04-09T03:38:39+00:00</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>406-0798045-4525148</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>FBA79662</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>B0DQ4YWSMC</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>X00270AW07</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>SDEG</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>CARRIER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>MISORDERED</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>LPNSDEGF168570</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-04-08T10:17:09+00:00</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>406-3115014-9939528</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
           <t>FBA79167</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>B0CPFS24ML</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E146" t="inlineStr">
         <is>
           <t>X001Y5UYX1</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F146" t="inlineStr">
         <is>
           <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
-      <c r="G142" t="n">
-        <v>1</v>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>BLR7</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>DEL4</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
         <is>
           <t>SELLABLE</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>NOT_COMPATIBLE</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>LPNBLR7Y6062118</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr"/>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>UNDELIVERABLE_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>LPNDEL4AA2155169</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-04-08T09:53:57+00:00</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>403-7697438-5361950</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>FBA79167</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>X001Y5UYX1</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>MAA4</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>CARRIER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>UNDELIVERABLE_REFUSED</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>LPNMAA4Z0044638</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-04-07T23:27:35+00:00</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>402-3182844-0423531</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>FBA79167</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>X001Y5UYX1</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>CCX1</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>SELLABLE</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>NO_REASON_GIVEN</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>LPNCCX1B1676425</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/raw/returns/WhiteMulberry.xlsx
+++ b/data/raw/returns/WhiteMulberry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L148"/>
+  <dimension ref="A1:L149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06T12:33:49+00:00</t>
+          <t>2026-07-06T21:23:52+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>404-5401376-5513111</t>
+          <t>406-6590377-2621105</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -514,22 +514,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>LPNHYD8EJ59560</t>
+          <t>LPNBLR8Z4815212</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -537,12 +537,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-05T20:21:02+00:00</t>
+          <t>2026-07-06T21:22:13+00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>408-9802796-1211539</t>
+          <t>407-1625560-1723518</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>LPNCCX1A8722775</t>
+          <t>LPNBLR8Z4815211</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -593,12 +593,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-05T07:23:15+00:00</t>
+          <t>2026-07-06T12:33:49+00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>407-2308442-1499512</t>
+          <t>404-5401376-5513111</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,22 +626,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4813630</t>
+          <t>LPNHYD8EJ59560</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -649,12 +649,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-05T06:48:36+00:00</t>
+          <t>2026-07-05T20:21:02+00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>407-8970250-4543519</t>
+          <t>408-9802796-1211539</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4814250</t>
+          <t>LPNCCX1A8722775</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -705,12 +705,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-05T04:41:04+00:00</t>
+          <t>2026-07-05T07:23:15+00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>405-1245096-1377920</t>
+          <t>407-2308442-1499512</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LPNBOM5F5826513</t>
+          <t>LPNBLR8Z4813630</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -761,12 +761,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-04T12:12:23+00:00</t>
+          <t>2026-07-05T06:48:36+00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>404-7913029-6157962</t>
+          <t>407-8970250-4543519</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LPNHYD8EJ58729</t>
+          <t>LPNBLR8Z4814250</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -817,12 +817,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-04T08:48:05+00:00</t>
+          <t>2026-07-05T04:41:04+00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>405-3423037-8257160</t>
+          <t>405-1245096-1377920</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -850,22 +850,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>DAMAGED_BY_FC</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3108992</t>
+          <t>LPNBOM5F5826513</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -873,12 +873,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-04T04:21:28+00:00</t>
+          <t>2026-07-04T12:12:23+00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>405-3646440-7662737</t>
+          <t>404-7913029-6157962</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>LPNBOM5F5455146</t>
+          <t>LPNHYD8EJ58729</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -929,12 +929,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-03T19:29:57+00:00</t>
+          <t>2026-07-04T08:48:05+00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>403-0547582-3197132</t>
+          <t>405-3423037-8257160</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -962,22 +962,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DAMAGED_BY_FC</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>LPNCCX1B4102605</t>
+          <t>LPNDEL4AA3108992</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -985,32 +985,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-03T14:02:46+00:00</t>
+          <t>2026-07-04T04:21:28+00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>171-7464293-7220360</t>
+          <t>405-3646440-7662737</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1018,22 +1018,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>NO_REASON_GIVEN</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>LPNSBOB1392052</t>
+          <t>LPNBOM5F5455146</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1041,12 +1041,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-03T11:38:57+00:00</t>
+          <t>2026-07-03T19:29:57+00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>403-6645337-2467540</t>
+          <t>403-0547582-3197132</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2082724</t>
+          <t>LPNCCX1B4102605</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1097,32 +1097,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-02T17:30:33+00:00</t>
+          <t>2026-07-03T14:02:46+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>402-1004506-0818747</t>
+          <t>171-7464293-7220360</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1130,22 +1130,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NO_REASON_GIVEN</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>LPNBLR8Z5514346</t>
+          <t>LPNSBOB1392052</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1153,12 +1153,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-02T14:56:15+00:00</t>
+          <t>2026-07-03T11:38:57+00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>407-7003476-1816350</t>
+          <t>403-6645337-2467540</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>NO_REASON_GIVEN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3108265</t>
+          <t>LPNDEL4AA2082724</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1209,12 +1209,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-02T11:24:54+00:00</t>
+          <t>2026-07-02T17:30:33+00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>408-9621782-0261114</t>
+          <t>402-1004506-0818747</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3950616</t>
+          <t>LPNBLR8Z5514346</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1265,12 +1265,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-02T06:41:10+00:00</t>
+          <t>2026-07-02T14:56:15+00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>403-6072724-5581966</t>
+          <t>407-7003476-1816350</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>NO_REASON_GIVEN</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4303742</t>
+          <t>LPNDEL4AA3108265</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1321,12 +1321,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-01T22:20:26+00:00</t>
+          <t>2026-07-02T11:24:54+00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>402-4598141-9561917</t>
+          <t>408-9621782-0261114</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1364,12 +1364,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>LPNCCX1B4170658</t>
+          <t>LPNDEL4AA3950616</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1377,32 +1377,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-01T15:09:10+00:00</t>
+          <t>2026-07-02T06:41:10+00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>402-3081497-7409144</t>
+          <t>403-6072724-5581966</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1410,22 +1410,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>LPNBLX1C093497</t>
+          <t>LPNBLR8Z4303742</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1433,12 +1433,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-01T09:24:20+00:00</t>
+          <t>2026-07-01T22:20:26+00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>405-3824107-9644368</t>
+          <t>402-4598141-9561917</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>LPNBOM5F5465051</t>
+          <t>LPNCCX1B4170658</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1489,32 +1489,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-01T06:49:32+00:00</t>
+          <t>2026-07-01T15:09:10+00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>404-6104605-6788338</t>
+          <t>402-3081497-7409144</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1522,22 +1522,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>LPNBOM5F5435891</t>
+          <t>LPNBLX1C093497</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1545,12 +1545,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-01T05:46:54+00:00</t>
+          <t>2026-07-01T09:24:20+00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>407-2497737-1874765</t>
+          <t>405-3824107-9644368</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1588,12 +1588,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>LPNBOM5F5407228</t>
+          <t>LPNBOM5F5465051</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1601,12 +1601,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-01T03:55:07+00:00</t>
+          <t>2026-07-01T06:49:32+00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>403-6044286-1801115</t>
+          <t>404-6104605-6788338</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>CCX2</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>LPNCCX2B2262224</t>
+          <t>LPNBOM5F5435891</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1657,12 +1657,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-29T12:22:41+00:00</t>
+          <t>2026-07-01T05:46:54+00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>405-6904525-0069903</t>
+          <t>407-2497737-1874765</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1690,22 +1690,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>LPNHYD8EF20503</t>
+          <t>LPNBOM5F5407228</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1713,12 +1713,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-28T19:38:03+00:00</t>
+          <t>2026-07-01T03:55:07+00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>402-4296829-1337133</t>
+          <t>403-6044286-1801115</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>CCX2</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>LPNCCX1B2440445</t>
+          <t>LPNCCX2B2262224</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1769,12 +1769,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-28T08:39:43+00:00</t>
+          <t>2026-06-29T12:22:41+00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>402-6090489-2032337</t>
+          <t>405-6904525-0069903</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7855923</t>
+          <t>LPNHYD8EF20503</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1825,12 +1825,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-27T11:00:01+00:00</t>
+          <t>2026-06-28T19:38:03+00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>408-3896665-0021948</t>
+          <t>402-4296829-1337133</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1858,22 +1858,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7855626</t>
+          <t>LPNCCX1B2440445</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1881,32 +1881,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-27T10:32:22+00:00</t>
+          <t>2026-06-28T08:39:43+00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>407-5462207-4616334</t>
+          <t>402-6090489-2032337</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1914,22 +1914,22 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>LPNSBOB1388621</t>
+          <t>LPNBLR7Y7855923</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1937,32 +1937,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-26T18:08:18+00:00</t>
+          <t>2026-06-27T11:00:01+00:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>171-5586406-9945900</t>
+          <t>408-3896665-0021948</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1970,22 +1970,22 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>LPNSBOB1388302</t>
+          <t>LPNBLR7Y7855626</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -1993,32 +1993,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-26T06:57:42+00:00</t>
+          <t>2026-06-27T10:32:22+00:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>405-2746376-7486724</t>
+          <t>407-5462207-4616334</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2026,22 +2026,22 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>LPNBLX1C140655</t>
+          <t>LPNSBOB1388621</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2049,32 +2049,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-26T05:19:18+00:00</t>
+          <t>2026-06-26T18:08:18+00:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>406-4442109-5330751</t>
+          <t>171-5586406-9945900</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2082,22 +2082,22 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3990308</t>
+          <t>LPNSBOB1388302</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2105,12 +2105,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-25T18:24:43+00:00</t>
+          <t>2026-06-26T06:57:42+00:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>405-2433007-9289947</t>
+          <t>405-2746376-7486724</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2138,22 +2138,22 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>LPNSBOB1387687</t>
+          <t>LPNBLX1C140655</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2161,12 +2161,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-25T10:05:58+00:00</t>
+          <t>2026-06-26T05:19:18+00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>407-3034951-4675566</t>
+          <t>406-4442109-5330751</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2273850</t>
+          <t>LPNDEL4AA3990308</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2217,32 +2217,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-24T08:29:31+00:00</t>
+          <t>2026-06-25T18:24:43+00:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>402-0120877-0312362</t>
+          <t>405-2433007-9289947</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2250,22 +2250,22 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>LPNSPUN59333</t>
+          <t>LPNSBOB1387687</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2273,12 +2273,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-24T06:17:22+00:00</t>
+          <t>2026-06-25T10:05:58+00:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>403-8864299-1768360</t>
+          <t>407-3034951-4675566</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2306,22 +2306,22 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7854241</t>
+          <t>LPNMAA4Z2273850</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2329,32 +2329,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-23T15:36:47+00:00</t>
+          <t>2026-06-24T08:29:31+00:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>402-8717460-5700310</t>
+          <t>402-0120877-0312362</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>LPNHDX8A005873</t>
+          <t>LPNSPUN59333</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2385,12 +2385,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-23T11:54:27+00:00</t>
+          <t>2026-06-24T06:17:22+00:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>403-7688253-5273167</t>
+          <t>403-8864299-1768360</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2418,22 +2418,22 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>LPNBOM5F5694482</t>
+          <t>LPNBLR7Y7854241</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2441,32 +2441,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-23T09:27:19+00:00</t>
+          <t>2026-06-23T15:36:47+00:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>408-9857262-4357961</t>
+          <t>402-8717460-5700310</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2474,22 +2474,22 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7853975</t>
+          <t>LPNHDX8A005873</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2497,12 +2497,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-23T08:32:44+00:00</t>
+          <t>2026-06-23T11:54:27+00:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>404-2029470-0977929</t>
+          <t>403-7688253-5273167</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2540,12 +2540,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3925027</t>
+          <t>LPNBOM5F5694482</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -2553,32 +2553,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-23T06:25:18+00:00</t>
+          <t>2026-06-23T09:27:19+00:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>408-7120729-6837923</t>
+          <t>408-9857262-4357961</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>LPNSBOB1385946</t>
+          <t>LPNBLR7Y7853975</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -2609,32 +2609,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-23T05:29:18+00:00</t>
+          <t>2026-06-23T08:32:44+00:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>403-5101653-2865108</t>
+          <t>404-2029470-0977929</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2642,22 +2642,22 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>LPNHDX8005941</t>
+          <t>LPNDEL4AA3925027</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2665,32 +2665,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-22T15:00:37+00:00</t>
+          <t>2026-06-23T06:25:18+00:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>408-2886313-6344340</t>
+          <t>408-7120729-6837923</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2703,17 +2703,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>LPNSBOB1385291</t>
+          <t>LPNSBOB1385946</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -2721,32 +2721,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-22T15:00:11+00:00</t>
+          <t>2026-06-23T05:29:18+00:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>403-4065197-2565940</t>
+          <t>403-5101653-2865108</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>LPNSBOB1385290</t>
+          <t>LPNHDX8005941</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -2777,32 +2777,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-22T13:49:32+00:00</t>
+          <t>2026-06-22T15:00:37+00:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>171-3328269-2691534</t>
+          <t>408-2886313-6344340</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2810,22 +2810,22 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>LPNBLX1C049419</t>
+          <t>LPNSBOB1385291</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2833,32 +2833,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-22T13:44:52+00:00</t>
+          <t>2026-06-22T15:00:11+00:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>407-2806960-6949923</t>
+          <t>403-4065197-2565940</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>LPNBLX1C049418</t>
+          <t>LPNSBOB1385290</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -2889,32 +2889,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-22T12:43:38+00:00</t>
+          <t>2026-06-22T13:49:32+00:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>402-2531413-4073130</t>
+          <t>171-3328269-2691534</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>LPNHYD8EF41160</t>
+          <t>LPNBLX1C049419</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -2945,32 +2945,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-22T09:02:33+00:00</t>
+          <t>2026-06-22T13:44:52+00:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>404-4254275-9061104</t>
+          <t>407-2806960-6949923</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2978,22 +2978,22 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>LPNHYD8ED01352</t>
+          <t>LPNBLX1C049418</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3001,12 +3001,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-22T06:27:11+00:00</t>
+          <t>2026-06-22T12:43:38+00:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>407-5289320-1468336</t>
+          <t>402-2531413-4073130</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7287766</t>
+          <t>LPNHYD8EF41160</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3057,32 +3057,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-21T15:48:42+00:00</t>
+          <t>2026-06-22T09:02:33+00:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>408-1433377-1765942</t>
+          <t>404-4254275-9061104</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3090,22 +3090,22 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>LPNSBOB1385218</t>
+          <t>LPNHYD8ED01352</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -3113,12 +3113,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-21T09:50:13+00:00</t>
+          <t>2026-06-22T06:27:11+00:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>405-1204534-8479517</t>
+          <t>407-5289320-1468336</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3146,22 +3146,22 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>LPNDEL4AA4027730</t>
+          <t>LPNBLR7Y7287766</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -3169,32 +3169,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-21T08:35:03+00:00</t>
+          <t>2026-06-21T15:48:42+00:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>171-0025867-6612374</t>
+          <t>408-1433377-1765942</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3202,22 +3202,22 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7853300</t>
+          <t>LPNSBOB1385218</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3225,12 +3225,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-20T13:05:37+00:00</t>
+          <t>2026-06-21T09:50:13+00:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>402-8590404-8535510</t>
+          <t>405-1204534-8479517</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>LPNMAA4G898204</t>
+          <t>LPNDEL4AA4027730</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3281,32 +3281,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-19T14:24:04+00:00</t>
+          <t>2026-06-21T08:35:03+00:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>403-3269966-6849104</t>
+          <t>171-0025867-6612374</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>LPNHDX8A004693</t>
+          <t>LPNBLR7Y7853300</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -3337,12 +3337,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-18T09:53:43+00:00</t>
+          <t>2026-06-20T13:05:37+00:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>408-1513827-8090763</t>
+          <t>402-8590404-8535510</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3375,17 +3375,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2273003</t>
+          <t>LPNMAA4G898204</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -3393,32 +3393,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-18T09:01:23+00:00</t>
+          <t>2026-06-19T14:24:04+00:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>402-6972876-7770702</t>
+          <t>403-3269966-6849104</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FBA76765</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B0BMQQQ7YD</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>X001O7YYCV</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>White Mulberry Motorized Height Adjustable Sit-Stand Desk | Electronic Height Adjustable | Motor &amp; Memory Preset Controller | Office, Workstation or Home | Carbon Fibre | 120 * 60*H(75-118) cm</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3426,22 +3426,22 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>LPNSPUN58279</t>
+          <t>LPNHDX8A004693</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -3449,32 +3449,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-18T06:34:47+00:00</t>
+          <t>2026-06-18T09:53:43+00:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>171-5595331-6677926</t>
+          <t>408-1513827-8090763</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3482,22 +3482,22 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>LPNSPUN58332</t>
+          <t>LPNMAA4Z2273003</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -3505,32 +3505,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-18T06:13:54+00:00</t>
+          <t>2026-06-18T09:01:23+00:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>405-9716650-4190754</t>
+          <t>402-6972876-7770702</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76765</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BMQQQ7YD</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001O7YYCV</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Motorized Height Adjustable Sit-Stand Desk | Electronic Height Adjustable | Motor &amp; Memory Preset Controller | Office, Workstation or Home | Carbon Fibre | 120 * 60*H(75-118) cm</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>LPNSPUN58348</t>
+          <t>LPNSPUN58279</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -3561,32 +3561,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-18T05:06:11+00:00</t>
+          <t>2026-06-18T06:34:47+00:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>405-0242402-8315559</t>
+          <t>171-5595331-6677926</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>LPNHYD8DY89222</t>
+          <t>LPNSPUN58332</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3617,32 +3617,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-18T03:18:32+00:00</t>
+          <t>2026-06-18T06:13:54+00:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>403-8790017-7829152</t>
+          <t>405-9716650-4190754</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>LPNHYD8DY89148</t>
+          <t>LPNSPUN58348</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -3673,12 +3673,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-06-17T17:18:11+00:00</t>
+          <t>2026-06-18T05:06:11+00:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>408-3294486-3424329</t>
+          <t>405-0242402-8315559</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>LPNCCX1B4206954</t>
+          <t>LPNHYD8DY89222</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -3729,32 +3729,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-06-17T11:01:26+00:00</t>
+          <t>2026-06-18T03:18:32+00:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>171-3399563-8885966</t>
+          <t>403-8790017-7829152</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>LPNLMAA0019039</t>
+          <t>LPNHYD8DY89148</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -3785,12 +3785,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-06-15T09:24:30+00:00</t>
+          <t>2026-06-17T17:18:11+00:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>171-3194001-5187538</t>
+          <t>408-3294486-3424329</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3818,22 +3818,22 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>DAMAGED</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>LPNHYD8DY92591</t>
+          <t>LPNCCX1B4206954</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -3841,32 +3841,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-06-15T08:53:22+00:00</t>
+          <t>2026-06-17T11:01:26+00:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>406-3765893-9779536</t>
+          <t>171-3399563-8885966</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -3874,22 +3874,22 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>LPNHDX8A0002233</t>
+          <t>LPNLMAA0019039</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -3897,12 +3897,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-06-14T11:15:53+00:00</t>
+          <t>2026-06-15T09:24:30+00:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>171-1282309-9677932</t>
+          <t>171-3194001-5187538</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2198432</t>
+          <t>LPNHYD8DY92591</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -3953,32 +3953,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-06-14T06:26:57+00:00</t>
+          <t>2026-06-15T08:53:22+00:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>407-1845667-2313146</t>
+          <t>406-3765893-9779536</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -3986,22 +3986,22 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3677498</t>
+          <t>LPNHDX8A0002233</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4009,32 +4009,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-06-13T12:21:24+00:00</t>
+          <t>2026-06-14T11:15:53+00:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>405-5466299-6857906</t>
+          <t>171-1282309-9677932</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>LPNSBOB1375958</t>
+          <t>LPNMAA4Z2198432</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -4065,32 +4065,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-06-13T12:20:57+00:00</t>
+          <t>2026-06-14T06:26:57+00:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>404-9976514-7382743</t>
+          <t>407-1845667-2313146</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -4098,22 +4098,22 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>LPNSBOB1375957</t>
+          <t>LPNDEL4AA3677498</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -4121,12 +4121,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-06-12T11:47:28+00:00</t>
+          <t>2026-06-13T12:21:24+00:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>407-2845785-4936332</t>
+          <t>405-5466299-6857906</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4154,22 +4154,22 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>LPNSHTI00009280</t>
+          <t>LPNSBOB1375958</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -4177,32 +4177,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-06-11T12:39:34+00:00</t>
+          <t>2026-06-13T12:20:57+00:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>405-0836953-9114742</t>
+          <t>404-9976514-7382743</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -4210,22 +4210,22 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>LPNHDX8A001607</t>
+          <t>LPNSBOB1375957</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -4233,32 +4233,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-06-11T10:43:03+00:00</t>
+          <t>2026-06-12T11:47:28+00:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>407-7053626-1929962</t>
+          <t>407-2845785-4936332</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FBA79667</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>B0DQPK7MFH</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>X0027512Z1</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk with Shelf|DIY Assembly| Monitor Raising Shelf |Engineered Wood &amp; Sturdy Steel Leg|Perfect for Computer Table Office Home Gaming Study Desk|L(130+130)*45*77cm|White</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -4266,22 +4266,22 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>SCUY</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>LPNSCUY00017897</t>
+          <t>LPNSHTI00009280</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -4289,32 +4289,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-06-10T22:26:08+00:00</t>
+          <t>2026-06-11T12:39:34+00:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>404-0639682-6860336</t>
+          <t>405-0836953-9114742</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -4322,22 +4322,22 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>LPNCX1B4784440</t>
+          <t>LPNHDX8A001607</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -4345,32 +4345,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-06-10T12:14:02+00:00</t>
+          <t>2026-06-11T10:43:03+00:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>171-1027170-0049924</t>
+          <t>407-7053626-1929962</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79667</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQPK7MFH</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0027512Z1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk with Shelf|DIY Assembly| Monitor Raising Shelf |Engineered Wood &amp; Sturdy Steel Leg|Perfect for Computer Table Office Home Gaming Study Desk|L(130+130)*45*77cm|White</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -4378,22 +4378,22 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>SCUY</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2407733</t>
+          <t>LPNSCUY00017897</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -4401,32 +4401,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-06-10T08:20:03+00:00</t>
+          <t>2026-06-10T22:26:08+00:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>406-6295410-5869130</t>
+          <t>404-0639682-6860336</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -4434,22 +4434,22 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>LPNBLX1C159057</t>
+          <t>LPNCX1B4784440</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -4457,12 +4457,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-06-10T05:42:02+00:00</t>
+          <t>2026-06-10T12:14:02+00:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>405-8329990-8940345</t>
+          <t>171-1027170-0049924</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4745942</t>
+          <t>LPNMAA4Z2407733</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -4513,32 +4513,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-06-10T04:51:41+00:00</t>
+          <t>2026-06-10T08:20:03+00:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>405-7954322-6131539</t>
+          <t>406-6295410-5869130</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -4546,22 +4546,22 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>LPNBOM5F5675078</t>
+          <t>LPNBLX1C159057</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -4569,12 +4569,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-06-10T03:51:05+00:00</t>
+          <t>2026-06-10T05:42:02+00:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>407-5527946-4998741</t>
+          <t>405-8329990-8940345</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7287766</t>
+          <t>LPNBLR7Y4745942</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -4625,12 +4625,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-06-08T09:59:30+00:00</t>
+          <t>2026-06-10T04:51:41+00:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>404-4052225-7064331</t>
+          <t>405-7954322-6131539</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4658,22 +4658,22 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3631375</t>
+          <t>LPNBOM5F5675078</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -4681,32 +4681,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-06-08T08:59:50+00:00</t>
+          <t>2026-06-10T03:51:05+00:00</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>404-3123106-0929939</t>
+          <t>407-5527946-4998741</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FBK76387</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>B0BF4S7V8C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>X00242V9DH</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -4714,22 +4714,22 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>LPNSPUN56234</t>
+          <t>LPNBLR7Y7287766</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -4737,32 +4737,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-06-08T08:59:02+00:00</t>
+          <t>2026-06-08T09:59:30+00:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>408-8800113-8391502</t>
+          <t>404-4052225-7064331</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -4770,22 +4770,22 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>LPNSPUN56235</t>
+          <t>LPNDEL4AA3631375</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -4793,32 +4793,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-06-08T08:43:30+00:00</t>
+          <t>2026-06-08T08:59:50+00:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>407-4254200-0562712</t>
+          <t>404-3123106-0929939</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBK76387</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BF4S7V8C</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00242V9DH</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | White</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -4826,22 +4826,22 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3631346</t>
+          <t>LPNSPUN56234</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -4849,32 +4849,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-06-07T16:09:41+00:00</t>
+          <t>2026-06-08T08:59:02+00:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>405-9852474-3831538</t>
+          <t>408-8800113-8391502</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>LPNCCX1B4179343</t>
+          <t>LPNSPUN56235</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -4905,32 +4905,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-06-07T11:20:49+00:00</t>
+          <t>2026-06-08T08:43:30+00:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>406-9783608-9093148</t>
+          <t>407-4254200-0562712</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -4938,22 +4938,22 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>LPNLMAA0016237</t>
+          <t>LPNDEL4AA3631346</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -4961,32 +4961,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-06-07T10:24:17+00:00</t>
+          <t>2026-06-07T16:09:41+00:00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>406-6392223-8173930</t>
+          <t>405-9852474-3831538</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>LPNBLX1C047099</t>
+          <t>LPNCCX1B4179343</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -5017,32 +5017,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-06-06T10:45:59+00:00</t>
+          <t>2026-06-07T11:20:49+00:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>406-9111649-3125130</t>
+          <t>406-9783608-9093148</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -5050,22 +5050,22 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>LPNBOM5F5579985</t>
+          <t>LPNLMAA0016237</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -5073,32 +5073,32 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-06-05T09:54:50+00:00</t>
+          <t>2026-06-07T10:24:17+00:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>405-7328472-7893901</t>
+          <t>406-6392223-8173930</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -5106,22 +5106,22 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679697</t>
+          <t>LPNBLX1C047099</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -5129,32 +5129,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-06-05T08:35:28+00:00</t>
+          <t>2026-06-06T10:45:59+00:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>404-9218549-9930734</t>
+          <t>406-9111649-3125130</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FBA79659</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>X0026ZDA2F</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, Black, 3 Year Warranty</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>LPNSDEGF082043</t>
+          <t>LPNBOM5F5579985</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -5185,12 +5185,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-06-05T08:17:03+00:00</t>
+          <t>2026-06-05T09:54:50+00:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>171-6540897-0152357</t>
+          <t>405-7328472-7893901</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679650</t>
+          <t>LPNDEL4AA3679697</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -5241,32 +5241,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-06-05T04:33:06+00:00</t>
+          <t>2026-06-05T08:35:28+00:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>171-6354444-3723505</t>
+          <t>404-9218549-9930734</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79659</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZDA2F</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, Black, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -5274,22 +5274,22 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>LPNBOM5F5574228</t>
+          <t>LPNSDEGF082043</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -5297,12 +5297,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-06-05T04:28:18+00:00</t>
+          <t>2026-06-05T08:17:03+00:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>406-6103690-9310748</t>
+          <t>171-6540897-0152357</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679535</t>
+          <t>LPNDEL4AA3679650</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -5353,12 +5353,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-06-04T03:47:36+00:00</t>
+          <t>2026-06-05T04:33:06+00:00</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>406-2278126-7841949</t>
+          <t>171-6354444-3723505</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5386,22 +5386,22 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679185</t>
+          <t>LPNBOM5F5574228</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -5409,12 +5409,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-06-01T09:32:55+00:00</t>
+          <t>2026-06-05T04:28:18+00:00</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>402-3794541-2581168</t>
+          <t>406-6103690-9310748</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4743333</t>
+          <t>LPNDEL4AA3679535</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -5465,12 +5465,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-06-01T04:42:36+00:00</t>
+          <t>2026-06-04T03:47:36+00:00</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>408-0143238-4374708</t>
+          <t>406-2278126-7841949</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>LPNBOM5F5524445</t>
+          <t>LPNDEL4AA3679185</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -5521,12 +5521,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-06-01T03:58:27+00:00</t>
+          <t>2026-06-01T09:32:55+00:00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>406-4355667-6072332</t>
+          <t>402-3794541-2581168</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4743158</t>
+          <t>LPNBLR7Y4743333</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -5577,12 +5577,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-31T09:10:34+00:00</t>
+          <t>2026-06-01T04:42:36+00:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>404-2518539-4406712</t>
+          <t>408-0143238-4374708</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5610,22 +5610,22 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3976607</t>
+          <t>LPNBOM5F5524445</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -5633,12 +5633,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-30T22:18:28+00:00</t>
+          <t>2026-06-01T03:58:27+00:00</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>407-1474707-0478726</t>
+          <t>406-4355667-6072332</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>LPNCCX1B4554643</t>
+          <t>LPNBLR7Y4743158</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -5689,12 +5689,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-30T04:13:42+00:00</t>
+          <t>2026-05-31T09:10:34+00:00</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>406-7941139-9225906</t>
+          <t>404-2518539-4406712</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5722,22 +5722,22 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>LPNBOM5F5507643</t>
+          <t>LPNDEL4AA3976607</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -5745,12 +5745,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-29T23:01:15+00:00</t>
+          <t>2026-05-30T22:18:28+00:00</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>405-0096078-8521126</t>
+          <t>407-1474707-0478726</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>LPNCCX1B2941120</t>
+          <t>LPNCCX1B4554643</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -5801,12 +5801,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-29T15:27:20+00:00</t>
+          <t>2026-05-30T04:13:42+00:00</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>404-8418070-5981124</t>
+          <t>406-7941139-9225906</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5834,12 +5834,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>LPNCCX1B4508596</t>
+          <t>LPNBOM5F5507643</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -5857,12 +5857,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-29T05:18:33+00:00</t>
+          <t>2026-05-29T23:01:15+00:00</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>171-0407209-4266756</t>
+          <t>405-0096078-8521126</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5890,22 +5890,22 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937926</t>
+          <t>LPNCCX1B2941120</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -5913,12 +5913,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-28T11:56:49+00:00</t>
+          <t>2026-05-29T15:27:20+00:00</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>407-4902279-0189155</t>
+          <t>404-8418070-5981124</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5956,12 +5956,12 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7363000</t>
+          <t>LPNCCX1B4508596</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -5969,12 +5969,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-28T08:40:02+00:00</t>
+          <t>2026-05-29T05:18:33+00:00</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>408-1128142-0248321</t>
+          <t>171-0407209-4266756</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6007,17 +6007,17 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>DAMAGED_BY_FC</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937756</t>
+          <t>LPNDEL4AA3937926</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -6025,12 +6025,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-28T06:36:17+00:00</t>
+          <t>2026-05-28T11:56:49+00:00</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>402-4776409-4471512</t>
+          <t>407-4902279-0189155</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7286354</t>
+          <t>LPNBLR7Y7363000</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -6081,12 +6081,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-27T12:42:16+00:00</t>
+          <t>2026-05-28T08:40:02+00:00</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>404-6762038-7137955</t>
+          <t>408-1128142-0248321</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>DAMAGED_BY_FC</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937575</t>
+          <t>LPNDEL4AA3937756</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -6137,12 +6137,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-27T09:44:17+00:00</t>
+          <t>2026-05-28T06:36:17+00:00</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>403-3444915-0085109</t>
+          <t>402-4776409-4471512</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7362686</t>
+          <t>LPNBLR7Y7286354</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -6193,32 +6193,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-27T09:25:47+00:00</t>
+          <t>2026-05-27T12:42:16+00:00</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>405-8410325-7933918</t>
+          <t>404-6762038-7137955</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -6226,22 +6226,22 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>LPNSPUN53913</t>
+          <t>LPNDEL4AA3937575</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -6249,12 +6249,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-26T23:02:43+00:00</t>
+          <t>2026-05-27T09:44:17+00:00</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>407-0645348-4574732</t>
+          <t>403-3444915-0085109</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6282,22 +6282,22 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>LPNCCX1B5292913</t>
+          <t>LPNBLR7Y7362686</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -6305,32 +6305,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-26T11:06:29+00:00</t>
+          <t>2026-05-27T09:25:47+00:00</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>402-2949127-9513917</t>
+          <t>405-8410325-7933918</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -6338,22 +6338,22 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937227</t>
+          <t>LPNSPUN53913</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -6361,12 +6361,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-26T08:48:10+00:00</t>
+          <t>2026-05-26T23:02:43+00:00</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>403-5510263-6469912</t>
+          <t>407-0645348-4574732</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6394,22 +6394,22 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273675</t>
+          <t>LPNCCX1B5292913</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -6417,12 +6417,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-25T15:22:25+00:00</t>
+          <t>2026-05-26T11:06:29+00:00</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>402-5203149-1906724</t>
+          <t>402-2949127-9513917</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>LPNCCX1B5331017</t>
+          <t>LPNDEL4AA3937227</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -6473,12 +6473,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-24T09:24:39+00:00</t>
+          <t>2026-05-26T08:48:10+00:00</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>171-7709339-0701117</t>
+          <t>403-5510263-6469912</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6516,12 +6516,12 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273169</t>
+          <t>LPNBLR7Y7273675</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -6529,12 +6529,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-24T08:29:52+00:00</t>
+          <t>2026-05-25T15:22:25+00:00</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>406-7042486-7436314</t>
+          <t>402-5203149-1906724</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6572,12 +6572,12 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273150</t>
+          <t>LPNCCX1B5331017</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -6585,32 +6585,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-23T23:07:27+00:00</t>
+          <t>2026-05-24T09:24:39+00:00</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>406-2954542-5857925</t>
+          <t>171-7709339-0701117</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -6618,22 +6618,22 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>LPNSBOB1370158</t>
+          <t>LPNBLR7Y7273169</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -6641,12 +6641,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-23T10:58:04+00:00</t>
+          <t>2026-05-24T08:29:52+00:00</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>406-4758725-2077907</t>
+          <t>406-7042486-7436314</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7272896</t>
+          <t>LPNBLR7Y7273150</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -6697,12 +6697,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-22T09:58:26+00:00</t>
+          <t>2026-05-23T23:07:27+00:00</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>403-7800011-6937966</t>
+          <t>406-2954542-5857925</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6730,22 +6730,22 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>LPNSDEGF010003</t>
+          <t>LPNSBOB1370158</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
@@ -6753,32 +6753,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-21T04:38:32+00:00</t>
+          <t>2026-05-23T10:58:04+00:00</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>403-2400247-1930753</t>
+          <t>406-4758725-2077907</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>LPNSDEGF099136</t>
+          <t>LPNBLR7Y7272896</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -6809,32 +6809,32 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-20T11:30:45+00:00</t>
+          <t>2026-05-22T09:58:26+00:00</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>406-2648444-6601917</t>
+          <t>403-7800011-6937966</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2147464</t>
+          <t>LPNSDEGF010003</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
@@ -6865,32 +6865,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-19T08:03:32+00:00</t>
+          <t>2026-05-21T04:38:32+00:00</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>405-4744559-6958733</t>
+          <t>403-2400247-1930753</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>LPNSDEGF097985</t>
+          <t>LPNSDEGF099136</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -6921,32 +6921,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-18T11:36:05+00:00</t>
+          <t>2026-05-20T11:30:45+00:00</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>171-1585723-0908356</t>
+          <t>406-2648444-6601917</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -6954,22 +6954,22 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>LPNBLX1C155145</t>
+          <t>LPNDEL4AA2147464</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -6977,32 +6977,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-15T08:29:30+00:00</t>
+          <t>2026-05-19T08:03:32+00:00</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>402-4856546-1261939</t>
+          <t>405-4744559-6958733</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>LPNSDEGF074601</t>
+          <t>LPNSDEGF097985</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -7033,32 +7033,32 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-13T13:50:43+00:00</t>
+          <t>2026-05-18T11:36:05+00:00</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>403-7495250-9937954</t>
+          <t>171-1585723-0908356</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -7076,12 +7076,12 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>LPNBLX1C154096</t>
+          <t>LPNBLX1C155145</t>
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
@@ -7089,32 +7089,32 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-12T07:19:54+00:00</t>
+          <t>2026-05-15T08:29:30+00:00</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>408-0473775-6641108</t>
+          <t>402-4856546-1261939</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -7122,22 +7122,22 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>LPNSBOB1362246</t>
+          <t>LPNSDEGF074601</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -7145,32 +7145,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-11T10:31:39+00:00</t>
+          <t>2026-05-13T13:50:43+00:00</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>404-1750959-8518722</t>
+          <t>403-7495250-9937954</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>LPNSHTI00006165</t>
+          <t>LPNBLX1C154096</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -7201,32 +7201,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-10T09:15:43+00:00</t>
+          <t>2026-05-12T07:19:54+00:00</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>402-1548587-3227555</t>
+          <t>408-0473775-6641108</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>LPNBOM5F5057136</t>
+          <t>LPNSBOB1362246</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -7257,12 +7257,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-08T15:43:17+00:00</t>
+          <t>2026-05-11T10:31:39+00:00</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>402-8374307-7441113</t>
+          <t>404-1750959-8518722</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7290,22 +7290,22 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>LPNSDEGF064205</t>
+          <t>LPNSHTI00006165</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
@@ -7313,32 +7313,32 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-08T13:25:23+00:00</t>
+          <t>2026-05-10T09:15:43+00:00</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>171-7381542-8368365</t>
+          <t>402-1548587-3227555</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7356,12 +7356,12 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>LPNBLX1C042486</t>
+          <t>LPNBOM5F5057136</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -7369,32 +7369,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-08T07:49:38+00:00</t>
+          <t>2026-05-08T15:43:17+00:00</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>403-3056736-6311553</t>
+          <t>402-8374307-7441113</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -7402,22 +7402,22 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5321963</t>
+          <t>LPNSDEGF064205</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -7425,32 +7425,32 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-06T06:52:28+00:00</t>
+          <t>2026-05-08T13:25:23+00:00</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>403-2654029-0716338</t>
+          <t>171-7381542-8368365</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -7458,22 +7458,22 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>LPNSHTI00005958</t>
+          <t>LPNBLX1C042486</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -7481,12 +7481,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-06T05:51:00+00:00</t>
+          <t>2026-05-08T07:49:38+00:00</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>404-9426288-6037168</t>
+          <t>403-3056736-6311553</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7514,22 +7514,22 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>LPNBOM5F5236158</t>
+          <t>LPNBLR7Y5321963</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -7537,32 +7537,32 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-02T04:54:42+00:00</t>
+          <t>2026-05-06T06:52:28+00:00</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>407-6201969-2856316</t>
+          <t>403-2654029-0716338</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -7570,22 +7570,22 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>LPNLMAA0004457</t>
+          <t>LPNSHTI00005958</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -7593,32 +7593,32 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-28T08:52:43+00:00</t>
+          <t>2026-05-06T05:51:00+00:00</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>171-6713241-8377149</t>
+          <t>404-9426288-6037168</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -7626,22 +7626,22 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>LPNLMAA0003844</t>
+          <t>LPNBOM5F5236158</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -7649,32 +7649,32 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-27T06:04:11+00:00</t>
+          <t>2026-05-02T04:54:42+00:00</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>403-6021111-3520325</t>
+          <t>407-6201969-2856316</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -7687,17 +7687,17 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>LPNLMAA0003335</t>
+          <t>LPNLMAA0004457</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -7705,32 +7705,32 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-04-26T08:09:27+00:00</t>
+          <t>2026-04-28T08:52:43+00:00</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>402-4881396-1030704</t>
+          <t>171-6713241-8377149</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -7738,22 +7738,22 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2253845</t>
+          <t>LPNLMAA0003844</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -7761,32 +7761,32 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-04-26T04:14:08+00:00</t>
+          <t>2026-04-27T06:04:11+00:00</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>408-1134010-7973925</t>
+          <t>403-6021111-3520325</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5321963</t>
+          <t>LPNLMAA0003335</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -7817,32 +7817,32 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-04-26T03:22:50+00:00</t>
+          <t>2026-04-26T08:09:27+00:00</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>406-9614580-4613163</t>
+          <t>402-4881396-1030704</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -7850,22 +7850,22 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>LPNSPUN46511</t>
+          <t>LPNDEL4AA2253845</t>
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
@@ -7873,32 +7873,32 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-04-25T05:33:44+00:00</t>
+          <t>2026-04-26T04:14:08+00:00</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>171-3077342-1790757</t>
+          <t>408-1134010-7973925</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -7906,12 +7906,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>LPNLMAA0002840</t>
+          <t>LPNBLR7Y5321963</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
@@ -7929,32 +7929,32 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-04-25T03:48:59+00:00</t>
+          <t>2026-04-26T03:22:50+00:00</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>404-4908572-3783532</t>
+          <t>406-9614580-4613163</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>X002FOAUSJ</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>LPNBLR7Y6090385</t>
+          <t>LPNSPUN46511</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -7985,32 +7985,32 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-04-22T10:55:13+00:00</t>
+          <t>2026-04-25T05:33:44+00:00</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>407-4868470-8499505</t>
+          <t>171-3077342-1790757</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -8023,17 +8023,17 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>LPNLMAA0001354</t>
+          <t>LPNLMAA0002840</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -8041,32 +8041,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-04-22T04:17:57+00:00</t>
+          <t>2026-04-25T03:48:59+00:00</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>406-5030280-5555520</t>
+          <t>404-4908572-3783532</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X002FOAUSJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -8074,22 +8074,22 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>LPNSDEGF117193</t>
+          <t>LPNBLR7Y6090385</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
@@ -8097,32 +8097,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-04-21T20:42:51+00:00</t>
+          <t>2026-04-22T10:55:13+00:00</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>403-7744956-9735520</t>
+          <t>407-4868470-8499505</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -8130,22 +8130,22 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>LPNCCX1B1519621</t>
+          <t>LPNLMAA0001354</t>
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
@@ -8153,32 +8153,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-04-20T05:04:40+00:00</t>
+          <t>2026-04-22T04:17:57+00:00</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>171-5598784-9947515</t>
+          <t>406-5030280-5555520</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>X002FOAUSJ</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5552415</t>
+          <t>LPNSDEGF117193</t>
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
@@ -8209,12 +8209,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-04-18T05:41:14+00:00</t>
+          <t>2026-04-21T20:42:51+00:00</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>404-0309463-1310709</t>
+          <t>403-7744956-9735520</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8242,12 +8242,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>LPNDEL4AA0788989</t>
+          <t>LPNCCX1B1519621</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
@@ -8265,32 +8265,32 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-04-15T13:55:57+00:00</t>
+          <t>2026-04-20T05:04:40+00:00</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>407-7885481-2445152</t>
+          <t>171-5598784-9947515</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X002FOAUSJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -8298,22 +8298,22 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>SMAB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>LPNSMAB1153810</t>
+          <t>LPNBLR7Y5552415</t>
         </is>
       </c>
       <c r="L141" t="inlineStr"/>
@@ -8321,32 +8321,32 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-04-15T08:47:44+00:00</t>
+          <t>2026-04-18T05:41:14+00:00</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>407-3585151-4323522</t>
+          <t>404-0309463-1310709</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -8354,22 +8354,22 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>LPNSDEGF027993</t>
+          <t>LPNDEL4AA0788989</t>
         </is>
       </c>
       <c r="L142" t="inlineStr"/>
@@ -8377,32 +8377,32 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-04-12T10:47:54+00:00</t>
+          <t>2026-04-15T13:55:57+00:00</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>407-0802588-3857957</t>
+          <t>407-7885481-2445152</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -8410,22 +8410,22 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>SMAB</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>LPNSDEGF026167</t>
+          <t>LPNSMAB1153810</t>
         </is>
       </c>
       <c r="L143" t="inlineStr"/>
@@ -8433,32 +8433,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-04-11T06:17:07+00:00</t>
+          <t>2026-04-15T08:47:44+00:00</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>408-2417441-1123516</t>
+          <t>407-3585151-4323522</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>FBK76764</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>B0BMV1WPHL</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>X00242TZTH</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>White Mulberry Ergonomic Sit Stand Desk | Standing Desk for Office, Home &amp; Study | Everyday Ergonomic Desk | 1200mm x 600mm | Carbon Fibre</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -8466,22 +8466,22 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>LPNSHTI00004704</t>
+          <t>LPNSDEGF027993</t>
         </is>
       </c>
       <c r="L144" t="inlineStr"/>
@@ -8489,32 +8489,32 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-04-09T03:38:39+00:00</t>
+          <t>2026-04-12T10:47:54+00:00</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>406-0798045-4525148</t>
+          <t>407-0802588-3857957</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -8527,17 +8527,17 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>LPNSDEGF168570</t>
+          <t>LPNSDEGF026167</t>
         </is>
       </c>
       <c r="L145" t="inlineStr"/>
@@ -8545,32 +8545,32 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-04-08T10:17:09+00:00</t>
+          <t>2026-04-11T06:17:07+00:00</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>406-3115014-9939528</t>
+          <t>408-2417441-1123516</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBK76764</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BMV1WPHL</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00242TZTH</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Ergonomic Sit Stand Desk | Standing Desk for Office, Home &amp; Study | Everyday Ergonomic Desk | 1200mm x 600mm | Carbon Fibre</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -8578,22 +8578,22 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2155169</t>
+          <t>LPNSHTI00004704</t>
         </is>
       </c>
       <c r="L146" t="inlineStr"/>
@@ -8601,32 +8601,32 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-04-08T09:53:57+00:00</t>
+          <t>2026-04-09T03:38:39+00:00</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>403-7697438-5361950</t>
+          <t>406-0798045-4525148</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>LPNMAA4Z0044638</t>
+          <t>LPNSDEGF168570</t>
         </is>
       </c>
       <c r="L147" t="inlineStr"/>
@@ -8657,12 +8657,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-04-07T23:27:35+00:00</t>
+          <t>2026-04-08T10:17:09+00:00</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>402-3182844-0423531</t>
+          <t>406-3115014-9939528</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -8700,15 +8700,71 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>NO_REASON_GIVEN</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>LPNCCX1B1676425</t>
+          <t>LPNDEL4AA2155169</t>
         </is>
       </c>
       <c r="L148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-04-08T09:53:57+00:00</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>403-7697438-5361950</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>FBA79167</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>X001Y5UYX1</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>MAA4</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>CARRIER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>UNDELIVERABLE_REFUSED</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>LPNMAA4Z0044638</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/raw/returns/WhiteMulberry.xlsx
+++ b/data/raw/returns/WhiteMulberry.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,66 +425,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L149"/>
+  <dimension ref="A1:L161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>return-date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>order-id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fnsku</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>product-name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>fulfillment-center-id</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>detailed-disposition</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>license-plate-number</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>customer-comments</t>
         </is>
@@ -481,12 +493,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06T21:23:52+00:00</t>
+          <t>2026-07-13T07:03:07+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>406-6590377-2621105</t>
+          <t>405-0681203-5996333</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -524,12 +536,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4815212</t>
+          <t>LPNBLR8Z4739661</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -537,32 +549,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06T21:22:13+00:00</t>
+          <t>2026-07-12T18:38:59+00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>407-1625560-1723518</t>
+          <t>408-6399475-0434747</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -570,7 +582,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -585,7 +597,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4815211</t>
+          <t>LPNSDEGA045352</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -593,12 +605,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06T12:33:49+00:00</t>
+          <t>2026-07-12T12:11:34+00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>404-5401376-5513111</t>
+          <t>405-3614422-8705902</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,7 +638,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -636,12 +648,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LPNHYD8EJ59560</t>
+          <t>LPNBLR7Y8671012</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -649,12 +661,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-05T20:21:02+00:00</t>
+          <t>2026-07-12T11:18:57+00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>408-9802796-1211539</t>
+          <t>171-1476461-2065906</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -682,22 +694,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LPNCCX1A8722775</t>
+          <t>LPNDEL4AA3731833</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -705,12 +717,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-05T07:23:15+00:00</t>
+          <t>2026-07-12T09:48:52+00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>407-2308442-1499512</t>
+          <t>407-1690927-4321928</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -738,12 +750,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -753,7 +765,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4813630</t>
+          <t>LPNBLR7Y8670945</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -761,32 +773,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-05T06:48:36+00:00</t>
+          <t>2026-07-11T15:19:09+00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>407-8970250-4543519</t>
+          <t>407-1918094-9025938</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -794,7 +806,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -809,7 +821,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4814250</t>
+          <t>LPNSDEGA049360</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -817,12 +829,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-05T04:41:04+00:00</t>
+          <t>2026-07-11T04:41:50+00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>405-1245096-1377920</t>
+          <t>402-4732739-0177111</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -850,7 +862,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -865,7 +877,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>LPNBOM5F5826513</t>
+          <t>LPNBLR8Z3333062</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -873,32 +885,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-04T12:12:23+00:00</t>
+          <t>2026-07-10T11:34:53+00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>404-7913029-6157962</t>
+          <t>402-4127261-8261957</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -906,7 +918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -916,12 +928,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>LPNHYD8EJ58729</t>
+          <t>LPNSHTI00014264</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -929,12 +941,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-04T08:48:05+00:00</t>
+          <t>2026-07-10T11:22:36+00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>405-3423037-8257160</t>
+          <t>402-4627500-7082749</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -967,17 +979,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>DAMAGED_BY_FC</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3108992</t>
+          <t>LPNDEL4AA3300048</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -985,12 +997,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-04T04:21:28+00:00</t>
+          <t>2026-07-10T08:11:09+00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>405-3646440-7662737</t>
+          <t>407-2441104-3469917</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1018,7 +1030,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1028,12 +1040,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>LPNBOM5F5455146</t>
+          <t>LPNBLR8Z3342252</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1041,12 +1053,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-03T19:29:57+00:00</t>
+          <t>2026-07-10T03:24:58+00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>403-0547582-3197132</t>
+          <t>404-4351909-9563522</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1074,7 +1086,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1089,7 +1101,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>LPNCCX1B4102605</t>
+          <t>LPNDEL4AA3919248</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1097,32 +1109,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-03T14:02:46+00:00</t>
+          <t>2026-07-09T04:11:50+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>171-7464293-7220360</t>
+          <t>402-4684050-2008333</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1130,22 +1142,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>DAMAGED</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>NO_REASON_GIVEN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>LPNSBOB1392052</t>
+          <t>LPNBLR8Z4305793</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1153,12 +1165,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-03T11:38:57+00:00</t>
+          <t>2026-07-08T20:07:54+00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>403-6645337-2467540</t>
+          <t>171-5139545-1381155</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1186,7 +1198,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1201,7 +1213,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2082724</t>
+          <t>LPNCCX1A7424707</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1209,12 +1221,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-02T17:30:33+00:00</t>
+          <t>2026-07-08T06:12:17+00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>402-1004506-0818747</t>
+          <t>406-6599709-8196355</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1242,7 +1254,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1252,12 +1264,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>LPNBLR8Z5514346</t>
+          <t>LPNDEL4AA3951631</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1265,32 +1277,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-02T14:56:15+00:00</t>
+          <t>2026-07-07T14:57:35+00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>407-7003476-1816350</t>
+          <t>403-7360454-8443505</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1298,22 +1310,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>NO_REASON_GIVEN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3108265</t>
+          <t>LPNSDEGA048066</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1321,12 +1333,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-02T11:24:54+00:00</t>
+          <t>2026-07-07T12:17:02+00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>408-9621782-0261114</t>
+          <t>404-3937409-4657901</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1359,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1369,7 +1381,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3950616</t>
+          <t>LPNDEL4AA3951212</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1377,32 +1389,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-02T06:41:10+00:00</t>
+          <t>2026-07-07T09:02:25+00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>403-6072724-5581966</t>
+          <t>406-5155095-5494705</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1410,22 +1422,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4303742</t>
+          <t>LPNLMAA0027050</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1433,12 +1445,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-01T22:20:26+00:00</t>
+          <t>2026-07-06T21:23:52+00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>402-4598141-9561917</t>
+          <t>406-6590377-2621105</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1466,7 +1478,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1481,7 +1493,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>LPNCCX1B4170658</t>
+          <t>LPNBLR8Z4815212</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1489,32 +1501,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-01T15:09:10+00:00</t>
+          <t>2026-07-06T21:22:13+00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>402-3081497-7409144</t>
+          <t>407-1625560-1723518</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1522,22 +1534,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>LPNBLX1C093497</t>
+          <t>LPNBLR8Z4815211</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1545,12 +1557,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-01T09:24:20+00:00</t>
+          <t>2026-07-06T12:33:49+00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>405-3824107-9644368</t>
+          <t>404-5401376-5513111</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1578,22 +1590,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>LPNBOM5F5465051</t>
+          <t>LPNHYD8EJ59560</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1601,12 +1613,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-01T06:49:32+00:00</t>
+          <t>2026-07-05T20:21:02+00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>404-6104605-6788338</t>
+          <t>408-9802796-1211539</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1634,7 +1646,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1649,7 +1661,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>LPNBOM5F5435891</t>
+          <t>LPNCCX1A8722775</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1657,12 +1669,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-01T05:46:54+00:00</t>
+          <t>2026-07-05T07:23:15+00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>407-2497737-1874765</t>
+          <t>407-2308442-1499512</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1690,7 +1702,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1705,7 +1717,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>LPNBOM5F5407228</t>
+          <t>LPNBLR8Z4813630</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1713,12 +1725,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-01T03:55:07+00:00</t>
+          <t>2026-07-05T06:48:36+00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>403-6044286-1801115</t>
+          <t>407-8970250-4543519</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1746,7 +1758,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>CCX2</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1761,7 +1773,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>LPNCCX2B2262224</t>
+          <t>LPNBLR8Z4814250</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1769,12 +1781,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-29T12:22:41+00:00</t>
+          <t>2026-07-05T04:41:04+00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>405-6904525-0069903</t>
+          <t>405-1245096-1377920</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1802,22 +1814,22 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>LPNHYD8EF20503</t>
+          <t>LPNBOM5F5826513</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1825,12 +1837,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-28T19:38:03+00:00</t>
+          <t>2026-07-04T12:12:23+00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>402-4296829-1337133</t>
+          <t>404-7913029-6157962</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1858,22 +1870,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>LPNCCX1B2440445</t>
+          <t>LPNHYD8EJ58729</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1881,12 +1893,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-28T08:39:43+00:00</t>
+          <t>2026-07-04T08:48:05+00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>402-6090489-2032337</t>
+          <t>405-3423037-8257160</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1914,22 +1926,22 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DAMAGED_BY_FC</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7855923</t>
+          <t>LPNDEL4AA3108992</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1937,12 +1949,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-27T11:00:01+00:00</t>
+          <t>2026-07-04T04:21:28+00:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>408-3896665-0021948</t>
+          <t>405-3646440-7662737</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1970,7 +1982,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1980,12 +1992,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7855626</t>
+          <t>LPNBOM5F5455146</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -1993,32 +2005,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-27T10:32:22+00:00</t>
+          <t>2026-07-03T19:29:57+00:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>407-5462207-4616334</t>
+          <t>403-0547582-3197132</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2026,22 +2038,22 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>LPNSBOB1388621</t>
+          <t>LPNCCX1B4102605</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2049,32 +2061,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-26T18:08:18+00:00</t>
+          <t>2026-07-03T14:02:46+00:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>171-5586406-9945900</t>
+          <t>171-7464293-7220360</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2092,12 +2104,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>NO_REASON_GIVEN</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>LPNSBOB1388302</t>
+          <t>LPNSBOB1392052</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2105,32 +2117,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-26T06:57:42+00:00</t>
+          <t>2026-07-03T11:38:57+00:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>405-2746376-7486724</t>
+          <t>403-6645337-2467540</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2138,12 +2150,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2153,7 +2165,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>LPNBLX1C140655</t>
+          <t>LPNDEL4AA2082724</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2161,12 +2173,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-26T05:19:18+00:00</t>
+          <t>2026-07-02T17:30:33+00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>406-4442109-5330751</t>
+          <t>402-1004506-0818747</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2194,7 +2206,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2209,7 +2221,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3990308</t>
+          <t>LPNBLR8Z5514346</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2217,32 +2229,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-25T18:24:43+00:00</t>
+          <t>2026-07-02T14:56:15+00:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>405-2433007-9289947</t>
+          <t>407-7003476-1816350</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2250,22 +2262,22 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>NO_REASON_GIVEN</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>LPNSBOB1387687</t>
+          <t>LPNDEL4AA3108265</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2273,12 +2285,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-25T10:05:58+00:00</t>
+          <t>2026-07-02T11:24:54+00:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>407-3034951-4675566</t>
+          <t>408-9621782-0261114</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2306,7 +2318,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2321,7 +2333,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2273850</t>
+          <t>LPNDEL4AA3950616</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2329,32 +2341,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-24T08:29:31+00:00</t>
+          <t>2026-07-02T06:41:10+00:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>402-0120877-0312362</t>
+          <t>403-6072724-5581966</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2362,22 +2374,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>LPNSPUN59333</t>
+          <t>LPNBLR8Z4303742</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2385,12 +2397,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-24T06:17:22+00:00</t>
+          <t>2026-07-01T22:20:26+00:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>403-8864299-1768360</t>
+          <t>402-4598141-9561917</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2418,22 +2430,22 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7854241</t>
+          <t>LPNCCX1B4170658</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2441,32 +2453,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-23T15:36:47+00:00</t>
+          <t>2026-07-01T15:09:10+00:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>402-8717460-5700310</t>
+          <t>402-3081497-7409144</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2474,7 +2486,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2484,12 +2496,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>LPNHDX8A005873</t>
+          <t>LPNBLX1C093497</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2497,12 +2509,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-23T11:54:27+00:00</t>
+          <t>2026-07-01T09:24:20+00:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>403-7688253-5273167</t>
+          <t>405-3824107-9644368</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2540,12 +2552,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>LPNBOM5F5694482</t>
+          <t>LPNBOM5F5465051</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -2553,12 +2565,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-23T09:27:19+00:00</t>
+          <t>2026-07-01T06:49:32+00:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>408-9857262-4357961</t>
+          <t>404-6104605-6788338</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2586,7 +2598,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2601,7 +2613,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7853975</t>
+          <t>LPNBOM5F5435891</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -2609,12 +2621,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-23T08:32:44+00:00</t>
+          <t>2026-07-01T05:46:54+00:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>404-2029470-0977929</t>
+          <t>407-2497737-1874765</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2642,7 +2654,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2652,12 +2664,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3925027</t>
+          <t>LPNBOM5F5407228</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2665,32 +2677,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-23T06:25:18+00:00</t>
+          <t>2026-07-01T03:55:07+00:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>408-7120729-6837923</t>
+          <t>403-6044286-1801115</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2698,7 +2710,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>CCX2</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2713,7 +2725,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>LPNSBOB1385946</t>
+          <t>LPNCCX2B2262224</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -2721,32 +2733,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-23T05:29:18+00:00</t>
+          <t>2026-06-29T12:22:41+00:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>403-5101653-2865108</t>
+          <t>405-6904525-0069903</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2754,7 +2766,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2764,12 +2776,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>LPNHDX8005941</t>
+          <t>LPNHYD8EF20503</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -2777,32 +2789,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-22T15:00:37+00:00</t>
+          <t>2026-06-28T19:38:03+00:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>408-2886313-6344340</t>
+          <t>402-4296829-1337133</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2810,22 +2822,22 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>LPNSBOB1385291</t>
+          <t>LPNCCX1B2440445</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2833,32 +2845,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-22T15:00:11+00:00</t>
+          <t>2026-06-28T08:39:43+00:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>403-4065197-2565940</t>
+          <t>402-6090489-2032337</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2866,22 +2878,22 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>LPNSBOB1385290</t>
+          <t>LPNBLR7Y7855923</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -2889,32 +2901,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-22T13:49:32+00:00</t>
+          <t>2026-06-27T11:00:01+00:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>171-3328269-2691534</t>
+          <t>408-3896665-0021948</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2922,7 +2934,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2932,12 +2944,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>LPNBLX1C049419</t>
+          <t>LPNBLR7Y7855626</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -2945,32 +2957,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-22T13:44:52+00:00</t>
+          <t>2026-06-27T10:32:22+00:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>407-2806960-6949923</t>
+          <t>407-5462207-4616334</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2978,7 +2990,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2988,12 +3000,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>LPNBLX1C049418</t>
+          <t>LPNSBOB1388621</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3001,32 +3013,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-22T12:43:38+00:00</t>
+          <t>2026-06-26T18:08:18+00:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>402-2531413-4073130</t>
+          <t>171-5586406-9945900</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3034,22 +3046,22 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>LPNHYD8EF41160</t>
+          <t>LPNSBOB1388302</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3057,32 +3069,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-22T09:02:33+00:00</t>
+          <t>2026-06-26T06:57:42+00:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>404-4254275-9061104</t>
+          <t>405-2746376-7486724</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3090,7 +3102,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3100,12 +3112,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>LPNHYD8ED01352</t>
+          <t>LPNBLX1C140655</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -3113,12 +3125,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-22T06:27:11+00:00</t>
+          <t>2026-06-26T05:19:18+00:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>407-5289320-1468336</t>
+          <t>406-4442109-5330751</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3146,22 +3158,22 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7287766</t>
+          <t>LPNDEL4AA3990308</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -3169,32 +3181,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-21T15:48:42+00:00</t>
+          <t>2026-06-25T18:24:43+00:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>408-1433377-1765942</t>
+          <t>405-2433007-9289947</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3212,12 +3224,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>LPNSBOB1385218</t>
+          <t>LPNSBOB1387687</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3225,12 +3237,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-21T09:50:13+00:00</t>
+          <t>2026-06-25T10:05:58+00:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>405-1204534-8479517</t>
+          <t>407-3034951-4675566</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3258,7 +3270,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3268,12 +3280,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>LPNDEL4AA4027730</t>
+          <t>LPNMAA4Z2273850</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3281,32 +3293,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-21T08:35:03+00:00</t>
+          <t>2026-06-24T08:29:31+00:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>171-0025867-6612374</t>
+          <t>402-0120877-0312362</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3314,22 +3326,22 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7853300</t>
+          <t>LPNSPUN59333</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -3337,12 +3349,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-20T13:05:37+00:00</t>
+          <t>2026-06-24T06:17:22+00:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>402-8590404-8535510</t>
+          <t>403-8864299-1768360</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3370,22 +3382,22 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>LPNMAA4G898204</t>
+          <t>LPNBLR7Y7854241</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -3393,32 +3405,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-19T14:24:04+00:00</t>
+          <t>2026-06-23T15:36:47+00:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>403-3269966-6849104</t>
+          <t>402-8717460-5700310</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3431,17 +3443,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>LPNHDX8A004693</t>
+          <t>LPNHDX8A005873</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -3449,12 +3461,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-18T09:53:43+00:00</t>
+          <t>2026-06-23T11:54:27+00:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>408-1513827-8090763</t>
+          <t>403-7688253-5273167</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3482,22 +3494,22 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2273003</t>
+          <t>LPNBOM5F5694482</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -3505,32 +3517,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-18T09:01:23+00:00</t>
+          <t>2026-06-23T09:27:19+00:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>402-6972876-7770702</t>
+          <t>408-9857262-4357961</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FBA76765</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>B0BMQQQ7YD</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>X001O7YYCV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>White Mulberry Motorized Height Adjustable Sit-Stand Desk | Electronic Height Adjustable | Motor &amp; Memory Preset Controller | Office, Workstation or Home | Carbon Fibre | 120 * 60*H(75-118) cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3538,22 +3550,22 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>LPNSPUN58279</t>
+          <t>LPNBLR7Y7853975</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -3561,32 +3573,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-18T06:34:47+00:00</t>
+          <t>2026-06-23T08:32:44+00:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>171-5595331-6677926</t>
+          <t>404-2029470-0977929</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3594,12 +3606,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3609,7 +3621,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>LPNSPUN58332</t>
+          <t>LPNDEL4AA3925027</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3617,32 +3629,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-18T06:13:54+00:00</t>
+          <t>2026-06-23T06:25:18+00:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>405-9716650-4190754</t>
+          <t>408-7120729-6837923</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -3650,22 +3662,22 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>LPNSPUN58348</t>
+          <t>LPNSBOB1385946</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -3673,32 +3685,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-06-18T05:06:11+00:00</t>
+          <t>2026-06-23T05:29:18+00:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>405-0242402-8315559</t>
+          <t>403-5101653-2865108</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -3706,22 +3718,22 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>LPNHYD8DY89222</t>
+          <t>LPNHDX8005941</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -3729,32 +3741,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-06-18T03:18:32+00:00</t>
+          <t>2026-06-22T15:00:37+00:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>403-8790017-7829152</t>
+          <t>408-2886313-6344340</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3762,22 +3774,22 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>LPNHYD8DY89148</t>
+          <t>LPNSBOB1385291</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -3785,32 +3797,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-06-17T17:18:11+00:00</t>
+          <t>2026-06-22T15:00:11+00:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>408-3294486-3424329</t>
+          <t>403-4065197-2565940</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -3818,22 +3830,22 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>LPNCCX1B4206954</t>
+          <t>LPNSBOB1385290</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -3841,32 +3853,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-06-17T11:01:26+00:00</t>
+          <t>2026-06-22T13:49:32+00:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>171-3399563-8885966</t>
+          <t>171-3328269-2691534</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -3874,22 +3886,22 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>LPNLMAA0019039</t>
+          <t>LPNBLX1C049419</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -3897,32 +3909,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-06-15T09:24:30+00:00</t>
+          <t>2026-06-22T13:44:52+00:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>171-3194001-5187538</t>
+          <t>407-2806960-6949923</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -3930,22 +3942,22 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>LPNHYD8DY92591</t>
+          <t>LPNBLX1C049418</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -3953,32 +3965,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-06-15T08:53:22+00:00</t>
+          <t>2026-06-22T12:43:38+00:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>406-3765893-9779536</t>
+          <t>402-2531413-4073130</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -3986,22 +3998,22 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>LPNHDX8A0002233</t>
+          <t>LPNHYD8EF41160</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4009,12 +4021,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-06-14T11:15:53+00:00</t>
+          <t>2026-06-22T09:02:33+00:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>171-1282309-9677932</t>
+          <t>404-4254275-9061104</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4042,7 +4054,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4052,12 +4064,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2198432</t>
+          <t>LPNHYD8ED01352</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -4065,12 +4077,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-06-14T06:26:57+00:00</t>
+          <t>2026-06-22T06:27:11+00:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>407-1845667-2313146</t>
+          <t>407-5289320-1468336</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4098,22 +4110,22 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3677498</t>
+          <t>LPNBLR7Y7287766</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -4121,32 +4133,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-06-13T12:21:24+00:00</t>
+          <t>2026-06-21T15:48:42+00:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>405-5466299-6857906</t>
+          <t>408-1433377-1765942</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -4159,17 +4171,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>LPNSBOB1375958</t>
+          <t>LPNSBOB1385218</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -4177,32 +4189,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-06-13T12:20:57+00:00</t>
+          <t>2026-06-21T09:50:13+00:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>404-9976514-7382743</t>
+          <t>405-1204534-8479517</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -4210,22 +4222,22 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>LPNSBOB1375957</t>
+          <t>LPNDEL4AA4027730</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -4233,32 +4245,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-06-12T11:47:28+00:00</t>
+          <t>2026-06-21T08:35:03+00:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>407-2845785-4936332</t>
+          <t>171-0025867-6612374</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -4266,7 +4278,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4276,12 +4288,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>LPNSHTI00009280</t>
+          <t>LPNBLR7Y7853300</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -4289,32 +4301,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-06-11T12:39:34+00:00</t>
+          <t>2026-06-20T13:05:37+00:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>405-0836953-9114742</t>
+          <t>402-8590404-8535510</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -4322,7 +4334,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4332,12 +4344,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>LPNHDX8A001607</t>
+          <t>LPNMAA4G898204</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -4345,32 +4357,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-06-11T10:43:03+00:00</t>
+          <t>2026-06-19T14:24:04+00:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>407-7053626-1929962</t>
+          <t>403-3269966-6849104</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FBA79667</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>B0DQPK7MFH</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>X0027512Z1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk with Shelf|DIY Assembly| Monitor Raising Shelf |Engineered Wood &amp; Sturdy Steel Leg|Perfect for Computer Table Office Home Gaming Study Desk|L(130+130)*45*77cm|White</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -4378,22 +4390,22 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>SCUY</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>LPNSCUY00017897</t>
+          <t>LPNHDX8A004693</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -4401,12 +4413,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-06-10T22:26:08+00:00</t>
+          <t>2026-06-18T09:53:43+00:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>404-0639682-6860336</t>
+          <t>408-1513827-8090763</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4434,22 +4446,22 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>LPNCX1B4784440</t>
+          <t>LPNMAA4Z2273003</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -4457,32 +4469,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-06-10T12:14:02+00:00</t>
+          <t>2026-06-18T09:01:23+00:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>171-1027170-0049924</t>
+          <t>402-6972876-7770702</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76765</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BMQQQ7YD</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001O7YYCV</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Motorized Height Adjustable Sit-Stand Desk | Electronic Height Adjustable | Motor &amp; Memory Preset Controller | Office, Workstation or Home | Carbon Fibre | 120 * 60*H(75-118) cm</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -4490,22 +4502,22 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2407733</t>
+          <t>LPNSPUN58279</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -4513,32 +4525,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-06-10T08:20:03+00:00</t>
+          <t>2026-06-18T06:34:47+00:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>406-6295410-5869130</t>
+          <t>171-5595331-6677926</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -4546,22 +4558,22 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>LPNBLX1C159057</t>
+          <t>LPNSPUN58332</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -4569,32 +4581,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-06-10T05:42:02+00:00</t>
+          <t>2026-06-18T06:13:54+00:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>405-8329990-8940345</t>
+          <t>405-9716650-4190754</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -4602,22 +4614,22 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4745942</t>
+          <t>LPNSPUN58348</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -4625,12 +4637,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-06-10T04:51:41+00:00</t>
+          <t>2026-06-18T05:06:11+00:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>405-7954322-6131539</t>
+          <t>405-0242402-8315559</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4658,7 +4670,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4673,7 +4685,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>LPNBOM5F5675078</t>
+          <t>LPNHYD8DY89222</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -4681,12 +4693,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-06-10T03:51:05+00:00</t>
+          <t>2026-06-18T03:18:32+00:00</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>407-5527946-4998741</t>
+          <t>403-8790017-7829152</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4714,12 +4726,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4729,7 +4741,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7287766</t>
+          <t>LPNHYD8DY89148</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -4737,12 +4749,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-06-08T09:59:30+00:00</t>
+          <t>2026-06-17T17:18:11+00:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>404-4052225-7064331</t>
+          <t>408-3294486-3424329</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4770,22 +4782,22 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>DAMAGED</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3631375</t>
+          <t>LPNCCX1B4206954</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -4793,32 +4805,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-06-08T08:59:50+00:00</t>
+          <t>2026-06-17T11:01:26+00:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>404-3123106-0929939</t>
+          <t>171-3399563-8885966</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FBK76387</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>B0BF4S7V8C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>X00242V9DH</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | White</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -4826,7 +4838,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4836,12 +4848,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>LPNSPUN56234</t>
+          <t>LPNLMAA0019039</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -4849,32 +4861,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-06-08T08:59:02+00:00</t>
+          <t>2026-06-15T09:24:30+00:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>408-8800113-8391502</t>
+          <t>171-3194001-5187538</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -4882,22 +4894,22 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>LPNSPUN56235</t>
+          <t>LPNHYD8DY92591</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -4905,32 +4917,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-06-08T08:43:30+00:00</t>
+          <t>2026-06-15T08:53:22+00:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>407-4254200-0562712</t>
+          <t>406-3765893-9779536</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -4938,22 +4950,22 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3631346</t>
+          <t>LPNHDX8A0002233</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -4961,12 +4973,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-06-07T16:09:41+00:00</t>
+          <t>2026-06-14T11:15:53+00:00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>405-9852474-3831538</t>
+          <t>171-1282309-9677932</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4994,22 +5006,22 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>LPNCCX1B4179343</t>
+          <t>LPNMAA4Z2198432</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -5017,32 +5029,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-06-07T11:20:49+00:00</t>
+          <t>2026-06-14T06:26:57+00:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>406-9783608-9093148</t>
+          <t>407-1845667-2313146</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -5050,22 +5062,22 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>LPNLMAA0016237</t>
+          <t>LPNDEL4AA3677498</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -5073,32 +5085,32 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-06-07T10:24:17+00:00</t>
+          <t>2026-06-13T12:21:24+00:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>406-6392223-8173930</t>
+          <t>405-5466299-6857906</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -5106,22 +5118,22 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>LPNBLX1C047099</t>
+          <t>LPNSBOB1375958</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -5129,32 +5141,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-06-06T10:45:59+00:00</t>
+          <t>2026-06-13T12:20:57+00:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>406-9111649-3125130</t>
+          <t>404-9976514-7382743</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -5162,22 +5174,22 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>LPNBOM5F5579985</t>
+          <t>LPNSBOB1375957</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -5185,32 +5197,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-06-05T09:54:50+00:00</t>
+          <t>2026-06-12T11:47:28+00:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>405-7328472-7893901</t>
+          <t>407-2845785-4936332</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -5218,7 +5230,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5228,12 +5240,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679697</t>
+          <t>LPNSHTI00009280</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -5241,32 +5253,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-06-05T08:35:28+00:00</t>
+          <t>2026-06-11T12:39:34+00:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>404-9218549-9930734</t>
+          <t>405-0836953-9114742</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FBA79659</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>X0026ZDA2F</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, Black, 3 Year Warranty</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -5274,7 +5286,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5284,12 +5296,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>LPNSDEGF082043</t>
+          <t>LPNHDX8A001607</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -5297,32 +5309,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-06-05T08:17:03+00:00</t>
+          <t>2026-06-11T10:43:03+00:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>171-6540897-0152357</t>
+          <t>407-7053626-1929962</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79667</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQPK7MFH</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0027512Z1</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk with Shelf|DIY Assembly| Monitor Raising Shelf |Engineered Wood &amp; Sturdy Steel Leg|Perfect for Computer Table Office Home Gaming Study Desk|L(130+130)*45*77cm|White</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -5330,22 +5342,22 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SCUY</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679650</t>
+          <t>LPNSCUY00017897</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -5353,12 +5365,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-06-05T04:33:06+00:00</t>
+          <t>2026-06-10T22:26:08+00:00</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>171-6354444-3723505</t>
+          <t>404-0639682-6860336</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5386,22 +5398,22 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>LPNBOM5F5574228</t>
+          <t>LPNCX1B4784440</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -5409,12 +5421,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-06-05T04:28:18+00:00</t>
+          <t>2026-06-10T12:14:02+00:00</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>406-6103690-9310748</t>
+          <t>171-1027170-0049924</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5442,7 +5454,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5452,12 +5464,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679535</t>
+          <t>LPNMAA4Z2407733</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -5465,32 +5477,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-06-04T03:47:36+00:00</t>
+          <t>2026-06-10T08:20:03+00:00</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>406-2278126-7841949</t>
+          <t>406-6295410-5869130</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -5498,22 +5510,22 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679185</t>
+          <t>LPNBLX1C159057</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -5521,12 +5533,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-06-01T09:32:55+00:00</t>
+          <t>2026-06-10T05:42:02+00:00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>402-3794541-2581168</t>
+          <t>405-8329990-8940345</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5569,7 +5581,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4743333</t>
+          <t>LPNBLR7Y4745942</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -5577,12 +5589,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-06-01T04:42:36+00:00</t>
+          <t>2026-06-10T04:51:41+00:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>408-0143238-4374708</t>
+          <t>405-7954322-6131539</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5615,7 +5627,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5625,7 +5637,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>LPNBOM5F5524445</t>
+          <t>LPNBOM5F5675078</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -5633,12 +5645,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-06-01T03:58:27+00:00</t>
+          <t>2026-06-10T03:51:05+00:00</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>406-4355667-6072332</t>
+          <t>407-5527946-4998741</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5676,12 +5688,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4743158</t>
+          <t>LPNBLR7Y7287766</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -5689,12 +5701,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-31T09:10:34+00:00</t>
+          <t>2026-06-08T09:59:30+00:00</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>404-2518539-4406712</t>
+          <t>404-4052225-7064331</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5727,17 +5739,17 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3976607</t>
+          <t>LPNDEL4AA3631375</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -5745,32 +5757,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-30T22:18:28+00:00</t>
+          <t>2026-06-08T08:59:50+00:00</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>407-1474707-0478726</t>
+          <t>404-3123106-0929939</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBK76387</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BF4S7V8C</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00242V9DH</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | White</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -5778,22 +5790,22 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>LPNCCX1B4554643</t>
+          <t>LPNSPUN56234</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -5801,32 +5813,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-30T04:13:42+00:00</t>
+          <t>2026-06-08T08:59:02+00:00</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>406-7941139-9225906</t>
+          <t>408-8800113-8391502</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -5834,7 +5846,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5844,12 +5856,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>LPNBOM5F5507643</t>
+          <t>LPNSPUN56235</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -5857,12 +5869,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-29T23:01:15+00:00</t>
+          <t>2026-06-08T08:43:30+00:00</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>405-0096078-8521126</t>
+          <t>407-4254200-0562712</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5890,7 +5902,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5905,7 +5917,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>LPNCCX1B2941120</t>
+          <t>LPNDEL4AA3631346</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -5913,12 +5925,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-29T15:27:20+00:00</t>
+          <t>2026-06-07T16:09:41+00:00</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>404-8418070-5981124</t>
+          <t>405-9852474-3831538</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5951,17 +5963,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>LPNCCX1B4508596</t>
+          <t>LPNCCX1B4179343</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -5969,32 +5981,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-29T05:18:33+00:00</t>
+          <t>2026-06-07T11:20:49+00:00</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>171-0407209-4266756</t>
+          <t>406-9783608-9093148</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -6002,22 +6014,22 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937926</t>
+          <t>LPNLMAA0016237</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -6025,32 +6037,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-28T11:56:49+00:00</t>
+          <t>2026-06-07T10:24:17+00:00</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>407-4902279-0189155</t>
+          <t>406-6392223-8173930</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -6058,12 +6070,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6073,7 +6085,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7363000</t>
+          <t>LPNBLX1C047099</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -6081,12 +6093,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-28T08:40:02+00:00</t>
+          <t>2026-06-06T10:45:59+00:00</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>408-1128142-0248321</t>
+          <t>406-9111649-3125130</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6114,7 +6126,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6124,12 +6136,12 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>DAMAGED_BY_FC</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937756</t>
+          <t>LPNBOM5F5579985</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -6137,12 +6149,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-28T06:36:17+00:00</t>
+          <t>2026-06-05T09:54:50+00:00</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>402-4776409-4471512</t>
+          <t>405-7328472-7893901</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6170,7 +6182,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6180,12 +6192,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7286354</t>
+          <t>LPNDEL4AA3679697</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -6193,32 +6205,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-27T12:42:16+00:00</t>
+          <t>2026-06-05T08:35:28+00:00</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>404-6762038-7137955</t>
+          <t>404-9218549-9930734</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79659</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZDA2F</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, Black, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -6226,7 +6238,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6236,12 +6248,12 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937575</t>
+          <t>LPNSDEGF082043</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -6249,12 +6261,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-27T09:44:17+00:00</t>
+          <t>2026-06-05T08:17:03+00:00</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>403-3444915-0085109</t>
+          <t>171-6540897-0152357</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6282,7 +6294,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6292,12 +6304,12 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7362686</t>
+          <t>LPNDEL4AA3679650</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -6305,32 +6317,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-27T09:25:47+00:00</t>
+          <t>2026-06-05T04:33:06+00:00</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>405-8410325-7933918</t>
+          <t>171-6354444-3723505</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -6338,22 +6350,22 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>LPNSPUN53913</t>
+          <t>LPNBOM5F5574228</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -6361,12 +6373,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-26T23:02:43+00:00</t>
+          <t>2026-06-05T04:28:18+00:00</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>407-0645348-4574732</t>
+          <t>406-6103690-9310748</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6394,22 +6406,22 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>LPNCCX1B5292913</t>
+          <t>LPNDEL4AA3679535</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -6417,12 +6429,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-26T11:06:29+00:00</t>
+          <t>2026-06-04T03:47:36+00:00</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>402-2949127-9513917</t>
+          <t>406-2278126-7841949</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6460,12 +6472,12 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937227</t>
+          <t>LPNDEL4AA3679185</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -6473,12 +6485,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-26T08:48:10+00:00</t>
+          <t>2026-06-01T09:32:55+00:00</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>403-5510263-6469912</t>
+          <t>402-3794541-2581168</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6521,7 +6533,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273675</t>
+          <t>LPNBLR7Y4743333</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -6529,12 +6541,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-25T15:22:25+00:00</t>
+          <t>2026-06-01T04:42:36+00:00</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>402-5203149-1906724</t>
+          <t>408-0143238-4374708</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6562,7 +6574,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6572,12 +6584,12 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>LPNCCX1B5331017</t>
+          <t>LPNBOM5F5524445</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -6585,12 +6597,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-24T09:24:39+00:00</t>
+          <t>2026-06-01T03:58:27+00:00</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>171-7709339-0701117</t>
+          <t>406-4355667-6072332</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6628,12 +6640,12 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273169</t>
+          <t>LPNBLR7Y4743158</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -6641,12 +6653,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-24T08:29:52+00:00</t>
+          <t>2026-05-31T09:10:34+00:00</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>406-7042486-7436314</t>
+          <t>404-2518539-4406712</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6674,22 +6686,22 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273150</t>
+          <t>LPNDEL4AA3976607</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -6697,32 +6709,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-23T23:07:27+00:00</t>
+          <t>2026-05-30T22:18:28+00:00</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>406-2954542-5857925</t>
+          <t>407-1474707-0478726</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -6730,22 +6742,22 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>LPNSBOB1370158</t>
+          <t>LPNCCX1B4554643</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
@@ -6753,12 +6765,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-23T10:58:04+00:00</t>
+          <t>2026-05-30T04:13:42+00:00</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>406-4758725-2077907</t>
+          <t>406-7941139-9225906</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6786,12 +6798,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6801,7 +6813,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7272896</t>
+          <t>LPNBOM5F5507643</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -6809,32 +6821,32 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-22T09:58:26+00:00</t>
+          <t>2026-05-29T23:01:15+00:00</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>403-7800011-6937966</t>
+          <t>405-0096078-8521126</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -6842,7 +6854,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6857,7 +6869,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>LPNSDEGF010003</t>
+          <t>LPNCCX1B2941120</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
@@ -6865,32 +6877,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-21T04:38:32+00:00</t>
+          <t>2026-05-29T15:27:20+00:00</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>403-2400247-1930753</t>
+          <t>404-8418070-5981124</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -6898,7 +6910,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -6913,7 +6925,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>LPNSDEGF099136</t>
+          <t>LPNCCX1B4508596</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -6921,12 +6933,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-20T11:30:45+00:00</t>
+          <t>2026-05-29T05:18:33+00:00</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>406-2648444-6601917</t>
+          <t>171-0407209-4266756</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6959,17 +6971,17 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2147464</t>
+          <t>LPNDEL4AA3937926</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -6977,32 +6989,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-19T08:03:32+00:00</t>
+          <t>2026-05-28T11:56:49+00:00</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>405-4744559-6958733</t>
+          <t>407-4902279-0189155</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -7010,7 +7022,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7020,12 +7032,12 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>LPNSDEGF097985</t>
+          <t>LPNBLR7Y7363000</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -7033,32 +7045,32 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-18T11:36:05+00:00</t>
+          <t>2026-05-28T08:40:02+00:00</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>171-1585723-0908356</t>
+          <t>408-1128142-0248321</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -7066,22 +7078,22 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DAMAGED_BY_FC</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>LPNBLX1C155145</t>
+          <t>LPNDEL4AA3937756</t>
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
@@ -7089,32 +7101,32 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-15T08:29:30+00:00</t>
+          <t>2026-05-28T06:36:17+00:00</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>402-4856546-1261939</t>
+          <t>402-4776409-4471512</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -7122,7 +7134,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7132,12 +7144,12 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>LPNSDEGF074601</t>
+          <t>LPNBLR7Y7286354</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -7145,32 +7157,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-13T13:50:43+00:00</t>
+          <t>2026-05-27T12:42:16+00:00</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>403-7495250-9937954</t>
+          <t>404-6762038-7137955</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -7178,12 +7190,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7193,7 +7205,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>LPNBLX1C154096</t>
+          <t>LPNDEL4AA3937575</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -7201,32 +7213,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-12T07:19:54+00:00</t>
+          <t>2026-05-27T09:44:17+00:00</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>408-0473775-6641108</t>
+          <t>403-3444915-0085109</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -7234,22 +7246,22 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>LPNSBOB1362246</t>
+          <t>LPNBLR7Y7362686</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -7257,32 +7269,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-11T10:31:39+00:00</t>
+          <t>2026-05-27T09:25:47+00:00</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>404-1750959-8518722</t>
+          <t>405-8410325-7933918</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -7290,7 +7302,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7300,12 +7312,12 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>LPNSHTI00006165</t>
+          <t>LPNSPUN53913</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
@@ -7313,12 +7325,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-10T09:15:43+00:00</t>
+          <t>2026-05-26T23:02:43+00:00</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>402-1548587-3227555</t>
+          <t>407-0645348-4574732</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7346,7 +7358,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7361,7 +7373,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>LPNBOM5F5057136</t>
+          <t>LPNCCX1B5292913</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -7369,32 +7381,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-08T15:43:17+00:00</t>
+          <t>2026-05-26T11:06:29+00:00</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>402-8374307-7441113</t>
+          <t>402-2949127-9513917</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -7402,22 +7414,22 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>LPNSDEGF064205</t>
+          <t>LPNDEL4AA3937227</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -7425,32 +7437,32 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-08T13:25:23+00:00</t>
+          <t>2026-05-26T08:48:10+00:00</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>171-7381542-8368365</t>
+          <t>403-5510263-6469912</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -7458,22 +7470,22 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>LPNBLX1C042486</t>
+          <t>LPNBLR7Y7273675</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -7481,12 +7493,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-08T07:49:38+00:00</t>
+          <t>2026-05-25T15:22:25+00:00</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>403-3056736-6311553</t>
+          <t>402-5203149-1906724</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7514,22 +7526,22 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5321963</t>
+          <t>LPNCCX1B5331017</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -7537,32 +7549,32 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-06T06:52:28+00:00</t>
+          <t>2026-05-24T09:24:39+00:00</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>403-2654029-0716338</t>
+          <t>171-7709339-0701117</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -7570,7 +7582,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7580,12 +7592,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>LPNSHTI00005958</t>
+          <t>LPNBLR7Y7273169</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -7593,12 +7605,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-06T05:51:00+00:00</t>
+          <t>2026-05-24T08:29:52+00:00</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>404-9426288-6037168</t>
+          <t>406-7042486-7436314</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7626,22 +7638,22 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>LPNBOM5F5236158</t>
+          <t>LPNBLR7Y7273150</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -7649,32 +7661,32 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-02T04:54:42+00:00</t>
+          <t>2026-05-23T23:07:27+00:00</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>407-6201969-2856316</t>
+          <t>406-2954542-5857925</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -7682,22 +7694,22 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>LPNLMAA0004457</t>
+          <t>LPNSBOB1370158</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -7705,32 +7717,32 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-04-28T08:52:43+00:00</t>
+          <t>2026-05-23T10:58:04+00:00</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>171-6713241-8377149</t>
+          <t>406-4758725-2077907</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -7738,22 +7750,22 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>LPNLMAA0003844</t>
+          <t>LPNBLR7Y7272896</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -7761,32 +7773,32 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-04-27T06:04:11+00:00</t>
+          <t>2026-05-22T09:58:26+00:00</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>403-6021111-3520325</t>
+          <t>403-7800011-6937966</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -7794,7 +7806,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7809,7 +7821,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>LPNLMAA0003335</t>
+          <t>LPNSDEGF010003</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -7817,32 +7829,32 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-04-26T08:09:27+00:00</t>
+          <t>2026-05-21T04:38:32+00:00</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>402-4881396-1030704</t>
+          <t>403-2400247-1930753</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -7850,7 +7862,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -7860,12 +7872,12 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2253845</t>
+          <t>LPNSDEGF099136</t>
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
@@ -7873,12 +7885,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-04-26T04:14:08+00:00</t>
+          <t>2026-05-20T11:30:45+00:00</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>408-1134010-7973925</t>
+          <t>406-2648444-6601917</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7906,7 +7918,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7916,12 +7928,12 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5321963</t>
+          <t>LPNDEL4AA2147464</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
@@ -7929,32 +7941,32 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-04-26T03:22:50+00:00</t>
+          <t>2026-05-19T08:03:32+00:00</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>406-9614580-4613163</t>
+          <t>405-4744559-6958733</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -7962,22 +7974,22 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>LPNSPUN46511</t>
+          <t>LPNSDEGF097985</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -7985,32 +7997,32 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-04-25T05:33:44+00:00</t>
+          <t>2026-05-18T11:36:05+00:00</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>171-3077342-1790757</t>
+          <t>171-1585723-0908356</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -8018,7 +8030,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8028,12 +8040,12 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>LPNLMAA0002840</t>
+          <t>LPNBLX1C155145</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -8041,32 +8053,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-04-25T03:48:59+00:00</t>
+          <t>2026-05-15T08:29:30+00:00</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>404-4908572-3783532</t>
+          <t>402-4856546-1261939</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>X002FOAUSJ</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -8074,12 +8086,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8089,7 +8101,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>LPNBLR7Y6090385</t>
+          <t>LPNSDEGF074601</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
@@ -8097,32 +8109,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-04-22T10:55:13+00:00</t>
+          <t>2026-05-13T13:50:43+00:00</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>407-4868470-8499505</t>
+          <t>403-7495250-9937954</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -8130,12 +8142,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8145,7 +8157,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>LPNLMAA0001354</t>
+          <t>LPNBLX1C154096</t>
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
@@ -8153,32 +8165,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-04-22T04:17:57+00:00</t>
+          <t>2026-05-12T07:19:54+00:00</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>406-5030280-5555520</t>
+          <t>408-0473775-6641108</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -8186,7 +8198,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8196,12 +8208,12 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>LPNSDEGF117193</t>
+          <t>LPNSBOB1362246</t>
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
@@ -8209,32 +8221,32 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-04-21T20:42:51+00:00</t>
+          <t>2026-05-11T10:31:39+00:00</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>403-7744956-9735520</t>
+          <t>404-1750959-8518722</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -8242,7 +8254,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8252,12 +8264,12 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>LPNCCX1B1519621</t>
+          <t>LPNSHTI00006165</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
@@ -8265,32 +8277,32 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-04-20T05:04:40+00:00</t>
+          <t>2026-05-10T09:15:43+00:00</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>171-5598784-9947515</t>
+          <t>402-1548587-3227555</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>X002FOAUSJ</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -8298,7 +8310,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8308,12 +8320,12 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5552415</t>
+          <t>LPNBOM5F5057136</t>
         </is>
       </c>
       <c r="L141" t="inlineStr"/>
@@ -8321,32 +8333,32 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-04-18T05:41:14+00:00</t>
+          <t>2026-05-08T15:43:17+00:00</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>404-0309463-1310709</t>
+          <t>402-8374307-7441113</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -8354,22 +8366,22 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>LPNDEL4AA0788989</t>
+          <t>LPNSDEGF064205</t>
         </is>
       </c>
       <c r="L142" t="inlineStr"/>
@@ -8377,32 +8389,32 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-04-15T13:55:57+00:00</t>
+          <t>2026-05-08T13:25:23+00:00</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>407-7885481-2445152</t>
+          <t>171-7381542-8368365</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -8410,22 +8422,22 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>SMAB</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>LPNSMAB1153810</t>
+          <t>LPNBLX1C042486</t>
         </is>
       </c>
       <c r="L143" t="inlineStr"/>
@@ -8433,32 +8445,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-04-15T08:47:44+00:00</t>
+          <t>2026-05-08T07:49:38+00:00</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>407-3585151-4323522</t>
+          <t>403-3056736-6311553</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -8466,22 +8478,22 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>LPNSDEGF027993</t>
+          <t>LPNBLR7Y5321963</t>
         </is>
       </c>
       <c r="L144" t="inlineStr"/>
@@ -8489,32 +8501,32 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-04-12T10:47:54+00:00</t>
+          <t>2026-05-06T06:52:28+00:00</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>407-0802588-3857957</t>
+          <t>403-2654029-0716338</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -8522,7 +8534,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8532,12 +8544,12 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>LPNSDEGF026167</t>
+          <t>LPNSHTI00005958</t>
         </is>
       </c>
       <c r="L145" t="inlineStr"/>
@@ -8545,32 +8557,32 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-04-11T06:17:07+00:00</t>
+          <t>2026-05-06T05:51:00+00:00</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>408-2417441-1123516</t>
+          <t>404-9426288-6037168</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>FBK76764</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>B0BMV1WPHL</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>X00242TZTH</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>White Mulberry Ergonomic Sit Stand Desk | Standing Desk for Office, Home &amp; Study | Everyday Ergonomic Desk | 1200mm x 600mm | Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -8578,12 +8590,12 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8593,7 +8605,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>LPNSHTI00004704</t>
+          <t>LPNBOM5F5236158</t>
         </is>
       </c>
       <c r="L146" t="inlineStr"/>
@@ -8601,32 +8613,32 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-04-09T03:38:39+00:00</t>
+          <t>2026-05-02T04:54:42+00:00</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>406-0798045-4525148</t>
+          <t>407-6201969-2856316</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -8634,7 +8646,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -8644,12 +8656,12 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>LPNSDEGF168570</t>
+          <t>LPNLMAA0004457</t>
         </is>
       </c>
       <c r="L147" t="inlineStr"/>
@@ -8657,32 +8669,32 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-04-08T10:17:09+00:00</t>
+          <t>2026-04-28T08:52:43+00:00</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>406-3115014-9939528</t>
+          <t>171-6713241-8377149</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -8690,22 +8702,22 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2155169</t>
+          <t>LPNLMAA0003844</t>
         </is>
       </c>
       <c r="L148" t="inlineStr"/>
@@ -8713,32 +8725,32 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-04-08T09:53:57+00:00</t>
+          <t>2026-04-27T06:04:11+00:00</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>403-7697438-5361950</t>
+          <t>403-6021111-3520325</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -8746,25 +8758,697 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
+          <t>SELLABLE</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>UNDELIVERABLE_REFUSED</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>LPNLMAA0003335</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-04-26T08:09:27+00:00</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>402-4881396-1030704</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>FBA79167</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>X001Y5UYX1</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>DEL4</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>SELLABLE</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>UNDELIVERABLE_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>LPNDEL4AA2253845</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-04-26T04:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>408-1134010-7973925</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>FBA79167</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>X001Y5UYX1</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>BLR7</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>SELLABLE</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>QUALITY_UNACCEPTABLE</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>LPNBLR7Y5321963</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-04-26T03:22:50+00:00</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>406-9614580-4613163</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>FBA76417</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>X001MZZQ8V</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>SPUN</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
           <t>CARRIER_DAMAGED</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr">
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>QUALITY_UNACCEPTABLE</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>LPNSPUN46511</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-04-25T05:33:44+00:00</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>171-3077342-1790757</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>FBA79662</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>B0DQ4YWSMC</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>X00270AW07</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>LMAA</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>CARRIER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>QUALITY_UNACCEPTABLE</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>LPNLMAA0002840</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-04-25T03:48:59+00:00</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>404-4908572-3783532</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>FBA76864</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>B0BPLZ5CGV</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>X002FOAUSJ</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>BLR7</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>CARRIER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
         <is>
           <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>LPNMAA4Z0044638</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>LPNBLR7Y6090385</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-04-22T10:55:13+00:00</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>407-4868470-8499505</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>FBA76417</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>X001MZZQ8V</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>LMAA</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>SELLABLE</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>UNDELIVERABLE_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>LPNLMAA0001354</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-04-22T04:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>406-5030280-5555520</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>FBA76416</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>B0BFW59TRG</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>X001N02VPV</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>SDEG</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>CUSTOMER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>SWITCHEROO</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>LPNSDEGF117193</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-04-21T20:42:51+00:00</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>403-7744956-9735520</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>FBA79167</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>X001Y5UYX1</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>CCX1</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>CARRIER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>UNDELIVERABLE_REFUSED</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>LPNCCX1B1519621</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-04-20T05:04:40+00:00</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>171-5598784-9947515</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>FBA76864</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>B0BPLZ5CGV</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>X002FOAUSJ</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>BLR7</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>CUSTOMER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>DEFECTIVE</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>LPNBLR7Y5552415</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-04-18T05:41:14+00:00</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>404-0309463-1310709</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>FBA79167</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>X001Y5UYX1</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>DEL4</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>SELLABLE</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>UNDELIVERABLE_REFUSED</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>LPNDEL4AA0788989</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-04-15T13:55:57+00:00</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>407-7885481-2445152</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>FBA76417</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>X001MZZQ8V</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>SMAB</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>CARRIER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>UNDELIVERABLE_REFUSED</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>LPNSMAB1153810</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-04-15T08:47:44+00:00</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>407-3585151-4323522</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>FBA76417</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>X001MZZQ8V</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>1</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>SDEG</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>CUSTOMER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>DEFECTIVE</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>LPNSDEGF027993</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/raw/returns/WhiteMulberry.xlsx
+++ b/data/raw/returns/WhiteMulberry.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,66 +413,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L161"/>
+  <dimension ref="A1:L162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>return-date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>order-id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>fnsku</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>product-name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>fulfillment-center-id</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>detailed-disposition</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>license-plate-number</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>customer-comments</t>
         </is>
@@ -493,32 +481,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-13T07:03:07+00:00</t>
+          <t>2026-07-13T10:39:08+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>405-0681203-5996333</t>
+          <t>406-6722735-1149137</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -526,22 +514,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4739661</t>
+          <t>LPNSPUN63412</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -549,32 +537,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-12T18:38:59+00:00</t>
+          <t>2026-07-13T07:03:07+00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>408-6399475-0434747</t>
+          <t>405-0681203-5996333</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -582,7 +570,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -592,12 +580,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>LPNSDEGA045352</t>
+          <t>LPNBLR8Z4739661</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -605,32 +593,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-12T12:11:34+00:00</t>
+          <t>2026-07-12T18:38:59+00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>405-3614422-8705902</t>
+          <t>408-6399475-0434747</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -638,22 +626,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LPNBLR7Y8671012</t>
+          <t>LPNSDEGA045352</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -661,12 +649,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-12T11:18:57+00:00</t>
+          <t>2026-07-12T12:11:34+00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>171-1476461-2065906</t>
+          <t>405-3614422-8705902</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -694,7 +682,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -704,12 +692,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3731833</t>
+          <t>LPNBLR7Y8671012</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -717,12 +705,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-12T09:48:52+00:00</t>
+          <t>2026-07-12T11:18:57+00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>407-1690927-4321928</t>
+          <t>171-1476461-2065906</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -750,22 +738,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LPNBLR7Y8670945</t>
+          <t>LPNDEL4AA3731833</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -773,32 +761,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-11T15:19:09+00:00</t>
+          <t>2026-07-12T09:48:52+00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>407-1918094-9025938</t>
+          <t>407-1690927-4321928</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -806,12 +794,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -821,7 +809,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LPNSDEGA049360</t>
+          <t>LPNBLR7Y8670945</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -829,32 +817,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-11T04:41:50+00:00</t>
+          <t>2026-07-11T15:19:09+00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>402-4732739-0177111</t>
+          <t>407-1918094-9025938</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -862,7 +850,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -877,7 +865,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>LPNBLR8Z3333062</t>
+          <t>LPNSDEGA049360</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -885,32 +873,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10T11:34:53+00:00</t>
+          <t>2026-07-11T04:41:50+00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>402-4127261-8261957</t>
+          <t>402-4732739-0177111</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -918,7 +906,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -928,12 +916,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>LPNSHTI00014264</t>
+          <t>LPNBLR8Z3333062</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -941,32 +929,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10T11:22:36+00:00</t>
+          <t>2026-07-10T11:34:53+00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>402-4627500-7082749</t>
+          <t>402-4127261-8261957</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -974,7 +962,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -984,12 +972,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3300048</t>
+          <t>LPNSHTI00014264</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -997,12 +985,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-10T08:11:09+00:00</t>
+          <t>2026-07-10T11:22:36+00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>407-2441104-3469917</t>
+          <t>402-4627500-7082749</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1030,7 +1018,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1040,12 +1028,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>LPNBLR8Z3342252</t>
+          <t>LPNDEL4AA3300048</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1053,12 +1041,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10T03:24:58+00:00</t>
+          <t>2026-07-10T08:11:09+00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>404-4351909-9563522</t>
+          <t>407-2441104-3469917</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1086,7 +1074,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1101,7 +1089,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3919248</t>
+          <t>LPNBLR8Z3342252</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1109,12 +1097,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09T04:11:50+00:00</t>
+          <t>2026-07-10T03:24:58+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>402-4684050-2008333</t>
+          <t>404-4351909-9563522</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1142,12 +1130,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1157,7 +1145,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4305793</t>
+          <t>LPNDEL4AA3919248</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1165,12 +1153,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08T20:07:54+00:00</t>
+          <t>2026-07-09T04:11:50+00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>171-5139545-1381155</t>
+          <t>402-4684050-2008333</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1198,12 +1186,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>DAMAGED</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1213,7 +1201,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>LPNCCX1A7424707</t>
+          <t>LPNBLR8Z4305793</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1221,12 +1209,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08T06:12:17+00:00</t>
+          <t>2026-07-08T20:07:54+00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>406-6599709-8196355</t>
+          <t>171-5139545-1381155</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1254,22 +1242,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3951631</t>
+          <t>LPNCCX1A7424707</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1277,32 +1265,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-07T14:57:35+00:00</t>
+          <t>2026-07-08T06:12:17+00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>403-7360454-8443505</t>
+          <t>406-6599709-8196355</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1310,22 +1298,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LPNSDEGA048066</t>
+          <t>LPNDEL4AA3951631</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1333,32 +1321,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-07T12:17:02+00:00</t>
+          <t>2026-07-07T14:57:35+00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>404-3937409-4657901</t>
+          <t>403-7360454-8443505</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1366,7 +1354,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1376,12 +1364,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3951212</t>
+          <t>LPNSDEGA048066</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1389,32 +1377,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-07T09:02:25+00:00</t>
+          <t>2026-07-07T12:17:02+00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>406-5155095-5494705</t>
+          <t>404-3937409-4657901</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1422,7 +1410,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1432,12 +1420,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>LPNLMAA0027050</t>
+          <t>LPNDEL4AA3951212</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1445,32 +1433,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-06T21:23:52+00:00</t>
+          <t>2026-07-07T09:02:25+00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>406-6590377-2621105</t>
+          <t>406-5155095-5494705</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1478,22 +1466,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4815212</t>
+          <t>LPNLMAA0027050</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1501,12 +1489,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-06T21:22:13+00:00</t>
+          <t>2026-07-06T21:23:52+00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>407-1625560-1723518</t>
+          <t>406-6590377-2621105</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1549,7 +1537,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4815211</t>
+          <t>LPNBLR8Z4815212</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1557,12 +1545,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-06T12:33:49+00:00</t>
+          <t>2026-07-06T21:22:13+00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>404-5401376-5513111</t>
+          <t>407-1625560-1723518</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1590,22 +1578,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>LPNHYD8EJ59560</t>
+          <t>LPNBLR8Z4815211</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1613,12 +1601,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-05T20:21:02+00:00</t>
+          <t>2026-07-06T12:33:49+00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>408-9802796-1211539</t>
+          <t>404-5401376-5513111</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1646,22 +1634,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>LPNCCX1A8722775</t>
+          <t>LPNHYD8EJ59560</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1669,12 +1657,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-05T07:23:15+00:00</t>
+          <t>2026-07-05T20:21:02+00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>407-2308442-1499512</t>
+          <t>408-9802796-1211539</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1702,7 +1690,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1717,7 +1705,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4813630</t>
+          <t>LPNCCX1A8722775</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1725,12 +1713,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-05T06:48:36+00:00</t>
+          <t>2026-07-05T07:23:15+00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>407-8970250-4543519</t>
+          <t>407-2308442-1499512</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1773,7 +1761,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4814250</t>
+          <t>LPNBLR8Z4813630</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1781,12 +1769,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-05T04:41:04+00:00</t>
+          <t>2026-07-05T06:48:36+00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>405-1245096-1377920</t>
+          <t>407-8970250-4543519</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1814,7 +1802,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1829,7 +1817,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>LPNBOM5F5826513</t>
+          <t>LPNBLR8Z4814250</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1837,12 +1825,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-04T12:12:23+00:00</t>
+          <t>2026-07-05T04:41:04+00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>404-7913029-6157962</t>
+          <t>405-1245096-1377920</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1870,7 +1858,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1880,12 +1868,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>LPNHYD8EJ58729</t>
+          <t>LPNBOM5F5826513</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1893,12 +1881,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-04T08:48:05+00:00</t>
+          <t>2026-07-04T12:12:23+00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>405-3423037-8257160</t>
+          <t>404-7913029-6157962</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1926,22 +1914,22 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>DAMAGED_BY_FC</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3108992</t>
+          <t>LPNHYD8EJ58729</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1949,12 +1937,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-04T04:21:28+00:00</t>
+          <t>2026-07-04T08:48:05+00:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>405-3646440-7662737</t>
+          <t>405-3423037-8257160</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1982,22 +1970,22 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>DAMAGED_BY_FC</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>LPNBOM5F5455146</t>
+          <t>LPNDEL4AA3108992</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -2005,12 +1993,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-03T19:29:57+00:00</t>
+          <t>2026-07-04T04:21:28+00:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>403-0547582-3197132</t>
+          <t>405-3646440-7662737</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2038,7 +2026,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2048,12 +2036,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>LPNCCX1B4102605</t>
+          <t>LPNBOM5F5455146</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2061,32 +2049,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-03T14:02:46+00:00</t>
+          <t>2026-07-03T19:29:57+00:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>171-7464293-7220360</t>
+          <t>403-0547582-3197132</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2094,22 +2082,22 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>NO_REASON_GIVEN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>LPNSBOB1392052</t>
+          <t>LPNCCX1B4102605</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2117,32 +2105,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-03T11:38:57+00:00</t>
+          <t>2026-07-03T14:02:46+00:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>403-6645337-2467540</t>
+          <t>171-7464293-7220360</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2150,22 +2138,22 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NO_REASON_GIVEN</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2082724</t>
+          <t>LPNSBOB1392052</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2173,12 +2161,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-02T17:30:33+00:00</t>
+          <t>2026-07-03T11:38:57+00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>402-1004506-0818747</t>
+          <t>403-6645337-2467540</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2206,12 +2194,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2221,7 +2209,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>LPNBLR8Z5514346</t>
+          <t>LPNDEL4AA2082724</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2229,12 +2217,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-02T14:56:15+00:00</t>
+          <t>2026-07-02T17:30:33+00:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>407-7003476-1816350</t>
+          <t>402-1004506-0818747</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2262,7 +2250,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2272,12 +2260,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>NO_REASON_GIVEN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3108265</t>
+          <t>LPNBLR8Z5514346</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2285,12 +2273,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-02T11:24:54+00:00</t>
+          <t>2026-07-02T14:56:15+00:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>408-9621782-0261114</t>
+          <t>407-7003476-1816350</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2328,12 +2316,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>NO_REASON_GIVEN</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3950616</t>
+          <t>LPNDEL4AA3108265</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2341,12 +2329,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-02T06:41:10+00:00</t>
+          <t>2026-07-02T11:24:54+00:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>403-6072724-5581966</t>
+          <t>408-9621782-0261114</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2374,7 +2362,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2384,12 +2372,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4303742</t>
+          <t>LPNDEL4AA3950616</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2397,12 +2385,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-01T22:20:26+00:00</t>
+          <t>2026-07-02T06:41:10+00:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>402-4598141-9561917</t>
+          <t>403-6072724-5581966</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2430,7 +2418,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2440,12 +2428,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>LPNCCX1B4170658</t>
+          <t>LPNBLR8Z4303742</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2453,32 +2441,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-01T15:09:10+00:00</t>
+          <t>2026-07-01T22:20:26+00:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>402-3081497-7409144</t>
+          <t>402-4598141-9561917</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2486,22 +2474,22 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>LPNBLX1C093497</t>
+          <t>LPNCCX1B4170658</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2509,32 +2497,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-01T09:24:20+00:00</t>
+          <t>2026-07-01T15:09:10+00:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>405-3824107-9644368</t>
+          <t>402-3081497-7409144</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2542,22 +2530,22 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>LPNBOM5F5465051</t>
+          <t>LPNBLX1C093497</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -2565,12 +2553,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-01T06:49:32+00:00</t>
+          <t>2026-07-01T09:24:20+00:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>404-6104605-6788338</t>
+          <t>405-3824107-9644368</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2608,12 +2596,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>LPNBOM5F5435891</t>
+          <t>LPNBOM5F5465051</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -2621,12 +2609,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-01T05:46:54+00:00</t>
+          <t>2026-07-01T06:49:32+00:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>407-2497737-1874765</t>
+          <t>404-6104605-6788338</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2669,7 +2657,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>LPNBOM5F5407228</t>
+          <t>LPNBOM5F5435891</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2677,12 +2665,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-01T03:55:07+00:00</t>
+          <t>2026-07-01T05:46:54+00:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>403-6044286-1801115</t>
+          <t>407-2497737-1874765</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2710,7 +2698,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>CCX2</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2725,7 +2713,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>LPNCCX2B2262224</t>
+          <t>LPNBOM5F5407228</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -2733,12 +2721,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-29T12:22:41+00:00</t>
+          <t>2026-07-01T03:55:07+00:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>405-6904525-0069903</t>
+          <t>403-6044286-1801115</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2766,22 +2754,22 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>CCX2</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>LPNHYD8EF20503</t>
+          <t>LPNCCX2B2262224</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -2789,12 +2777,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-28T19:38:03+00:00</t>
+          <t>2026-06-29T12:22:41+00:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>402-4296829-1337133</t>
+          <t>405-6904525-0069903</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2822,22 +2810,22 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>LPNCCX1B2440445</t>
+          <t>LPNHYD8EF20503</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2845,12 +2833,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-28T08:39:43+00:00</t>
+          <t>2026-06-28T19:38:03+00:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>402-6090489-2032337</t>
+          <t>402-4296829-1337133</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2878,7 +2866,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2893,7 +2881,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7855923</t>
+          <t>LPNCCX1B2440445</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -2901,12 +2889,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-27T11:00:01+00:00</t>
+          <t>2026-06-28T08:39:43+00:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>408-3896665-0021948</t>
+          <t>402-6090489-2032337</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2939,17 +2927,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7855626</t>
+          <t>LPNBLR7Y7855923</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -2957,32 +2945,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-27T10:32:22+00:00</t>
+          <t>2026-06-27T11:00:01+00:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>407-5462207-4616334</t>
+          <t>408-3896665-0021948</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2990,12 +2978,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3005,7 +2993,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>LPNSBOB1388621</t>
+          <t>LPNBLR7Y7855626</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3013,32 +3001,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-26T18:08:18+00:00</t>
+          <t>2026-06-27T10:32:22+00:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>171-5586406-9945900</t>
+          <t>407-5462207-4616334</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3056,12 +3044,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>LPNSBOB1388302</t>
+          <t>LPNSBOB1388621</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3069,12 +3057,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-26T06:57:42+00:00</t>
+          <t>2026-06-26T18:08:18+00:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>405-2746376-7486724</t>
+          <t>171-5586406-9945900</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3102,22 +3090,22 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>LPNBLX1C140655</t>
+          <t>LPNSBOB1388302</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -3125,32 +3113,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-26T05:19:18+00:00</t>
+          <t>2026-06-26T06:57:42+00:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>406-4442109-5330751</t>
+          <t>405-2746376-7486724</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3158,7 +3146,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3173,7 +3161,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3990308</t>
+          <t>LPNBLX1C140655</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -3181,32 +3169,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-25T18:24:43+00:00</t>
+          <t>2026-06-26T05:19:18+00:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>405-2433007-9289947</t>
+          <t>406-4442109-5330751</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3214,22 +3202,22 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>LPNSBOB1387687</t>
+          <t>LPNDEL4AA3990308</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3237,32 +3225,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-25T10:05:58+00:00</t>
+          <t>2026-06-25T18:24:43+00:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>407-3034951-4675566</t>
+          <t>405-2433007-9289947</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -3270,22 +3258,22 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2273850</t>
+          <t>LPNSBOB1387687</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3293,32 +3281,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-24T08:29:31+00:00</t>
+          <t>2026-06-25T10:05:58+00:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>402-0120877-0312362</t>
+          <t>407-3034951-4675566</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3326,22 +3314,22 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>LPNSPUN59333</t>
+          <t>LPNMAA4Z2273850</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -3349,32 +3337,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-24T06:17:22+00:00</t>
+          <t>2026-06-24T08:29:31+00:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>403-8864299-1768360</t>
+          <t>402-0120877-0312362</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3382,22 +3370,22 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7854241</t>
+          <t>LPNSPUN59333</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -3405,32 +3393,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-23T15:36:47+00:00</t>
+          <t>2026-06-24T06:17:22+00:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>402-8717460-5700310</t>
+          <t>403-8864299-1768360</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3438,7 +3426,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3448,12 +3436,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>LPNHDX8A005873</t>
+          <t>LPNBLR7Y7854241</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -3461,32 +3449,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-23T11:54:27+00:00</t>
+          <t>2026-06-23T15:36:47+00:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>403-7688253-5273167</t>
+          <t>402-8717460-5700310</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3494,22 +3482,22 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>LPNBOM5F5694482</t>
+          <t>LPNHDX8A005873</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -3517,12 +3505,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-23T09:27:19+00:00</t>
+          <t>2026-06-23T11:54:27+00:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>408-9857262-4357961</t>
+          <t>403-7688253-5273167</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3550,7 +3538,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3565,7 +3553,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7853975</t>
+          <t>LPNBOM5F5694482</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -3573,12 +3561,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-23T08:32:44+00:00</t>
+          <t>2026-06-23T09:27:19+00:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>404-2029470-0977929</t>
+          <t>408-9857262-4357961</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3606,7 +3594,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3616,12 +3604,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3925027</t>
+          <t>LPNBLR7Y7853975</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3629,32 +3617,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-23T06:25:18+00:00</t>
+          <t>2026-06-23T08:32:44+00:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>408-7120729-6837923</t>
+          <t>404-2029470-0977929</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -3662,7 +3650,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3672,12 +3660,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>LPNSBOB1385946</t>
+          <t>LPNDEL4AA3925027</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -3685,12 +3673,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-06-23T05:29:18+00:00</t>
+          <t>2026-06-23T06:25:18+00:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>403-5101653-2865108</t>
+          <t>408-7120729-6837923</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3718,22 +3706,22 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>LPNHDX8005941</t>
+          <t>LPNSBOB1385946</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -3741,32 +3729,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-06-22T15:00:37+00:00</t>
+          <t>2026-06-23T05:29:18+00:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>408-2886313-6344340</t>
+          <t>403-5101653-2865108</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3774,7 +3762,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3784,12 +3772,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>LPNSBOB1385291</t>
+          <t>LPNHDX8005941</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -3797,32 +3785,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-06-22T15:00:11+00:00</t>
+          <t>2026-06-22T15:00:37+00:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>403-4065197-2565940</t>
+          <t>408-2886313-6344340</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -3845,7 +3833,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>LPNSBOB1385290</t>
+          <t>LPNSBOB1385291</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -3853,32 +3841,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-06-22T13:49:32+00:00</t>
+          <t>2026-06-22T15:00:11+00:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>171-3328269-2691534</t>
+          <t>403-4065197-2565940</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -3886,22 +3874,22 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>LPNBLX1C049419</t>
+          <t>LPNSBOB1385290</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -3909,32 +3897,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-06-22T13:44:52+00:00</t>
+          <t>2026-06-22T13:49:32+00:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>407-2806960-6949923</t>
+          <t>171-3328269-2691534</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -3947,17 +3935,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>LPNBLX1C049418</t>
+          <t>LPNBLX1C049419</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -3965,32 +3953,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-06-22T12:43:38+00:00</t>
+          <t>2026-06-22T13:44:52+00:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>402-2531413-4073130</t>
+          <t>407-2806960-6949923</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -3998,22 +3986,22 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>LPNHYD8EF41160</t>
+          <t>LPNBLX1C049418</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4021,12 +4009,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-06-22T09:02:33+00:00</t>
+          <t>2026-06-22T12:43:38+00:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>404-4254275-9061104</t>
+          <t>402-2531413-4073130</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4059,17 +4047,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>LPNHYD8ED01352</t>
+          <t>LPNHYD8EF41160</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -4077,12 +4065,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-06-22T06:27:11+00:00</t>
+          <t>2026-06-22T09:02:33+00:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>407-5289320-1468336</t>
+          <t>404-4254275-9061104</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4110,22 +4098,22 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7287766</t>
+          <t>LPNHYD8ED01352</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -4133,32 +4121,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-06-21T15:48:42+00:00</t>
+          <t>2026-06-22T06:27:11+00:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>408-1433377-1765942</t>
+          <t>407-5289320-1468336</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -4166,22 +4154,22 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>LPNSBOB1385218</t>
+          <t>LPNBLR7Y7287766</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -4189,32 +4177,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-06-21T09:50:13+00:00</t>
+          <t>2026-06-21T15:48:42+00:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>405-1204534-8479517</t>
+          <t>408-1433377-1765942</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -4222,22 +4210,22 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>LPNDEL4AA4027730</t>
+          <t>LPNSBOB1385218</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -4245,12 +4233,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-06-21T08:35:03+00:00</t>
+          <t>2026-06-21T09:50:13+00:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>171-0025867-6612374</t>
+          <t>405-1204534-8479517</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4278,7 +4266,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4293,7 +4281,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7853300</t>
+          <t>LPNDEL4AA4027730</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -4301,12 +4289,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-06-20T13:05:37+00:00</t>
+          <t>2026-06-21T08:35:03+00:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>402-8590404-8535510</t>
+          <t>171-0025867-6612374</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4334,7 +4322,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4349,7 +4337,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>LPNMAA4G898204</t>
+          <t>LPNBLR7Y7853300</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -4357,32 +4345,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-06-19T14:24:04+00:00</t>
+          <t>2026-06-20T13:05:37+00:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>403-3269966-6849104</t>
+          <t>402-8590404-8535510</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -4390,7 +4378,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4405,7 +4393,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>LPNHDX8A004693</t>
+          <t>LPNMAA4G898204</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -4413,32 +4401,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-06-18T09:53:43+00:00</t>
+          <t>2026-06-19T14:24:04+00:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>408-1513827-8090763</t>
+          <t>403-3269966-6849104</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -4446,22 +4434,22 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2273003</t>
+          <t>LPNHDX8A004693</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -4469,32 +4457,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-06-18T09:01:23+00:00</t>
+          <t>2026-06-18T09:53:43+00:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>402-6972876-7770702</t>
+          <t>408-1513827-8090763</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FBA76765</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>B0BMQQQ7YD</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>X001O7YYCV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>White Mulberry Motorized Height Adjustable Sit-Stand Desk | Electronic Height Adjustable | Motor &amp; Memory Preset Controller | Office, Workstation or Home | Carbon Fibre | 120 * 60*H(75-118) cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -4502,22 +4490,22 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>LPNSPUN58279</t>
+          <t>LPNMAA4Z2273003</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -4525,32 +4513,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-06-18T06:34:47+00:00</t>
+          <t>2026-06-18T09:01:23+00:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>171-5595331-6677926</t>
+          <t>402-6972876-7770702</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA76765</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BMQQQ7YD</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001O7YYCV</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Motorized Height Adjustable Sit-Stand Desk | Electronic Height Adjustable | Motor &amp; Memory Preset Controller | Office, Workstation or Home | Carbon Fibre | 120 * 60*H(75-118) cm</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -4568,12 +4556,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>LPNSPUN58332</t>
+          <t>LPNSPUN58279</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -4581,32 +4569,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-06-18T06:13:54+00:00</t>
+          <t>2026-06-18T06:34:47+00:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>405-9716650-4190754</t>
+          <t>171-5595331-6677926</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -4624,12 +4612,12 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>LPNSPUN58348</t>
+          <t>LPNSPUN58332</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -4637,32 +4625,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-06-18T05:06:11+00:00</t>
+          <t>2026-06-18T06:13:54+00:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>405-0242402-8315559</t>
+          <t>405-9716650-4190754</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -4670,7 +4658,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4680,12 +4668,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>LPNHYD8DY89222</t>
+          <t>LPNSPUN58348</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -4693,12 +4681,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-06-18T03:18:32+00:00</t>
+          <t>2026-06-18T05:06:11+00:00</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>403-8790017-7829152</t>
+          <t>405-0242402-8315559</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4741,7 +4729,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>LPNHYD8DY89148</t>
+          <t>LPNHYD8DY89222</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -4749,12 +4737,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-06-17T17:18:11+00:00</t>
+          <t>2026-06-18T03:18:32+00:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>408-3294486-3424329</t>
+          <t>403-8790017-7829152</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4782,12 +4770,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4797,7 +4785,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>LPNCCX1B4206954</t>
+          <t>LPNHYD8DY89148</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -4805,32 +4793,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-06-17T11:01:26+00:00</t>
+          <t>2026-06-17T17:18:11+00:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>171-3399563-8885966</t>
+          <t>408-3294486-3424329</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -4838,22 +4826,22 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>DAMAGED</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>LPNLMAA0019039</t>
+          <t>LPNCCX1B4206954</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -4861,32 +4849,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-06-15T09:24:30+00:00</t>
+          <t>2026-06-17T11:01:26+00:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>171-3194001-5187538</t>
+          <t>171-3399563-8885966</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -4894,22 +4882,22 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>LPNHYD8DY92591</t>
+          <t>LPNLMAA0019039</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -4917,32 +4905,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-06-15T08:53:22+00:00</t>
+          <t>2026-06-15T09:24:30+00:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>406-3765893-9779536</t>
+          <t>171-3194001-5187538</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -4950,22 +4938,22 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>LPNHDX8A0002233</t>
+          <t>LPNHYD8DY92591</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -4973,32 +4961,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-06-14T11:15:53+00:00</t>
+          <t>2026-06-15T08:53:22+00:00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>171-1282309-9677932</t>
+          <t>406-3765893-9779536</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -5006,22 +4994,22 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2198432</t>
+          <t>LPNHDX8A0002233</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -5029,12 +5017,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-06-14T06:26:57+00:00</t>
+          <t>2026-06-14T11:15:53+00:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>407-1845667-2313146</t>
+          <t>171-1282309-9677932</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5062,7 +5050,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5077,7 +5065,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3677498</t>
+          <t>LPNMAA4Z2198432</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -5085,32 +5073,32 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-06-13T12:21:24+00:00</t>
+          <t>2026-06-14T06:26:57+00:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>405-5466299-6857906</t>
+          <t>407-1845667-2313146</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -5118,12 +5106,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5133,7 +5121,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>LPNSBOB1375958</t>
+          <t>LPNDEL4AA3677498</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -5141,32 +5129,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-06-13T12:20:57+00:00</t>
+          <t>2026-06-13T12:21:24+00:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>404-9976514-7382743</t>
+          <t>405-5466299-6857906</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -5179,17 +5167,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>LPNSBOB1375957</t>
+          <t>LPNSBOB1375958</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -5197,32 +5185,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-06-12T11:47:28+00:00</t>
+          <t>2026-06-13T12:20:57+00:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>407-2845785-4936332</t>
+          <t>404-9976514-7382743</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -5230,22 +5218,22 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>LPNSHTI00009280</t>
+          <t>LPNSBOB1375957</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -5253,32 +5241,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-06-11T12:39:34+00:00</t>
+          <t>2026-06-12T11:47:28+00:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>405-0836953-9114742</t>
+          <t>407-2845785-4936332</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -5286,7 +5274,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5296,12 +5284,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>LPNHDX8A001607</t>
+          <t>LPNSHTI00009280</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -5309,32 +5297,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-06-11T10:43:03+00:00</t>
+          <t>2026-06-11T12:39:34+00:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>407-7053626-1929962</t>
+          <t>405-0836953-9114742</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FBA79667</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>B0DQPK7MFH</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>X0027512Z1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk with Shelf|DIY Assembly| Monitor Raising Shelf |Engineered Wood &amp; Sturdy Steel Leg|Perfect for Computer Table Office Home Gaming Study Desk|L(130+130)*45*77cm|White</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -5342,22 +5330,22 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>SCUY</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>LPNSCUY00017897</t>
+          <t>LPNHDX8A001607</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -5365,32 +5353,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-06-10T22:26:08+00:00</t>
+          <t>2026-06-11T10:43:03+00:00</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>404-0639682-6860336</t>
+          <t>407-7053626-1929962</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79667</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQPK7MFH</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0027512Z1</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk with Shelf|DIY Assembly| Monitor Raising Shelf |Engineered Wood &amp; Sturdy Steel Leg|Perfect for Computer Table Office Home Gaming Study Desk|L(130+130)*45*77cm|White</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -5398,7 +5386,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SCUY</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5408,12 +5396,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>LPNCX1B4784440</t>
+          <t>LPNSCUY00017897</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -5421,12 +5409,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-06-10T12:14:02+00:00</t>
+          <t>2026-06-10T22:26:08+00:00</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>171-1027170-0049924</t>
+          <t>404-0639682-6860336</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5454,12 +5442,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5469,7 +5457,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2407733</t>
+          <t>LPNCX1B4784440</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -5477,32 +5465,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-06-10T08:20:03+00:00</t>
+          <t>2026-06-10T12:14:02+00:00</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>406-6295410-5869130</t>
+          <t>171-1027170-0049924</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -5510,22 +5498,22 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>LPNBLX1C159057</t>
+          <t>LPNMAA4Z2407733</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -5533,32 +5521,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-06-10T05:42:02+00:00</t>
+          <t>2026-06-10T08:20:03+00:00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>405-8329990-8940345</t>
+          <t>406-6295410-5869130</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -5566,22 +5554,22 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4745942</t>
+          <t>LPNBLX1C159057</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -5589,12 +5577,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-06-10T04:51:41+00:00</t>
+          <t>2026-06-10T05:42:02+00:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>405-7954322-6131539</t>
+          <t>405-8329990-8940345</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5622,12 +5610,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5637,7 +5625,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>LPNBOM5F5675078</t>
+          <t>LPNBLR7Y4745942</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -5645,12 +5633,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-06-10T03:51:05+00:00</t>
+          <t>2026-06-10T04:51:41+00:00</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>407-5527946-4998741</t>
+          <t>405-7954322-6131539</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5678,12 +5666,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5693,7 +5681,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7287766</t>
+          <t>LPNBOM5F5675078</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -5701,12 +5689,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-06-08T09:59:30+00:00</t>
+          <t>2026-06-10T03:51:05+00:00</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>404-4052225-7064331</t>
+          <t>407-5527946-4998741</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5734,7 +5722,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5744,12 +5732,12 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3631375</t>
+          <t>LPNBLR7Y7287766</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -5757,32 +5745,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-06-08T08:59:50+00:00</t>
+          <t>2026-06-08T09:59:30+00:00</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>404-3123106-0929939</t>
+          <t>404-4052225-7064331</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FBK76387</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>B0BF4S7V8C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>X00242V9DH</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -5790,22 +5778,22 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>LPNSPUN56234</t>
+          <t>LPNDEL4AA3631375</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -5813,32 +5801,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-06-08T08:59:02+00:00</t>
+          <t>2026-06-08T08:59:50+00:00</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>408-8800113-8391502</t>
+          <t>404-3123106-0929939</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBK76387</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0BF4S7V8C</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X00242V9DH</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | White</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -5856,12 +5844,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>LPNSPUN56235</t>
+          <t>LPNSPUN56234</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -5869,32 +5857,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-06-08T08:43:30+00:00</t>
+          <t>2026-06-08T08:59:02+00:00</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>407-4254200-0562712</t>
+          <t>408-8800113-8391502</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -5902,22 +5890,22 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3631346</t>
+          <t>LPNSPUN56235</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -5925,12 +5913,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-06-07T16:09:41+00:00</t>
+          <t>2026-06-08T08:43:30+00:00</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>405-9852474-3831538</t>
+          <t>407-4254200-0562712</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5958,22 +5946,22 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>LPNCCX1B4179343</t>
+          <t>LPNDEL4AA3631346</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -5981,32 +5969,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-06-07T11:20:49+00:00</t>
+          <t>2026-06-07T16:09:41+00:00</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>406-9783608-9093148</t>
+          <t>405-9852474-3831538</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -6014,7 +6002,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6024,12 +6012,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>LPNLMAA0016237</t>
+          <t>LPNCCX1B4179343</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -6037,32 +6025,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-06-07T10:24:17+00:00</t>
+          <t>2026-06-07T11:20:49+00:00</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>406-6392223-8173930</t>
+          <t>406-9783608-9093148</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -6070,12 +6058,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6085,7 +6073,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>LPNBLX1C047099</t>
+          <t>LPNLMAA0016237</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -6093,32 +6081,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-06-06T10:45:59+00:00</t>
+          <t>2026-06-07T10:24:17+00:00</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>406-9111649-3125130</t>
+          <t>406-6392223-8173930</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -6126,22 +6114,22 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>LPNBOM5F5579985</t>
+          <t>LPNBLX1C047099</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -6149,12 +6137,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-06-05T09:54:50+00:00</t>
+          <t>2026-06-06T10:45:59+00:00</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>405-7328472-7893901</t>
+          <t>406-9111649-3125130</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6182,7 +6170,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6192,12 +6180,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679697</t>
+          <t>LPNBOM5F5579985</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -6205,32 +6193,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-06-05T08:35:28+00:00</t>
+          <t>2026-06-05T09:54:50+00:00</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>404-9218549-9930734</t>
+          <t>405-7328472-7893901</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FBA79659</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>X0026ZDA2F</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, Black, 3 Year Warranty</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -6238,7 +6226,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6248,12 +6236,12 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>LPNSDEGF082043</t>
+          <t>LPNDEL4AA3679697</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -6261,32 +6249,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-06-05T08:17:03+00:00</t>
+          <t>2026-06-05T08:35:28+00:00</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>171-6540897-0152357</t>
+          <t>404-9218549-9930734</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79659</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZDA2F</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, Black, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -6294,7 +6282,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6304,12 +6292,12 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679650</t>
+          <t>LPNSDEGF082043</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -6317,12 +6305,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-06-05T04:33:06+00:00</t>
+          <t>2026-06-05T08:17:03+00:00</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>171-6354444-3723505</t>
+          <t>171-6540897-0152357</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6350,22 +6338,22 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>LPNBOM5F5574228</t>
+          <t>LPNDEL4AA3679650</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -6373,12 +6361,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-06-05T04:28:18+00:00</t>
+          <t>2026-06-05T04:33:06+00:00</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>406-6103690-9310748</t>
+          <t>171-6354444-3723505</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6406,22 +6394,22 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679535</t>
+          <t>LPNBOM5F5574228</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -6429,12 +6417,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-06-04T03:47:36+00:00</t>
+          <t>2026-06-05T04:28:18+00:00</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>406-2278126-7841949</t>
+          <t>406-6103690-9310748</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6477,7 +6465,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679185</t>
+          <t>LPNDEL4AA3679535</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -6485,12 +6473,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-06-01T09:32:55+00:00</t>
+          <t>2026-06-04T03:47:36+00:00</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>402-3794541-2581168</t>
+          <t>406-2278126-7841949</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6518,7 +6506,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6528,12 +6516,12 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4743333</t>
+          <t>LPNDEL4AA3679185</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -6541,12 +6529,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-06-01T04:42:36+00:00</t>
+          <t>2026-06-01T09:32:55+00:00</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>408-0143238-4374708</t>
+          <t>402-3794541-2581168</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6574,7 +6562,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6589,7 +6577,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>LPNBOM5F5524445</t>
+          <t>LPNBLR7Y4743333</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -6597,12 +6585,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-06-01T03:58:27+00:00</t>
+          <t>2026-06-01T04:42:36+00:00</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>406-4355667-6072332</t>
+          <t>408-0143238-4374708</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6630,7 +6618,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6640,12 +6628,12 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4743158</t>
+          <t>LPNBOM5F5524445</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -6653,12 +6641,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-31T09:10:34+00:00</t>
+          <t>2026-06-01T03:58:27+00:00</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>404-2518539-4406712</t>
+          <t>406-4355667-6072332</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6686,22 +6674,22 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3976607</t>
+          <t>LPNBLR7Y4743158</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -6709,12 +6697,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-30T22:18:28+00:00</t>
+          <t>2026-05-31T09:10:34+00:00</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>407-1474707-0478726</t>
+          <t>404-2518539-4406712</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6742,22 +6730,22 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>LPNCCX1B4554643</t>
+          <t>LPNDEL4AA3976607</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
@@ -6765,12 +6753,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-30T04:13:42+00:00</t>
+          <t>2026-05-30T22:18:28+00:00</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>406-7941139-9225906</t>
+          <t>407-1474707-0478726</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6798,12 +6786,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6813,7 +6801,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>LPNBOM5F5507643</t>
+          <t>LPNCCX1B4554643</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -6821,12 +6809,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-29T23:01:15+00:00</t>
+          <t>2026-05-30T04:13:42+00:00</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>405-0096078-8521126</t>
+          <t>406-7941139-9225906</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6854,12 +6842,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6869,7 +6857,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>LPNCCX1B2941120</t>
+          <t>LPNBOM5F5507643</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
@@ -6877,12 +6865,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-29T15:27:20+00:00</t>
+          <t>2026-05-29T23:01:15+00:00</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>404-8418070-5981124</t>
+          <t>405-0096078-8521126</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6925,7 +6913,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>LPNCCX1B4508596</t>
+          <t>LPNCCX1B2941120</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -6933,12 +6921,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-29T05:18:33+00:00</t>
+          <t>2026-05-29T15:27:20+00:00</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>171-0407209-4266756</t>
+          <t>404-8418070-5981124</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6966,22 +6954,22 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937926</t>
+          <t>LPNCCX1B4508596</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -6989,12 +6977,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-28T11:56:49+00:00</t>
+          <t>2026-05-29T05:18:33+00:00</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>407-4902279-0189155</t>
+          <t>171-0407209-4266756</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7022,22 +7010,22 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7363000</t>
+          <t>LPNDEL4AA3937926</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -7045,12 +7033,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-28T08:40:02+00:00</t>
+          <t>2026-05-28T11:56:49+00:00</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>408-1128142-0248321</t>
+          <t>407-4902279-0189155</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7078,7 +7066,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7088,12 +7076,12 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>DAMAGED_BY_FC</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937756</t>
+          <t>LPNBLR7Y7363000</t>
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
@@ -7101,12 +7089,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-28T06:36:17+00:00</t>
+          <t>2026-05-28T08:40:02+00:00</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>402-4776409-4471512</t>
+          <t>408-1128142-0248321</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7134,7 +7122,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7144,12 +7132,12 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>DAMAGED_BY_FC</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7286354</t>
+          <t>LPNDEL4AA3937756</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -7157,12 +7145,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-27T12:42:16+00:00</t>
+          <t>2026-05-28T06:36:17+00:00</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>404-6762038-7137955</t>
+          <t>402-4776409-4471512</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7190,7 +7178,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7200,12 +7188,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937575</t>
+          <t>LPNBLR7Y7286354</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -7213,12 +7201,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-27T09:44:17+00:00</t>
+          <t>2026-05-27T12:42:16+00:00</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>403-3444915-0085109</t>
+          <t>404-6762038-7137955</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7246,7 +7234,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7261,7 +7249,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7362686</t>
+          <t>LPNDEL4AA3937575</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -7269,32 +7257,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-27T09:25:47+00:00</t>
+          <t>2026-05-27T09:44:17+00:00</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>405-8410325-7933918</t>
+          <t>403-3444915-0085109</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -7302,22 +7290,22 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>LPNSPUN53913</t>
+          <t>LPNBLR7Y7362686</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
@@ -7325,32 +7313,32 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-26T23:02:43+00:00</t>
+          <t>2026-05-27T09:25:47+00:00</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>407-0645348-4574732</t>
+          <t>405-8410325-7933918</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -7358,22 +7346,22 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>LPNCCX1B5292913</t>
+          <t>LPNSPUN53913</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -7381,12 +7369,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-26T11:06:29+00:00</t>
+          <t>2026-05-26T23:02:43+00:00</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>402-2949127-9513917</t>
+          <t>407-0645348-4574732</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7414,22 +7402,22 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937227</t>
+          <t>LPNCCX1B5292913</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -7437,12 +7425,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-26T08:48:10+00:00</t>
+          <t>2026-05-26T11:06:29+00:00</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>403-5510263-6469912</t>
+          <t>402-2949127-9513917</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7470,7 +7458,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7485,7 +7473,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273675</t>
+          <t>LPNDEL4AA3937227</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -7493,12 +7481,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-25T15:22:25+00:00</t>
+          <t>2026-05-26T08:48:10+00:00</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>402-5203149-1906724</t>
+          <t>403-5510263-6469912</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7526,7 +7514,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7536,12 +7524,12 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>LPNCCX1B5331017</t>
+          <t>LPNBLR7Y7273675</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -7549,12 +7537,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-24T09:24:39+00:00</t>
+          <t>2026-05-25T15:22:25+00:00</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>171-7709339-0701117</t>
+          <t>402-5203149-1906724</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7582,7 +7570,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7592,12 +7580,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273169</t>
+          <t>LPNCCX1B5331017</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -7605,12 +7593,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-24T08:29:52+00:00</t>
+          <t>2026-05-24T09:24:39+00:00</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>406-7042486-7436314</t>
+          <t>171-7709339-0701117</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7653,7 +7641,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273150</t>
+          <t>LPNBLR7Y7273169</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -7661,32 +7649,32 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-23T23:07:27+00:00</t>
+          <t>2026-05-24T08:29:52+00:00</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>406-2954542-5857925</t>
+          <t>406-7042486-7436314</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -7694,22 +7682,22 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>LPNSBOB1370158</t>
+          <t>LPNBLR7Y7273150</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -7717,32 +7705,32 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-23T10:58:04+00:00</t>
+          <t>2026-05-23T23:07:27+00:00</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>406-4758725-2077907</t>
+          <t>406-2954542-5857925</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -7750,22 +7738,22 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7272896</t>
+          <t>LPNSBOB1370158</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -7773,32 +7761,32 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-22T09:58:26+00:00</t>
+          <t>2026-05-23T10:58:04+00:00</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>403-7800011-6937966</t>
+          <t>406-4758725-2077907</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -7806,7 +7794,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7821,7 +7809,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>LPNSDEGF010003</t>
+          <t>LPNBLR7Y7272896</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -7829,32 +7817,32 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-21T04:38:32+00:00</t>
+          <t>2026-05-22T09:58:26+00:00</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>403-2400247-1930753</t>
+          <t>403-7800011-6937966</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -7877,7 +7865,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>LPNSDEGF099136</t>
+          <t>LPNSDEGF010003</t>
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
@@ -7885,32 +7873,32 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-20T11:30:45+00:00</t>
+          <t>2026-05-21T04:38:32+00:00</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>406-2648444-6601917</t>
+          <t>403-2400247-1930753</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -7918,7 +7906,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7928,12 +7916,12 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2147464</t>
+          <t>LPNSDEGF099136</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
@@ -7941,32 +7929,32 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-19T08:03:32+00:00</t>
+          <t>2026-05-20T11:30:45+00:00</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>405-4744559-6958733</t>
+          <t>406-2648444-6601917</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -7974,7 +7962,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7984,12 +7972,12 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>LPNSDEGF097985</t>
+          <t>LPNDEL4AA2147464</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -7997,32 +7985,32 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-18T11:36:05+00:00</t>
+          <t>2026-05-19T08:03:32+00:00</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>171-1585723-0908356</t>
+          <t>405-4744559-6958733</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -8030,12 +8018,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8045,7 +8033,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>LPNBLX1C155145</t>
+          <t>LPNSDEGF097985</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -8053,32 +8041,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-15T08:29:30+00:00</t>
+          <t>2026-05-18T11:36:05+00:00</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>402-4856546-1261939</t>
+          <t>171-1585723-0908356</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -8086,12 +8074,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8101,7 +8089,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>LPNSDEGF074601</t>
+          <t>LPNBLX1C155145</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
@@ -8109,12 +8097,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-13T13:50:43+00:00</t>
+          <t>2026-05-15T08:29:30+00:00</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>403-7495250-9937954</t>
+          <t>402-4856546-1261939</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8142,22 +8130,22 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>LPNBLX1C154096</t>
+          <t>LPNSDEGF074601</t>
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
@@ -8165,32 +8153,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-12T07:19:54+00:00</t>
+          <t>2026-05-13T13:50:43+00:00</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>408-0473775-6641108</t>
+          <t>403-7495250-9937954</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -8198,22 +8186,22 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>LPNSBOB1362246</t>
+          <t>LPNBLX1C154096</t>
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
@@ -8221,12 +8209,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-11T10:31:39+00:00</t>
+          <t>2026-05-12T07:19:54+00:00</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>404-1750959-8518722</t>
+          <t>408-0473775-6641108</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8254,22 +8242,22 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>LPNSHTI00006165</t>
+          <t>LPNSBOB1362246</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
@@ -8277,32 +8265,32 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-10T09:15:43+00:00</t>
+          <t>2026-05-11T10:31:39+00:00</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>402-1548587-3227555</t>
+          <t>404-1750959-8518722</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -8310,22 +8298,22 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>LPNBOM5F5057136</t>
+          <t>LPNSHTI00006165</t>
         </is>
       </c>
       <c r="L141" t="inlineStr"/>
@@ -8333,32 +8321,32 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-08T15:43:17+00:00</t>
+          <t>2026-05-10T09:15:43+00:00</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>402-8374307-7441113</t>
+          <t>402-1548587-3227555</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -8366,7 +8354,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8381,7 +8369,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>LPNSDEGF064205</t>
+          <t>LPNBOM5F5057136</t>
         </is>
       </c>
       <c r="L142" t="inlineStr"/>
@@ -8389,32 +8377,32 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-08T13:25:23+00:00</t>
+          <t>2026-05-08T15:43:17+00:00</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>171-7381542-8368365</t>
+          <t>402-8374307-7441113</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -8422,7 +8410,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8432,12 +8420,12 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>LPNBLX1C042486</t>
+          <t>LPNSDEGF064205</t>
         </is>
       </c>
       <c r="L143" t="inlineStr"/>
@@ -8445,32 +8433,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-08T07:49:38+00:00</t>
+          <t>2026-05-08T13:25:23+00:00</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>403-3056736-6311553</t>
+          <t>171-7381542-8368365</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -8478,22 +8466,22 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5321963</t>
+          <t>LPNBLX1C042486</t>
         </is>
       </c>
       <c r="L144" t="inlineStr"/>
@@ -8501,32 +8489,32 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-06T06:52:28+00:00</t>
+          <t>2026-05-08T07:49:38+00:00</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>403-2654029-0716338</t>
+          <t>403-3056736-6311553</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -8534,12 +8522,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8549,7 +8537,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>LPNSHTI00005958</t>
+          <t>LPNBLR7Y5321963</t>
         </is>
       </c>
       <c r="L145" t="inlineStr"/>
@@ -8557,32 +8545,32 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-06T05:51:00+00:00</t>
+          <t>2026-05-06T06:52:28+00:00</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>404-9426288-6037168</t>
+          <t>403-2654029-0716338</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -8590,22 +8578,22 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>LPNBOM5F5236158</t>
+          <t>LPNSHTI00005958</t>
         </is>
       </c>
       <c r="L146" t="inlineStr"/>
@@ -8613,32 +8601,32 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-02T04:54:42+00:00</t>
+          <t>2026-05-06T05:51:00+00:00</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>407-6201969-2856316</t>
+          <t>404-9426288-6037168</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -8646,22 +8634,22 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>LPNLMAA0004457</t>
+          <t>LPNBOM5F5236158</t>
         </is>
       </c>
       <c r="L147" t="inlineStr"/>
@@ -8669,12 +8657,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-04-28T08:52:43+00:00</t>
+          <t>2026-05-02T04:54:42+00:00</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>171-6713241-8377149</t>
+          <t>407-6201969-2856316</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -8717,7 +8705,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>LPNLMAA0003844</t>
+          <t>LPNLMAA0004457</t>
         </is>
       </c>
       <c r="L148" t="inlineStr"/>
@@ -8725,32 +8713,32 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-04-27T06:04:11+00:00</t>
+          <t>2026-04-28T08:52:43+00:00</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>403-6021111-3520325</t>
+          <t>171-6713241-8377149</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -8763,17 +8751,17 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>LPNLMAA0003335</t>
+          <t>LPNLMAA0003844</t>
         </is>
       </c>
       <c r="L149" t="inlineStr"/>
@@ -8781,32 +8769,32 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-04-26T08:09:27+00:00</t>
+          <t>2026-04-27T06:04:11+00:00</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>402-4881396-1030704</t>
+          <t>403-6021111-3520325</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -8814,7 +8802,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -8824,12 +8812,12 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2253845</t>
+          <t>LPNLMAA0003335</t>
         </is>
       </c>
       <c r="L150" t="inlineStr"/>
@@ -8837,12 +8825,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-04-26T04:14:08+00:00</t>
+          <t>2026-04-26T08:09:27+00:00</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>408-1134010-7973925</t>
+          <t>402-4881396-1030704</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -8870,7 +8858,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -8880,12 +8868,12 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5321963</t>
+          <t>LPNDEL4AA2253845</t>
         </is>
       </c>
       <c r="L151" t="inlineStr"/>
@@ -8893,32 +8881,32 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-04-26T03:22:50+00:00</t>
+          <t>2026-04-26T04:14:08+00:00</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>406-9614580-4613163</t>
+          <t>408-1134010-7973925</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -8926,12 +8914,12 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -8941,7 +8929,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>LPNSPUN46511</t>
+          <t>LPNBLR7Y5321963</t>
         </is>
       </c>
       <c r="L152" t="inlineStr"/>
@@ -8949,32 +8937,32 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-04-25T05:33:44+00:00</t>
+          <t>2026-04-26T03:22:50+00:00</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>171-3077342-1790757</t>
+          <t>406-9614580-4613163</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -8982,7 +8970,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -8997,7 +8985,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>LPNLMAA0002840</t>
+          <t>LPNSPUN46511</t>
         </is>
       </c>
       <c r="L153" t="inlineStr"/>
@@ -9005,32 +8993,32 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-04-25T03:48:59+00:00</t>
+          <t>2026-04-25T05:33:44+00:00</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>404-4908572-3783532</t>
+          <t>171-3077342-1790757</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>X002FOAUSJ</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -9038,7 +9026,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9048,12 +9036,12 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>LPNBLR7Y6090385</t>
+          <t>LPNLMAA0002840</t>
         </is>
       </c>
       <c r="L154" t="inlineStr"/>
@@ -9061,32 +9049,32 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-04-22T10:55:13+00:00</t>
+          <t>2026-04-25T03:48:59+00:00</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>407-4868470-8499505</t>
+          <t>404-4908572-3783532</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X002FOAUSJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -9094,22 +9082,22 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>LPNLMAA0001354</t>
+          <t>LPNBLR7Y6090385</t>
         </is>
       </c>
       <c r="L155" t="inlineStr"/>
@@ -9117,32 +9105,32 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-04-22T04:17:57+00:00</t>
+          <t>2026-04-22T10:55:13+00:00</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>406-5030280-5555520</t>
+          <t>407-4868470-8499505</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -9150,22 +9138,22 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>LPNSDEGF117193</t>
+          <t>LPNLMAA0001354</t>
         </is>
       </c>
       <c r="L156" t="inlineStr"/>
@@ -9173,32 +9161,32 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-04-21T20:42:51+00:00</t>
+          <t>2026-04-22T04:17:57+00:00</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>403-7744956-9735520</t>
+          <t>406-5030280-5555520</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -9206,22 +9194,22 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>LPNCCX1B1519621</t>
+          <t>LPNSDEGF117193</t>
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
@@ -9229,32 +9217,32 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-04-20T05:04:40+00:00</t>
+          <t>2026-04-21T20:42:51+00:00</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>171-5598784-9947515</t>
+          <t>403-7744956-9735520</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>X002FOAUSJ</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -9262,22 +9250,22 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5552415</t>
+          <t>LPNCCX1B1519621</t>
         </is>
       </c>
       <c r="L158" t="inlineStr"/>
@@ -9285,32 +9273,32 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-04-18T05:41:14+00:00</t>
+          <t>2026-04-20T05:04:40+00:00</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>404-0309463-1310709</t>
+          <t>171-5598784-9947515</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X002FOAUSJ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -9318,22 +9306,22 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>LPNDEL4AA0788989</t>
+          <t>LPNBLR7Y5552415</t>
         </is>
       </c>
       <c r="L159" t="inlineStr"/>
@@ -9341,32 +9329,32 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-04-15T13:55:57+00:00</t>
+          <t>2026-04-18T05:41:14+00:00</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>407-7885481-2445152</t>
+          <t>404-0309463-1310709</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -9374,12 +9362,12 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>SMAB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9389,7 +9377,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>LPNSMAB1153810</t>
+          <t>LPNDEL4AA0788989</t>
         </is>
       </c>
       <c r="L160" t="inlineStr"/>
@@ -9397,58 +9385,114 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
+          <t>2026-04-15T13:55:57+00:00</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>407-7885481-2445152</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>FBA76417</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>X001MZZQ8V</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>1</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>SMAB</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>CARRIER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>UNDELIVERABLE_REFUSED</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>LPNSMAB1153810</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
           <t>2026-04-15T08:47:44+00:00</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>407-3585151-4323522</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
+      <c r="C162" t="inlineStr">
         <is>
           <t>FBA76417</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D162" t="inlineStr">
         <is>
           <t>B0BFVMDJ2K</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="E162" t="inlineStr">
         <is>
           <t>X001MZZQ8V</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
+      <c r="F162" t="inlineStr">
         <is>
           <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
-      <c r="G161" t="n">
-        <v>1</v>
-      </c>
-      <c r="H161" t="inlineStr">
+      <c r="G162" t="n">
+        <v>1</v>
+      </c>
+      <c r="H162" t="inlineStr">
         <is>
           <t>SDEG</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
+      <c r="I162" t="inlineStr">
         <is>
           <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr">
+      <c r="J162" t="inlineStr">
         <is>
           <t>DEFECTIVE</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
+      <c r="K162" t="inlineStr">
         <is>
           <t>LPNSDEGF027993</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/raw/returns/WhiteMulberry.xlsx
+++ b/data/raw/returns/WhiteMulberry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L162"/>
+  <dimension ref="A1:L164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,32 +481,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-13T10:39:08+00:00</t>
+          <t>2026-07-14T11:35:26+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>406-6722735-1149137</t>
+          <t>404-1923155-9840369</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -514,22 +514,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>LPNSPUN63412</t>
+          <t>LPNHYD8ES18705</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -537,12 +537,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-13T07:03:07+00:00</t>
+          <t>2026-07-14T10:22:02+00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>405-0681203-5996333</t>
+          <t>404-6435287-4639504</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4739661</t>
+          <t>LPNHYD8EO08417</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -593,32 +593,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-12T18:38:59+00:00</t>
+          <t>2026-07-14T10:20:12+00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>408-6399475-0434747</t>
+          <t>402-9517562-6803567</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LPNSDEGA045352</t>
+          <t>LPNHYD8EO08416</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -649,12 +649,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-12T12:11:34+00:00</t>
+          <t>2026-07-14T04:29:52+00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>405-3614422-8705902</t>
+          <t>403-9285316-3177122</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -682,22 +682,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>DAMAGED</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LPNBLR7Y8671012</t>
+          <t>LPNBLR8Z4739955</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -705,32 +705,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-12T11:18:57+00:00</t>
+          <t>2026-07-13T10:39:08+00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>171-1476461-2065906</t>
+          <t>406-6722735-1149137</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -738,22 +738,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3731833</t>
+          <t>LPNSPUN63412</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -761,12 +761,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-12T09:48:52+00:00</t>
+          <t>2026-07-13T07:03:07+00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>407-1690927-4321928</t>
+          <t>405-0681203-5996333</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -794,22 +794,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LPNBLR7Y8670945</t>
+          <t>LPNBLR8Z4739661</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -817,32 +817,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-11T15:19:09+00:00</t>
+          <t>2026-07-12T18:38:59+00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>407-1918094-9025938</t>
+          <t>408-6399475-0434747</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -865,7 +865,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>LPNSDEGA049360</t>
+          <t>LPNSDEGA045352</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -873,12 +873,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-11T04:41:50+00:00</t>
+          <t>2026-07-12T12:11:34+00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>402-4732739-0177111</t>
+          <t>405-3614422-8705902</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -906,22 +906,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>LPNBLR8Z3333062</t>
+          <t>LPNBLR7Y8671012</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -929,32 +929,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10T11:34:53+00:00</t>
+          <t>2026-07-12T11:18:57+00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>402-4127261-8261957</t>
+          <t>171-1476461-2065906</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -962,22 +962,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>LPNSHTI00014264</t>
+          <t>LPNDEL4AA3731833</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -985,12 +985,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-10T11:22:36+00:00</t>
+          <t>2026-07-12T09:48:52+00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>402-4627500-7082749</t>
+          <t>407-1690927-4321928</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1018,22 +1018,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3300048</t>
+          <t>LPNBLR7Y8670945</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1041,32 +1041,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10T08:11:09+00:00</t>
+          <t>2026-07-11T15:19:09+00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>407-2441104-3469917</t>
+          <t>407-1918094-9025938</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>LPNBLR8Z3342252</t>
+          <t>LPNSDEGA049360</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1097,12 +1097,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-10T03:24:58+00:00</t>
+          <t>2026-07-11T04:41:50+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>404-4351909-9563522</t>
+          <t>402-4732739-0177111</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3919248</t>
+          <t>LPNBLR8Z3333062</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1153,32 +1153,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09T04:11:50+00:00</t>
+          <t>2026-07-10T11:34:53+00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>402-4684050-2008333</t>
+          <t>402-4127261-8261957</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1186,22 +1186,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4305793</t>
+          <t>LPNSHTI00014264</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1209,12 +1209,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08T20:07:54+00:00</t>
+          <t>2026-07-10T11:22:36+00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>171-5139545-1381155</t>
+          <t>402-4627500-7082749</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1242,22 +1242,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>LPNCCX1A7424707</t>
+          <t>LPNDEL4AA3300048</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1265,12 +1265,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-08T06:12:17+00:00</t>
+          <t>2026-07-10T08:11:09+00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>406-6599709-8196355</t>
+          <t>407-2441104-3469917</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3951631</t>
+          <t>LPNBLR8Z3342252</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1321,32 +1321,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-07T14:57:35+00:00</t>
+          <t>2026-07-10T03:24:58+00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>403-7360454-8443505</t>
+          <t>404-4351909-9563522</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>LPNSDEGA048066</t>
+          <t>LPNDEL4AA3919248</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1377,12 +1377,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-07T12:17:02+00:00</t>
+          <t>2026-07-09T04:11:50+00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>404-3937409-4657901</t>
+          <t>402-4684050-2008333</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1410,22 +1410,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>DAMAGED</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3951212</t>
+          <t>LPNBLR8Z4305793</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1433,32 +1433,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-07T09:02:25+00:00</t>
+          <t>2026-07-08T20:07:54+00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>406-5155095-5494705</t>
+          <t>171-5139545-1381155</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>LPNLMAA0027050</t>
+          <t>LPNCCX1A7424707</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1489,12 +1489,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-06T21:23:52+00:00</t>
+          <t>2026-07-08T06:12:17+00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>406-6590377-2621105</t>
+          <t>406-6599709-8196355</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4815212</t>
+          <t>LPNDEL4AA3951631</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1545,32 +1545,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-06T21:22:13+00:00</t>
+          <t>2026-07-07T14:57:35+00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>407-1625560-1723518</t>
+          <t>403-7360454-8443505</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4815211</t>
+          <t>LPNSDEGA048066</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1601,12 +1601,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-06T12:33:49+00:00</t>
+          <t>2026-07-07T12:17:02+00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>404-5401376-5513111</t>
+          <t>404-3937409-4657901</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1634,22 +1634,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>LPNHYD8EJ59560</t>
+          <t>LPNDEL4AA3951212</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1657,32 +1657,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-05T20:21:02+00:00</t>
+          <t>2026-07-07T09:02:25+00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>408-9802796-1211539</t>
+          <t>406-5155095-5494705</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1690,22 +1690,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>LPNCCX1A8722775</t>
+          <t>LPNLMAA0027050</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1713,12 +1713,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-05T07:23:15+00:00</t>
+          <t>2026-07-06T21:23:52+00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>407-2308442-1499512</t>
+          <t>406-6590377-2621105</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4813630</t>
+          <t>LPNBLR8Z4815212</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1769,12 +1769,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-05T06:48:36+00:00</t>
+          <t>2026-07-06T21:22:13+00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>407-8970250-4543519</t>
+          <t>407-1625560-1723518</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4814250</t>
+          <t>LPNBLR8Z4815211</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1825,12 +1825,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-05T04:41:04+00:00</t>
+          <t>2026-07-06T12:33:49+00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>405-1245096-1377920</t>
+          <t>404-5401376-5513111</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1858,22 +1858,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>LPNBOM5F5826513</t>
+          <t>LPNHYD8EJ59560</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1881,12 +1881,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-04T12:12:23+00:00</t>
+          <t>2026-07-05T20:21:02+00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>404-7913029-6157962</t>
+          <t>408-9802796-1211539</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>LPNHYD8EJ58729</t>
+          <t>LPNCCX1A8722775</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1937,12 +1937,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-04T08:48:05+00:00</t>
+          <t>2026-07-05T07:23:15+00:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>405-3423037-8257160</t>
+          <t>407-2308442-1499512</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1970,22 +1970,22 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>DAMAGED_BY_FC</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3108992</t>
+          <t>LPNBLR8Z4813630</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -1993,12 +1993,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-04T04:21:28+00:00</t>
+          <t>2026-07-05T06:48:36+00:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>405-3646440-7662737</t>
+          <t>407-8970250-4543519</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2036,12 +2036,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>LPNBOM5F5455146</t>
+          <t>LPNBLR8Z4814250</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2049,12 +2049,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-03T19:29:57+00:00</t>
+          <t>2026-07-05T04:41:04+00:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>403-0547582-3197132</t>
+          <t>405-1245096-1377920</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>LPNCCX1B4102605</t>
+          <t>LPNBOM5F5826513</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2105,32 +2105,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-03T14:02:46+00:00</t>
+          <t>2026-07-04T12:12:23+00:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>171-7464293-7220360</t>
+          <t>404-7913029-6157962</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2138,22 +2138,22 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>NO_REASON_GIVEN</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>LPNSBOB1392052</t>
+          <t>LPNHYD8EJ58729</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2161,12 +2161,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-03T11:38:57+00:00</t>
+          <t>2026-07-04T08:48:05+00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>403-6645337-2467540</t>
+          <t>405-3423037-8257160</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2199,17 +2199,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DAMAGED_BY_FC</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2082724</t>
+          <t>LPNDEL4AA3108992</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2217,12 +2217,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-02T17:30:33+00:00</t>
+          <t>2026-07-04T04:21:28+00:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>402-1004506-0818747</t>
+          <t>405-3646440-7662737</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>LPNBLR8Z5514346</t>
+          <t>LPNBOM5F5455146</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2273,12 +2273,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-02T14:56:15+00:00</t>
+          <t>2026-07-03T19:29:57+00:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>407-7003476-1816350</t>
+          <t>403-0547582-3197132</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>NO_REASON_GIVEN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3108265</t>
+          <t>LPNCCX1B4102605</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2329,32 +2329,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-02T11:24:54+00:00</t>
+          <t>2026-07-03T14:02:46+00:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>408-9621782-0261114</t>
+          <t>171-7464293-7220360</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>NO_REASON_GIVEN</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3950616</t>
+          <t>LPNSBOB1392052</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2385,12 +2385,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-02T06:41:10+00:00</t>
+          <t>2026-07-03T11:38:57+00:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>403-6072724-5581966</t>
+          <t>403-6645337-2467540</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2418,22 +2418,22 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4303742</t>
+          <t>LPNDEL4AA2082724</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2441,12 +2441,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-01T22:20:26+00:00</t>
+          <t>2026-07-02T17:30:33+00:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>402-4598141-9561917</t>
+          <t>402-1004506-0818747</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>LPNCCX1B4170658</t>
+          <t>LPNBLR8Z5514346</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2497,32 +2497,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-01T15:09:10+00:00</t>
+          <t>2026-07-02T14:56:15+00:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>402-3081497-7409144</t>
+          <t>407-7003476-1816350</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2530,22 +2530,22 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>NO_REASON_GIVEN</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>LPNBLX1C093497</t>
+          <t>LPNDEL4AA3108265</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -2553,12 +2553,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-01T09:24:20+00:00</t>
+          <t>2026-07-02T11:24:54+00:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>405-3824107-9644368</t>
+          <t>408-9621782-0261114</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>LPNBOM5F5465051</t>
+          <t>LPNDEL4AA3950616</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -2609,12 +2609,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-01T06:49:32+00:00</t>
+          <t>2026-07-02T06:41:10+00:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>404-6104605-6788338</t>
+          <t>403-6072724-5581966</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>LPNBOM5F5435891</t>
+          <t>LPNBLR8Z4303742</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2665,12 +2665,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-01T05:46:54+00:00</t>
+          <t>2026-07-01T22:20:26+00:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>407-2497737-1874765</t>
+          <t>402-4598141-9561917</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>LPNBOM5F5407228</t>
+          <t>LPNCCX1B4170658</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -2721,32 +2721,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-01T03:55:07+00:00</t>
+          <t>2026-07-01T15:09:10+00:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>403-6044286-1801115</t>
+          <t>402-3081497-7409144</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2754,22 +2754,22 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>CCX2</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>LPNCCX2B2262224</t>
+          <t>LPNBLX1C093497</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -2777,12 +2777,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-29T12:22:41+00:00</t>
+          <t>2026-07-01T09:24:20+00:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>405-6904525-0069903</t>
+          <t>405-3824107-9644368</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2810,22 +2810,22 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>LPNHYD8EF20503</t>
+          <t>LPNBOM5F5465051</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2833,12 +2833,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-28T19:38:03+00:00</t>
+          <t>2026-07-01T06:49:32+00:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>402-4296829-1337133</t>
+          <t>404-6104605-6788338</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>LPNCCX1B2440445</t>
+          <t>LPNBOM5F5435891</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -2889,12 +2889,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-28T08:39:43+00:00</t>
+          <t>2026-07-01T05:46:54+00:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>402-6090489-2032337</t>
+          <t>407-2497737-1874765</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7855923</t>
+          <t>LPNBOM5F5407228</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -2945,12 +2945,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-27T11:00:01+00:00</t>
+          <t>2026-07-01T03:55:07+00:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>408-3896665-0021948</t>
+          <t>403-6044286-1801115</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX2</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7855626</t>
+          <t>LPNCCX2B2262224</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3001,32 +3001,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-27T10:32:22+00:00</t>
+          <t>2026-06-29T12:22:41+00:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>407-5462207-4616334</t>
+          <t>405-6904525-0069903</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>LPNSBOB1388621</t>
+          <t>LPNHYD8EF20503</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3057,32 +3057,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-26T18:08:18+00:00</t>
+          <t>2026-06-28T19:38:03+00:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>171-5586406-9945900</t>
+          <t>402-4296829-1337133</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3090,22 +3090,22 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>LPNSBOB1388302</t>
+          <t>LPNCCX1B2440445</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -3113,32 +3113,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-26T06:57:42+00:00</t>
+          <t>2026-06-28T08:39:43+00:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>405-2746376-7486724</t>
+          <t>402-6090489-2032337</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>LPNBLX1C140655</t>
+          <t>LPNBLR7Y7855923</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -3169,12 +3169,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-26T05:19:18+00:00</t>
+          <t>2026-06-27T11:00:01+00:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>406-4442109-5330751</t>
+          <t>408-3896665-0021948</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3212,12 +3212,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3990308</t>
+          <t>LPNBLR7Y7855626</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3225,32 +3225,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-25T18:24:43+00:00</t>
+          <t>2026-06-27T10:32:22+00:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>405-2433007-9289947</t>
+          <t>407-5462207-4616334</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>LPNSBOB1387687</t>
+          <t>LPNSBOB1388621</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3281,32 +3281,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-25T10:05:58+00:00</t>
+          <t>2026-06-26T18:08:18+00:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>407-3034951-4675566</t>
+          <t>171-5586406-9945900</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2273850</t>
+          <t>LPNSBOB1388302</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -3337,32 +3337,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-24T08:29:31+00:00</t>
+          <t>2026-06-26T06:57:42+00:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>402-0120877-0312362</t>
+          <t>405-2746376-7486724</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3370,22 +3370,22 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>LPNSPUN59333</t>
+          <t>LPNBLX1C140655</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -3393,12 +3393,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-24T06:17:22+00:00</t>
+          <t>2026-06-26T05:19:18+00:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>403-8864299-1768360</t>
+          <t>406-4442109-5330751</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3426,22 +3426,22 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7854241</t>
+          <t>LPNDEL4AA3990308</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -3449,32 +3449,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-23T15:36:47+00:00</t>
+          <t>2026-06-25T18:24:43+00:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>402-8717460-5700310</t>
+          <t>405-2433007-9289947</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>LPNHDX8A005873</t>
+          <t>LPNSBOB1387687</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -3505,12 +3505,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-23T11:54:27+00:00</t>
+          <t>2026-06-25T10:05:58+00:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>403-7688253-5273167</t>
+          <t>407-3034951-4675566</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>LPNBOM5F5694482</t>
+          <t>LPNMAA4Z2273850</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -3561,32 +3561,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-23T09:27:19+00:00</t>
+          <t>2026-06-24T08:29:31+00:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>408-9857262-4357961</t>
+          <t>402-0120877-0312362</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3594,22 +3594,22 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7853975</t>
+          <t>LPNSPUN59333</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3617,12 +3617,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-23T08:32:44+00:00</t>
+          <t>2026-06-24T06:17:22+00:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>404-2029470-0977929</t>
+          <t>403-8864299-1768360</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3650,22 +3650,22 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3925027</t>
+          <t>LPNBLR7Y7854241</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -3673,32 +3673,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-06-23T06:25:18+00:00</t>
+          <t>2026-06-23T15:36:47+00:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>408-7120729-6837923</t>
+          <t>402-8717460-5700310</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -3706,22 +3706,22 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>LPNSBOB1385946</t>
+          <t>LPNHDX8A005873</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -3729,32 +3729,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-06-23T05:29:18+00:00</t>
+          <t>2026-06-23T11:54:27+00:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>403-5101653-2865108</t>
+          <t>403-7688253-5273167</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3762,22 +3762,22 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>LPNHDX8005941</t>
+          <t>LPNBOM5F5694482</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -3785,32 +3785,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-06-22T15:00:37+00:00</t>
+          <t>2026-06-23T09:27:19+00:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>408-2886313-6344340</t>
+          <t>408-9857262-4357961</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -3818,22 +3818,22 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>LPNSBOB1385291</t>
+          <t>LPNBLR7Y7853975</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -3841,32 +3841,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-06-22T15:00:11+00:00</t>
+          <t>2026-06-23T08:32:44+00:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>403-4065197-2565940</t>
+          <t>404-2029470-0977929</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -3874,22 +3874,22 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>LPNSBOB1385290</t>
+          <t>LPNDEL4AA3925027</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -3897,32 +3897,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-06-22T13:49:32+00:00</t>
+          <t>2026-06-23T06:25:18+00:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>171-3328269-2691534</t>
+          <t>408-7120729-6837923</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>LPNBLX1C049419</t>
+          <t>LPNSBOB1385946</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -3953,32 +3953,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-06-22T13:44:52+00:00</t>
+          <t>2026-06-23T05:29:18+00:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>407-2806960-6949923</t>
+          <t>403-5101653-2865108</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>LPNBLX1C049418</t>
+          <t>LPNHDX8005941</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4009,32 +4009,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-06-22T12:43:38+00:00</t>
+          <t>2026-06-22T15:00:37+00:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>402-2531413-4073130</t>
+          <t>408-2886313-6344340</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -4042,22 +4042,22 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>LPNHYD8EF41160</t>
+          <t>LPNSBOB1385291</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -4065,32 +4065,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-06-22T09:02:33+00:00</t>
+          <t>2026-06-22T15:00:11+00:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>404-4254275-9061104</t>
+          <t>403-4065197-2565940</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -4098,22 +4098,22 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>LPNHYD8ED01352</t>
+          <t>LPNSBOB1385290</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -4121,32 +4121,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-06-22T06:27:11+00:00</t>
+          <t>2026-06-22T13:49:32+00:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>407-5289320-1468336</t>
+          <t>171-3328269-2691534</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -4154,22 +4154,22 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7287766</t>
+          <t>LPNBLX1C049419</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -4177,12 +4177,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-06-21T15:48:42+00:00</t>
+          <t>2026-06-22T13:44:52+00:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>408-1433377-1765942</t>
+          <t>407-2806960-6949923</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>LPNSBOB1385218</t>
+          <t>LPNBLX1C049418</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -4233,12 +4233,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-06-21T09:50:13+00:00</t>
+          <t>2026-06-22T12:43:38+00:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>405-1204534-8479517</t>
+          <t>402-2531413-4073130</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4266,12 +4266,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>LPNDEL4AA4027730</t>
+          <t>LPNHYD8EF41160</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -4289,12 +4289,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-06-21T08:35:03+00:00</t>
+          <t>2026-06-22T09:02:33+00:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>171-0025867-6612374</t>
+          <t>404-4254275-9061104</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7853300</t>
+          <t>LPNHYD8ED01352</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -4345,12 +4345,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-06-20T13:05:37+00:00</t>
+          <t>2026-06-22T06:27:11+00:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>402-8590404-8535510</t>
+          <t>407-5289320-1468336</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4378,22 +4378,22 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>LPNMAA4G898204</t>
+          <t>LPNBLR7Y7287766</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -4401,12 +4401,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-06-19T14:24:04+00:00</t>
+          <t>2026-06-21T15:48:42+00:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>403-3269966-6849104</t>
+          <t>408-1433377-1765942</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4434,22 +4434,22 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>LPNHDX8A004693</t>
+          <t>LPNSBOB1385218</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -4457,12 +4457,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-06-18T09:53:43+00:00</t>
+          <t>2026-06-21T09:50:13+00:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>408-1513827-8090763</t>
+          <t>405-1204534-8479517</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4490,22 +4490,22 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2273003</t>
+          <t>LPNDEL4AA4027730</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -4513,32 +4513,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-06-18T09:01:23+00:00</t>
+          <t>2026-06-21T08:35:03+00:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>402-6972876-7770702</t>
+          <t>171-0025867-6612374</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FBA76765</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>B0BMQQQ7YD</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>X001O7YYCV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>White Mulberry Motorized Height Adjustable Sit-Stand Desk | Electronic Height Adjustable | Motor &amp; Memory Preset Controller | Office, Workstation or Home | Carbon Fibre | 120 * 60*H(75-118) cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -4546,22 +4546,22 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>LPNSPUN58279</t>
+          <t>LPNBLR7Y7853300</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -4569,32 +4569,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-06-18T06:34:47+00:00</t>
+          <t>2026-06-20T13:05:37+00:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>171-5595331-6677926</t>
+          <t>402-8590404-8535510</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -4602,22 +4602,22 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>LPNSPUN58332</t>
+          <t>LPNMAA4G898204</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -4625,12 +4625,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-06-18T06:13:54+00:00</t>
+          <t>2026-06-19T14:24:04+00:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>405-9716650-4190754</t>
+          <t>403-3269966-6849104</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4658,22 +4658,22 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>LPNSPUN58348</t>
+          <t>LPNHDX8A004693</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -4681,12 +4681,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-06-18T05:06:11+00:00</t>
+          <t>2026-06-18T09:53:43+00:00</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>405-0242402-8315559</t>
+          <t>408-1513827-8090763</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4714,22 +4714,22 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>LPNHYD8DY89222</t>
+          <t>LPNMAA4Z2273003</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -4737,32 +4737,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-06-18T03:18:32+00:00</t>
+          <t>2026-06-18T09:01:23+00:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>403-8790017-7829152</t>
+          <t>402-6972876-7770702</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76765</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BMQQQ7YD</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001O7YYCV</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Motorized Height Adjustable Sit-Stand Desk | Electronic Height Adjustable | Motor &amp; Memory Preset Controller | Office, Workstation or Home | Carbon Fibre | 120 * 60*H(75-118) cm</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>LPNHYD8DY89148</t>
+          <t>LPNSPUN58279</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -4793,32 +4793,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-06-17T17:18:11+00:00</t>
+          <t>2026-06-18T06:34:47+00:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>408-3294486-3424329</t>
+          <t>171-5595331-6677926</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -4826,22 +4826,22 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>LPNCCX1B4206954</t>
+          <t>LPNSPUN58332</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -4849,12 +4849,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-06-17T11:01:26+00:00</t>
+          <t>2026-06-18T06:13:54+00:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>171-3399563-8885966</t>
+          <t>405-9716650-4190754</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>LPNLMAA0019039</t>
+          <t>LPNSPUN58348</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -4905,12 +4905,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-06-15T09:24:30+00:00</t>
+          <t>2026-06-18T05:06:11+00:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>171-3194001-5187538</t>
+          <t>405-0242402-8315559</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4943,17 +4943,17 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>LPNHYD8DY92591</t>
+          <t>LPNHYD8DY89222</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -4961,32 +4961,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-06-15T08:53:22+00:00</t>
+          <t>2026-06-18T03:18:32+00:00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>406-3765893-9779536</t>
+          <t>403-8790017-7829152</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>LPNHDX8A0002233</t>
+          <t>LPNHYD8DY89148</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -5017,12 +5017,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-06-14T11:15:53+00:00</t>
+          <t>2026-06-17T17:18:11+00:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>171-1282309-9677932</t>
+          <t>408-3294486-3424329</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5050,12 +5050,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>DAMAGED</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2198432</t>
+          <t>LPNCCX1B4206954</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -5073,32 +5073,32 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-06-14T06:26:57+00:00</t>
+          <t>2026-06-17T11:01:26+00:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>407-1845667-2313146</t>
+          <t>171-3399563-8885966</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -5106,22 +5106,22 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3677498</t>
+          <t>LPNLMAA0019039</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -5129,32 +5129,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-06-13T12:21:24+00:00</t>
+          <t>2026-06-15T09:24:30+00:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>405-5466299-6857906</t>
+          <t>171-3194001-5187538</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -5162,22 +5162,22 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>LPNSBOB1375958</t>
+          <t>LPNHYD8DY92591</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -5185,32 +5185,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-06-13T12:20:57+00:00</t>
+          <t>2026-06-15T08:53:22+00:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>404-9976514-7382743</t>
+          <t>406-3765893-9779536</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5228,12 +5228,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>LPNSBOB1375957</t>
+          <t>LPNHDX8A0002233</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -5241,32 +5241,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-06-12T11:47:28+00:00</t>
+          <t>2026-06-14T11:15:53+00:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>407-2845785-4936332</t>
+          <t>171-1282309-9677932</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>LPNSHTI00009280</t>
+          <t>LPNMAA4Z2198432</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -5297,32 +5297,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-06-11T12:39:34+00:00</t>
+          <t>2026-06-14T06:26:57+00:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>405-0836953-9114742</t>
+          <t>407-1845667-2313146</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>LPNHDX8A001607</t>
+          <t>LPNDEL4AA3677498</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -5353,32 +5353,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-06-11T10:43:03+00:00</t>
+          <t>2026-06-13T12:21:24+00:00</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>407-7053626-1929962</t>
+          <t>405-5466299-6857906</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FBA79667</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>B0DQPK7MFH</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>X0027512Z1</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk with Shelf|DIY Assembly| Monitor Raising Shelf |Engineered Wood &amp; Sturdy Steel Leg|Perfect for Computer Table Office Home Gaming Study Desk|L(130+130)*45*77cm|White</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>SCUY</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5396,12 +5396,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>LPNSCUY00017897</t>
+          <t>LPNSBOB1375958</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -5409,32 +5409,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-06-10T22:26:08+00:00</t>
+          <t>2026-06-13T12:20:57+00:00</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>404-0639682-6860336</t>
+          <t>404-9976514-7382743</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -5442,22 +5442,22 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>LPNCX1B4784440</t>
+          <t>LPNSBOB1375957</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -5465,32 +5465,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-06-10T12:14:02+00:00</t>
+          <t>2026-06-12T11:47:28+00:00</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>171-1027170-0049924</t>
+          <t>407-2845785-4936332</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2407733</t>
+          <t>LPNSHTI00009280</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -5521,32 +5521,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-06-10T08:20:03+00:00</t>
+          <t>2026-06-11T12:39:34+00:00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>406-6295410-5869130</t>
+          <t>405-0836953-9114742</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, White, 130+130×45×77 cm</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>LPNBLX1C159057</t>
+          <t>LPNHDX8A001607</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -5577,32 +5577,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-06-10T05:42:02+00:00</t>
+          <t>2026-06-11T10:43:03+00:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>405-8329990-8940345</t>
+          <t>407-7053626-1929962</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79667</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQPK7MFH</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0027512Z1</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk with Shelf|DIY Assembly| Monitor Raising Shelf |Engineered Wood &amp; Sturdy Steel Leg|Perfect for Computer Table Office Home Gaming Study Desk|L(130+130)*45*77cm|White</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -5610,22 +5610,22 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SCUY</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4745942</t>
+          <t>LPNSCUY00017897</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -5633,12 +5633,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-06-10T04:51:41+00:00</t>
+          <t>2026-06-10T22:26:08+00:00</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>405-7954322-6131539</t>
+          <t>404-0639682-6860336</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>LPNBOM5F5675078</t>
+          <t>LPNCX1B4784440</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -5689,12 +5689,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-06-10T03:51:05+00:00</t>
+          <t>2026-06-10T12:14:02+00:00</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>407-5527946-4998741</t>
+          <t>171-1027170-0049924</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7287766</t>
+          <t>LPNMAA4Z2407733</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -5745,32 +5745,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-06-08T09:59:30+00:00</t>
+          <t>2026-06-10T08:20:03+00:00</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>404-4052225-7064331</t>
+          <t>406-6295410-5869130</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -5778,22 +5778,22 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3631375</t>
+          <t>LPNBLX1C159057</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -5801,32 +5801,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-06-08T08:59:50+00:00</t>
+          <t>2026-06-10T05:42:02+00:00</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>404-3123106-0929939</t>
+          <t>405-8329990-8940345</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FBK76387</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>B0BF4S7V8C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>X00242V9DH</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -5834,22 +5834,22 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>LPNSPUN56234</t>
+          <t>LPNBLR7Y4745942</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -5857,32 +5857,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-06-08T08:59:02+00:00</t>
+          <t>2026-06-10T04:51:41+00:00</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>408-8800113-8391502</t>
+          <t>405-7954322-6131539</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>LPNSPUN56235</t>
+          <t>LPNBOM5F5675078</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -5913,12 +5913,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-06-08T08:43:30+00:00</t>
+          <t>2026-06-10T03:51:05+00:00</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>407-4254200-0562712</t>
+          <t>407-5527946-4998741</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3631346</t>
+          <t>LPNBLR7Y7287766</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -5969,12 +5969,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-06-07T16:09:41+00:00</t>
+          <t>2026-06-08T09:59:30+00:00</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>405-9852474-3831538</t>
+          <t>404-4052225-7064331</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6002,22 +6002,22 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>LPNCCX1B4179343</t>
+          <t>LPNDEL4AA3631375</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -6025,32 +6025,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-06-07T11:20:49+00:00</t>
+          <t>2026-06-08T08:59:50+00:00</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>406-9783608-9093148</t>
+          <t>404-3123106-0929939</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBK76387</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0BF4S7V8C</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X00242V9DH</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
+          <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | White</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>LPNLMAA0016237</t>
+          <t>LPNSPUN56234</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -6081,32 +6081,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-06-07T10:24:17+00:00</t>
+          <t>2026-06-08T08:59:02+00:00</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>406-6392223-8173930</t>
+          <t>408-8800113-8391502</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -6114,22 +6114,22 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>LPNBLX1C047099</t>
+          <t>LPNSPUN56235</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -6137,12 +6137,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-06-06T10:45:59+00:00</t>
+          <t>2026-06-08T08:43:30+00:00</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>406-9111649-3125130</t>
+          <t>407-4254200-0562712</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>LPNBOM5F5579985</t>
+          <t>LPNDEL4AA3631346</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -6193,12 +6193,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-06-05T09:54:50+00:00</t>
+          <t>2026-06-07T16:09:41+00:00</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>405-7328472-7893901</t>
+          <t>405-9852474-3831538</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6226,22 +6226,22 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679697</t>
+          <t>LPNCCX1B4179343</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -6249,32 +6249,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-06-05T08:35:28+00:00</t>
+          <t>2026-06-07T11:20:49+00:00</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>404-9218549-9930734</t>
+          <t>406-9783608-9093148</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FBA79659</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>X0026ZDA2F</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, Black, 3 Year Warranty</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, White, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -6282,22 +6282,22 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>LPNSDEGF082043</t>
+          <t>LPNLMAA0016237</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -6305,32 +6305,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-06-05T08:17:03+00:00</t>
+          <t>2026-06-07T10:24:17+00:00</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>171-6540897-0152357</t>
+          <t>406-6392223-8173930</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -6338,22 +6338,22 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679650</t>
+          <t>LPNBLX1C047099</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -6361,12 +6361,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-06-05T04:33:06+00:00</t>
+          <t>2026-06-06T10:45:59+00:00</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>171-6354444-3723505</t>
+          <t>406-9111649-3125130</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6399,17 +6399,17 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>MISORDERED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>LPNBOM5F5574228</t>
+          <t>LPNBOM5F5579985</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -6417,12 +6417,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-06-05T04:28:18+00:00</t>
+          <t>2026-06-05T09:54:50+00:00</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>406-6103690-9310748</t>
+          <t>405-7328472-7893901</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679535</t>
+          <t>LPNDEL4AA3679697</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -6473,32 +6473,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-06-04T03:47:36+00:00</t>
+          <t>2026-06-05T08:35:28+00:00</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>406-2278126-7841949</t>
+          <t>404-9218549-9930734</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79659</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZDA2F</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry Manual Height Adjustable Table for Office Work | 120×60 cm Ergonomic Sit Stand Desk for Office Work &amp; Study Multi-Purpose Standing Desk with 80 Kg Load Capacity, Black, 3 Year Warranty</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6516,12 +6516,12 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3679185</t>
+          <t>LPNSDEGF082043</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -6529,12 +6529,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-06-01T09:32:55+00:00</t>
+          <t>2026-06-05T08:17:03+00:00</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>402-3794541-2581168</t>
+          <t>171-6540897-0152357</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6572,12 +6572,12 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4743333</t>
+          <t>LPNDEL4AA3679650</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -6585,12 +6585,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-06-01T04:42:36+00:00</t>
+          <t>2026-06-05T04:33:06+00:00</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>408-0143238-4374708</t>
+          <t>171-6354444-3723505</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6623,17 +6623,17 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>LPNBOM5F5524445</t>
+          <t>LPNBOM5F5574228</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -6641,12 +6641,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-06-01T03:58:27+00:00</t>
+          <t>2026-06-05T04:28:18+00:00</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>406-4355667-6072332</t>
+          <t>406-6103690-9310748</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>LPNBLR7Y4743158</t>
+          <t>LPNDEL4AA3679535</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -6697,12 +6697,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-31T09:10:34+00:00</t>
+          <t>2026-06-04T03:47:36+00:00</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>404-2518539-4406712</t>
+          <t>406-2278126-7841949</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6735,17 +6735,17 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3976607</t>
+          <t>LPNDEL4AA3679185</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
@@ -6753,12 +6753,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-30T22:18:28+00:00</t>
+          <t>2026-06-01T09:32:55+00:00</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>407-1474707-0478726</t>
+          <t>402-3794541-2581168</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>LPNCCX1B4554643</t>
+          <t>LPNBLR7Y4743333</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -6809,12 +6809,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-30T04:13:42+00:00</t>
+          <t>2026-06-01T04:42:36+00:00</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>406-7941139-9225906</t>
+          <t>408-0143238-4374708</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>LPNBOM5F5507643</t>
+          <t>LPNBOM5F5524445</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
@@ -6865,12 +6865,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-29T23:01:15+00:00</t>
+          <t>2026-06-01T03:58:27+00:00</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>405-0096078-8521126</t>
+          <t>406-4355667-6072332</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>LPNCCX1B2941120</t>
+          <t>LPNBLR7Y4743158</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -6921,12 +6921,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-29T15:27:20+00:00</t>
+          <t>2026-05-31T09:10:34+00:00</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>404-8418070-5981124</t>
+          <t>404-2518539-4406712</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6954,22 +6954,22 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>LPNCCX1B4508596</t>
+          <t>LPNDEL4AA3976607</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -6977,12 +6977,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-29T05:18:33+00:00</t>
+          <t>2026-05-30T22:18:28+00:00</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>171-0407209-4266756</t>
+          <t>407-1474707-0478726</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7010,22 +7010,22 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937926</t>
+          <t>LPNCCX1B4554643</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -7033,12 +7033,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-28T11:56:49+00:00</t>
+          <t>2026-05-30T04:13:42+00:00</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>407-4902279-0189155</t>
+          <t>406-7941139-9225906</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7066,22 +7066,22 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7363000</t>
+          <t>LPNBOM5F5507643</t>
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
@@ -7089,12 +7089,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-28T08:40:02+00:00</t>
+          <t>2026-05-29T23:01:15+00:00</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>408-1128142-0248321</t>
+          <t>405-0096078-8521126</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7132,12 +7132,12 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>DAMAGED_BY_FC</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937756</t>
+          <t>LPNCCX1B2941120</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -7145,12 +7145,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-28T06:36:17+00:00</t>
+          <t>2026-05-29T15:27:20+00:00</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>402-4776409-4471512</t>
+          <t>404-8418070-5981124</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7286354</t>
+          <t>LPNCCX1B4508596</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -7201,12 +7201,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-27T12:42:16+00:00</t>
+          <t>2026-05-29T05:18:33+00:00</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>404-6762038-7137955</t>
+          <t>171-0407209-4266756</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7239,17 +7239,17 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937575</t>
+          <t>LPNDEL4AA3937926</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -7257,12 +7257,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-27T09:44:17+00:00</t>
+          <t>2026-05-28T11:56:49+00:00</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>403-3444915-0085109</t>
+          <t>407-4902279-0189155</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7362686</t>
+          <t>LPNBLR7Y7363000</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
@@ -7313,32 +7313,32 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-27T09:25:47+00:00</t>
+          <t>2026-05-28T08:40:02+00:00</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>405-8410325-7933918</t>
+          <t>408-1128142-0248321</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -7346,22 +7346,22 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>DAMAGED_BY_FC</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>LPNSPUN53913</t>
+          <t>LPNDEL4AA3937756</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -7369,12 +7369,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-26T23:02:43+00:00</t>
+          <t>2026-05-28T06:36:17+00:00</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>407-0645348-4574732</t>
+          <t>402-4776409-4471512</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7402,22 +7402,22 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>LPNCCX1B5292913</t>
+          <t>LPNBLR7Y7286354</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -7425,12 +7425,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-26T11:06:29+00:00</t>
+          <t>2026-05-27T12:42:16+00:00</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>402-2949127-9513917</t>
+          <t>404-6762038-7137955</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3937227</t>
+          <t>LPNDEL4AA3937575</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -7481,12 +7481,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-26T08:48:10+00:00</t>
+          <t>2026-05-27T09:44:17+00:00</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>403-5510263-6469912</t>
+          <t>403-3444915-0085109</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273675</t>
+          <t>LPNBLR7Y7362686</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -7537,32 +7537,32 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-25T15:22:25+00:00</t>
+          <t>2026-05-27T09:25:47+00:00</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>402-5203149-1906724</t>
+          <t>405-8410325-7933918</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -7570,22 +7570,22 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>LPNCCX1B5331017</t>
+          <t>LPNSPUN53913</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -7593,12 +7593,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-24T09:24:39+00:00</t>
+          <t>2026-05-26T23:02:43+00:00</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>171-7709339-0701117</t>
+          <t>407-0645348-4574732</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7626,22 +7626,22 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273169</t>
+          <t>LPNCCX1B5292913</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -7649,12 +7649,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-24T08:29:52+00:00</t>
+          <t>2026-05-26T11:06:29+00:00</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>406-7042486-7436314</t>
+          <t>402-2949127-9513917</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7692,12 +7692,12 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7273150</t>
+          <t>LPNDEL4AA3937227</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -7705,32 +7705,32 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-23T23:07:27+00:00</t>
+          <t>2026-05-26T08:48:10+00:00</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>406-2954542-5857925</t>
+          <t>403-5510263-6469912</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -7738,22 +7738,22 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>LPNSBOB1370158</t>
+          <t>LPNBLR7Y7273675</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -7761,12 +7761,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-23T10:58:04+00:00</t>
+          <t>2026-05-25T15:22:25+00:00</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>406-4758725-2077907</t>
+          <t>402-5203149-1906724</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>LPNBLR7Y7272896</t>
+          <t>LPNCCX1B5331017</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -7817,32 +7817,32 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-22T09:58:26+00:00</t>
+          <t>2026-05-24T09:24:39+00:00</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>403-7800011-6937966</t>
+          <t>171-7709339-0701117</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>X0026ZHXR3</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>LPNSDEGF010003</t>
+          <t>LPNBLR7Y7273169</t>
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
@@ -7873,32 +7873,32 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-21T04:38:32+00:00</t>
+          <t>2026-05-24T08:29:52+00:00</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>403-2400247-1930753</t>
+          <t>406-7042486-7436314</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>LPNSDEGF099136</t>
+          <t>LPNBLR7Y7273150</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
@@ -7929,32 +7929,32 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-20T11:30:45+00:00</t>
+          <t>2026-05-23T23:07:27+00:00</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>406-2648444-6601917</t>
+          <t>406-2954542-5857925</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -7962,22 +7962,22 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2147464</t>
+          <t>LPNSBOB1370158</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -7985,32 +7985,32 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-19T08:03:32+00:00</t>
+          <t>2026-05-23T10:58:04+00:00</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>405-4744559-6958733</t>
+          <t>406-4758725-2077907</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>LPNSDEGF097985</t>
+          <t>LPNBLR7Y7272896</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -8041,12 +8041,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-18T11:36:05+00:00</t>
+          <t>2026-05-22T09:58:26+00:00</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>171-1585723-0908356</t>
+          <t>403-7800011-6937966</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>LPNBLX1C155145</t>
+          <t>LPNSDEGF010003</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
@@ -8097,32 +8097,32 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-15T08:29:30+00:00</t>
+          <t>2026-05-21T04:38:32+00:00</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>402-4856546-1261939</t>
+          <t>403-2400247-1930753</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>LPNSDEGF074601</t>
+          <t>LPNSDEGF099136</t>
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
@@ -8153,32 +8153,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-13T13:50:43+00:00</t>
+          <t>2026-05-20T11:30:45+00:00</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>403-7495250-9937954</t>
+          <t>406-2648444-6601917</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>LPNBLX1C154096</t>
+          <t>LPNDEL4AA2147464</t>
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
@@ -8209,32 +8209,32 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-12T07:19:54+00:00</t>
+          <t>2026-05-19T08:03:32+00:00</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>408-0473775-6641108</t>
+          <t>405-4744559-6958733</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -8242,22 +8242,22 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>LPNSBOB1362246</t>
+          <t>LPNSDEGF097985</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
@@ -8265,32 +8265,32 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-11T10:31:39+00:00</t>
+          <t>2026-05-18T11:36:05+00:00</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>404-1750959-8518722</t>
+          <t>171-1585723-0908356</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X0026ZHXR3</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>LPNSHTI00006165</t>
+          <t>LPNBLX1C155145</t>
         </is>
       </c>
       <c r="L141" t="inlineStr"/>
@@ -8321,32 +8321,32 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-10T09:15:43+00:00</t>
+          <t>2026-05-15T08:29:30+00:00</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>402-1548587-3227555</t>
+          <t>402-4856546-1261939</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -8354,22 +8354,22 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>LPNBOM5F5057136</t>
+          <t>LPNSDEGF074601</t>
         </is>
       </c>
       <c r="L142" t="inlineStr"/>
@@ -8377,32 +8377,32 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-08T15:43:17+00:00</t>
+          <t>2026-05-13T13:50:43+00:00</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>402-8374307-7441113</t>
+          <t>403-7495250-9937954</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -8410,22 +8410,22 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>LPNSDEGF064205</t>
+          <t>LPNBLX1C154096</t>
         </is>
       </c>
       <c r="L143" t="inlineStr"/>
@@ -8433,32 +8433,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-08T13:25:23+00:00</t>
+          <t>2026-05-12T07:19:54+00:00</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>171-7381542-8368365</t>
+          <t>408-0473775-6641108</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>SBOB</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>LPNBLX1C042486</t>
+          <t>LPNSBOB1362246</t>
         </is>
       </c>
       <c r="L144" t="inlineStr"/>
@@ -8489,32 +8489,32 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-08T07:49:38+00:00</t>
+          <t>2026-05-11T10:31:39+00:00</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>403-3056736-6311553</t>
+          <t>404-1750959-8518722</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5321963</t>
+          <t>LPNSHTI00006165</t>
         </is>
       </c>
       <c r="L145" t="inlineStr"/>
@@ -8545,32 +8545,32 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-06T06:52:28+00:00</t>
+          <t>2026-05-10T09:15:43+00:00</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>403-2654029-0716338</t>
+          <t>402-1548587-3227555</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -8578,22 +8578,22 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>SHTI</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>LPNSHTI00005958</t>
+          <t>LPNBOM5F5057136</t>
         </is>
       </c>
       <c r="L146" t="inlineStr"/>
@@ -8601,32 +8601,32 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-06T05:51:00+00:00</t>
+          <t>2026-05-08T15:43:17+00:00</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>404-9426288-6037168</t>
+          <t>402-8374307-7441113</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>LPNBOM5F5236158</t>
+          <t>LPNSDEGF064205</t>
         </is>
       </c>
       <c r="L147" t="inlineStr"/>
@@ -8657,32 +8657,32 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-02T04:54:42+00:00</t>
+          <t>2026-05-08T13:25:23+00:00</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>407-6201969-2856316</t>
+          <t>171-7381542-8368365</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -8690,22 +8690,22 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>LPNLMAA0004457</t>
+          <t>LPNBLX1C042486</t>
         </is>
       </c>
       <c r="L148" t="inlineStr"/>
@@ -8713,32 +8713,32 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-04-28T08:52:43+00:00</t>
+          <t>2026-05-08T07:49:38+00:00</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>171-6713241-8377149</t>
+          <t>403-3056736-6311553</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>LPNLMAA0003844</t>
+          <t>LPNBLR7Y5321963</t>
         </is>
       </c>
       <c r="L149" t="inlineStr"/>
@@ -8769,12 +8769,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-04-27T06:04:11+00:00</t>
+          <t>2026-05-06T06:52:28+00:00</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>403-6021111-3520325</t>
+          <t>403-2654029-0716338</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>LPNLMAA0003335</t>
+          <t>LPNSHTI00005958</t>
         </is>
       </c>
       <c r="L150" t="inlineStr"/>
@@ -8825,12 +8825,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-04-26T08:09:27+00:00</t>
+          <t>2026-05-06T05:51:00+00:00</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>402-4881396-1030704</t>
+          <t>404-9426288-6037168</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -8858,22 +8858,22 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2253845</t>
+          <t>LPNBOM5F5236158</t>
         </is>
       </c>
       <c r="L151" t="inlineStr"/>
@@ -8881,32 +8881,32 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-04-26T04:14:08+00:00</t>
+          <t>2026-05-02T04:54:42+00:00</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>408-1134010-7973925</t>
+          <t>407-6201969-2856316</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -8914,22 +8914,22 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5321963</t>
+          <t>LPNLMAA0004457</t>
         </is>
       </c>
       <c r="L152" t="inlineStr"/>
@@ -8937,32 +8937,32 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-04-26T03:22:50+00:00</t>
+          <t>2026-04-28T08:52:43+00:00</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>406-9614580-4613163</t>
+          <t>171-6713241-8377149</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -8980,12 +8980,12 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>LPNSPUN46511</t>
+          <t>LPNLMAA0003844</t>
         </is>
       </c>
       <c r="L153" t="inlineStr"/>
@@ -8993,32 +8993,32 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-04-25T05:33:44+00:00</t>
+          <t>2026-04-27T06:04:11+00:00</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>171-3077342-1790757</t>
+          <t>403-6021111-3520325</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -9031,17 +9031,17 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>LPNLMAA0002840</t>
+          <t>LPNLMAA0003335</t>
         </is>
       </c>
       <c r="L154" t="inlineStr"/>
@@ -9049,32 +9049,32 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-04-25T03:48:59+00:00</t>
+          <t>2026-04-26T08:09:27+00:00</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>404-4908572-3783532</t>
+          <t>402-4881396-1030704</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>X002FOAUSJ</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -9082,22 +9082,22 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>LPNBLR7Y6090385</t>
+          <t>LPNDEL4AA2253845</t>
         </is>
       </c>
       <c r="L155" t="inlineStr"/>
@@ -9105,32 +9105,32 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-04-22T10:55:13+00:00</t>
+          <t>2026-04-26T04:14:08+00:00</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>407-4868470-8499505</t>
+          <t>408-1134010-7973925</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>LPNLMAA0001354</t>
+          <t>LPNBLR7Y5321963</t>
         </is>
       </c>
       <c r="L156" t="inlineStr"/>
@@ -9161,32 +9161,32 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-04-22T04:17:57+00:00</t>
+          <t>2026-04-26T03:22:50+00:00</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>406-5030280-5555520</t>
+          <t>406-9614580-4613163</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>X001N02VPV</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -9194,22 +9194,22 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>LPNSDEGF117193</t>
+          <t>LPNSPUN46511</t>
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
@@ -9217,32 +9217,32 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-04-21T20:42:51+00:00</t>
+          <t>2026-04-25T05:33:44+00:00</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>403-7744956-9735520</t>
+          <t>171-3077342-1790757</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X00270AW07</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9260,12 +9260,12 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>LPNCCX1B1519621</t>
+          <t>LPNLMAA0002840</t>
         </is>
       </c>
       <c r="L158" t="inlineStr"/>
@@ -9273,12 +9273,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-04-20T05:04:40+00:00</t>
+          <t>2026-04-25T03:48:59+00:00</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>171-5598784-9947515</t>
+          <t>404-4908572-3783532</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9311,17 +9311,17 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>LPNBLR7Y5552415</t>
+          <t>LPNBLR7Y6090385</t>
         </is>
       </c>
       <c r="L159" t="inlineStr"/>
@@ -9329,32 +9329,32 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-04-18T05:41:14+00:00</t>
+          <t>2026-04-22T10:55:13+00:00</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>404-0309463-1310709</t>
+          <t>407-4868470-8499505</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9372,12 +9372,12 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>LPNDEL4AA0788989</t>
+          <t>LPNLMAA0001354</t>
         </is>
       </c>
       <c r="L160" t="inlineStr"/>
@@ -9385,32 +9385,32 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-04-15T13:55:57+00:00</t>
+          <t>2026-04-22T04:17:57+00:00</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>407-7885481-2445152</t>
+          <t>406-5030280-5555520</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001N02VPV</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -9418,22 +9418,22 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>SMAB</t>
+          <t>SDEG</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>LPNSMAB1153810</t>
+          <t>LPNSDEGF117193</t>
         </is>
       </c>
       <c r="L161" t="inlineStr"/>
@@ -9441,32 +9441,32 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-04-15T08:47:44+00:00</t>
+          <t>2026-04-21T20:42:51+00:00</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>407-3585151-4323522</t>
+          <t>403-7744956-9735520</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>X001MZZQ8V</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -9474,25 +9474,137 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>SDEG</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
+          <t>CARRIER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>UNDELIVERABLE_REFUSED</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>LPNCCX1B1519621</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-04-20T05:04:40+00:00</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>171-5598784-9947515</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>FBA76864</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>B0BPLZ5CGV</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>X002FOAUSJ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Audio Array AI-04 HD 2x2 Gen 3 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power | 24bit/192kHz Hi-Fi Recording | XLR/MIC/LINE inputs | Plug &amp; Play-No Drivers | 2 in 3 out | Metal Body | Red</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>BLR7</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
           <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
-      <c r="J162" t="inlineStr">
+      <c r="J163" t="inlineStr">
         <is>
           <t>DEFECTIVE</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>LPNSDEGF027993</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>LPNBLR7Y5552415</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-04-18T05:41:14+00:00</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>404-0309463-1310709</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>FBA79167</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>X001Y5UYX1</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>1</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>DEL4</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>SELLABLE</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>UNDELIVERABLE_REFUSED</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>LPNDEL4AA0788989</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/raw/returns/WhiteMulberry.xlsx
+++ b/data/raw/returns/WhiteMulberry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L164"/>
+  <dimension ref="A1:L177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,32 +481,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-14T11:35:26+00:00</t>
+          <t>2026-07-20T14:27:48+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>404-1923155-9840369</t>
+          <t>402-7800453-8105920</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -514,7 +514,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BLX1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>LPNHYD8ES18705</t>
+          <t>LPNBLX1C122860</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -537,32 +537,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-14T10:22:02+00:00</t>
+          <t>2026-07-20T10:57:40+00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>404-6435287-4639504</t>
+          <t>406-6235473-9511564</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -570,22 +570,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>LPNHYD8EO08417</t>
+          <t>LPNLMAA0033150</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -593,12 +593,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-14T10:20:12+00:00</t>
+          <t>2026-07-19T07:46:40+00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>402-9517562-6803567</t>
+          <t>406-2615755-2712327</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LPNHYD8EO08416</t>
+          <t>LPNDEL4AA3277650</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -649,12 +649,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-14T04:29:52+00:00</t>
+          <t>2026-07-19T07:33:20+00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>403-9285316-3177122</t>
+          <t>408-4449822-0069144</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,17 +687,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4739955</t>
+          <t>LPNBLR8Z4290048</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -705,32 +705,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-13T10:39:08+00:00</t>
+          <t>2026-07-19T05:00:11+00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>406-6722735-1149137</t>
+          <t>404-1321279-6548337</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -738,22 +738,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SPUN</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LPNSPUN63412</t>
+          <t>LPNDEL4AA3228959</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -761,32 +761,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13T07:03:07+00:00</t>
+          <t>2026-07-18T06:35:25+00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>405-0681203-5996333</t>
+          <t>407-0032753-7899572</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -794,22 +794,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>NEVER_ARRIVED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4739661</t>
+          <t>LPNSHTI00016894</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -817,32 +817,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-12T18:38:59+00:00</t>
+          <t>2026-07-18T04:23:42+00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>408-6399475-0434747</t>
+          <t>404-2137215-8512345</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>X001Y62M1H</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -850,7 +850,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>LPNSDEGA045352</t>
+          <t>LPNBOM5F5860048</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -873,12 +873,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-12T12:11:34+00:00</t>
+          <t>2026-07-18T04:20:37+00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>405-3614422-8705902</t>
+          <t>407-7803173-5803508</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>LPNBLR7Y8671012</t>
+          <t>LPNBOM5F5860047</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -929,32 +929,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-12T11:18:57+00:00</t>
+          <t>2026-07-17T06:10:46+00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>171-1476461-2065906</t>
+          <t>406-9466812-0307530</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZZQ8V</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -962,22 +962,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>MISORDERED</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3731833</t>
+          <t>LPNSHTI00015771</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -985,32 +985,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-12T09:48:52+00:00</t>
+          <t>2026-07-17T05:36:35+00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>407-1690927-4321928</t>
+          <t>404-4881025-9701134</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1018,22 +1018,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BLR7</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>LPNBLR7Y8670945</t>
+          <t>LPNSDEGA022034</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1041,32 +1041,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-11T15:19:09+00:00</t>
+          <t>2026-07-17T04:27:08+00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>407-1918094-9025938</t>
+          <t>403-7070034-4251513</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1074,22 +1074,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>LPNSDEGA049360</t>
+          <t>LPNBOM5F5880090</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1097,12 +1097,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-11T04:41:50+00:00</t>
+          <t>2026-07-16T04:23:29+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>402-4732739-0177111</t>
+          <t>402-7083284-9815526</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1135,17 +1135,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>LPNBLR8Z3333062</t>
+          <t>LPNBLR8Z4288074</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1153,32 +1153,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-10T11:34:53+00:00</t>
+          <t>2026-07-15T06:26:59+00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>402-4127261-8261957</t>
+          <t>406-4377845-3815554</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>LPNSHTI00014264</t>
+          <t>LPNSHTI00015258</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1209,12 +1209,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10T11:22:36+00:00</t>
+          <t>2026-07-15T04:04:13+00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>402-4627500-7082749</t>
+          <t>402-9813575-3732337</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3300048</t>
+          <t>LPNBLR8Z4740222</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1265,12 +1265,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10T08:11:09+00:00</t>
+          <t>2026-07-15T04:03:54+00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>407-2441104-3469917</t>
+          <t>405-2194455-2222741</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LPNBLR8Z3342252</t>
+          <t>LPNBLR8Z3463901</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1321,12 +1321,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10T03:24:58+00:00</t>
+          <t>2026-07-14T11:35:26+00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>404-4351909-9563522</t>
+          <t>404-1923155-9840369</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3919248</t>
+          <t>LPNHYD8ES18705</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1377,12 +1377,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-09T04:11:50+00:00</t>
+          <t>2026-07-14T10:22:02+00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>402-4684050-2008333</t>
+          <t>404-6435287-4639504</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1410,22 +1410,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4305793</t>
+          <t>LPNHYD8EO08417</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1433,12 +1433,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-08T20:07:54+00:00</t>
+          <t>2026-07-14T10:20:12+00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>171-5139545-1381155</t>
+          <t>402-9517562-6803567</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>LPNCCX1A7424707</t>
+          <t>LPNHYD8EO08416</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1489,12 +1489,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-08T06:12:17+00:00</t>
+          <t>2026-07-14T04:29:52+00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>406-6599709-8196355</t>
+          <t>403-9285316-3177122</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1522,22 +1522,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>DAMAGED</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3951631</t>
+          <t>LPNBLR8Z4739955</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1545,12 +1545,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-07T14:57:35+00:00</t>
+          <t>2026-07-13T10:39:08+00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>403-7360454-8443505</t>
+          <t>406-6722735-1149137</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>HDX8</t>
+          <t>SPUN</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1588,12 +1588,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>LPNSDEGA048066</t>
+          <t>LPNSPUN63412</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1601,12 +1601,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-07T12:17:02+00:00</t>
+          <t>2026-07-13T07:03:07+00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>404-3937409-4657901</t>
+          <t>405-0681203-5996333</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1634,22 +1634,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>NEVER_ARRIVED</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3951212</t>
+          <t>LPNBLR8Z4739661</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1657,32 +1657,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-07T09:02:25+00:00</t>
+          <t>2026-07-12T18:38:59+00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>406-5155095-5494705</t>
+          <t>408-6399475-0434747</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y62M1H</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Height Adjustable Table for Office Work | Electric Desk with Memory Preset Controller | Standing Table | Adjustable Standing Desk for Home Office &amp; Study | 120x60cm Carbon Fibre</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1690,22 +1690,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>LMAA</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CARRIER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>LPNLMAA0027050</t>
+          <t>LPNSDEGA045352</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1713,12 +1713,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-06T21:23:52+00:00</t>
+          <t>2026-07-12T12:11:34+00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>406-6590377-2621105</t>
+          <t>405-3614422-8705902</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1746,22 +1746,22 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4815212</t>
+          <t>LPNBLR7Y8671012</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1769,12 +1769,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-06T21:22:13+00:00</t>
+          <t>2026-07-12T11:18:57+00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>407-1625560-1723518</t>
+          <t>171-1476461-2065906</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4815211</t>
+          <t>LPNDEL4AA3731833</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1825,12 +1825,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-06T12:33:49+00:00</t>
+          <t>2026-07-12T09:48:52+00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>404-5401376-5513111</t>
+          <t>407-1690927-4321928</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1858,22 +1858,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BLR7</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>LPNHYD8EJ59560</t>
+          <t>LPNBLR7Y8670945</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1881,32 +1881,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-05T20:21:02+00:00</t>
+          <t>2026-07-11T15:19:09+00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>408-9802796-1211539</t>
+          <t>407-1918094-9025938</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>LPNCCX1A8722775</t>
+          <t>LPNSDEGA049360</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1937,12 +1937,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-05T07:23:15+00:00</t>
+          <t>2026-07-11T04:41:50+00:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>407-2308442-1499512</t>
+          <t>402-4732739-0177111</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4813630</t>
+          <t>LPNBLR8Z3333062</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -1993,32 +1993,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-05T06:48:36+00:00</t>
+          <t>2026-07-10T11:34:53+00:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>407-8970250-4543519</t>
+          <t>402-4127261-8261957</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>SHTI</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2036,12 +2036,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4814250</t>
+          <t>LPNSHTI00014264</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2049,12 +2049,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-05T04:41:04+00:00</t>
+          <t>2026-07-10T11:22:36+00:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>405-1245096-1377920</t>
+          <t>402-4627500-7082749</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>LPNBOM5F5826513</t>
+          <t>LPNDEL4AA3300048</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2105,12 +2105,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-04T12:12:23+00:00</t>
+          <t>2026-07-10T08:11:09+00:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>404-7913029-6157962</t>
+          <t>407-2441104-3469917</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>LPNHYD8EJ58729</t>
+          <t>LPNBLR8Z3342252</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2161,12 +2161,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-04T08:48:05+00:00</t>
+          <t>2026-07-10T03:24:58+00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>405-3423037-8257160</t>
+          <t>404-4351909-9563522</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2199,17 +2199,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>DAMAGED_BY_FC</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3108992</t>
+          <t>LPNDEL4AA3919248</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2217,12 +2217,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-04T04:21:28+00:00</t>
+          <t>2026-07-09T04:11:50+00:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>405-3646440-7662737</t>
+          <t>402-4684050-2008333</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2250,22 +2250,22 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>DAMAGED</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>LPNBOM5F5455146</t>
+          <t>LPNBLR8Z4305793</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2273,12 +2273,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-03T19:29:57+00:00</t>
+          <t>2026-07-08T20:07:54+00:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>403-0547582-3197132</t>
+          <t>171-5139545-1381155</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>LPNCCX1B4102605</t>
+          <t>LPNCCX1A7424707</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2329,32 +2329,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-03T14:02:46+00:00</t>
+          <t>2026-07-08T06:12:17+00:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>171-7464293-7220360</t>
+          <t>406-6599709-8196355</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>X00270AW07</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>White Mulberry Height Adjustable Table For Office Work | Electric Standing Desk 120x60cm White | Motorized Sit Stand Desk With Digital Screen &amp; Memory Presets | White Ergonomic Home Office Workstation</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SBOB</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>NO_REASON_GIVEN</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>LPNSBOB1392052</t>
+          <t>LPNDEL4AA3951631</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2385,32 +2385,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-03T11:38:57+00:00</t>
+          <t>2026-07-07T14:57:35+00:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>403-6645337-2467540</t>
+          <t>403-7360454-8443505</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious Study Table for Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Carbon Fiber (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>HDX8</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>LPNDEL4AA2082724</t>
+          <t>LPNSDEGA048066</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2441,12 +2441,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-02T17:30:33+00:00</t>
+          <t>2026-07-07T12:17:02+00:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>402-1004506-0818747</t>
+          <t>404-3937409-4657901</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2474,22 +2474,22 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>BLR8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>LPNBLR8Z5514346</t>
+          <t>LPNDEL4AA3951212</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2497,32 +2497,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-02T14:56:15+00:00</t>
+          <t>2026-07-07T09:02:25+00:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>407-7003476-1816350</t>
+          <t>406-5155095-5494705</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>X001Y5UYX1</t>
+          <t>X001MZYX7L</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
+          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2530,22 +2530,22 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>LMAA</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CARRIER_DAMAGED</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>NO_REASON_GIVEN</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3108265</t>
+          <t>LPNLMAA0027050</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -2553,12 +2553,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-02T11:24:54+00:00</t>
+          <t>2026-07-06T21:23:52+00:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>408-9621782-0261114</t>
+          <t>406-6590377-2621105</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>DEL4</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>LPNDEL4AA3950616</t>
+          <t>LPNBLR8Z4815212</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -2609,12 +2609,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-02T06:41:10+00:00</t>
+          <t>2026-07-06T21:22:13+00:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>403-6072724-5581966</t>
+          <t>407-1625560-1723518</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>LPNBLR8Z4303742</t>
+          <t>LPNBLR8Z4815211</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2665,12 +2665,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-01T22:20:26+00:00</t>
+          <t>2026-07-06T12:33:49+00:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>402-4598141-9561917</t>
+          <t>404-5401376-5513111</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2698,22 +2698,22 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>LPNCCX1B4170658</t>
+          <t>LPNHYD8EJ59560</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -2721,32 +2721,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-01T15:09:10+00:00</t>
+          <t>2026-07-05T20:21:02+00:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>402-3081497-7409144</t>
+          <t>408-9802796-1211539</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>X001MZYX7L</t>
+          <t>X001Y5UYX1</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>White Mulberry L Shaped Computer Table | Spacious L Shape Study Table For Home with Monitor Raising Shelf, Engineered Wood Top &amp; Steel Legs for Home, Office, Gaming &amp; Study, Black, (130+130)*45 * 77cm</t>
+          <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (110 * 60 * 75 CM)</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2754,22 +2754,22 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>BLX1</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>LPNBLX1C093497</t>
+          <t>LPNCCX1A8722775</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -2777,12 +2777,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-01T09:24:20+00:00</t>
+          <t>2026-07-05T07:23:15+00:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>405-3824107-9644368</t>
+          <t>407-2308442-1499512</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>LPNBOM5F5465051</t>
+          <t>LPNBLR8Z4813630</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2833,12 +2833,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-01T06:49:32+00:00</t>
+          <t>2026-07-05T06:48:36+00:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>404-6104605-6788338</t>
+          <t>407-8970250-4543519</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>BOM5</t>
+          <t>BLR8</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>LPNBOM5F5435891</t>
+          <t>LPNBLR8Z4814250</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -2889,12 +2889,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-01T05:46:54+00:00</t>
+          <t>2026-07-05T04:41:04+00:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>407-2497737-1874765</t>
+          <t>405-1245096-1377920</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>LPNBOM5F5407228</t>
+          <t>LPNBOM5F5826513</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -2945,12 +2945,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-01T03:55:07+00:00</t>
+          <t>2026-07-04T12:12:23+00:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>403-6044286-1801115</t>
+          <t>404-7913029-6157962</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CCX2</t>
+          <t>HYD8</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>LPNCCX2B2262224</t>
+          <t>LPNHYD8EJ58729</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3001,12 +3001,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-29T12:22:41+00:00</t>
+          <t>2026-07-04T08:48:05+00:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>405-6904525-0069903</t>
+          <t>405-3423037-8257160</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>HYD8</t>
+          <t>DEL4</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>DAMAGED_BY_FC</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>LPNHYD8EF20503</t>
+          <t>LPNDEL4AA3108992</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3057,12 +3057,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-28T19:38:03+00:00</t>
+          <t>2026-07-04T04:21:28+00:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>402-4296829-1337133</t>
+          <t>405-3646440-7662737</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3090,22 +3090,22 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BOM5</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>